--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{412FD772-A3AC-E246-A2E3-050742830F16}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D34189C-27E0-3042-A5C9-6888A0450835}"/>
   <bookViews>
-    <workbookView xWindow="8660" yWindow="600" windowWidth="35120" windowHeight="24600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6940" yWindow="600" windowWidth="35120" windowHeight="24600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="251">
   <si>
     <t>ID période</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Analyse et réception critique</t>
   </si>
   <si>
-    <t>Lien vidéo</t>
-  </si>
-  <si>
     <t>Citation</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
     <t xml:space="preserve">Capitulation du Troisième Reich (mai). L'Allemagne est en ruines (Année Zéro). Début de l'occupation alliée et de l'amnésie collective sur le passé nazi. Le pays et berlin sont partagés en zone sous contrôle des différentes forces alliées. </t>
   </si>
   <si>
-    <t>Le cinéma est en ruines. Période des films de décombres ( Trümmerfilme ) comme Les assassins sont parmi nous (Staudte, 1946).</t>
-  </si>
-  <si>
     <t>Naissance de Rainer Werner Fassbinder le 31 mai à Bad Wörishofen, Bavière.</t>
   </si>
   <si>
@@ -302,18 +296,12 @@
     <t>Naissance de Rainer Werner Fassbinder le 31 mai à Bad Wörishofen, Bavière. Père médecin généraliste, mère traductrice. Première année passée chez son oncle paternel</t>
   </si>
   <si>
-    <t>Fassbinder.jpeg</t>
-  </si>
-  <si>
     <t>Fassbinder enfant</t>
   </si>
   <si>
     <t>Bohm.jpg</t>
   </si>
   <si>
-    <t>Bohm</t>
-  </si>
-  <si>
     <t>Portrait d'Adenauer</t>
   </si>
   <si>
@@ -321,9 +309,6 @@
   </si>
   <si>
     <t>Le procès de Nuremberg</t>
-  </si>
-  <si>
-    <t>A l'initiative de Hans Werner Richter, fondation du Groupe 47 qui réunit l'avant-garde littéraire allemande qui compte dans ses membres Gunter Grass et Heinrich Boll.  Le Groupe cherche à constituer une élite exemplairement démocratique dans le domaine des lettres et à développer de nouvelles formes d'écriture pour permettre aux lettres allemandes d'exprimer au mieux des enjeux esthétiques et politiques en adéquation avec la société d'après-guerre.</t>
   </si>
   <si>
     <t>Elsaesser, Wikipedia</t>
@@ -835,9 +820,6 @@
     <t>Période de disette la plus terrible depuis la fin de la guerre. Les Trümmerfrauen (les femmes des ruines) constituent un des piliers de la reconstruction.</t>
   </si>
   <si>
-    <t xml:space="preserve">"Nous devons nous débarrasser du passé pour construire l'avenir". </t>
-  </si>
-  <si>
     <t>De l'année zéro au miracle économique</t>
   </si>
   <si>
@@ -850,11 +832,6 @@
   </si>
   <si>
     <t>l-industrie-de-l-industrie-automobile-l-usine-volkswagen-vue-de-l-interieur-usine-wolfsburg-vers-1950.jpg</t>
-  </si>
-  <si>
-    <t>La RFA signe le traité de Rome qui institue la Communautée Européenne (CEE). 
-Un scandale secoue le monde politique et financier : une prostituée  qui comptait parmi ses clients de nombreux hommes poli-tiques  ou industriels, est assassinée à Francfort.
-Adenauer tente d'imposer le fait que la RFA se dote de l'arme nucléaire mais se heurte à un front de protestation, notamment du monde scientifique.</t>
   </si>
   <si>
     <t xml:space="preserve">Le constructeur automobile Volkswagen est privatisé à hauteur de 60% de son capital. 78% des ménages ouest-allemands disposent d'un réfrigérateur contre 25% en France. 42% mossèdent une voiture. La société de consommation de masse est une réalité en RFA.
@@ -979,10 +956,6 @@
     <t>Visite de J.F Kennedy à Berlin-ouest : "ich bin ein Berliner". 
 Procès d'Auschwitz à Francfort (1963-1965)
 Démission d'Adenauer à 87 ans.</t>
-  </si>
-  <si>
-    <t>A l'occaision du festival du film documentaire d'Oberhausen, publication du Manifeste d'Oberhausen : naissance du Nouveau Cinéma Allemand ("Le vieux cinéma est mort").
-Les Beatles commencent leur carrière par un concert à Hambourg</t>
   </si>
   <si>
     <t>Machorka Muff de Jean-Marie Straub</t>
@@ -1053,6 +1026,48 @@
   </si>
   <si>
     <t>Portrait de Straub et carrière</t>
+  </si>
+  <si>
+    <t>"Nous devons nous débarrasser du passé pour construire l'avenir". Konrad Adenauer</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le cinéma est en ruines. Période des films de décombres ( Trümmerfilme ) comme </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Les assassins sont parmi nous </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Staudte, 1946).</t>
+    </r>
+  </si>
+  <si>
+    <t>A l'initiative de Hans Werner Richter, fondation du Groupe 47 qui réunit l'avant-garde littéraire allemande dont Gunter Grass et Heinrich Böll.  Le Groupe cherche à constituer une élite exemplairement démocratique dans le domaine des lettres et à développer de nouvelles formes d'écriture pour permettre aux lettres allemandes d'exprimer au mieux des enjeux esthétiques et politiques en adéquation avec la société d'après-guerre.</t>
+  </si>
+  <si>
+    <t>Liens</t>
+  </si>
+  <si>
+    <t>La RFA signe le traité de Rome qui institue la Communauté Européenne (CEE). 
+Un scandale secoue le monde politique et financier : une prostituée  qui comptait parmi ses clients de nombreux hommes poli-tiques  ou industriels, est assassinée à Francfort.
+Adenauer tente d'imposer le fait que la RFA se dote de l'arme nucléaire mais se heurte à un front de protestation, notamment du monde scientifique.</t>
+  </si>
+  <si>
+    <t>A l'occasion du festival du film documentaire d'Oberhausen, publication du Manifeste d'Oberhausen : naissance du Nouveau Cinéma Allemand ("Le vieux cinéma est mort").
+Les Beatles entament eur carrière par un concert à Hambourg</t>
   </si>
 </sst>
 </file>
@@ -1213,7 +1228,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1269,26 +1284,22 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -1632,7 +1643,7 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Œuvres"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="ID films - Œuvres"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Analyse et réception critique"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Lien vidéo"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Liens"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Citation"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Image"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Legende"/>
@@ -1643,29 +1654,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T28" totalsRowShown="0" headerRowDxfId="22" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T28" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A1:T28" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Lien vidéo" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1896,76 +1907,76 @@
         <v>8</v>
       </c>
       <c r="J1" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="H2" s="2" t="str">
         <f>IF(G2="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
       <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>245</v>
+      </c>
+      <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="M2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
-        <v>228</v>
-      </c>
-      <c r="L2" t="s">
+    </row>
+    <row r="3" spans="1:14" s="23" customFormat="1" ht="98" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M2" t="s">
+      <c r="B3" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="25" customFormat="1" ht="98" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="4" t="str">
@@ -1973,93 +1984,93 @@
         <v/>
       </c>
       <c r="I3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="L3" s="27" t="s">
-        <v>232</v>
+        <v>26</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="H4" s="4" t="str">
         <f>IF(G4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
       <c r="J4" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="85" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>IF(G5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="98" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="H6" s="4" t="str">
         <f>IF(G6="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -2069,75 +2080,75 @@
     </row>
     <row r="7" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="H7" s="4" t="str">
         <f>IF(G7="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="H8" s="4" t="str">
         <f>IF(G8="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1978-l-annee-des-treize-lunes; film-1979-le-mariage-de-maria-braun</v>
       </c>
       <c r="N8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="H9" s="4" t="str">
         <f>IF(G9="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -2151,16 +2162,16 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="H10" s="4" t="str">
         <f>IF(G10="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -2200,7 +2211,7 @@
   <sheetData>
     <row r="1" spans="1:21" s="15" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -2218,49 +2229,49 @@
         <v>6</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="K1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="J1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="S1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="U1" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2268,44 +2279,36 @@
         <v>1945</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F2" s="17"/>
       <c r="G2" s="1"/>
       <c r="H2" s="18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I2" s="18"/>
       <c r="J2" s="18"/>
       <c r="K2" s="18"/>
       <c r="L2" s="1"/>
       <c r="M2" s="19" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="N2" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="P2" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q2" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" s="19" t="s">
-        <v>91</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
       <c r="S2" s="19"/>
       <c r="T2" s="19"/>
       <c r="U2" s="2" t="str">
@@ -2318,21 +2321,21 @@
         <v>1946</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F3" s="19"/>
       <c r="G3" s="1"/>
       <c r="H3" s="18" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
@@ -2356,13 +2359,13 @@
         <v>1947</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>94</v>
+        <v>247</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="19"/>
@@ -2380,7 +2383,7 @@
       <c r="R4" s="19"/>
       <c r="S4" s="19"/>
       <c r="T4" s="20" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="U4" s="2" t="str">
         <f>IF(F4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -2392,28 +2395,28 @@
         <v>1948</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="19"/>
       <c r="G5" s="1"/>
       <c r="H5" s="18" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="J5" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>218</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="19"/>
@@ -2434,29 +2437,29 @@
         <v>1949</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="19"/>
       <c r="G6" s="1"/>
       <c r="H6" s="18" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="I6" s="18"/>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="1"/>
       <c r="M6" s="19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O6" s="19"/>
       <c r="P6" s="19"/>
@@ -2474,12 +2477,12 @@
         <v>1950</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F7" s="19"/>
       <c r="G7" s="1"/>
@@ -2487,13 +2490,17 @@
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
+      <c r="M7" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="O7" s="19"/>
       <c r="P7" s="19"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S7" s="19"/>
       <c r="T7" s="19"/>
@@ -2507,14 +2514,14 @@
         <v>1951</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="19"/>
@@ -2523,8 +2530,12 @@
       <c r="J8" s="19"/>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
+      <c r="M8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N8" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="O8" s="19"/>
       <c r="P8" s="19"/>
       <c r="Q8" s="19"/>
@@ -2541,16 +2552,16 @@
         <v>1952</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="19"/>
@@ -2560,13 +2571,17 @@
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
+        <v>85</v>
+      </c>
+      <c r="O9" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -2581,26 +2596,30 @@
         <v>1953</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="19"/>
-      <c r="H10" s="21" t="s">
-        <v>216</v>
+      <c r="H10" s="18" t="s">
+        <v>211</v>
       </c>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
+      <c r="M10" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="O10" s="19"/>
       <c r="P10" s="19"/>
       <c r="Q10" s="19"/>
@@ -2617,32 +2636,36 @@
         <v>1954</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="19"/>
       <c r="H11" s="18" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N11" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
+        <v>103</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="P11" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
       <c r="S11" s="19"/>
@@ -2657,12 +2680,12 @@
         <v>1955</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="19"/>
@@ -2689,28 +2712,32 @@
         <v>1956</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="19"/>
       <c r="H13" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I13" s="19"/>
       <c r="J13" s="19"/>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
+      <c r="M13" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="O13" s="19"/>
       <c r="P13" s="19"/>
       <c r="Q13" s="19"/>
@@ -2727,30 +2754,23 @@
         <v>1957</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="23"/>
       <c r="H14" s="18"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
+      <c r="M14" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="1:21" ht="101" customHeight="1" x14ac:dyDescent="0.2">
@@ -2758,28 +2778,32 @@
         <v>1959</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="28" t="s">
-        <v>237</v>
+      <c r="G15" s="25" t="s">
+        <v>230</v>
       </c>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
       <c r="J15" s="19"/>
       <c r="K15" s="19"/>
       <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
+      <c r="M15" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="O15" s="19"/>
       <c r="P15" s="19"/>
       <c r="Q15" s="19"/>
@@ -2796,16 +2820,16 @@
         <v>1960</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="19"/>
@@ -2814,8 +2838,12 @@
       <c r="J16" s="19"/>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
+      <c r="M16" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="O16" s="19"/>
       <c r="P16" s="19"/>
       <c r="Q16" s="19"/>
@@ -2832,14 +2860,14 @@
         <v>1961</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
@@ -2848,8 +2876,12 @@
       <c r="J17" s="19"/>
       <c r="K17" s="19"/>
       <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
+      <c r="M17" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="O17" s="19"/>
       <c r="P17" s="19"/>
       <c r="Q17" s="19"/>
@@ -2866,13 +2898,13 @@
         <v>1962</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -2882,8 +2914,12 @@
       <c r="J18" s="19"/>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
+      <c r="M18" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N18" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="O18" s="19"/>
       <c r="P18" s="19"/>
       <c r="Q18" s="19"/>
@@ -2901,39 +2937,32 @@
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="H19" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J19" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="J19" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="N19" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
+      <c r="M19" t="s">
+        <v>240</v>
+      </c>
+      <c r="N19" t="s">
+        <v>241</v>
+      </c>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="1:21" ht="56" customHeight="1" x14ac:dyDescent="0.2">
@@ -2944,23 +2973,10 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="23"/>
       <c r="H20" s="18"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
       <c r="U20" s="2"/>
     </row>
     <row r="21" spans="1:21" ht="70" customHeight="1" x14ac:dyDescent="0.2">
@@ -2968,13 +2984,13 @@
         <v>1966</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
@@ -3000,12 +3016,12 @@
         <v>1967</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="19"/>
@@ -3032,22 +3048,22 @@
         <v>1968</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>113</v>
+      <c r="G23" s="21" t="s">
+        <v>108</v>
       </c>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
@@ -3072,19 +3088,19 @@
         <v>1971</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="19"/>
@@ -3093,17 +3109,17 @@
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
       <c r="M24" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="T24" s="19"/>
       <c r="U24" s="2" t="str">
@@ -3116,22 +3132,22 @@
         <v>1975</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="G25" s="20" t="s">
         <v>54</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>56</v>
       </c>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
@@ -3156,19 +3172,19 @@
         <v>1977</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
@@ -3194,22 +3210,22 @@
         <v>1980</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="G27" s="11" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
@@ -3237,16 +3253,16 @@
         <v>1982</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="G28" s="19"/>
       <c r="H28" s="19"/>
@@ -3298,330 +3314,330 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -3644,40 +3660,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B1" s="13"/>
     </row>
     <row r="2" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D34189C-27E0-3042-A5C9-6888A0450835}"/>
+  <xr:revisionPtr revIDLastSave="287" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B13D415-5C7F-CA41-B4EE-97C238D14A11}"/>
   <bookViews>
-    <workbookView xWindow="6940" yWindow="600" windowWidth="35120" windowHeight="24600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7320" yWindow="620" windowWidth="30760" windowHeight="24600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
     <sheet name="Années" sheetId="2" r:id="rId2"/>
-    <sheet name="Référentiel films" sheetId="3" r:id="rId3"/>
-    <sheet name="Mode_emploi" sheetId="4" r:id="rId4"/>
+    <sheet name="Sources générales" sheetId="5" r:id="rId3"/>
+    <sheet name="Référentiel films" sheetId="3" r:id="rId4"/>
+    <sheet name="Mode_emploi" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="289">
   <si>
     <t>ID période</t>
   </si>
@@ -83,9 +84,6 @@
     <t>1945-1946</t>
   </si>
   <si>
-    <t>Les ruines</t>
-  </si>
-  <si>
     <t>Le "point zéro" de l'histoire de l'Allemagne d'après-guerre est-il un point zéro pour la vie et l'œuvre de RWF ?</t>
   </si>
   <si>
@@ -113,15 +111,9 @@
     <t>Le miracle économique</t>
   </si>
   <si>
-    <t>Domination du "cinéma de papa" ( Papas Kino ) : films de terroir ( Heimatfilm ) et comédies légères dépolitisées.</t>
-  </si>
-  <si>
     <t>Enfance marquée par le divorce de ses parents (1951) et l'absence du père. Passion précoce pour le cinéma (refuge). Première lecture de Berlin Alexanderplatz vers 14 ans.</t>
   </si>
   <si>
-    <t>Fassbinder analyse rétrospectivement cette période (mensonges du miracle économique) dans la future Trilogie de la RFA .</t>
-  </si>
-  <si>
     <t>1961-1966</t>
   </si>
   <si>
@@ -131,9 +123,6 @@
     <t>Construction du Mur de Berlin (1961). Procès d'Auschwitz à Francfort (1963-1965). Démission d'Adenauer. Grande Coalition (1966).</t>
   </si>
   <si>
-    <t>Manifeste d'Oberhausen (1962) : naissance du Nouveau Cinéma Allemand. Fondation de l'école de cinéma DFFB à Berlin (1966).</t>
-  </si>
-  <si>
     <t>Échec au concours d'entrée de la DFFB. Rencontre Hanna Schygulla et Irm Hermann dans un cours d'art dramatique. Rejoint l'Action-Theater (1967).</t>
   </si>
   <si>
@@ -176,9 +165,6 @@
     <t>Terrorisme de la RAF (arrestations en 1972). Attentat des JO de Munich (1972). Démission de Willy Brandt (1974) suite à l'affaire Guillaume.</t>
   </si>
   <si>
-    <t>Découverte des mélodrames de Douglas Sirk . Fondation du Filmverlag der Autoren (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).</t>
-  </si>
-  <si>
     <t>Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international.</t>
   </si>
   <si>
@@ -377,9 +363,6 @@
     <t>Maria_braun.jpeg</t>
   </si>
   <si>
-    <t>Adaptant librement, près d'un siècle après sa parution - et quarante ans après la série culte de Fassbinder - le chef-d'oeuvre polyphonique d'Alfred Döblin, le réalisateur germano-afghan Burhan Qurbani en modernise le propos de manière radicale, en imaginant un réfugié sans papiers dans la peau de Franz Biberkopf, antihéros en quête de rédemption. Il transpose également à l'image l'audace formelle du roman, saturant les sens dans un tourbillon de musique, de mouvements et de couleurs. </t>
-  </si>
-  <si>
     <t>Titre canonique</t>
   </si>
   <si>
@@ -651,45 +634,6 @@
   </si>
   <si>
     <t>Lorsqu’une nouvelle fiche Film est créée, ajouter son titre et son ID dans Référentiel films.</t>
-  </si>
-  <si>
-    <r>
-      <t>Sissi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> d'Ernst Marischka avec Romy Schneider et Karlheinz Böhm, qui deviendra un acteur récurrent du cinéma de Fassbinder </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Avec sa femme Helene Weigel, Brecht fonde le Berliner Ensemble à Berlin-Est, où il crée </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cambria"/>
-        <family val="1"/>
-      </rPr>
-      <t>Mère courage et ses enfants</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cambria"/>
-        <family val="1"/>
-      </rPr>
-      <t>. Thomas Mann donne des conférences  en Allemagne de l'ouest et en République démocratique (voir le film de Pavec Pwalikoscki Fatherland (2026))</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">La mère de Fassbinder Lisolette Eder, née Pempeit, dite aussi Lilo Pempeit, est hospitalisée pour cause de tuberculose. </t>
@@ -712,63 +656,6 @@
     <t>La révolte des ouvriers est-allemands</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Le film de Rossellini </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Allemagne année zéro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> offre une vision réaliste et critique de l'Allemagne en ruine</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Allemagne année zéro </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>de Rossellini (1948) ) Le protagoniste Edmund tente de vendre un enregistrement d'un discours d'Hitler sur disque à des soldats alliés. La voix du Fürher se met à résonner dans les ruines du Reichstag, siège du parlement incendié en 1933</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Affiche du </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Mariage de Maria Braun</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Remariage de Lilo avec un journaliste, Wolff Eder. Relations difficiles entre RWF et son beau-père. 
 RWF revient à Munich mais vit dans un pensionnat. </t>
   </si>
@@ -951,11 +838,6 @@
   <si>
     <t>Construction du Mur de Berlin (1961). Adenauer est rééel chancelier fédéral.
 Procès d'Eichmann en Israel.</t>
-  </si>
-  <si>
-    <t>Visite de J.F Kennedy à Berlin-ouest : "ich bin ein Berliner". 
-Procès d'Auschwitz à Francfort (1963-1965)
-Démission d'Adenauer à 87 ans.</t>
   </si>
   <si>
     <t>Machorka Muff de Jean-Marie Straub</t>
@@ -1068,13 +950,617 @@
   <si>
     <t>A l'occasion du festival du film documentaire d'Oberhausen, publication du Manifeste d'Oberhausen : naissance du Nouveau Cinéma Allemand ("Le vieux cinéma est mort").
 Les Beatles entament eur carrière par un concert à Hambourg</t>
+  </si>
+  <si>
+    <t>Catégorie</t>
+  </si>
+  <si>
+    <t>Référence bibliographique</t>
+  </si>
+  <si>
+    <t>Usage dans la frise</t>
+  </si>
+  <si>
+    <t>Lien</t>
+  </si>
+  <si>
+    <t>Histoire allemande</t>
+  </si>
+  <si>
+    <t>Repères historiques, chronologie politique</t>
+  </si>
+  <si>
+    <t>URL éventuelle</t>
+  </si>
+  <si>
+    <t>Fassbinder</t>
+  </si>
+  <si>
+    <t>Référence complète</t>
+  </si>
+  <si>
+    <t>Biographie et filmographie</t>
+  </si>
+  <si>
+    <t>Cinéma allemand</t>
+  </si>
+  <si>
+    <t>Contexte culturel et esthétique</t>
+  </si>
+  <si>
+    <t>Archives et sites</t>
+  </si>
+  <si>
+    <t>Nom du site ou de l’institution</t>
+  </si>
+  <si>
+    <t>Documents et vérifications</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Je ne pense pas qu'il fait fait un seul que l'on pourrait qualifier de chef-d'œuvre. Le chef-d'œuvre, c'est les 41 films et la vie et tout le reste. Les films ne sont que le résidu de cette vie."Peter Chatel </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">in  Die Sehnsucht des Rainer Werner Fassbinder » (La Nostalgie de Rainer Werner Fassbinder), De Kurt Raab et Karsten Peters, 1982, éditions Bertelsmann </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>, de Thomas Elsaesser, Centre Pompidou, 2005</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>, de Thomas Elsaesser, Centre Pompidou, 2005</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>, pp. 490-507</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Domination du "cinéma de papa" ( Papas Kino ) : films de terroir ( Heimatfilm ), comédies légères dépolitisées, films en costumes , comédies musicales obitennent toujours les faveurs du public. Ces genres nés dans les années 10 et 20 ont été très exploités par les nazis. </t>
+  </si>
+  <si>
+    <t>Manifeste d'Oberhausen (1962) : naissance du Nouveau Cinéma Allemand. Une nouvelle génération de cinéastes s'affirme et conquiert son indépendance notamment par la création de structures de production indépendantes. Fondation de l'école de cinéma DFFB à Berlin (1966).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une grande coaltion chrétienne-démocrate voit le jour sous l'autorité du nouveau chancelier Kurt Georg Kiesinger. Willy Brandt est ministre des affaires étrangères et vice-chancelier. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une majorité sociale-libérale place Willy Brandt au pouvoir. </t>
+  </si>
+  <si>
+    <t>Visite de J.F Kennedy à Berlin-ouest : "ich bin ein Berliner". 
+Procès d'Auschwitz à Francfort (1963-1965)
+Démission d'Adenauer à 87 ans. Ludwijg Ehrard, père du "miracle économique", devient Chancelier de la RFA.</t>
+  </si>
+  <si>
+    <t>Terrorisme de la RAF (arrestations en 1972). Attentat des JO de Munich (1972). Démission de Willy Brandt (1974) suite à l'affaire Guillaume. Un virage conservateur s'opère.</t>
+  </si>
+  <si>
+    <t>Les ruines l'Heure zéro</t>
+  </si>
+  <si>
+    <t>Les années 55-75, celles pendant lesquelles RWF est sorti de l'enfance et s'est développé comme adolescent puis adulte, seront celles qui nourriront son inspiration cinémétographique et sa réflexion politique. Même les films dont l'action se situent avant 1945 sont à envisager comme "une archéologie de la société allemande d'après-guerre" (Elsaesser, p. 34)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le militantisme et l'action politique violente, marquée à l'extrême gauche après 1968 en Allemagne, sont le terreau de plusieurs films de Fassbinder : </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Voyage à Niklashausen, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Maman Kusters s'en va au ciel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, ou encore </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>La troisième génération</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Il est remarquable qu'un comique outrancier associer l'action violente à une forme de bêtise radicale. </t>
+    </r>
+  </si>
+  <si>
+    <t>Découverte des mélodrames de Douglas Sirk .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Fondation du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Filmverlag der Autoren</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).
+Plusieurs cinéastes allemands ( Schlöndorff, Herzog notamment) réalisent des charges politiques violentes contre la politique et la société allemande. </t>
+    </r>
+  </si>
+  <si>
+    <t>L'œuvre de Fassbinder analyse rétrospectivement cette période en mettant à distance le consensus social de la prospérité des années 50 et 60 et en révélant les mensonges du miracle économique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RWF projette d'adapter le roman de Freytag Soll und Haben (1855), œuvre notaoirement antismétique en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. </t>
+  </si>
+  <si>
+    <t>La première diffusion de Berlin Alexander Platz à la télévision déclenche une violente campagne de haine contre le réalisateur. Le journaliste Klaus Eder qualifie l'oeuvre de "mastubations malpropres" 
+Adaptant librement, près d'un siècle après sa parution - et quarante ans après la série culte de Fassbinder - le chef-d'oeuvre polyphonique d'Alfred Döblin, le réalisateur germano-afghan Burhan Qurbani en modernise le propos de manière radicale, en imaginant un réfugié sans papiers dans la peau de Franz Biberkopf, antihéros en quête de rédemption. Il transpose également à l'image l'audace formelle du roman, saturant les sens dans un tourbillon de musique, de mouvements et de couleurs. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Whity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Prenez garde à la sainte putain</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> Le mouvement atteint son apogée thématique et politique.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Film collectif </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'Allemagne en automne </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(1978).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le film de Rossellini </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Allemagne année zéro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> offre une vision réaliste et critique de l'Allemagne en ruine</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Allemagne année zéro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>de Rossellini (1948) ) Le protagoniste Edmund tente de vendre un enregistrement d'un discours d'Hitler sur disque à des soldats alliés. La voix du Fürher se met à résonner dans les ruines du Reichstag, siège du parlement incendié en 1933</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Avec sa femme Helene Weigel, Brecht fonde le Berliner Ensemble à Berlin-Est, où il crée </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mère courage et ses enfants</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Thomas Mann donne des conférences  en Allemagne de l'ouest et en République démocratique (voir le film de Pavec Pwalikoscki Fatherland (2026))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Sissi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> d'Ernst Marischka avec Romy Schneider et Karlheinz Böhm, qui deviendra un acteur récurrent du cinéma de Fassbinder </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Représenter l'Allemagne, ce n'est pas seulement adopter une position critique, c'est inventer une nouvelle manière". </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, de Thomas Elsaesser, Centre Pompidou, 2005, p.26</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Affiche du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mariage de Maria Braun</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"je trouve que l'Allemagne en particulier est dans une situation où beaucoup de choses régressent. Je dirais qu'en 1945, lorsque la guerre a pris fin, lorsque le troisième Reich a pris fin, on n'a pas perçu quelles chances s'offraient à l'Allemagne, mais je pense qu'au contraire, comme je l'ai écrit dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Die Zeit, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">les valeurs et les structures sur lesquelles repose cet Etat, aujourd'hui devenu démocratique, sont restées, fondamentalement les mêmes qu'autrefois. Cet état de fait, si on ajoute cette tendance régressive, va conduire à quelque chose, une forme d'Etat dans lequel je n'aimerais pas tellement vivre". Entreitne donné à Peter W. Jansen en 1978 et repris dans l'ouvra ge </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fassbinder par lui-même</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, p.342-343, G3J éditeur, 2010</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">L'épisode réalisé par RWF dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'Allemagne en automne </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>offre une relecture des actions commises par la RAF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"je ferai des films jusqu'à ce que j'ai conduit mon histoire de la RFA jusqu'à ici et aujourd'hui. Les histoires de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Lola </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">et </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Maria Braun</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ne sont possibles que dans l'époque où elles se déroulent. Et elles s'intègrent, je l'espère, dans un portrait d'ensemble de la République fédérale, elles aident à comprendre cette étrange entité, avec ses dangers et ses menaces. En ce sens, ce sont des films très politiques". in </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Rainer Werner Fassbinder, Dichter, Schapuspieler, Filmemacher, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Argon, 1992, p.77</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La première génération était celle de 1968. Des idéalistes qui voulaient changer le monde et qui s'imginaient pouvoir le faire avec des mots et des manifestes. La deuxième, celle du groupe Gaader-Meinhof, passa de la légalité à la lutte armée et à l'illégalité totale. la troisième génération est celle d'aujourd'hui, qui se contente d'agir sans réfélchir, qui n'a ni idéologie ni politique, et qui se fait manipuler à son insu comme une troupe de marionnettes" </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fassbinder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Jansen/Schütte, Collection Rivages-cinéma, 1986, p.106</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">La troisième génération, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">film inspiré par les actions de la RAF et la violence d'Etat, est compliqué à produire. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le Mariage de Maria Braun </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">allégorie de la reconstruction allemande, connaît un triomphe international.  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Année des treize lune</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">s est une œuvre radicale sur le désespoir. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Le monde sur un fil (1973)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, adaption libre d'un récit de science-fiction interroge la notion même de réalité. </t>
+    </r>
+  </si>
+  <si>
+    <t>Victoire de la CDU en octobre : Helmut Kohl devient chancelier. Fin d'une époque artistique et politique radicale.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1114,27 +1600,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color rgb="FFFFFFFF"/>
@@ -1154,23 +1619,6 @@
     <font>
       <i/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1178,6 +1626,47 @@
     <font>
       <i/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1254,39 +1743,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1294,12 +1760,39 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -1315,11 +1808,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="0"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1329,7 +1822,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1339,7 +1836,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1349,7 +1850,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1359,7 +1864,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1369,7 +1878,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1379,7 +1892,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1389,7 +1906,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1399,7 +1920,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1409,7 +1934,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1419,7 +1948,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1429,7 +1962,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1439,7 +1976,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1449,7 +1990,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1459,7 +2004,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1469,7 +2018,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1479,7 +2032,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1489,7 +2046,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1499,7 +2060,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1509,7 +2074,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1519,7 +2088,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1529,6 +2102,10 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -1631,7 +2208,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="22">
   <autoFilter ref="A1:N10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID période"/>
@@ -1654,8 +2231,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T28" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="A1:T28" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T33" totalsRowShown="0" headerRowDxfId="21" dataDxfId="0">
+  <autoFilter ref="A1:T33" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="19"/>
@@ -1878,7 +2455,7 @@
     <col min="12" max="14" width="27.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="15" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" s="12" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1907,7 +2484,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>9</v>
@@ -1927,56 +2504,56 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="H2" s="2" t="str">
         <f>IF(G2="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
       <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" t="s">
+        <v>233</v>
+      </c>
+      <c r="L2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
-        <v>245</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>20</v>
       </c>
-      <c r="M2" t="s">
+    </row>
+    <row r="3" spans="1:14" s="14" customFormat="1" ht="98" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" s="23" customFormat="1" ht="98" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>258</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="4" t="str">
@@ -1984,93 +2561,93 @@
         <v/>
       </c>
       <c r="I3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="L3" s="25" t="s">
-        <v>226</v>
+        <v>269</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>259</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H4" s="4" t="str">
         <f>IF(G4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
       <c r="J4" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="85" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>IF(G5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="98" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>45</v>
+        <v>268</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>46</v>
+        <v>267</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H6" s="4" t="str">
         <f>IF(G6="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -2080,75 +2657,75 @@
     </row>
     <row r="7" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H7" s="4" t="str">
         <f>IF(G7="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H8" s="4" t="str">
         <f>IF(G8="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1978-l-annee-des-treize-lunes; film-1979-le-mariage-de-maria-braun</v>
       </c>
       <c r="N8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H9" s="4" t="str">
         <f>IF(G9="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -2162,16 +2739,16 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H10" s="4" t="str">
         <f>IF(G10="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -2194,7 +2771,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="31.83203125" customWidth="1"/>
@@ -2209,9 +2786,9 @@
     <col min="21" max="21" width="56.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="15" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="12" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -2229,52 +2806,52 @@
         <v>6</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="S1" s="8" t="s">
         <v>12</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="98" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1945</v>
       </c>
@@ -2282,41 +2859,37 @@
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="17"/>
+        <v>79</v>
+      </c>
+      <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
+      <c r="H2" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="19"/>
-      <c r="T2" s="19"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
       <c r="U2" s="2" t="str">
         <f>IF(F2="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="224" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1946</v>
       </c>
@@ -2324,224 +2897,225 @@
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F3" s="19"/>
+        <v>83</v>
+      </c>
+      <c r="F3" s="20"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="H3" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="19"/>
-      <c r="T3" s="19"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
       <c r="U3" s="2" t="str">
         <f>IF(F3="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="244" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="182" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1947</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="19"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="20" t="s">
-        <v>90</v>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="U4" s="2" t="str">
         <f>IF(F4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="196" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1948</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>275</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="19"/>
+      <c r="F5" s="20"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="18" t="s">
-        <v>91</v>
+      <c r="H5" s="21" t="s">
+        <v>86</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>213</v>
+        <v>200</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>276</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L5" s="1"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
       <c r="U5" s="2" t="str">
         <f>IF(F5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="118" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" ht="112" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>1949</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>205</v>
+        <v>88</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>277</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="19"/>
+      <c r="F6" s="20"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
+      <c r="H6" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
+      <c r="M6" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
       <c r="U6" s="2" t="str">
         <f>IF(F6="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" ht="70" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>1950</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F7" s="19"/>
+        <v>198</v>
+      </c>
+      <c r="F7" s="20"/>
       <c r="G7" s="1"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
+      <c r="M7" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
       <c r="U7" s="2" t="str">
         <f>IF(F7="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" ht="56" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>1951</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N8" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
       <c r="U8" s="2" t="str">
         <f>IF(F8="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -2552,40 +3126,40 @@
         <v>1952</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
       <c r="M9" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="O9" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="P9" s="19" t="s">
-        <v>87</v>
+        <v>80</v>
+      </c>
+      <c r="O9" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="P9" s="20" t="s">
+        <v>82</v>
       </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="19"/>
+      <c r="T9" s="20"/>
       <c r="U9" s="2" t="str">
         <f>IF(F9="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -2596,36 +3170,36 @@
         <v>1953</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N10" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
       <c r="U10" s="2" t="str">
         <f>IF(F10="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -2636,40 +3210,40 @@
         <v>1954</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>278</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="N11" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="O11" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="P11" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="N11" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="O11" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="P11" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
       <c r="U11" s="2" t="str">
         <f>IF(F11="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -2680,28 +3254,28 @@
         <v>1955</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
       <c r="U12" s="2" t="str">
         <f>IF(F12="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -2712,38 +3286,38 @@
         <v>1956</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N13" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
       <c r="U13" s="2" t="str">
         <f>IF(F13="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -2754,218 +3328,238 @@
         <v>1957</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="H14" s="18"/>
-      <c r="M14" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N14" s="19" t="s">
-        <v>87</v>
-      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
       <c r="U14" s="2"/>
     </row>
-    <row r="15" spans="1:21" ht="101" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" ht="126" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>1959</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>215</v>
+        <v>218</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>204</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N15" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
+      <c r="G15" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
       <c r="U15" s="2" t="str">
         <f>IF(F15="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="152" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" ht="126" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>1960</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N16" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N16" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
       <c r="U16" s="2" t="str">
         <f>IF(F16="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="136" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" ht="126" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>1961</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D17" s="19"/>
+        <v>226</v>
+      </c>
+      <c r="D17" s="20"/>
       <c r="E17" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N17" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
+        <v>222</v>
+      </c>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N17" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
       <c r="U17" s="2" t="str">
         <f>IF(F17="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" ht="112" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>1962</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N18" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="M18" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
       <c r="U18" s="2" t="str">
         <f>IF(F18="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="110" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" ht="126" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>1963</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="F19" s="1"/>
-      <c r="H19" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="J19" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="M19" t="s">
-        <v>240</v>
-      </c>
-      <c r="N19" t="s">
-        <v>241</v>
-      </c>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="N19" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
       <c r="U19" s="2"/>
     </row>
-    <row r="20" spans="1:21" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="28" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>1964</v>
       </c>
@@ -2973,39 +3567,54 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="H20" s="18"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
       <c r="U20" s="2"/>
     </row>
-    <row r="21" spans="1:21" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" ht="70" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>1966</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>260</v>
+      </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
+        <v>28</v>
+      </c>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
       <c r="U21" s="2" t="str">
         <f>IF(F21="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3016,270 +3625,421 @@
         <v>1967</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F22" s="1"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
       <c r="U22" s="2" t="str">
         <f>IF(F22="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" ht="70" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>1968</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G23" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
+        <v>36</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
       <c r="U23" s="2" t="str">
         <f>IF(F23="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21" ht="28" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
+        <v>1969</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="2"/>
+    </row>
+    <row r="25" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>1970</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G25" s="25"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="2"/>
+    </row>
+    <row r="26" spans="1:21" ht="154" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
         <v>1971</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G24" s="1"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="T24" s="19"/>
-      <c r="U24" s="2" t="str">
-        <f>IF(F24="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" ht="70" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>1975</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="2" t="str">
-        <f>IF(F25="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>1977</v>
-      </c>
       <c r="B26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="N26" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="19"/>
-      <c r="S26" s="19"/>
-      <c r="T26" s="19"/>
+      <c r="T26" s="20"/>
       <c r="U26" s="2" t="str">
         <f>IF(F26="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1978-l-annee-des-treize-lunes; film-1979-le-mariage-de-maria-braun</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" ht="70" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>1980</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>112</v>
-      </c>
+        <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="42" x14ac:dyDescent="0.2">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="G27" s="1"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
       <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
       <c r="T27" s="19"/>
-      <c r="U27" s="2" t="str">
-        <f>IF(F27="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1980-berlin-alexanderplatz; film-1981-lili-marleen; film-1981-lola-une-femme-allemande</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U27" s="2"/>
+    </row>
+    <row r="28" spans="1:21" ht="56" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>1982</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1982</v>
+        <v>1975</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
+        <v>48</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
       <c r="U28" s="2" t="str">
         <f>IF(F28="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="252" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>1977</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="2" t="str">
+        <f>IF(F29="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="182" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>1978</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="2"/>
+    </row>
+    <row r="31" spans="1:21" ht="98" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>1979</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="2"/>
+    </row>
+    <row r="32" spans="1:21" ht="306" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>1980</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="2" t="str">
+        <f>IF(F32="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1980-berlin-alexanderplatz; film-1981-lili-marleen; film-1981-lola-une-femme-allemande</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="126" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1982</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="2" t="str">
+        <f>IF(F33="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1981-le-secret-de-veronika-voss; film-1982-querelle</v>
       </c>
     </row>
@@ -3304,6 +4064,89 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C07A15F-9849-0547-90EB-0E0C6153DA22}">
+  <dimension ref="A15:D19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="37.5" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A15" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.15">
+      <c r="A16" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="17"/>
+    </row>
+    <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.15">
+      <c r="A17" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="28" x14ac:dyDescent="0.15">
+      <c r="A18" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28" x14ac:dyDescent="0.15">
+      <c r="A19" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>254</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -3314,330 +4157,330 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B4" s="9" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+    <row r="5" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+    <row r="6" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+    <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+    <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+    <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+    <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="11" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+    <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
+    <row r="13" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+    <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+    <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+    <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B17" s="9" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
+    <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B18" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
+    <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B19" s="9" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+    <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
+    <row r="21" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B21" s="9" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
+    <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B22" s="9" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+    <row r="23" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B23" s="9" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="12" t="s">
+    <row r="24" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B24" s="9" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="12" t="s">
+    <row r="25" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B25" s="9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
+    <row r="26" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B26" s="9" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
+    <row r="27" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B27" s="9" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="12" t="s">
+    <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B28" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
+    <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A29" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B29" s="9" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="12" t="s">
+    <row r="30" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B30" s="9" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="12" t="s">
+    <row r="31" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B31" s="9" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="12" t="s">
+    <row r="32" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="12" t="s">
+    <row r="33" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A33" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B33" s="9" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A31" s="12" t="s">
+    <row r="34" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B34" s="9" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" s="12" t="s">
+    <row r="35" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B35" s="9" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="12" t="s">
+    <row r="36" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A34" s="12" t="s">
+    <row r="37" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B37" s="9" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A35" s="12" t="s">
+    <row r="38" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B38" s="9" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="12" t="s">
+    <row r="39" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A39" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B39" s="9" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="12" t="s">
+    <row r="40" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A38" s="12" t="s">
+    <row r="41" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B41" s="9" t="s">
         <v>188</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A39" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A40" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A41" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -3649,7 +4492,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -3659,41 +4502,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="10"/>
+    </row>
+    <row r="2" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="13"/>
-    </row>
-    <row r="2" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B5" s="7" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="287" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B13D415-5C7F-CA41-B4EE-97C238D14A11}"/>
+  <xr:revisionPtr revIDLastSave="316" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D42616BE-01C7-D54B-B6C1-DB7513A5FFE6}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="620" windowWidth="30760" windowHeight="24600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7320" yWindow="600" windowWidth="30760" windowHeight="24600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,11 @@
     <sheet name="Référentiel films" sheetId="3" r:id="rId4"/>
     <sheet name="Mode_emploi" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="295">
   <si>
     <t>ID période</t>
   </si>
@@ -69,6 +72,9 @@
     <t>Analyse et réception critique</t>
   </si>
   <si>
+    <t>Liens</t>
+  </si>
+  <si>
     <t>Citation</t>
   </si>
   <si>
@@ -84,12 +90,39 @@
     <t>1945-1946</t>
   </si>
   <si>
+    <t>Les ruines l'Heure zéro</t>
+  </si>
+  <si>
     <t>Le "point zéro" de l'histoire de l'Allemagne d'après-guerre est-il un point zéro pour la vie et l'œuvre de RWF ?</t>
   </si>
   <si>
     <t xml:space="preserve">Capitulation du Troisième Reich (mai). L'Allemagne est en ruines (Année Zéro). Début de l'occupation alliée et de l'amnésie collective sur le passé nazi. Le pays et berlin sont partagés en zone sous contrôle des différentes forces alliées. </t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">Le cinéma est en ruines. Période des films de décombres ( Trümmerfilme ) comme </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Les assassins sont parmi nous </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Staudte, 1946).</t>
+    </r>
+  </si>
+  <si>
     <t>Naissance de Rainer Werner Fassbinder le 31 mai à Bad Wörishofen, Bavière.</t>
   </si>
   <si>
@@ -99,6 +132,9 @@
     <t>Les génériques de Fassbinder</t>
   </si>
   <si>
+    <t>"Nous devons nous débarrasser du passé pour construire l'avenir". Konrad Adenauer</t>
+  </si>
+  <si>
     <t>Adenauer.jpeg</t>
   </si>
   <si>
@@ -111,9 +147,25 @@
     <t>Le miracle économique</t>
   </si>
   <si>
+    <t>Création de la RFA (1949). Ère Adenauer. Miracle économique ( Wirtschaftswunder )  entre 1950 et 1965 l'économie ouest-allemande croît de 8,2% en moyenne (contre 5% en France pendant les 30 glorieuses). La coccinelle de Wolkswagen devient l'emblème du "miracle économique". 
+Parallèmement, l'état  développe une politique sociale conservatrice. Réarmement de la RFA (1955).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domination du "cinéma de papa" ( Papas Kino ) : films de terroir ( Heimatfilm ), comédies légères dépolitisées, films en costumes , comédies musicales obitennent toujours les faveurs du public. Ces genres nés dans les années 10 et 20 ont été très exploités par les nazis. </t>
+  </si>
+  <si>
     <t>Enfance marquée par le divorce de ses parents (1951) et l'absence du père. Passion précoce pour le cinéma (refuge). Première lecture de Berlin Alexanderplatz vers 14 ans.</t>
   </si>
   <si>
+    <t>L'œuvre de Fassbinder analyse rétrospectivement cette période en mettant à distance le consensus social de la prospérité des années 50 et 60 et en révélant les mensonges du miracle économique.</t>
+  </si>
+  <si>
+    <t>De l'année zéro au miracle économique</t>
+  </si>
+  <si>
+    <t>l-industrie-de-l-industrie-automobile-l-usine-volkswagen-vue-de-l-interieur-usine-wolfsburg-vers-1950.jpg</t>
+  </si>
+  <si>
     <t>1961-1966</t>
   </si>
   <si>
@@ -123,6 +175,9 @@
     <t>Construction du Mur de Berlin (1961). Procès d'Auschwitz à Francfort (1963-1965). Démission d'Adenauer. Grande Coalition (1966).</t>
   </si>
   <si>
+    <t>Manifeste d'Oberhausen (1962) : naissance du Nouveau Cinéma Allemand. Une nouvelle génération de cinéastes s'affirme et conquiert son indépendance notamment par la création de structures de production indépendantes. Fondation de l'école de cinéma DFFB à Berlin (1966).</t>
+  </si>
+  <si>
     <t>Échec au concours d'entrée de la DFFB. Rencontre Hanna Schygulla et Irm Hermann dans un cours d'art dramatique. Rejoint l'Action-Theater (1967).</t>
   </si>
   <si>
@@ -150,12 +205,6 @@
     <t>Fonde l' antiteater (1968). Collaboration intense avec sa "troupe" (Schygulla, Hermann, Raab, Baer, Lommel). Mariage avec Ingrid Caven (1970).</t>
   </si>
   <si>
-    <t>L'amour est plus froid que la mort (1969),  Le Bouc (1969, succès à Mannheim) : critique de la xénophobie et de l'apathie bourgeoise.</t>
-  </si>
-  <si>
-    <t>Premier film accueilli froidement à Berlin. Le second est une critique de la xénophobie et de l'apathie bourgeoise</t>
-  </si>
-  <si>
     <t>1971-1974</t>
   </si>
   <si>
@@ -165,7 +214,7 @@
     <t>Terrorisme de la RAF (arrestations en 1972). Attentat des JO de Munich (1972). Démission de Willy Brandt (1974) suite à l'affaire Guillaume.</t>
   </si>
   <si>
-    <t>Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international.</t>
+    <t>Découverte des mélodrames de Douglas Sirk .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international.</t>
   </si>
   <si>
     <t>Période Sirkienne : Le Marchand des quatre saisons (1971). Tous les autres s'appellent Ali (1974, succès mondial à Cannes) : critique du racisme ordinaire. Martha (1974).</t>
@@ -174,9 +223,6 @@
     <t>1975-1976</t>
   </si>
   <si>
-    <t>,,,,,,,,,,,,,,,,</t>
-  </si>
-  <si>
     <t>Tensions sociales et crises du logement (Westend). Débats sur la visibilité des minorités. Lois limitant les libertés civiles.</t>
   </si>
   <si>
@@ -276,461 +322,301 @@
     <t>IDs films — Œuvres</t>
   </si>
   <si>
+    <t>Les alliés aident à la relance de médias d'information et promeuvent une nouvelle politique éducative. 
+Les alliés organisent un vaste programme de démocratisation, décartellisation, démilatarisation et dénazification</t>
+  </si>
+  <si>
     <t xml:space="preserve">Le cinéma est en ruines. Premières projection des Moulins de la mort (Todesmühen), un documentaire sur les camps de concentration. </t>
   </si>
   <si>
     <t>Naissance de Rainer Werner Fassbinder le 31 mai à Bad Wörishofen, Bavière. Père médecin généraliste, mère traductrice. Première année passée chez son oncle paternel</t>
   </si>
   <si>
+    <t xml:space="preserve">Premières élections municipales dans la zone américaine. 
+La « loi d'élimination du national-socialisme et du militarisme » du 5 mars 1946 définit dans son article 4 les niveaux de responsabilité : Hauptschuldige (principaux coupables), Belastete (charges importantes), Minderbelastete (charges mineures), Mitläufer (suivistes), Entlastete (libérés, les procès en dénazification pouvant déclarer les prévenus nicht betroffen, « non concernés » par cette loi). Procès de Nuremberg : 12 des 24 accusés sont condamnés à mort pour crimes de guerre.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fondation de la DEFA (Deutsch Film AG) à Berlin Est. Premières productions de films allemands de fiction depuis la fin de la guerre. 
+Vogue de l'évocation mélancolique de la patrie dans la chanson de variété allemande avec "Möwe, di fliegst in die Heimat" de Magda Hein. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le couple Fassbinder prend l'enfant avec eux à Munich. Une partie de la famille vit dans le même appartement, notamment la grand-mère de Rainer. </t>
+  </si>
+  <si>
+    <t>Le procès de Nuremberg</t>
+  </si>
+  <si>
+    <t>Période de disette la plus terrible depuis la fin de la guerre. Les Trümmerfrauen (les femmes des ruines) constituent un des piliers de la reconstruction.</t>
+  </si>
+  <si>
+    <t>A l'initiative de Hans Werner Richter, fondation du Groupe 47 qui réunit l'avant-garde littéraire allemande dont Gunter Grass et Heinrich Böll.  Le Groupe cherche à constituer une élite exemplairement démocratique dans le domaine des lettres et à développer de nouvelles formes d'écriture pour permettre aux lettres allemandes d'exprimer au mieux des enjeux esthétiques et politiques en adéquation avec la société d'après-guerre.</t>
+  </si>
+  <si>
+    <t>Elsaesser, Wikipedia</t>
+  </si>
+  <si>
+    <t>Réforme monétaire de l'Allemagne de l'Ouest, acte fondateur du "miracle économique" comme de la séparation entre blocs est et ouest. Ludwig Erhard, professeur d'économie, développe l'économie sociale de marché. Le Plan Marshall participe à la relance de l'économie ouest-allemande. 
+Blocus de Berlin par les soviétiques, l'une des premières crises de la Guerre Froide. Un pont aérien est mise en place à l'initiative des Etats-Unis et de la Grande-Bretagne.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le film de Rossellini </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Allemagne année zéro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> offre une vision réaliste et critique de l'Allemagne en ruine</t>
+    </r>
+  </si>
+  <si>
+    <t>Le blocus de Berlin en 3 minutes</t>
+  </si>
+  <si>
+    <t>Allemagne_annee_0_Reichstag.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Allemagne année zéro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>de Rossellini (1948) ) Le protagoniste Edmund tente de vendre un enregistrement d'un discours d'Hitler sur disque à des soldats alliés. La voix du Fürher se met à résonner dans les ruines du Reichstag, siège du parlement incendié en 1933</t>
+    </r>
+  </si>
+  <si>
+    <t>Comment Rossellini traduit-il une relation complexe avec l'Histoire, entre fascination, terreur, et hantise ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création de l'OTAN. Création de la RFA. Konrad Adenauer est élu chancelier fédéral avec une courte majorité. La division de l'Allemande en deux états indépendants est reconnue par la communauté internationale. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Avec sa femme Helene Weigel, Brecht fonde le Berliner Ensemble à Berlin-Est, où il crée </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mère courage et ses enfants</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Thomas Mann donne des conférences  en Allemagne de l'ouest et en République démocratique (voir le film de Pavec Pwalikoscki Fatherland (2026))</t>
+    </r>
+  </si>
+  <si>
+    <t>Bande Annonce de Fatherland de Pavel Pawlikoski</t>
+  </si>
+  <si>
+    <t>Portrait d'Adenauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mère de Fassbinder Lisolette Eder, née Pempeit, dite aussi Lilo Pempeit, est hospitalisée pour cause de tuberculose. </t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création du Traité de "la communauté du charbon et de l'acier", début de la construction européenne autour de 6 pays. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divorce des parents. Le père de RWF, Helmut Fassbinder, s'installe à Cologne. RWF reste à Munich avec sa mère. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traité de réparation avec Israël signé par Adenauer. </t>
+  </si>
+  <si>
+    <t>Première émission de télévision dans le nord et l'ouest de la RFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mère de RWF l'inscrit dans une école Rudolf Steiner. Nbx séjours de la mère à l'hopital ou en sanatorium. RWF est confié à des voisins ou parents. Il commence à fréquenter assidument les salles de cinéma. </t>
+  </si>
+  <si>
+    <t>Fassbinder_enfant.jpeg</t>
+  </si>
+  <si>
     <t>Fassbinder enfant</t>
-  </si>
-  <si>
-    <t>Bohm.jpg</t>
-  </si>
-  <si>
-    <t>Portrait d'Adenauer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le couple Fassbinder prend l'enfant avec eux à Munich. Une partie de la famille vit dans le même appartement, notamment la grand-mère de Rainer. </t>
-  </si>
-  <si>
-    <t>Le procès de Nuremberg</t>
-  </si>
-  <si>
-    <t>Elsaesser, Wikipedia</t>
-  </si>
-  <si>
-    <t>Le blocus de Berlin en 3 minutes</t>
-  </si>
-  <si>
-    <t>Comment Rossellini traduit-il une relation complexe avec l'Histoire, entre fascination, terreur, et hantise ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création de l'OTAN. Création de la RFA. Konrad Adenauer est élu chancelier fédéral avec une courte majorité. La division de l'Allemande en deux états indépendants est reconnue par la communauté internationale. </t>
-  </si>
-  <si>
-    <t>Bande Annonce de Fatherland de Pavel Pawlikoski</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création du Traité de "la communauté du charbon et de l'acier", début de la construction européenne autour de 6 pays. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traité de réparation avec Israël signé par Adenauer. </t>
-  </si>
-  <si>
-    <t>Première émission de télévision dans le nord et l'ouest de la RFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La mère de RWF l'inscrit dans une école Rudolf Steiner. Nbx séjours de la mère à l'hopital ou en sanatorium. RWF est confié à des voisins ou parents. Il commence à fréquenter assidument les salles de cinéma. </t>
-  </si>
-  <si>
-    <t>Fassbinder_enfant.jpeg</t>
-  </si>
-  <si>
-    <t>Premiers concerts de rock'n'roll en RFA à Hambourg et Francfort.</t>
-  </si>
-  <si>
-    <t>Bande Annonce de Sissi (1955)</t>
-  </si>
-  <si>
-    <t>Karlheinz Böhm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RWF est lycéen à Munich. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RWF est pensionnaire à Augsbourg, sa mère étant hospitalisée pendant près de deux ans à la suite d'une opération. Il continue à fréquenter les salles obscures. </t>
-  </si>
-  <si>
-    <t>RWF commence à écrire des nouvelles et de petites pièces de théâtre</t>
-  </si>
-  <si>
-    <t>Rejoint l'Action-Theater (1967).</t>
-  </si>
-  <si>
-    <t>Premier film accueili froidement à Berlin. Le second est une critique de la xénophobie et de l'apathie bourgeoise</t>
-  </si>
-  <si>
-    <t>Fondation du Filmverlag der Autoren (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).</t>
-  </si>
-  <si>
-    <t>Découverte des mélodrames de Douglas Sirk . Période Sirkienne : Le Marchand des quatre saisons (1971). Tous les autres s'appellent Ali (1974, succès mondial à Cannes) : critique du racisme ordinaire. Martha (1974).</t>
-  </si>
-  <si>
-    <t>Maria_braun.jpeg</t>
-  </si>
-  <si>
-    <t>Titre canonique</t>
-  </si>
-  <si>
-    <t>ID canonique</t>
-  </si>
-  <si>
-    <t>L’Amour est plus froid que la mort</t>
-  </si>
-  <si>
-    <t>film-1969-l-amour-est-plus-froid-que-la-mort</t>
-  </si>
-  <si>
-    <t>Le Bouc</t>
-  </si>
-  <si>
-    <t>film-1969-le-bouc</t>
-  </si>
-  <si>
-    <t>Les Dieux de la peste</t>
-  </si>
-  <si>
-    <t>film-1970-les-dieux-de-la-peste</t>
-  </si>
-  <si>
-    <t>Pourquoi M. R. est-il atteint de folie meurtrière ?</t>
-  </si>
-  <si>
-    <t>film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere</t>
-  </si>
-  <si>
-    <t>Le Soldat américain</t>
-  </si>
-  <si>
-    <t>film-1970-le-soldat-americain</t>
-  </si>
-  <si>
-    <t>Le Voyage à Niklashausen</t>
-  </si>
-  <si>
-    <t>film-1970-le-voyage-a-niklashausen</t>
-  </si>
-  <si>
-    <t>Whity</t>
-  </si>
-  <si>
-    <t>film-1971-whity</t>
-  </si>
-  <si>
-    <t>Prenez garde à la sainte putain</t>
-  </si>
-  <si>
-    <t>film-1971-prenez-garde-a-la-sainte-putain</t>
-  </si>
-  <si>
-    <t>Pionniers à Ingolstadt</t>
-  </si>
-  <si>
-    <t>film-1971-pionniers-a-ingolstadt</t>
-  </si>
-  <si>
-    <t>Le Marchand des quatre saisons</t>
-  </si>
-  <si>
-    <t>film-1972-le-marchand-des-quatre-saisons</t>
-  </si>
-  <si>
-    <t>Les Larmes amères de Petra von Kant</t>
-  </si>
-  <si>
-    <t>film-1972-les-larmes-ameres-de-petra-von-kant</t>
-  </si>
-  <si>
-    <t>Liberté à Brême</t>
-  </si>
-  <si>
-    <t>film-1972-liberte-a-breme</t>
-  </si>
-  <si>
-    <t>Huit heures ne font pas un jour</t>
-  </si>
-  <si>
-    <t>film-1972-huit-heures-ne-font-pas-un-jour</t>
-  </si>
-  <si>
-    <t>Gibier de passage</t>
-  </si>
-  <si>
-    <t>film-1973-gibier-de-passage</t>
-  </si>
-  <si>
-    <t>Le Monde sur un fil</t>
-  </si>
-  <si>
-    <t>film-1973-le-monde-sur-un-fil</t>
-  </si>
-  <si>
-    <t>Tous les autres s’appellent Ali</t>
-  </si>
-  <si>
-    <t>film-1974-tous-les-autres-s-appellent-ali</t>
-  </si>
-  <si>
-    <t>Effi Briest</t>
-  </si>
-  <si>
-    <t>film-1974-effi-briest</t>
-  </si>
-  <si>
-    <t>Nora Helmer</t>
-  </si>
-  <si>
-    <t>film-1974-nora-helmer</t>
-  </si>
-  <si>
-    <t>Martha</t>
-  </si>
-  <si>
-    <t>film-1974-martha</t>
-  </si>
-  <si>
-    <t>Le Droit du plus fort</t>
-  </si>
-  <si>
-    <t>film-1975-le-droit-du-plus-fort</t>
-  </si>
-  <si>
-    <t>Maman Küsters s’en va au ciel</t>
-  </si>
-  <si>
-    <t>film-1975-maman-kusters-s-en-va-au-ciel</t>
-  </si>
-  <si>
-    <t>Comme un oiseau sur le fil</t>
-  </si>
-  <si>
-    <t>film-1975-comme-un-oiseau-sur-le-fil</t>
-  </si>
-  <si>
-    <t>Peur de la peur</t>
-  </si>
-  <si>
-    <t>film-1975-peur-de-la-peur</t>
-  </si>
-  <si>
-    <t>L’Ombre des anges</t>
-  </si>
-  <si>
-    <t>film-1976-l-ombre-des-anges</t>
-  </si>
-  <si>
-    <t>Le Rôti de Satan</t>
-  </si>
-  <si>
-    <t>film-1976-le-roti-de-satan</t>
-  </si>
-  <si>
-    <t>Roulette chinoise</t>
-  </si>
-  <si>
-    <t>film-1976-roulette-chinoise</t>
-  </si>
-  <si>
-    <t>Je veux seulement que vous m’aimiez</t>
-  </si>
-  <si>
-    <t>film-1976-je-veux-seulement-que-vous-m-aimiez</t>
-  </si>
-  <si>
-    <t>Femmes à New York</t>
-  </si>
-  <si>
-    <t>film-1977-femmes-a-new-york</t>
-  </si>
-  <si>
-    <t>La Femme du chef de gare</t>
-  </si>
-  <si>
-    <t>film-1977-la-femme-du-chef-de-gare</t>
-  </si>
-  <si>
-    <t>L’Allemagne en automne</t>
-  </si>
-  <si>
-    <t>film-1978-l-allemagne-en-automne</t>
-  </si>
-  <si>
-    <t>Despair</t>
-  </si>
-  <si>
-    <t>film-1978-despair</t>
-  </si>
-  <si>
-    <t>L’Année des treize lunes</t>
-  </si>
-  <si>
-    <t>film-1978-l-annee-des-treize-lunes</t>
-  </si>
-  <si>
-    <t>Le Mariage de Maria Braun</t>
-  </si>
-  <si>
-    <t>film-1979-le-mariage-de-maria-braun</t>
-  </si>
-  <si>
-    <t>La Troisième génération</t>
-  </si>
-  <si>
-    <t>film-1979-la-troisieme-generation</t>
-  </si>
-  <si>
-    <t>Berlin Alexanderplatz</t>
-  </si>
-  <si>
-    <t>film-1980-berlin-alexanderplatz</t>
-  </si>
-  <si>
-    <t>Lili Marleen</t>
-  </si>
-  <si>
-    <t>film-1981-lili-marleen</t>
-  </si>
-  <si>
-    <t>Théâtre en transe</t>
-  </si>
-  <si>
-    <t>film-1981-theatre-en-transe</t>
-  </si>
-  <si>
-    <t>Lola, une femme allemande</t>
-  </si>
-  <si>
-    <t>film-1981-lola-une-femme-allemande</t>
-  </si>
-  <si>
-    <t>Le Secret de Veronika Voss</t>
-  </si>
-  <si>
-    <t>film-1981-le-secret-de-veronika-voss</t>
-  </si>
-  <si>
-    <t>Querelle</t>
-  </si>
-  <si>
-    <t>film-1982-querelle</t>
-  </si>
-  <si>
-    <t>RWF_Frise — IDs automatiques</t>
-  </si>
-  <si>
-    <t>Principe</t>
-  </si>
-  <si>
-    <t>Les colonnes IDs films — Œuvres sont calculées à partir des titres canoniques présents dans Œuvres.</t>
-  </si>
-  <si>
-    <t>Saisie</t>
-  </si>
-  <si>
-    <t>Employer les titres français canoniques du référentiel. Plusieurs titres peuvent figurer dans la même cellule.</t>
-  </si>
-  <si>
-    <t>Absence d’ID</t>
-  </si>
-  <si>
-    <t>Une œuvre absente du référentiel Films reste sans ID : aucun identifiant n’est inventé.</t>
-  </si>
-  <si>
-    <t>Mise à jour</t>
-  </si>
-  <si>
-    <t>Lorsqu’une nouvelle fiche Film est créée, ajouter son titre et son ID dans Référentiel films.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La mère de Fassbinder Lisolette Eder, née Pempeit, dite aussi Lilo Pempeit, est hospitalisée pour cause de tuberculose. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Divorce des parents. Le père de RWF, Helmut Fassbinder, s'installe à Cologne. RWF reste à Munich avec sa mère. </t>
-  </si>
-  <si>
-    <t>Allemagne_annee_0_Reichstag.mp4</t>
   </si>
   <si>
     <t>Révolte des ouvriers berlinois est-allemands écrasée par les chars soviétiques. 
 Adenauer est réélu chancelier avec une coalition de centre droit</t>
   </si>
   <si>
+    <t>Premiers concerts de rock'n'roll en RFA à Hambourg et Francfort.</t>
+  </si>
+  <si>
+    <t>La révolte des ouvriers est-allemands</t>
+  </si>
+  <si>
     <t xml:space="preserve">La RFA devient un état souverain, doté de sa propre armée. Elle est admise au sein de l'OTAN.
 Les premiers travailleurs immigrés commencent à arriver de Grèce et d'Italie pour soutenir le "miracle économique". </t>
   </si>
   <si>
-    <t>La révolte des ouvriers est-allemands</t>
+    <r>
+      <t>Sissi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> d'Ernst Marischka avec Romy Schneider et Karlheinz Böhm, qui deviendra un acteur récurrent du cinéma de Fassbinder </t>
+    </r>
+  </si>
+  <si>
+    <t>Bande Annonce de Sissi (1955)</t>
+  </si>
+  <si>
+    <t>Bohm.jpg</t>
+  </si>
+  <si>
+    <t>Karlheinz Böhm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RWF est lycéen à Munich. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adenauer fête ses 80 ans. 
+Le KDP, parti communiste ouest-allemand, est interdit. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Décès de Bertold Brecht
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Nuit et brouillard </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>d'Alain Resnais</t>
+    </r>
+  </si>
+  <si>
+    <t>découvrir Brecht avec l'INA</t>
+  </si>
+  <si>
+    <t>La RFA signe le traité de Rome qui institue la Communauté Européenne (CEE). 
+Un scandale secoue le monde politique et financier : une prostituée  qui comptait parmi ses clients de nombreux hommes poli-tiques  ou industriels, est assassinée à Francfort.
+Adenauer tente d'imposer le fait que la RFA se dote de l'arme nucléaire mais se heurte à un front de protestation, notamment du monde scientifique.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'opéra de quat'sous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de Brecht (1928) est diffusé à la télévision est obient un taux d'audience de 81,2%. 
+L'appel à boycotter les pièces de Brecht est refusé par la plupart des théâtres ouest-allemands. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Le SPD (parti social-démocrate allemand), adopte le programme de Bad-Godesberg : pour la première fois, le SPD abandonne formellement les idées d'inspiration marxiste. Il reconnaît l'économie de marché et se dit lié au peuple entier, non aux seuls travailleurs.
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La vogue du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">hula-hoop </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>déferle sur l'Allemagne</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Remariage de Lilo avec un journaliste, Wolff Eder. Relations difficiles entre RWF et son beau-père. 
 RWF revient à Munich mais vit dans un pensionnat. </t>
   </si>
   <si>
-    <t xml:space="preserve">Adenauer fête ses 80 ans. 
-Le KDP, parti communiste ouest-allemand, est interdit. </t>
-  </si>
-  <si>
-    <t>découvrir Brecht avec l'INA</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Décès de Bertold Brecht
-</t>
+    <r>
+      <t xml:space="preserve">Les œuvres de Fassbinder témoignent de l'influence du Rock'nRoll sur la culture populaire ouest-allemande, notamment dans </t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Nuit et brouillard </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>d'Alain Resnais</t>
-    </r>
-  </si>
-  <si>
-    <t>Les alliés aident à la relance de médias d'information et promeuvent une nouvelle politique éducative. 
-Les alliés organisent un vaste programme de démocratisation, décartellisation, démilatarisation et dénazification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fondation de la DEFA (Deutsch Film AG) à Berlin Est. Premières productions de films allemands de fiction depuis la fin de la guerre. 
-Vogue de l'évocation mélancolique de la patrie dans la chanson de variété allemande avec "Möwe, di fliegst in die Heimat" de Magda Hein. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premières élections municipales dans la zone américaine. 
-La « loi d'élimination du national-socialisme et du militarisme » du 5 mars 1946 définit dans son article 4 les niveaux de responsabilité : Hauptschuldige (principaux coupables), Belastete (charges importantes), Minderbelastete (charges mineures), Mitläufer (suivistes), Entlastete (libérés, les procès en dénazification pouvant déclarer les prévenus nicht betroffen, « non concernés » par cette loi). Procès de Nuremberg : 12 des 24 accusés sont condamnés à mort pour crimes de guerre.  </t>
-  </si>
-  <si>
-    <t>Période de disette la plus terrible depuis la fin de la guerre. Les Trümmerfrauen (les femmes des ruines) constituent un des piliers de la reconstruction.</t>
-  </si>
-  <si>
-    <t>De l'année zéro au miracle économique</t>
-  </si>
-  <si>
-    <t>Réforme monétaire de l'Allemagne de l'Ouest, acte fondateur du "miracle économique" comme de la séparation entre blocs est et ouest. Ludwig Erhard, professeur d'économie, développe l'économie sociale de marché. Le Plan Marshall participe à la relance de l'économie ouest-allemande. 
-Blocus de Berlin par les soviétiques, l'une des premières crises de la Guerre Froide. Un pont aérien est mise en place à l'initiative des Etats-Unis et de la Grande-Bretagne.</t>
-  </si>
-  <si>
-    <t>Création de la RFA (1949). Ère Adenauer. Miracle économique ( Wirtschaftswunder )  entre 1950 et 1965 l'économie ouest-allemande croît de 8,2% en moyenne (contre 5% en France pendant les 30 glorieuses). La coccinelle de Wolkswagen devient l'emblème du "miracle économique". 
-Parallèmement, l'état  développe une politique sociale conservatrice. Réarmement de la RFA (1955).</t>
-  </si>
-  <si>
-    <t>l-industrie-de-l-industrie-automobile-l-usine-volkswagen-vue-de-l-interieur-usine-wolfsburg-vers-1950.jpg</t>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">huit heures ne font pas un jour. </t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Le constructeur automobile Volkswagen est privatisé à hauteur de 60% de son capital. 78% des ménages ouest-allemands disposent d'un réfrigérateur contre 25% en France. 42% mossèdent une voiture. La société de consommation de masse est une réalité en RFA.
 Adolf Eichamnn est extradé en Israel. </t>
   </si>
   <si>
-    <t xml:space="preserve">Le SPD (parti social-démocrate allemand), adopte le programme de Bad-Godesberg : pour la première fois, le SPD abandonne formellement les idées d'inspiration marxiste. Il reconnaît l'économie de marché et se dit lié au peuple entier, non aux seuls travailleurs.
-</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">La vogue du </t>
+    <r>
+      <t xml:space="preserve">Fin de la série télévisée </t>
     </r>
     <r>
       <rPr>
@@ -740,7 +626,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">hula-hoop </t>
+      <t xml:space="preserve">Die familie Schölermann </t>
     </r>
     <r>
       <rPr>
@@ -749,107 +635,62 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>déferle sur l'Allemagne</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Les œuvres de Fassbinder témoignent de l'influence du Rock'nRoll sur la culture populaire ouest-allemande, notamment dans </t>
+      <t xml:space="preserve">(111 épisodes depuis 1954), extrêmement populaire (70% à 90% d'audience). Elle est remplacée par un nouveau feuilleton </t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">huit heures ne font pas un jour. </t>
-    </r>
-  </si>
-  <si>
-    <t>Exécution d'Eichmann après sa condamnation à la peine de mort</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Fin de la série télévisée </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Die familie Schölermann </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(111 épisodes depuis 1954), extrêmement populaire (70% à 90% d'audience). Elle est remplacée par un nouveau feuilleton </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Die Firma Hesselbach</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">RWF interrompt ses études avant le baccalauréat. Il rejoint son père à Cologne. Il collecte pour lui des loyers dans des immeubles principalement occupés par des Gastarbeiters (travaillers "invités" c'est-à-dire immigrés). RWF prend des cours du soir, écrit, f'équente les bars homosexuels. </t>
-  </si>
-  <si>
-    <t>RWF s'inscrit à l'école d'art dramatique Fridl Loeonhard</t>
-  </si>
-  <si>
-    <t>RWF retourne à Munich et contitnue d'écire, pièces, romans, scénarios. Il travaille quelques temps au département documentation au journal Südedeutsche Zeitung . 
-RWF prend des cours privés de théâtre.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'opéra de quat'sous</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> de Brecht (1928) est diffusé à la télévision est obient un taux d'audience de 81,2%. 
-L'appel à boycotter les pièces de Brecht est refusé par la plupart des théâtres ouest-allemands. </t>
-    </r>
+    <t>RWF commence à écrire des nouvelles et de petites pièces de théâtre</t>
   </si>
   <si>
     <t>Construction du Mur de Berlin (1961). Adenauer est rééel chancelier fédéral.
 Procès d'Eichmann en Israel.</t>
   </si>
   <si>
-    <t>Machorka Muff de Jean-Marie Straub</t>
-  </si>
-  <si>
-    <t>Jean-Marie Straub.jpg</t>
-  </si>
-  <si>
-    <t>Jean-Marie Straub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Court-métrage de Jean-Marie Straub. Straub exercera une influence certaine sur le début de carrière de RWF. Le court-métrage s'inscrit dans une réflexion sur le passé nazi de l'Allemagne et dénonce la remilitarisation de l'Allemagne. Pour en savoir plus : </t>
+    <t xml:space="preserve">RWF interrompt ses études avant le baccalauréat. Il rejoint son père à Cologne. Il collecte pour lui des loyers dans des immeubles principalement occupés par des Gastarbeiters (travaillers "invités" c'est-à-dire immigrés). RWF prend des cours du soir, écrit, f'équente les bars homosexuels. </t>
+  </si>
+  <si>
+    <t>Exécution d'Eichmann après sa condamnation à la peine de mort</t>
+  </si>
+  <si>
+    <t>A l'occasion du festival du film documentaire d'Oberhausen, publication du Manifeste d'Oberhausen : naissance du Nouveau Cinéma Allemand ("Le vieux cinéma est mort").
+Les Beatles entament eur carrière par un concert à Hambourg</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Représenter l'Allemagne, ce n'est pas seulement adopter une position critique, c'est inventer une nouvelle manière". </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, de Thomas Elsaesser, Centre Pompidou, 2005, p.26</t>
+    </r>
+  </si>
+  <si>
+    <t>Visite de J.F Kennedy à Berlin-ouest : "ich bin ein Berliner". 
+Procès d'Auschwitz à Francfort (1963-1965)
+Démission d'Adenauer à 87 ans. Ludwijg Ehrard, père du "miracle économique", devient Chancelier de la RFA.</t>
   </si>
   <si>
     <r>
@@ -907,15 +748,37 @@
     </r>
   </si>
   <si>
+    <t>RWF retourne à Munich et contitnue d'écire, pièces, romans, scénarios. Il travaille quelques temps au département documentation au journal Südedeutsche Zeitung . 
+RWF prend des cours privés de théâtre.</t>
+  </si>
+  <si>
     <t>Portrait de Straub et carrière</t>
   </si>
   <si>
-    <t>"Nous devons nous débarrasser du passé pour construire l'avenir". Konrad Adenauer</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Le cinéma est en ruines. Période des films de décombres ( Trümmerfilme ) comme </t>
-    </r>
+    <t>Machorka Muff de Jean-Marie Straub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Court-métrage de Jean-Marie Straub. Straub exercera une influence certaine sur le début de carrière de RWF. Le court-métrage s'inscrit dans une réflexion sur le passé nazi de l'Allemagne et dénonce la remilitarisation de l'Allemagne. </t>
+  </si>
+  <si>
+    <t>Jean-Marie Straub.jpg</t>
+  </si>
+  <si>
+    <t>Jean-Marie Straub</t>
+  </si>
+  <si>
+    <t>RWF s'inscrit à l'école d'art dramatique Fridl Loeonhard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une grande coaltion chrétienne-démocrate voit le jour sous l'autorité du nouveau chancelier Kurt Georg Kiesinger. Willy Brandt est ministre des affaires étrangères et vice-chancelier. </t>
+  </si>
+  <si>
+    <t>Rejoint l'Action-Theater (1967).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une majorité sociale-libérale place Willy Brandt au pouvoir. </t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i/>
@@ -924,7 +787,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Les assassins sont parmi nous </t>
+      <t>Whity</t>
     </r>
     <r>
       <rPr>
@@ -933,23 +796,309 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>(Staudte, 1946).</t>
-    </r>
-  </si>
-  <si>
-    <t>A l'initiative de Hans Werner Richter, fondation du Groupe 47 qui réunit l'avant-garde littéraire allemande dont Gunter Grass et Heinrich Böll.  Le Groupe cherche à constituer une élite exemplairement démocratique dans le domaine des lettres et à développer de nouvelles formes d'écriture pour permettre aux lettres allemandes d'exprimer au mieux des enjeux esthétiques et politiques en adéquation avec la société d'après-guerre.</t>
-  </si>
-  <si>
-    <t>Liens</t>
-  </si>
-  <si>
-    <t>La RFA signe le traité de Rome qui institue la Communauté Européenne (CEE). 
-Un scandale secoue le monde politique et financier : une prostituée  qui comptait parmi ses clients de nombreux hommes poli-tiques  ou industriels, est assassinée à Francfort.
-Adenauer tente d'imposer le fait que la RFA se dote de l'arme nucléaire mais se heurte à un front de protestation, notamment du monde scientifique.</t>
-  </si>
-  <si>
-    <t>A l'occasion du festival du film documentaire d'Oberhausen, publication du Manifeste d'Oberhausen : naissance du Nouveau Cinéma Allemand ("Le vieux cinéma est mort").
-Les Beatles entament eur carrière par un concert à Hambourg</t>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Prenez garde à la sainte putain</t>
+    </r>
+  </si>
+  <si>
+    <t>Terrorisme de la RAF (arrestations en 1972). Attentat des JO de Munich (1972). Démission de Willy Brandt (1974) suite à l'affaire Guillaume. Un virage conservateur s'opère.</t>
+  </si>
+  <si>
+    <t>Fondation du Filmverlag der Autoren (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).</t>
+  </si>
+  <si>
+    <t>Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international.</t>
+  </si>
+  <si>
+    <t>Maria_braun.jpeg</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Affiche du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mariage de Maria Braun</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Le monde sur un fil (1973)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, adaption libre d'un récit de science-fiction interroge la notion même de réalité. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> Le mouvement atteint son apogée thématique et politique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RWF projette d'adapter le roman de Freytag Soll und Haben (1855), œuvre notaoirement antismétique en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. </t>
+  </si>
+  <si>
+    <t>Les années 55-75, celles pendant lesquelles RWF est sorti de l'enfance et s'est développé comme adolescent puis adulte, seront celles qui nourriront son inspiration cinémétographique et sa réflexion politique. Même les films dont l'action se situent avant 1945 sont à envisager comme "une archéologie de la société allemande d'après-guerre" (Elsaesser, p. 34)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"je trouve que l'Allemagne en particulier est dans une situation où beaucoup de choses régressent. Je dirais qu'en 1945, lorsque la guerre a pris fin, lorsque le troisième Reich a pris fin, on n'a pas perçu quelles chances s'offraient à l'Allemagne, mais je pense qu'au contraire, comme je l'ai écrit dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Die Zeit, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">les valeurs et les structures sur lesquelles repose cet Etat, aujourd'hui devenu démocratique, sont restées, fondamentalement les mêmes qu'autrefois. Cet état de fait, si on ajoute cette tendance régressive, va conduire à quelque chose, une forme d'Etat dans lequel je n'aimerais pas tellement vivre". Entreitne donné à Peter W. Jansen en 1978 et repris dans l'ouvra ge </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fassbinder par lui-même</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, p.342-343, G3J éditeur, 2010</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Film collectif </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'Allemagne en automne </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(1978).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Année des treize lune</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">s est une œuvre radicale sur le désespoir. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">L'épisode réalisé par RWF dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'Allemagne en automne </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>offre une relecture des actions commises par la RAF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La première génération était celle de 1968. Des idéalistes qui voulaient changer le monde et qui s'imginaient pouvoir le faire avec des mots et des manifestes. La deuxième, celle du groupe Gaader-Meinhof, passa de la légalité à la lutte armée et à l'illégalité totale. la troisième génération est celle d'aujourd'hui, qui se contente d'agir sans réfélchir, qui n'a ni idéologie ni politique, et qui se fait manipuler à son insu comme une troupe de marionnettes" </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fassbinder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Jansen/Schütte, Collection Rivages-cinéma, 1986, p.106</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">La troisième génération, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">film inspiré par les actions de la RAF et la violence d'Etat, est compliqué à produire. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le Mariage de Maria Braun </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">allégorie de la reconstruction allemande, connaît un triomphe international.  </t>
+    </r>
+  </si>
+  <si>
+    <t>La première diffusion de Berlin Alexander Platz à la télévision déclenche une violente campagne de haine contre le réalisateur. Le journaliste Klaus Eder qualifie l'oeuvre de "mastubations malpropres" 
+Adaptant librement, près d'un siècle après sa parution - et quarante ans après la série culte de Fassbinder - le chef-d'oeuvre polyphonique d'Alfred Döblin, le réalisateur germano-afghan Burhan Qurbani en modernise le propos de manière radicale, en imaginant un réfugié sans papiers dans la peau de Franz Biberkopf, antihéros en quête de rédemption. Il transpose également à l'image l'audace formelle du roman, saturant les sens dans un tourbillon de musique, de mouvements et de couleurs. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"je ferai des films jusqu'à ce que j'ai conduit mon histoire de la RFA jusqu'à ici et aujourd'hui. Les histoires de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Lola </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">et </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Maria Braun</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ne sont possibles que dans l'époque où elles se déroulent. Et elles s'intègrent, je l'espère, dans un portrait d'ensemble de la République fédérale, elles aident à comprendre cette étrange entité, avec ses dangers et ses menaces. En ce sens, ce sont des films très politiques". in </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Rainer Werner Fassbinder, Dichter, Schapuspieler, Filmemacher, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Argon, 1992, p.77</t>
+    </r>
+  </si>
+  <si>
+    <t>Victoire de la CDU en octobre : Helmut Kohl devient chancelier. Fin d'une époque artistique et politique radicale.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Je ne pense pas qu'il fait fait un seul que l'on pourrait qualifier de chef-d'œuvre. Le chef-d'œuvre, c'est les 41 films et la vie et tout le reste. Les films ne sont que le résidu de cette vie."Peter Chatel </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">in  Die Sehnsucht des Rainer Werner Fassbinder » (La Nostalgie de Rainer Werner Fassbinder), De Kurt Raab et Karsten Peters, 1982, éditions Bertelsmann </t>
+    </r>
   </si>
   <si>
     <t>Catégorie</t>
@@ -965,65 +1114,6 @@
   </si>
   <si>
     <t>Histoire allemande</t>
-  </si>
-  <si>
-    <t>Repères historiques, chronologie politique</t>
-  </si>
-  <si>
-    <t>URL éventuelle</t>
-  </si>
-  <si>
-    <t>Fassbinder</t>
-  </si>
-  <si>
-    <t>Référence complète</t>
-  </si>
-  <si>
-    <t>Biographie et filmographie</t>
-  </si>
-  <si>
-    <t>Cinéma allemand</t>
-  </si>
-  <si>
-    <t>Contexte culturel et esthétique</t>
-  </si>
-  <si>
-    <t>Archives et sites</t>
-  </si>
-  <si>
-    <t>Nom du site ou de l’institution</t>
-  </si>
-  <si>
-    <t>Documents et vérifications</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"Je ne pense pas qu'il fait fait un seul que l'on pourrait qualifier de chef-d'œuvre. Le chef-d'œuvre, c'est les 41 films et la vie et tout le reste. Les films ne sont que le résidu de cette vie."Peter Chatel </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">in  Die Sehnsucht des Rainer Werner Fassbinder » (La Nostalgie de Rainer Werner Fassbinder), De Kurt Raab et Karsten Peters, 1982, éditions Bertelsmann </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t>, de Thomas Elsaesser, Centre Pompidou, 2005</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1046,34 +1136,326 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Domination du "cinéma de papa" ( Papas Kino ) : films de terroir ( Heimatfilm ), comédies légères dépolitisées, films en costumes , comédies musicales obitennent toujours les faveurs du public. Ces genres nés dans les années 10 et 20 ont été très exploités par les nazis. </t>
-  </si>
-  <si>
-    <t>Manifeste d'Oberhausen (1962) : naissance du Nouveau Cinéma Allemand. Une nouvelle génération de cinéastes s'affirme et conquiert son indépendance notamment par la création de structures de production indépendantes. Fondation de l'école de cinéma DFFB à Berlin (1966).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Une grande coaltion chrétienne-démocrate voit le jour sous l'autorité du nouveau chancelier Kurt Georg Kiesinger. Willy Brandt est ministre des affaires étrangères et vice-chancelier. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Une majorité sociale-libérale place Willy Brandt au pouvoir. </t>
-  </si>
-  <si>
-    <t>Visite de J.F Kennedy à Berlin-ouest : "ich bin ein Berliner". 
-Procès d'Auschwitz à Francfort (1963-1965)
-Démission d'Adenauer à 87 ans. Ludwijg Ehrard, père du "miracle économique", devient Chancelier de la RFA.</t>
-  </si>
-  <si>
-    <t>Terrorisme de la RAF (arrestations en 1972). Attentat des JO de Munich (1972). Démission de Willy Brandt (1974) suite à l'affaire Guillaume. Un virage conservateur s'opère.</t>
-  </si>
-  <si>
-    <t>Les ruines l'Heure zéro</t>
-  </si>
-  <si>
-    <t>Les années 55-75, celles pendant lesquelles RWF est sorti de l'enfance et s'est développé comme adolescent puis adulte, seront celles qui nourriront son inspiration cinémétographique et sa réflexion politique. Même les films dont l'action se situent avant 1945 sont à envisager comme "une archéologie de la société allemande d'après-guerre" (Elsaesser, p. 34)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Le militantisme et l'action politique violente, marquée à l'extrême gauche après 1968 en Allemagne, sont le terreau de plusieurs films de Fassbinder : </t>
+    <t>Repères historiques, chronologie politique</t>
+  </si>
+  <si>
+    <t>Fassbinder</t>
+  </si>
+  <si>
+    <r>
+      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>, de Thomas Elsaesser, Centre Pompidou, 2005</t>
+    </r>
+  </si>
+  <si>
+    <t>Biographie et filmographie</t>
+  </si>
+  <si>
+    <t>URL éventuelle</t>
+  </si>
+  <si>
+    <t>Cinéma allemand</t>
+  </si>
+  <si>
+    <t>Référence complète</t>
+  </si>
+  <si>
+    <t>Contexte culturel et esthétique</t>
+  </si>
+  <si>
+    <t>Archives et sites</t>
+  </si>
+  <si>
+    <t>Nom du site ou de l’institution</t>
+  </si>
+  <si>
+    <t>Documents et vérifications</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Titre canonique</t>
+  </si>
+  <si>
+    <t>ID canonique</t>
+  </si>
+  <si>
+    <t>L’Amour est plus froid que la mort</t>
+  </si>
+  <si>
+    <t>film-1969-l-amour-est-plus-froid-que-la-mort</t>
+  </si>
+  <si>
+    <t>Le Bouc</t>
+  </si>
+  <si>
+    <t>film-1969-le-bouc</t>
+  </si>
+  <si>
+    <t>Les Dieux de la peste</t>
+  </si>
+  <si>
+    <t>film-1970-les-dieux-de-la-peste</t>
+  </si>
+  <si>
+    <t>Pourquoi M. R. est-il atteint de folie meurtrière ?</t>
+  </si>
+  <si>
+    <t>film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere</t>
+  </si>
+  <si>
+    <t>Le Soldat américain</t>
+  </si>
+  <si>
+    <t>film-1970-le-soldat-americain</t>
+  </si>
+  <si>
+    <t>Le Voyage à Niklashausen</t>
+  </si>
+  <si>
+    <t>film-1970-le-voyage-a-niklashausen</t>
+  </si>
+  <si>
+    <t>Whity</t>
+  </si>
+  <si>
+    <t>film-1971-whity</t>
+  </si>
+  <si>
+    <t>Prenez garde à la sainte putain</t>
+  </si>
+  <si>
+    <t>film-1971-prenez-garde-a-la-sainte-putain</t>
+  </si>
+  <si>
+    <t>Pionniers à Ingolstadt</t>
+  </si>
+  <si>
+    <t>film-1971-pionniers-a-ingolstadt</t>
+  </si>
+  <si>
+    <t>Le Marchand des quatre saisons</t>
+  </si>
+  <si>
+    <t>film-1972-le-marchand-des-quatre-saisons</t>
+  </si>
+  <si>
+    <t>Les Larmes amères de Petra von Kant</t>
+  </si>
+  <si>
+    <t>film-1972-les-larmes-ameres-de-petra-von-kant</t>
+  </si>
+  <si>
+    <t>Liberté à Brême</t>
+  </si>
+  <si>
+    <t>film-1972-liberte-a-breme</t>
+  </si>
+  <si>
+    <t>Huit heures ne font pas un jour</t>
+  </si>
+  <si>
+    <t>film-1972-huit-heures-ne-font-pas-un-jour</t>
+  </si>
+  <si>
+    <t>Gibier de passage</t>
+  </si>
+  <si>
+    <t>film-1973-gibier-de-passage</t>
+  </si>
+  <si>
+    <t>Le Monde sur un fil</t>
+  </si>
+  <si>
+    <t>film-1973-le-monde-sur-un-fil</t>
+  </si>
+  <si>
+    <t>Tous les autres s’appellent Ali</t>
+  </si>
+  <si>
+    <t>film-1974-tous-les-autres-s-appellent-ali</t>
+  </si>
+  <si>
+    <t>Effi Briest</t>
+  </si>
+  <si>
+    <t>film-1974-effi-briest</t>
+  </si>
+  <si>
+    <t>Nora Helmer</t>
+  </si>
+  <si>
+    <t>film-1974-nora-helmer</t>
+  </si>
+  <si>
+    <t>Martha</t>
+  </si>
+  <si>
+    <t>film-1974-martha</t>
+  </si>
+  <si>
+    <t>Le Droit du plus fort</t>
+  </si>
+  <si>
+    <t>film-1975-le-droit-du-plus-fort</t>
+  </si>
+  <si>
+    <t>Maman Küsters s’en va au ciel</t>
+  </si>
+  <si>
+    <t>film-1975-maman-kusters-s-en-va-au-ciel</t>
+  </si>
+  <si>
+    <t>Comme un oiseau sur le fil</t>
+  </si>
+  <si>
+    <t>film-1975-comme-un-oiseau-sur-le-fil</t>
+  </si>
+  <si>
+    <t>Peur de la peur</t>
+  </si>
+  <si>
+    <t>film-1975-peur-de-la-peur</t>
+  </si>
+  <si>
+    <t>L’Ombre des anges</t>
+  </si>
+  <si>
+    <t>film-1976-l-ombre-des-anges</t>
+  </si>
+  <si>
+    <t>Le Rôti de Satan</t>
+  </si>
+  <si>
+    <t>film-1976-le-roti-de-satan</t>
+  </si>
+  <si>
+    <t>Roulette chinoise</t>
+  </si>
+  <si>
+    <t>film-1976-roulette-chinoise</t>
+  </si>
+  <si>
+    <t>Je veux seulement que vous m’aimiez</t>
+  </si>
+  <si>
+    <t>film-1976-je-veux-seulement-que-vous-m-aimiez</t>
+  </si>
+  <si>
+    <t>Femmes à New York</t>
+  </si>
+  <si>
+    <t>film-1977-femmes-a-new-york</t>
+  </si>
+  <si>
+    <t>La Femme du chef de gare</t>
+  </si>
+  <si>
+    <t>film-1977-la-femme-du-chef-de-gare</t>
+  </si>
+  <si>
+    <t>L’Allemagne en automne</t>
+  </si>
+  <si>
+    <t>film-1978-l-allemagne-en-automne</t>
+  </si>
+  <si>
+    <t>Despair</t>
+  </si>
+  <si>
+    <t>film-1978-despair</t>
+  </si>
+  <si>
+    <t>L’Année des treize lunes</t>
+  </si>
+  <si>
+    <t>film-1978-l-annee-des-treize-lunes</t>
+  </si>
+  <si>
+    <t>Le Mariage de Maria Braun</t>
+  </si>
+  <si>
+    <t>film-1979-le-mariage-de-maria-braun</t>
+  </si>
+  <si>
+    <t>La Troisième génération</t>
+  </si>
+  <si>
+    <t>film-1979-la-troisieme-generation</t>
+  </si>
+  <si>
+    <t>Berlin Alexanderplatz</t>
+  </si>
+  <si>
+    <t>film-1980-berlin-alexanderplatz</t>
+  </si>
+  <si>
+    <t>Lili Marleen</t>
+  </si>
+  <si>
+    <t>film-1981-lili-marleen</t>
+  </si>
+  <si>
+    <t>Théâtre en transe</t>
+  </si>
+  <si>
+    <t>film-1981-theatre-en-transe</t>
+  </si>
+  <si>
+    <t>Lola, une femme allemande</t>
+  </si>
+  <si>
+    <t>film-1981-lola-une-femme-allemande</t>
+  </si>
+  <si>
+    <t>Le Secret de Veronika Voss</t>
+  </si>
+  <si>
+    <t>film-1981-le-secret-de-veronika-voss</t>
+  </si>
+  <si>
+    <t>Querelle</t>
+  </si>
+  <si>
+    <t>film-1982-querelle</t>
+  </si>
+  <si>
+    <t>RWF_Frise — IDs automatiques</t>
+  </si>
+  <si>
+    <t>Principe</t>
+  </si>
+  <si>
+    <t>Les colonnes IDs films — Œuvres sont calculées à partir des titres canoniques présents dans Œuvres.</t>
+  </si>
+  <si>
+    <t>Saisie</t>
+  </si>
+  <si>
+    <t>Employer les titres français canoniques du référentiel. Plusieurs titres peuvent figurer dans la même cellule.</t>
+  </si>
+  <si>
+    <t>Absence d’ID</t>
+  </si>
+  <si>
+    <t>Une œuvre absente du référentiel Films reste sans ID : aucun identifiant n’est inventé.</t>
+  </si>
+  <si>
+    <t>Mise à jour</t>
+  </si>
+  <si>
+    <t>Lorsqu’une nouvelle fiche Film est créée, ajouter son titre et son ID dans Référentiel films.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Fondation du </t>
     </r>
     <r>
       <rPr>
@@ -1083,7 +1465,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Voyage à Niklashausen, </t>
+      <t>Filmverlag der Autoren</t>
     </r>
     <r>
       <rPr>
@@ -1092,7 +1474,26 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve"> (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).
+Plusieurs cinéastes allemands ( Schlöndorff, Herzog notamment) réalisent des charges politiques violentes contre la politique et la société allemande.
+A parti de 1968 l'industrie du cinéma commercial allemand agonise</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk . Période Sirkienne : Le Marchand des quatre saisons (1971). </t>
+  </si>
+  <si>
+    <t>Effi Briest, Martha</t>
+  </si>
+  <si>
+    <t>Effi Briest permet à RWF d'obetnir une reconnaissance plus large qui tempère sa réputation d'enfant terrible du cinéma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une rétrospective de l'œuvre de RWF à New York suscite l'enthousiasme de la presse américaine. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">L'amour est plus froid que la mort (1969),  </t>
     </r>
     <r>
       <rPr>
@@ -1102,7 +1503,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Maman Kusters s'en va au ciel</t>
+      <t xml:space="preserve">Le Bouc </t>
     </r>
     <r>
       <rPr>
@@ -1111,34 +1512,37 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">, ou encore </t>
-    </r>
+      <t>(1969, succès à Mannheim) : critique de la xénophobie et de l'apathie bourgeoise.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Premier film accueili froidement à Berlin. Le second,une critique de la xénophobie et de l'apathie bourgeoise,  remporte 5 distinctions cinématographiques en Allemagne. Le coût de production de 80000 marks est largement couvert : avec 650000 malrs de prix et 200000 marks de subventions a posteri, le film assure à RWF de quoi poursuivre son travail pour quelques années. </t>
+  </si>
+  <si>
+    <t>L'amour est plus froid que la mort (1969),  Le Bouc (1969)</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i/>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>La troisième génération</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>Le bouc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Il est remarquable qu'un comique outrancier associer l'action violente à une forme de bêtise radicale. </t>
-    </r>
-  </si>
-  <si>
-    <t>Découverte des mélodrames de Douglas Sirk .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> Fondation du </t>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve"> est un tournant  tant en termes de reconnaissance que du point de vue économique. Le film aborde des problématiques contemporaines (sort des travailleurs immigrés) et des thématiques chères à RWF (l'univers étriqué de la bourgeoisie, en particulière bavaroise). </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La pièce </t>
     </r>
     <r>
       <rPr>
@@ -1148,7 +1552,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Filmverlag der Autoren</t>
+      <t xml:space="preserve">outrage au public </t>
     </r>
     <r>
       <rPr>
@@ -1157,21 +1561,20 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).
-Plusieurs cinéastes allemands ( Schlöndorff, Herzog notamment) réalisent des charges politiques violentes contre la politique et la société allemande. </t>
-    </r>
-  </si>
-  <si>
-    <t>L'œuvre de Fassbinder analyse rétrospectivement cette période en mettant à distance le consensus social de la prospérité des années 50 et 60 et en révélant les mensonges du miracle économique.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RWF projette d'adapter le roman de Freytag Soll und Haben (1855), œuvre notaoirement antismétique en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. </t>
-  </si>
-  <si>
-    <t>La première diffusion de Berlin Alexander Platz à la télévision déclenche une violente campagne de haine contre le réalisateur. Le journaliste Klaus Eder qualifie l'oeuvre de "mastubations malpropres" 
-Adaptant librement, près d'un siècle après sa parution - et quarante ans après la série culte de Fassbinder - le chef-d'oeuvre polyphonique d'Alfred Döblin, le réalisateur germano-afghan Burhan Qurbani en modernise le propos de manière radicale, en imaginant un réfugié sans papiers dans la peau de Franz Biberkopf, antihéros en quête de rédemption. Il transpose également à l'image l'audace formelle du roman, saturant les sens dans un tourbillon de musique, de mouvements et de couleurs. </t>
-  </si>
-  <si>
+      <t xml:space="preserve">du dramaturge allemand Peter Handke témoigne du goût de l'avant-garde  artistique subentionnée pour une forme de provocation à l'égard du public, manière paradoxale de s'affranchir de la tutelle culturelle dont ils bénéficient. </t>
+    </r>
+  </si>
+  <si>
+    <t>RWF est pensionnaire à Augsbourg, sa mère étant hospitalisée pendant près de deux ans à la suite d'une opération. Il continue à fréquenter les salles obscures. Il voit toutes sortes de film sans distinction, des films noirs américains doublés en allemand, des films pornos sans budget qui se développent à partir de 1960</t>
+  </si>
+  <si>
+    <t>Si RWF ne renonce pas à l'expérimentation l'attention qu'il porte à la réception de ses films et donc au public est de plus en plus grande. L'intérêt pour le mélodrame, genre populaire américain, son travail pour la télévision et notamment la création de séries, plus tard le développement de productions internationales, traduisent sa volonté de toucher un public large et populaire.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le militantisme et l'action politique violente, marquée à l'extrême gauche après 1968 en Allemagne, sont le terreau de plusieurs films de Fassbinder : Voyage à Niklashausen, , Maman Kusters s'en va au ciel, ou encore La troisième génération. Il est remarquable qu'un comique outrancier associe l'action violente à une forme de bêtise radicale.
+Fassbinder joue le rôle principal du </t>
+    </r>
     <r>
       <rPr>
         <i/>
@@ -1180,7 +1583,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Whity</t>
+      <t>Droit du plus fort</t>
     </r>
     <r>
       <rPr>
@@ -1189,378 +1592,18 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Prenez garde à la sainte putain</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve"> Le mouvement atteint son apogée thématique et politique.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Film collectif </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">L'Allemagne en automne </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(1978).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Le film de Rossellini </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Allemagne année zéro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> offre une vision réaliste et critique de l'Allemagne en ruine</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Allemagne année zéro </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>de Rossellini (1948) ) Le protagoniste Edmund tente de vendre un enregistrement d'un discours d'Hitler sur disque à des soldats alliés. La voix du Fürher se met à résonner dans les ruines du Reichstag, siège du parlement incendié en 1933</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Avec sa femme Helene Weigel, Brecht fonde le Berliner Ensemble à Berlin-Est, où il crée </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mère courage et ses enfants</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Thomas Mann donne des conférences  en Allemagne de l'ouest et en République démocratique (voir le film de Pavec Pwalikoscki Fatherland (2026))</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Sissi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> d'Ernst Marischka avec Romy Schneider et Karlheinz Böhm, qui deviendra un acteur récurrent du cinéma de Fassbinder </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"Représenter l'Allemagne, ce n'est pas seulement adopter une position critique, c'est inventer une nouvelle manière". </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, de Thomas Elsaesser, Centre Pompidou, 2005, p.26</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Affiche du </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mariage de Maria Braun</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"je trouve que l'Allemagne en particulier est dans une situation où beaucoup de choses régressent. Je dirais qu'en 1945, lorsque la guerre a pris fin, lorsque le troisième Reich a pris fin, on n'a pas perçu quelles chances s'offraient à l'Allemagne, mais je pense qu'au contraire, comme je l'ai écrit dans </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Die Zeit, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">les valeurs et les structures sur lesquelles repose cet Etat, aujourd'hui devenu démocratique, sont restées, fondamentalement les mêmes qu'autrefois. Cet état de fait, si on ajoute cette tendance régressive, va conduire à quelque chose, une forme d'Etat dans lequel je n'aimerais pas tellement vivre". Entreitne donné à Peter W. Jansen en 1978 et repris dans l'ouvra ge </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fassbinder par lui-même</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, p.342-343, G3J éditeur, 2010</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">L'épisode réalisé par RWF dans </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">L'Allemagne en automne </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>offre une relecture des actions commises par la RAF</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"je ferai des films jusqu'à ce que j'ai conduit mon histoire de la RFA jusqu'à ici et aujourd'hui. Les histoires de </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Lola </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">et </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Maria Braun</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ne sont possibles que dans l'époque où elles se déroulent. Et elles s'intègrent, je l'espère, dans un portrait d'ensemble de la République fédérale, elles aident à comprendre cette étrange entité, avec ses dangers et ses menaces. En ce sens, ce sont des films très politiques". in </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Rainer Werner Fassbinder, Dichter, Schapuspieler, Filmemacher, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Argon, 1992, p.77</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">La première génération était celle de 1968. Des idéalistes qui voulaient changer le monde et qui s'imginaient pouvoir le faire avec des mots et des manifestes. La deuxième, celle du groupe Gaader-Meinhof, passa de la légalité à la lutte armée et à l'illégalité totale. la troisième génération est celle d'aujourd'hui, qui se contente d'agir sans réfélchir, qui n'a ni idéologie ni politique, et qui se fait manipuler à son insu comme une troupe de marionnettes" </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fassbinder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, Jansen/Schütte, Collection Rivages-cinéma, 1986, p.106</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">La troisième génération, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">film inspiré par les actions de la RAF et la violence d'Etat, est compliqué à produire. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le Mariage de Maria Braun </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">allégorie de la reconstruction allemande, connaît un triomphe international.  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'Année des treize lune</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">s est une œuvre radicale sur le désespoir. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Le monde sur un fil (1973)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, adaption libre d'un récit de science-fiction interroge la notion même de réalité. </t>
-    </r>
-  </si>
-  <si>
-    <t>Victoire de la CDU en octobre : Helmut Kohl devient chancelier. Fin d'une époque artistique et politique radicale.</t>
+      <t>, assumant une visibilité politique de son homosexualité.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Il m'est impossible de comprende qu'on puisse travailler avec un outil comme la caméra en ne se souciant pas du spectateur", interview avec Norbert Sparrow, in Cinéste, WIII/2 automne 1977</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1670,6 +1713,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1769,9 +1818,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1793,6 +1839,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -1808,6 +1857,20 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -2093,20 +2156,6 @@
         <scheme val="none"/>
       </font>
       <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2208,7 +2257,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:N10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID période"/>
@@ -2231,8 +2280,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T33" totalsRowShown="0" headerRowDxfId="21" dataDxfId="0">
-  <autoFilter ref="A1:T33" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T34" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="A1:T34" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="19"/>
@@ -2484,76 +2533,76 @@
         <v>8</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>236</v>
+        <v>9</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>264</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>234</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H2" s="2" t="str">
         <f>IF(G2="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
       <c r="I2" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>233</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="14" customFormat="1" ht="98" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>214</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>258</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="4" t="str">
@@ -2561,93 +2610,93 @@
         <v/>
       </c>
       <c r="I3" s="1" t="s">
-        <v>269</v>
+        <v>30</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>212</v>
+        <v>31</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>215</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>259</v>
+        <v>36</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H4" s="4" t="str">
         <f>IF(G4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
       <c r="J4" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="85" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>36</v>
+        <v>288</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>IF(G5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="98" customHeight="1" x14ac:dyDescent="0.15">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="124" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>267</v>
+        <v>49</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H6" s="4" t="str">
         <f>IF(G6="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -2657,75 +2706,73 @@
     </row>
     <row r="7" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>44</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H7" s="4" t="str">
         <f>IF(G7="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H8" s="4" t="str">
         <f>IF(G8="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1978-l-annee-des-treize-lunes; film-1979-le-mariage-de-maria-braun</v>
       </c>
       <c r="N8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H9" s="4" t="str">
         <f>IF(G9="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -2739,16 +2786,16 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H10" s="4" t="str">
         <f>IF(G10="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -2771,7 +2818,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="31.83203125" customWidth="1"/>
@@ -2788,7 +2835,7 @@
   <sheetData>
     <row r="1" spans="1:21" s="12" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -2806,49 +2853,49 @@
         <v>6</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>236</v>
+        <v>9</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="U1" s="12" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="98" x14ac:dyDescent="0.2">
@@ -2856,34 +2903,34 @@
         <v>1945</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>208</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
+      <c r="H2" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
       <c r="U2" s="2" t="str">
         <f>IF(F2="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -2894,34 +2941,34 @@
         <v>1946</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>210</v>
+        <v>88</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>209</v>
+        <v>89</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="20"/>
+        <v>90</v>
+      </c>
+      <c r="F3" s="19"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
+      <c r="H3" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
       <c r="U3" s="2" t="str">
         <f>IF(F3="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -2932,74 +2979,74 @@
         <v>1947</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>211</v>
+        <v>92</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>235</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="20"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
       <c r="T4" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="U4" s="2" t="str">
         <f>IF(F4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="196" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="182" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1948</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>275</v>
+        <v>95</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>96</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="20"/>
+      <c r="F5" s="19"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="21" t="s">
-        <v>86</v>
+      <c r="H5" s="20" t="s">
+        <v>97</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="J5" s="23" t="s">
-        <v>276</v>
+        <v>98</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>99</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L5" s="1"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="20"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
       <c r="U5" s="2" t="str">
         <f>IF(F5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3010,36 +3057,36 @@
         <v>1949</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>277</v>
+        <v>101</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>102</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="20"/>
+      <c r="F6" s="19"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
+      <c r="H6" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="20"/>
+      <c r="M6" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
       <c r="U6" s="2" t="str">
         <f>IF(F6="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3050,34 +3097,34 @@
         <v>1950</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F7" s="20"/>
+        <v>105</v>
+      </c>
+      <c r="F7" s="19"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="N7" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
+      <c r="M7" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
       <c r="U7" s="2" t="str">
         <f>IF(F7="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3088,34 +3135,34 @@
         <v>1951</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="N8" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
-      <c r="T8" s="20"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
       <c r="U8" s="2" t="str">
         <f>IF(F8="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3126,40 +3173,40 @@
         <v>1952</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
       <c r="M9" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="P9" s="20" t="s">
-        <v>82</v>
+        <v>113</v>
+      </c>
+      <c r="O9" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>104</v>
       </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="20"/>
+      <c r="T9" s="19"/>
       <c r="U9" s="2" t="str">
         <f>IF(F9="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3170,36 +3217,36 @@
         <v>1953</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>201</v>
+        <v>114</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="N10" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="20"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
       <c r="U10" s="2" t="str">
         <f>IF(F10="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3210,40 +3257,40 @@
         <v>1954</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>278</v>
+        <v>117</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>118</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="N11" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="O11" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="P11" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="20"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="N11" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="P11" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
       <c r="U11" s="2" t="str">
         <f>IF(F11="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3254,70 +3301,70 @@
         <v>1955</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="20"/>
-      <c r="T12" s="20"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
       <c r="U12" s="2" t="str">
         <f>IF(F12="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="70" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="126" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>1956</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>207</v>
+        <v>124</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>100</v>
+        <v>291</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="N13" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
       <c r="U13" s="2" t="str">
         <f>IF(F13="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3328,34 +3375,34 @@
         <v>1957</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>237</v>
+        <v>126</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>225</v>
+        <v>127</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="N14" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
-      <c r="T14" s="20"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="1:21" ht="126" x14ac:dyDescent="0.2">
@@ -3363,38 +3410,38 @@
         <v>1959</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>217</v>
+        <v>128</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>204</v>
+        <v>129</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>130</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="N15" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20"/>
-      <c r="T15" s="20"/>
+      <c r="G15" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
       <c r="U15" s="2" t="str">
         <f>IF(F15="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3405,36 +3452,36 @@
         <v>1960</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>221</v>
+        <v>133</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="N16" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
       <c r="U16" s="2" t="str">
         <f>IF(F16="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3445,34 +3492,34 @@
         <v>1961</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D17" s="20"/>
+        <v>135</v>
+      </c>
+      <c r="D17" s="19"/>
       <c r="E17" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="N17" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="20"/>
+        <v>136</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
       <c r="U17" s="2" t="str">
         <f>IF(F17="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3483,36 +3530,36 @@
         <v>1962</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>238</v>
+        <v>138</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="M18" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="N18" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20"/>
-      <c r="T18" s="20"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N18" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
       <c r="U18" s="2" t="str">
         <f>IF(F18="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3524,39 +3571,39 @@
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>262</v>
+        <v>140</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>224</v>
+        <v>142</v>
       </c>
       <c r="F19" s="1"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="J19" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="N19" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="20"/>
-      <c r="T19" s="20"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="N19" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="1:21" ht="28" x14ac:dyDescent="0.2">
@@ -3567,54 +3614,56 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>223</v>
+        <v>148</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
-      <c r="T20" s="20"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="19"/>
       <c r="U20" s="2"/>
     </row>
-    <row r="21" spans="1:21" ht="70" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" ht="112" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>1966</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D21" s="1"/>
+        <v>149</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>290</v>
+      </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
+        <v>38</v>
+      </c>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="19"/>
       <c r="U21" s="2" t="str">
         <f>IF(F21="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F21,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -3625,68 +3674,68 @@
         <v>1967</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="F22" s="1"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="20"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="19"/>
       <c r="U22" s="2" t="str">
         <f>IF(F22="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F22,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="70" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" ht="154" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>1968</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
-      <c r="T23" s="20"/>
+        <v>286</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="19"/>
       <c r="U23" s="2" t="str">
         <f>IF(F23="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
@@ -3697,28 +3746,28 @@
         <v>1969</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>261</v>
+        <v>151</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
       <c r="U24" s="2"/>
     </row>
     <row r="25" spans="1:21" ht="16" x14ac:dyDescent="0.2">
@@ -3730,22 +3779,22 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="G25" s="25"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
+        <v>152</v>
+      </c>
+      <c r="G25" s="24"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
       <c r="U25" s="2"/>
     </row>
     <row r="26" spans="1:21" ht="154" x14ac:dyDescent="0.2">
@@ -3753,293 +3802,328 @@
         <v>1971</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>263</v>
+        <v>153</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
+        <v>282</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19" t="s">
+        <v>294</v>
+      </c>
       <c r="M26" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="N26" s="22" t="s">
-        <v>280</v>
+        <v>156</v>
+      </c>
+      <c r="N26" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="T26" s="20"/>
+        <v>62</v>
+      </c>
+      <c r="T26" s="19"/>
       <c r="U26" s="2" t="str">
         <f>IF(F26="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
+        <v>film-1972-le-marchand-des-quatre-saisons</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="42" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
+      <c r="A27" s="1">
+        <v>1973</v>
+      </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="26" t="s">
-        <v>287</v>
+      <c r="F27" s="25" t="s">
+        <v>158</v>
       </c>
       <c r="G27" s="1"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
       <c r="M27" s="1"/>
-      <c r="N27" s="22"/>
+      <c r="N27" s="21"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="19"/>
+      <c r="T27" s="15"/>
       <c r="U27" s="2"/>
     </row>
     <row r="28" spans="1:21" ht="56" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
+        <v>1974</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="26"/>
+      <c r="U28" s="2"/>
+    </row>
+    <row r="29" spans="1:21" ht="196" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
         <v>1975</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
-      <c r="U28" s="2" t="str">
-        <f>IF(F28="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" ht="252" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>1977</v>
-      </c>
       <c r="B29" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>273</v>
+        <v>53</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="L29" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
+        <v>55</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
       <c r="U29" s="2" t="str">
         <f>IF(F29="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="252" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>1977</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="2" t="str">
+        <f>IF(F30="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="182" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
+    <row r="31" spans="1:21" ht="182" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
         <v>1978</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="20"/>
-      <c r="P30" s="20"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="20"/>
-      <c r="S30" s="20"/>
-      <c r="T30" s="20"/>
-      <c r="U30" s="2"/>
-    </row>
-    <row r="31" spans="1:21" ht="98" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
-        <v>1979</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>163</v>
+      </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
+      <c r="F31" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="19"/>
+      <c r="T31" s="19"/>
       <c r="U31" s="2"/>
     </row>
-    <row r="32" spans="1:21" ht="306" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" ht="84" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
+        <v>1979</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="2"/>
+    </row>
+    <row r="33" spans="1:21" ht="293" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
         <v>1980</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="20"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="20"/>
-      <c r="T32" s="20"/>
-      <c r="U32" s="2" t="str">
-        <f>IF(F32="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1980-berlin-alexanderplatz; film-1981-lili-marleen; film-1981-lola-une-femme-allemande</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" ht="126" x14ac:dyDescent="0.2">
-      <c r="A33" s="1">
-        <v>1982</v>
-      </c>
-      <c r="B33" s="1">
-        <v>1982</v>
+      <c r="B33" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>288</v>
+        <v>64</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="20"/>
-      <c r="T33" s="20"/>
+        <v>67</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="19"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="19"/>
       <c r="U33" s="2" t="str">
         <f>IF(F33="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1980-berlin-alexanderplatz; film-1981-lili-marleen; film-1981-lola-une-femme-allemande</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="126" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1982</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="2" t="str">
+        <f>IF(F34="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1981-le-secret-de-veronika-voss; film-1982-querelle</v>
       </c>
     </row>
@@ -4066,7 +4150,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C07A15F-9849-0547-90EB-0E0C6153DA22}">
   <dimension ref="A15:D19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="37.5" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
@@ -4075,70 +4159,70 @@
   <sheetData>
     <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="16" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>241</v>
+        <v>174</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>242</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.15">
       <c r="A16" s="17" t="s">
-        <v>243</v>
+        <v>176</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>257</v>
+        <v>177</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>244</v>
+        <v>178</v>
       </c>
       <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.15">
       <c r="A17" s="17" t="s">
-        <v>246</v>
+        <v>179</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>248</v>
+        <v>181</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>245</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" x14ac:dyDescent="0.15">
       <c r="A18" s="17" t="s">
-        <v>249</v>
+        <v>183</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>247</v>
+        <v>184</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>250</v>
+        <v>185</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>245</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" x14ac:dyDescent="0.15">
       <c r="A19" s="17" t="s">
-        <v>251</v>
+        <v>186</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>252</v>
+        <v>187</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>254</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -4157,330 +4241,330 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>108</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>110</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
-        <v>111</v>
+        <v>194</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>112</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>196</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>116</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>118</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>121</v>
+        <v>204</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>126</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>127</v>
+        <v>210</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>128</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>131</v>
+        <v>214</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>132</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>134</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>135</v>
+        <v>218</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>136</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>137</v>
+        <v>220</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>142</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>144</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>145</v>
+        <v>228</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>146</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>147</v>
+        <v>230</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>148</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>149</v>
+        <v>232</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>150</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>151</v>
+        <v>234</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>152</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>153</v>
+        <v>236</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>154</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>156</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>157</v>
+        <v>240</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>158</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>159</v>
+        <v>242</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>160</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>161</v>
+        <v>244</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>162</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>163</v>
+        <v>246</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>164</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>165</v>
+        <v>248</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>167</v>
+        <v>250</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>168</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>169</v>
+        <v>252</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>170</v>
+        <v>253</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>171</v>
+        <v>254</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>172</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>173</v>
+        <v>256</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>174</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>176</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>177</v>
+        <v>260</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>178</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>179</v>
+        <v>262</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>180</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>181</v>
+        <v>264</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>182</v>
+        <v>265</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>183</v>
+        <v>266</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>184</v>
+        <v>267</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>185</v>
+        <v>268</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>186</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>187</v>
+        <v>270</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>188</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -4503,40 +4587,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>190</v>
+        <v>273</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>191</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>192</v>
+        <v>275</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>193</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>194</v>
+        <v>277</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>195</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>196</v>
+        <v>279</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>197</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="316" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D42616BE-01C7-D54B-B6C1-DB7513A5FFE6}"/>
+  <xr:revisionPtr revIDLastSave="349" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48CC86CD-DD4D-F141-96C1-2A94EC968897}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="600" windowWidth="30760" windowHeight="24600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="297">
   <si>
     <t>ID période</t>
   </si>
@@ -151,18 +151,12 @@
 Parallèmement, l'état  développe une politique sociale conservatrice. Réarmement de la RFA (1955).</t>
   </si>
   <si>
-    <t xml:space="preserve">Domination du "cinéma de papa" ( Papas Kino ) : films de terroir ( Heimatfilm ), comédies légères dépolitisées, films en costumes , comédies musicales obitennent toujours les faveurs du public. Ces genres nés dans les années 10 et 20 ont été très exploités par les nazis. </t>
-  </si>
-  <si>
     <t>Enfance marquée par le divorce de ses parents (1951) et l'absence du père. Passion précoce pour le cinéma (refuge). Première lecture de Berlin Alexanderplatz vers 14 ans.</t>
   </si>
   <si>
     <t>L'œuvre de Fassbinder analyse rétrospectivement cette période en mettant à distance le consensus social de la prospérité des années 50 et 60 et en révélant les mensonges du miracle économique.</t>
   </si>
   <si>
-    <t>De l'année zéro au miracle économique</t>
-  </si>
-  <si>
     <t>l-industrie-de-l-industrie-automobile-l-usine-volkswagen-vue-de-l-interieur-usine-wolfsburg-vers-1950.jpg</t>
   </si>
   <si>
@@ -212,9 +206,6 @@
   </si>
   <si>
     <t>Terrorisme de la RAF (arrestations en 1972). Attentat des JO de Munich (1972). Démission de Willy Brandt (1974) suite à l'affaire Guillaume.</t>
-  </si>
-  <si>
-    <t>Découverte des mélodrames de Douglas Sirk .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international.</t>
   </si>
   <si>
     <t>Période Sirkienne : Le Marchand des quatre saisons (1971). Tous les autres s'appellent Ali (1974, succès mondial à Cannes) : critique du racisme ordinaire. Martha (1974).</t>
@@ -593,10 +584,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Remariage de Lilo avec un journaliste, Wolff Eder. Relations difficiles entre RWF et son beau-père. 
-RWF revient à Munich mais vit dans un pensionnat. </t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Les œuvres de Fassbinder témoignent de l'influence du Rock'nRoll sur la culture populaire ouest-allemande, notamment dans </t>
     </r>
@@ -851,9 +838,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve"> Le mouvement atteint son apogée thématique et politique.</t>
-  </si>
-  <si>
     <t xml:space="preserve">RWF projette d'adapter le roman de Freytag Soll und Haben (1855), œuvre notaoirement antismétique en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. </t>
   </si>
   <si>
@@ -896,73 +880,6 @@
         <family val="2"/>
       </rPr>
       <t>, p.342-343, G3J éditeur, 2010</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Film collectif </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">L'Allemagne en automne </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(1978).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'Année des treize lune</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">s est une œuvre radicale sur le désespoir. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">L'épisode réalisé par RWF dans </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">L'Allemagne en automne </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>offre une relecture des actions commises par la RAF</t>
     </r>
   </si>
   <si>
@@ -1484,12 +1401,6 @@
   </si>
   <si>
     <t>Effi Briest, Martha</t>
-  </si>
-  <si>
-    <t>Effi Briest permet à RWF d'obetnir une reconnaissance plus large qui tempère sa réputation d'enfant terrible du cinéma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Une rétrospective de l'œuvre de RWF à New York suscite l'enthousiasme de la presse américaine. </t>
   </si>
   <si>
     <r>
@@ -1565,10 +1476,28 @@
     </r>
   </si>
   <si>
-    <t>RWF est pensionnaire à Augsbourg, sa mère étant hospitalisée pendant près de deux ans à la suite d'une opération. Il continue à fréquenter les salles obscures. Il voit toutes sortes de film sans distinction, des films noirs américains doublés en allemand, des films pornos sans budget qui se développent à partir de 1960</t>
-  </si>
-  <si>
-    <t>Si RWF ne renonce pas à l'expérimentation l'attention qu'il porte à la réception de ses films et donc au public est de plus en plus grande. L'intérêt pour le mélodrame, genre populaire américain, son travail pour la télévision et notamment la création de séries, plus tard le développement de productions internationales, traduisent sa volonté de toucher un public large et populaire.</t>
+    <t>"Il m'est impossible de comprende qu'on puisse travailler avec un outil comme la caméra en ne se souciant pas du spectateur", interview avec Norbert Sparrow, in Cinéste, WIII/2 automne 1977</t>
+  </si>
+  <si>
+    <t>Remariage de Lilo avec un journaliste, Wolff Eder. Relations difficiles entre RWF et son beau-père. 
+RWF revient à Munich mais vit dans un pensionnat.
+RWF commence à assumer ouvertement son homosexualité, fait rare pour l'époque.</t>
+  </si>
+  <si>
+    <t>RWF est pensionnaire à Augsbourg, sa mère étant hospitalisée pendant près de deux ans à la suite d'une opération. Il continue à fréquenter les salles obscures. Il voit toutes sortes de film sans distinction, des films noirs américains doublés en allemand, des films pornos sans budget qui se développent à partir de 1960. Le cinéma hollywoodien est alors plutôt dénigré par la bourgeoisie.</t>
+  </si>
+  <si>
+    <t>Si RWF ne renonce pas à l'expérimentation l'attention qu'il porte à la réception de ses films et donc au public est de plus en plus grande. L'intérêt pour le mélodrame, genre populaire américain, son travail pour la télévision et notamment la création de séries, plus tard le développement de productions internationales, traduisent sa volonté de toucher un public large et populaire. RWF intègre dans oeuvre sentiment et distanciation réflexive, échappant à la seule création de cas sociaux.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domination du "cinéma de papa" ( Papas Kino ) : films de terroir ( Heimatfilm ), comédies légères dépolitisées, films en costumes , comédies musicales obitennent toujours les faveurs du public. Ces genres nés dans les années 10 et 20 ont été très exploités par les nazis.
+Freddy Quinn, Rocco Granata ou Catharina Valente sont les stars de la culture populaire allemande. </t>
+  </si>
+  <si>
+    <t>De l'année zéro au miracle économique;Jalousie de Catharina Valente</t>
+  </si>
+  <si>
+    <t>Effi Briest permet à RWF d'obtenir une reconnaissance plus large en Allemagne, qui tempère sa réputation d'enfant terrible du cinéma</t>
   </si>
   <si>
     <r>
@@ -1592,11 +1521,149 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>, assumant une visibilité politique de son homosexualité.</t>
-    </r>
-  </si>
-  <si>
-    <t>"Il m'est impossible de comprende qu'on puisse travailler avec un outil comme la caméra en ne se souciant pas du spectateur", interview avec Norbert Sparrow, in Cinéste, WIII/2 automne 1977</t>
+      <t xml:space="preserve">, assumant une visibilité politique de son homosexualité.
+Une rétrospective de l'œuvre de RWF à New York suscite l'enthousiasme de la presse américaine. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Suicide d'Armin Meier (31 mai 1978). Début de la collaboration avec Juliane Lorenz. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Film collectif </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'Allemagne en automne </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(1978) initié par Alexander Kluge.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Automne Allemand (1977) : enlèvement de Schleyer, détournement du Landshut, morts à Stammheim. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Le mouvement atteint son apogée thématique et politique.
+Diffusion de la série Holocaust (1979).</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Despair, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">deuxième coproduction internationale de RWF avec Dirk Bogarde et Andra Ferreol, deux acteurs importants du cinéma moderne européen.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Année des treize lune</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">s poursuit la réflexion entamée   sur le désespoir. 
+L'épisode réalisé par RWF dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Allemagne en automne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> offre une relecture des actions commises par la RAF sur le mode de l'autofiction.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dans les mélodrames de RWF , les personnages tentent en vain de s'affranchir des positions aliénantes produites par la famille, le couple, au sein du système capitaliste et de la classe bourgeoise. Une analogie s'établit alors entre famille et Allemagne. Le mélodrame fassbindérien met en scène des crises identitaires du sujet, comme crises de la perception (du regard), qui se traduit par une mise en crise de l'image (image de soi et image du film). Les films font dialogue subjectivité et affects avec mécanismes sociaux, évitant ainsi toute lecture simplisite etfigées de type psychologisque ou idéologique. Le mélidrame en interpénétrant le privé et le public, l'individuel et le collectif, joue d'un trouble qui participe à son caractère critique et prgoressiste : il est potentiellement facteur de changement pour un spectateur constamment soumis à la réflexion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international. Les films de RWF deviennent incontournables dans les grands festivals internationaux (Cannes, Venise, Berlin). </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Despair est le film le plus rempli d'espoirt que j'ai jamais fait " RWF, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'anarchie de l'imaginaire</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>p.80-81</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Le film constitue un nouveau tournant dans la carrière de RWF en l'intégrant au club fermé des auteurs importants du cinéma européen même si son écho critique reste mitigé. </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1766,7 +1833,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1839,9 +1906,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -1857,20 +1921,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -2156,6 +2206,20 @@
         <scheme val="none"/>
       </font>
       <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2252,12 +2316,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="22">
   <autoFilter ref="A1:N10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID période"/>
@@ -2280,29 +2340,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T34" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T34" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:T34" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2599,10 +2659,10 @@
         <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="4" t="str">
@@ -2610,169 +2670,171 @@
         <v/>
       </c>
       <c r="I3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" s="15" t="s">
         <v>30</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="H4" s="4" t="str">
         <f>IF(G4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
       <c r="J4" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="85" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>IF(G5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="124" customHeight="1" x14ac:dyDescent="0.15">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="303" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>49</v>
+        <v>295</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H6" s="4" t="str">
         <f>IF(G6="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
       </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="H7" s="4" t="str">
         <f>IF(G7="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="H8" s="4" t="str">
         <f>IF(G8="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1978-l-annee-des-treize-lunes; film-1979-le-mariage-de-maria-braun</v>
       </c>
       <c r="N8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="H9" s="4" t="str">
         <f>IF(G9="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -2786,16 +2848,16 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="H10" s="4" t="str">
         <f>IF(G10="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -2835,7 +2897,7 @@
   <sheetData>
     <row r="1" spans="1:21" s="12" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -2853,49 +2915,49 @@
         <v>6</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>10</v>
       </c>
       <c r="M1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="P1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="S1" s="8" t="s">
         <v>13</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="U1" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="98" x14ac:dyDescent="0.2">
@@ -2906,13 +2968,13 @@
         <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -2944,18 +3006,18 @@
         <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F3" s="19"/>
       <c r="G3" s="1"/>
       <c r="H3" s="20" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I3" s="20"/>
       <c r="J3" s="20"/>
@@ -2982,10 +3044,10 @@
         <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="19"/>
@@ -3003,7 +3065,7 @@
       <c r="R4" s="19"/>
       <c r="S4" s="19"/>
       <c r="T4" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="U4" s="2" t="str">
         <f>IF(F4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -3018,25 +3080,25 @@
         <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="19"/>
       <c r="G5" s="1"/>
       <c r="H5" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="19"/>
@@ -3060,16 +3122,16 @@
         <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="19"/>
       <c r="G6" s="1"/>
       <c r="H6" s="20" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I6" s="20"/>
       <c r="J6" s="20"/>
@@ -3079,7 +3141,7 @@
         <v>23</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O6" s="19"/>
       <c r="P6" s="19"/>
@@ -3102,7 +3164,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F7" s="19"/>
       <c r="G7" s="1"/>
@@ -3115,13 +3177,13 @@
         <v>23</v>
       </c>
       <c r="N7" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O7" s="19"/>
       <c r="P7" s="19"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S7" s="19"/>
       <c r="T7" s="19"/>
@@ -3138,11 +3200,11 @@
         <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="19"/>
@@ -3155,7 +3217,7 @@
         <v>23</v>
       </c>
       <c r="N8" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O8" s="19"/>
       <c r="P8" s="19"/>
@@ -3176,13 +3238,13 @@
         <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="19"/>
@@ -3192,16 +3254,16 @@
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O9" s="19" t="s">
         <v>23</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
@@ -3220,16 +3282,16 @@
         <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="19"/>
       <c r="H10" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
@@ -3239,7 +3301,7 @@
         <v>23</v>
       </c>
       <c r="N10" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O10" s="19"/>
       <c r="P10" s="19"/>
@@ -3260,32 +3322,32 @@
         <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="19"/>
       <c r="H11" s="20" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="N11" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O11" s="19" t="s">
         <v>23</v>
       </c>
       <c r="P11" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
@@ -3306,7 +3368,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="19"/>
@@ -3328,7 +3390,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="126" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="154" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>1956</v>
       </c>
@@ -3336,18 +3398,18 @@
         <v>25</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="19"/>
       <c r="H13" s="23" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I13" s="19"/>
       <c r="J13" s="19"/>
@@ -3357,7 +3419,7 @@
         <v>23</v>
       </c>
       <c r="N13" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O13" s="19"/>
       <c r="P13" s="19"/>
@@ -3378,10 +3440,10 @@
         <v>25</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -3395,7 +3457,7 @@
         <v>23</v>
       </c>
       <c r="N14" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O14" s="19"/>
       <c r="P14" s="19"/>
@@ -3413,17 +3475,17 @@
         <v>25</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>130</v>
+        <v>282</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="19" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
@@ -3434,7 +3496,7 @@
         <v>23</v>
       </c>
       <c r="N15" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O15" s="19"/>
       <c r="P15" s="19"/>
@@ -3455,13 +3517,13 @@
         <v>25</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="19"/>
@@ -3474,7 +3536,7 @@
         <v>23</v>
       </c>
       <c r="N16" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O16" s="19"/>
       <c r="P16" s="19"/>
@@ -3492,14 +3554,14 @@
         <v>1961</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
@@ -3512,7 +3574,7 @@
         <v>23</v>
       </c>
       <c r="N17" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O17" s="19"/>
       <c r="P17" s="19"/>
@@ -3530,13 +3592,13 @@
         <v>1962</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -3546,13 +3608,13 @@
       <c r="J18" s="19"/>
       <c r="K18" s="19"/>
       <c r="L18" s="19" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M18" s="19" t="s">
         <v>23</v>
       </c>
       <c r="N18" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O18" s="19"/>
       <c r="P18" s="19"/>
@@ -3571,32 +3633,32 @@
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="19"/>
       <c r="H19" s="23" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J19" s="19" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K19" s="19"/>
       <c r="L19" s="19"/>
       <c r="M19" s="19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N19" s="19" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="O19" s="19"/>
       <c r="P19" s="19"/>
@@ -3614,7 +3676,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="19"/>
@@ -3638,17 +3700,17 @@
         <v>1966</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
@@ -3674,12 +3736,12 @@
         <v>1967</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="19"/>
@@ -3706,22 +3768,22 @@
         <v>1968</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
@@ -3746,10 +3808,10 @@
         <v>1969</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -3779,7 +3841,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G25" s="24"/>
       <c r="H25" s="19"/>
@@ -3797,47 +3859,47 @@
       <c r="T25" s="19"/>
       <c r="U25" s="2"/>
     </row>
-    <row r="26" spans="1:21" ht="154" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" ht="196" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>1971</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
-      <c r="J26" s="26"/>
+      <c r="J26" s="15"/>
       <c r="K26" s="19"/>
       <c r="L26" s="19" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N26" s="21" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T26" s="19"/>
       <c r="U26" s="2" t="str">
@@ -3854,7 +3916,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="25" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="15"/>
@@ -3881,16 +3943,16 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="25" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
+        <v>287</v>
+      </c>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
       <c r="M28" s="1"/>
       <c r="N28" s="21"/>
       <c r="O28" s="1"/>
@@ -3898,30 +3960,30 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-      <c r="T28" s="26"/>
+      <c r="T28" s="15"/>
       <c r="U28" s="2"/>
     </row>
-    <row r="29" spans="1:21" ht="196" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21" ht="238" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>1975</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="G29" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
@@ -3946,31 +4008,27 @@
         <v>1977</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>58</v>
+        <v>291</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>159</v>
+        <v>292</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>285</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="F30" s="15"/>
+      <c r="G30" s="19"/>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
       <c r="K30" s="19" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="L30" s="19" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="M30" s="19"/>
       <c r="N30" s="19"/>
@@ -3981,7 +4039,7 @@
       <c r="S30" s="19"/>
       <c r="T30" s="19"/>
       <c r="U30" s="2" t="str">
-        <f>IF(F30="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <f>IF(E30="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
@@ -3992,21 +4050,23 @@
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E31" s="1"/>
+        <v>290</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="F31" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>165</v>
+        <v>293</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>296</v>
       </c>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
       <c r="J31" s="19"/>
       <c r="K31" s="19"/>
       <c r="L31" s="15" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="M31" s="19"/>
       <c r="N31" s="19"/>
@@ -4027,7 +4087,7 @@
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="15" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
@@ -4050,29 +4110,29 @@
         <v>1980</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="G33" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
       <c r="L33" s="19" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="M33" s="19"/>
       <c r="N33" s="19"/>
@@ -4095,16 +4155,16 @@
         <v>1982</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
@@ -4112,7 +4172,7 @@
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
       <c r="L34" s="19" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="M34" s="19"/>
       <c r="N34" s="19"/>
@@ -4159,70 +4219,70 @@
   <sheetData>
     <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="16" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.15">
       <c r="A16" s="17" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.15">
       <c r="A17" s="17" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" x14ac:dyDescent="0.15">
       <c r="A18" s="17" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" x14ac:dyDescent="0.15">
       <c r="A19" s="17" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -4241,330 +4301,330 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4587,40 +4647,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="349" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48CC86CD-DD4D-F141-96C1-2A94EC968897}"/>
+  <xr:revisionPtr revIDLastSave="360" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C4A64D7-391F-9844-88FF-D7BA65F4E17A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="298">
   <si>
     <t>ID période</t>
   </si>
@@ -1494,9 +1494,6 @@
 Freddy Quinn, Rocco Granata ou Catharina Valente sont les stars de la culture populaire allemande. </t>
   </si>
   <si>
-    <t>De l'année zéro au miracle économique;Jalousie de Catharina Valente</t>
-  </si>
-  <si>
     <t>Effi Briest permet à RWF d'obtenir une reconnaissance plus large en Allemagne, qui tempère sa réputation d'enfant terrible du cinéma</t>
   </si>
   <si>
@@ -1526,9 +1523,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Suicide d'Armin Meier (31 mai 1978). Début de la collaboration avec Juliane Lorenz. </t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Film collectif </t>
     </r>
@@ -1560,6 +1554,18 @@
 Diffusion de la série Holocaust (1979).</t>
   </si>
   <si>
+    <t>Dans les mélodrames de RWF , les personnages tentent en vain de s'affranchir des positions aliénantes produites par la famille, le couple, au sein du système capitaliste et de la classe bourgeoise. Une analogie s'établit alors entre famille et Allemagne. Le mélodrame fassbindérien met en scène des crises identitaires du sujet, comme crises de la perception (du regard), qui se traduit par une mise en crise de l'image (image de soi et image du film). Les films font dialogue subjectivité et affects avec mécanismes sociaux, évitant ainsi toute lecture simplisite etfigées de type psychologisque ou idéologique. Le mélidrame en interpénétrant le privé et le public, l'individuel et le collectif, joue d'un trouble qui participe à son caractère critique et prgoressiste : il est potentiellement facteur de changement pour un spectateur constamment soumis à la réflexion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international. Les films de RWF deviennent incontournables dans les grands festivals internationaux (Cannes, Venise, Berlin). </t>
+  </si>
+  <si>
+    <t>De l'année zéro au miracle économique; Jalousie de Catharina Valente</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Suicide d'Armin Meier (31 mai 1978). Début de la collaboration avec Juliane Lorenz. </t>
+    </r>
     <r>
       <rPr>
         <i/>
@@ -1568,6 +1574,119 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">L'année des treize lunes devient un film </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>expiatoire. Le tournage de</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Maria Braun </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>est compliqué : dépassement de budget, consommation explosive de cocaïne. Ceci explique peut être la fin de la collaboration entre Ballhaus et RWF.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Despair est le film le plus rempli d'espoirt que j'ai jamais fait " RWF, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'anarchie de l'imaginaire</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>p.80-81</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Le film constitue un nouveau tournant dans la carrière de RWF en l'intégrant au club fermé des auteurs importants du cinéma européen même si son écho critique reste mitigé. Mais RWF présente aussi à Cannes, en projection non officielle </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le mariage de Maria Braun. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ce film exclipse </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Despair</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> et fait de RWF et son actrice Hanna Schygulla des stars. Le rêve de RWF de réaliser un 'film hollywoodien allemand" semble accompli. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">Despair, </t>
     </r>
     <r>
@@ -1577,7 +1696,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">deuxième coproduction internationale de RWF avec Dirk Bogarde et Andra Ferreol, deux acteurs importants du cinéma moderne européen.
+      <t xml:space="preserve">deuxième coproduction internationale de RWF avec Dirk Bogarde et Andra Ferreol, deux acteurs importants du cinéma moderne européen, en compétition à Cannes en 1978
+Le mariage de Maria Braun, en compétition officielle à Berlin en 1979
 </t>
     </r>
     <r>
@@ -1621,49 +1741,7 @@
     </r>
   </si>
   <si>
-    <t>Dans les mélodrames de RWF , les personnages tentent en vain de s'affranchir des positions aliénantes produites par la famille, le couple, au sein du système capitaliste et de la classe bourgeoise. Une analogie s'établit alors entre famille et Allemagne. Le mélodrame fassbindérien met en scène des crises identitaires du sujet, comme crises de la perception (du regard), qui se traduit par une mise en crise de l'image (image de soi et image du film). Les films font dialogue subjectivité et affects avec mécanismes sociaux, évitant ainsi toute lecture simplisite etfigées de type psychologisque ou idéologique. Le mélidrame en interpénétrant le privé et le public, l'individuel et le collectif, joue d'un trouble qui participe à son caractère critique et prgoressiste : il est potentiellement facteur de changement pour un spectateur constamment soumis à la réflexion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international. Les films de RWF deviennent incontournables dans les grands festivals internationaux (Cannes, Venise, Berlin). </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"Despair est le film le plus rempli d'espoirt que j'ai jamais fait " RWF, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'anarchie de l'imaginaire</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>p.80-81</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Le film constitue un nouveau tournant dans la carrière de RWF en l'intégrant au club fermé des auteurs importants du cinéma européen même si son écho critique reste mitigé. </t>
-    </r>
+    <t>De l’année zéro au miracle économique|https://youtu.be/BC4BffkWyY8?si=e80MWCLF0K9Fgiub; Jalousie de Catharina Valente|https://youtu.be/-ugDTj7UFtU?si=vzGNySrsaYGKZW0k</t>
   </si>
 </sst>
 </file>
@@ -2316,6 +2394,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="22">
   <autoFilter ref="A1:N10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
@@ -2673,7 +2755,7 @@
         <v>29</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>30</v>
@@ -2737,6 +2819,9 @@
       <c r="I5" s="6" t="s">
         <v>279</v>
       </c>
+      <c r="K5" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="6" spans="1:14" ht="303" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
@@ -2753,7 +2838,7 @@
         <v>273</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>47</v>
@@ -2763,7 +2848,7 @@
         <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.2">
@@ -2868,12 +2953,11 @@
   <hyperlinks>
     <hyperlink ref="J2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="J4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="J3" r:id="rId3" display="de l'année zéro au mircale économique" xr:uid="{2FE19C63-891E-0F4A-B78A-8428D67FA342}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3946,7 +4030,7 @@
         <v>275</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
@@ -3983,7 +4067,7 @@
         <v>52</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
@@ -4011,10 +4095,10 @@
         <v>54</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>155</v>
@@ -4043,23 +4127,23 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="182" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" ht="224" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>1978</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="360" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C4A64D7-391F-9844-88FF-D7BA65F4E17A}"/>
+  <xr:revisionPtr revIDLastSave="399" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E33EDFAB-1071-244C-9F12-C4B23E71E635}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="307">
   <si>
     <t>ID période</t>
   </si>
@@ -465,10 +465,6 @@
   </si>
   <si>
     <t>La révolte des ouvriers est-allemands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La RFA devient un état souverain, doté de sa propre armée. Elle est admise au sein de l'OTAN.
-Les premiers travailleurs immigrés commencent à arriver de Grèce et d'Italie pour soutenir le "miracle économique". </t>
   </si>
   <si>
     <r>
@@ -800,9 +796,6 @@
     <t>Terrorisme de la RAF (arrestations en 1972). Attentat des JO de Munich (1972). Démission de Willy Brandt (1974) suite à l'affaire Guillaume. Un virage conservateur s'opère.</t>
   </si>
   <si>
-    <t>Fondation du Filmverlag der Autoren (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).</t>
-  </si>
-  <si>
     <t>Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international.</t>
   </si>
   <si>
@@ -836,9 +829,6 @@
       </rPr>
       <t xml:space="preserve">, adaption libre d'un récit de science-fiction interroge la notion même de réalité. </t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">RWF projette d'adapter le roman de Freytag Soll und Haben (1855), œuvre notaoirement antismétique en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. </t>
   </si>
   <si>
     <t>Les années 55-75, celles pendant lesquelles RWF est sorti de l'enfance et s'est développé comme adolescent puis adulte, seront celles qui nourriront son inspiration cinémétographique et sa réflexion politique. Même les films dont l'action se situent avant 1945 sont à envisager comme "une archéologie de la société allemande d'après-guerre" (Elsaesser, p. 34)</t>
@@ -1557,126 +1547,7 @@
     <t>Dans les mélodrames de RWF , les personnages tentent en vain de s'affranchir des positions aliénantes produites par la famille, le couple, au sein du système capitaliste et de la classe bourgeoise. Une analogie s'établit alors entre famille et Allemagne. Le mélodrame fassbindérien met en scène des crises identitaires du sujet, comme crises de la perception (du regard), qui se traduit par une mise en crise de l'image (image de soi et image du film). Les films font dialogue subjectivité et affects avec mécanismes sociaux, évitant ainsi toute lecture simplisite etfigées de type psychologisque ou idéologique. Le mélidrame en interpénétrant le privé et le public, l'individuel et le collectif, joue d'un trouble qui participe à son caractère critique et prgoressiste : il est potentiellement facteur de changement pour un spectateur constamment soumis à la réflexion.</t>
   </si>
   <si>
-    <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international. Les films de RWF deviennent incontournables dans les grands festivals internationaux (Cannes, Venise, Berlin). </t>
-  </si>
-  <si>
     <t>De l'année zéro au miracle économique; Jalousie de Catharina Valente</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Suicide d'Armin Meier (31 mai 1978). Début de la collaboration avec Juliane Lorenz. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">L'année des treize lunes devient un film </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>expiatoire. Le tournage de</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Maria Braun </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>est compliqué : dépassement de budget, consommation explosive de cocaïne. Ceci explique peut être la fin de la collaboration entre Ballhaus et RWF.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"Despair est le film le plus rempli d'espoirt que j'ai jamais fait " RWF, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'anarchie de l'imaginaire</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>p.80-81</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Le film constitue un nouveau tournant dans la carrière de RWF en l'intégrant au club fermé des auteurs importants du cinéma européen même si son écho critique reste mitigé. Mais RWF présente aussi à Cannes, en projection non officielle </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le mariage de Maria Braun. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ce film exclipse </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Despair</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> et fait de RWF et son actrice Hanna Schygulla des stars. Le rêve de RWF de réaliser un 'film hollywoodien allemand" semble accompli. </t>
-    </r>
   </si>
   <si>
     <r>
@@ -1742,6 +1613,235 @@
   </si>
   <si>
     <t>De l’année zéro au miracle économique|https://youtu.be/BC4BffkWyY8?si=e80MWCLF0K9Fgiub; Jalousie de Catharina Valente|https://youtu.be/-ugDTj7UFtU?si=vzGNySrsaYGKZW0k</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Production de séries monumentales pour la télévision. Le Nouveau Cinéma Allemand atteint une maturité formelle extrême.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le tambour </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>de Volker Schlondorff obtient l'oscar du meilleur film étranger</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Le tambour de Volker Schlondorff obtient la palme d'or à Cannes. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Despair est le film le plus rempli d'espoirt que j'ai jamais fait " RWF, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'anarchie de l'imaginaire</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>p.80-81</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Le film constitue un nouveau tournant dans la carrière de RWF en l'intégrant au club fermé des auteurs importants du cinéma européen même si son écho critique reste mitigé. Mais RWF présente aussi à Cannes, en projection non officielle </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le mariage de Maria Braun. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ce film exclipse </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Despair</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Fondation du Filmverlag der Autoren (1971), une société indépendante, par quelques cinéastes dont RWF. La société est d'abord autogérée.
+Accords Film-Télévision (1974) favorisant les coproductions (WDR).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFW devient actionnaire du Filmverlag der Autoren. </t>
+  </si>
+  <si>
+    <t>RWF projette d'adapter le roman de Freytag Soll und Haben (1855), œuvre notaoirement antismétique en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. 
+RWF quitte le Filmverlag der Autoren</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Suicide d'Armin Meier (31 mai 1978). Début de la collaboration avec Juliane Lorenz. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'année des treize lunes devient un film </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>expiatoire. Le tournage de</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Maria Braun </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">est compliqué : dépassement de budget, consommation explosive de cocaïne. Ceci explique peut être la fin de la collaboration entre Ballhaus et RWF.
+RWF travaille active à l'écriture de Berlin Alexander Platz, dont il dicte des passages dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'année des treize lunes. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le succès de Maria Braun amène RWF à espérer pour voir réaslier </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cocaïne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, l'adaptation d'un roman de Pitigrilli. Il lui permet aussi de renégocier à la hausse le budget de production de Berlin Alexander Platz : le projet devient le le plus couteux de l'histoire de la télévision allemande. </t>
+    </r>
+  </si>
+  <si>
+    <t>RWF parvient à évincer Werner Schroeter qui souhaitait réaliser une adaptation de Querelle de Jean Genet.  Mort de Fassbinder marquant symboliquement la fin du Nouveau Cinéma Allemand.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le mariage de Maria Braun </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">remporte un succès majeur en Allemagne et dans le monde, ouvrant les portes des studios américains à RWF. Aux Etats-Unis le film est distribué par United Artists. Le film fait de RWF et de son actrice Hanna Schygulla des stars et Fassbinder, l'enfant terrible du cinéma allemand, le metteur en scène des marges, devient paradoxalement l'incarnation même de la RFA. Le rêve de RWF de réaliser un "film hollywoodien allemand" semble accompli. Le film ouvre aussi la trilogie RFA. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Jusqu'à quel point les femmes de la trlogie RFA sont elles une allégorie de la nation allemande ? Quelle distance RWF prend-il avec la critique historique de son pays ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk grâce à Peer Raben .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international. Les films de RWF deviennent incontournables dans les grands festivals internationaux (Cannes, Venise, Berlin). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La RFA devient un état souverain, doté de sa propre armée. Elle est admise au sein de l'OTAN.
+La RFA remporte la coupe du monde de football, confirmation de son retour dans le concert des nations. 
+Les premiers travailleurs immigrés commencent à arriver de Grèce et d'Italie pour soutenir le "miracle économique". </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monumental Berlin Alexanderplatz (1980, 15h). </t>
+  </si>
+  <si>
+    <t>Suite de la Trilogie de la RFA : Lola, une femme allemande (1981) et Lili Marleen (1981).</t>
   </si>
 </sst>
 </file>
@@ -1911,7 +2011,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1982,6 +2082,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2422,8 +2525,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T34" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="A1:T34" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:T37" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="18"/>
@@ -2741,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>28</v>
@@ -2755,7 +2858,7 @@
         <v>29</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>30</v>
@@ -2810,17 +2913,17 @@
         <v>43</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>IF(G5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K5" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="303" customHeight="1" x14ac:dyDescent="0.15">
@@ -2835,10 +2938,10 @@
         <v>46</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>47</v>
@@ -2848,7 +2951,7 @@
         <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.2">
@@ -2882,7 +2985,9 @@
         <v>54</v>
       </c>
       <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>302</v>
+      </c>
       <c r="D8" s="1" t="s">
         <v>55</v>
       </c>
@@ -2964,7 +3069,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="31.83203125" customWidth="1"/>
@@ -3398,7 +3503,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="98" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" ht="140" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>1954</v>
       </c>
@@ -3406,26 +3511,26 @@
         <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>114</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>115</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="19"/>
       <c r="H11" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="N11" s="19" t="s">
         <v>117</v>
-      </c>
-      <c r="N11" s="19" t="s">
-        <v>118</v>
       </c>
       <c r="O11" s="19" t="s">
         <v>23</v>
@@ -3452,7 +3557,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="19"/>
@@ -3482,18 +3587,18 @@
         <v>25</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="19"/>
       <c r="H13" s="23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I13" s="19"/>
       <c r="J13" s="19"/>
@@ -3524,10 +3629,10 @@
         <v>25</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -3559,17 +3664,17 @@
         <v>25</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="E15" s="21" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
@@ -3601,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="19"/>
@@ -3641,11 +3746,11 @@
         <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
@@ -3679,10 +3784,10 @@
         <v>31</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -3692,7 +3797,7 @@
       <c r="J18" s="19"/>
       <c r="K18" s="19"/>
       <c r="L18" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M18" s="19" t="s">
         <v>23</v>
@@ -3717,32 +3822,32 @@
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="19"/>
       <c r="H19" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="I19" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="I19" s="23" t="s">
+      <c r="J19" s="19" t="s">
         <v>140</v>
-      </c>
-      <c r="J19" s="19" t="s">
-        <v>141</v>
       </c>
       <c r="K19" s="19"/>
       <c r="L19" s="19"/>
       <c r="M19" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="N19" s="19" t="s">
         <v>142</v>
-      </c>
-      <c r="N19" s="19" t="s">
-        <v>143</v>
       </c>
       <c r="O19" s="19"/>
       <c r="P19" s="19"/>
@@ -3760,7 +3865,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="19"/>
@@ -3787,10 +3892,10 @@
         <v>31</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
@@ -3825,7 +3930,7 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="19"/>
@@ -3864,10 +3969,10 @@
         <v>43</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
@@ -3895,7 +4000,7 @@
         <v>39</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -3925,7 +4030,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G25" s="24"/>
       <c r="H25" s="19"/>
@@ -3951,32 +4056,32 @@
         <v>44</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="15"/>
       <c r="K26" s="19"/>
       <c r="L26" s="19" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N26" s="21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -3991,18 +4096,16 @@
         <v>film-1972-le-marchand-des-quatre-saisons</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="42" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="G27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="15"/>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
@@ -4018,20 +4121,18 @@
       <c r="T27" s="15"/>
       <c r="U27" s="2"/>
     </row>
-    <row r="28" spans="1:21" ht="56" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21" ht="42" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="25" t="s">
-        <v>275</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>286</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="G28" s="1"/>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
@@ -4047,73 +4148,62 @@
       <c r="T28" s="15"/>
       <c r="U28" s="2"/>
     </row>
-    <row r="29" spans="1:21" ht="238" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21" ht="56" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
+        <v>1974</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="15"/>
+      <c r="U29" s="2"/>
+    </row>
+    <row r="30" spans="1:21" ht="238" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
         <v>1975</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
-      <c r="S29" s="19"/>
-      <c r="T29" s="19"/>
-      <c r="U29" s="2" t="str">
-        <f>IF(F29="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" ht="252" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>1977</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="19"/>
+      <c r="G30" s="1" t="s">
+        <v>284</v>
+      </c>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
-      <c r="K30" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="L30" s="19" t="s">
-        <v>157</v>
-      </c>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
       <c r="M30" s="19"/>
       <c r="N30" s="19"/>
       <c r="O30" s="19"/>
@@ -4123,62 +4213,66 @@
       <c r="S30" s="19"/>
       <c r="T30" s="19"/>
       <c r="U30" s="2" t="str">
-        <f>IF(E30="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(E30,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:21" ht="224" x14ac:dyDescent="0.2">
+        <f>IF(F30="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="28" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>1978</v>
-      </c>
-      <c r="B31" s="1"/>
+        <v>1976</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="C31" s="1"/>
-      <c r="D31" s="1" t="s">
-        <v>288</v>
-      </c>
+      <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F31" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="G31" s="15" t="s">
-        <v>295</v>
-      </c>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19"/>
-      <c r="T31" s="19"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
       <c r="U31" s="2"/>
     </row>
-    <row r="32" spans="1:21" ht="84" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" ht="252" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>1979</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="15" t="s">
-        <v>159</v>
-      </c>
+        <v>1977</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F32" s="15"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
+      <c r="K32" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>154</v>
+      </c>
       <c r="M32" s="19"/>
       <c r="N32" s="19"/>
       <c r="O32" s="19"/>
@@ -4187,36 +4281,35 @@
       <c r="R32" s="19"/>
       <c r="S32" s="19"/>
       <c r="T32" s="19"/>
-      <c r="U32" s="2"/>
-    </row>
-    <row r="33" spans="1:21" ht="293" x14ac:dyDescent="0.2">
+      <c r="U32" s="2" t="str">
+        <f>IF(E32="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="196" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>1980</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>61</v>
-      </c>
+        <v>1978</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>62</v>
+        <v>285</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>63</v>
+        <v>298</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>160</v>
+        <v>290</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>294</v>
       </c>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
-      <c r="L33" s="19" t="s">
-        <v>161</v>
+      <c r="L33" s="15" t="s">
+        <v>155</v>
       </c>
       <c r="M33" s="19"/>
       <c r="N33" s="19"/>
@@ -4226,38 +4319,31 @@
       <c r="R33" s="19"/>
       <c r="S33" s="19"/>
       <c r="T33" s="19"/>
-      <c r="U33" s="2" t="str">
-        <f>IF(F33="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1980-berlin-alexanderplatz; film-1981-lili-marleen; film-1981-lola-une-femme-allemande</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" ht="126" x14ac:dyDescent="0.2">
+      <c r="U33" s="2"/>
+    </row>
+    <row r="34" spans="1:21" ht="210" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>1982</v>
-      </c>
-      <c r="B34" s="1">
-        <v>1982</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>162</v>
-      </c>
+        <v>1979</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>66</v>
+        <v>293</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G34" s="19"/>
+        <v>299</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>301</v>
+      </c>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
-      <c r="L34" s="19" t="s">
-        <v>163</v>
-      </c>
+      <c r="L34" s="19"/>
       <c r="M34" s="19"/>
       <c r="N34" s="19"/>
       <c r="O34" s="19"/>
@@ -4266,8 +4352,112 @@
       <c r="R34" s="19"/>
       <c r="S34" s="19"/>
       <c r="T34" s="19"/>
-      <c r="U34" s="2" t="str">
-        <f>IF(F34="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+      <c r="U34" s="2"/>
+    </row>
+    <row r="35" spans="1:21" ht="293" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>1980</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="19"/>
+      <c r="Q35" s="19"/>
+      <c r="R35" s="19"/>
+      <c r="S35" s="19"/>
+      <c r="T35" s="19"/>
+      <c r="U35" s="2" t="str">
+        <f>IF(F35="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F35,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1980-berlin-alexanderplatz</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="42" x14ac:dyDescent="0.2">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="26"/>
+      <c r="Q36" s="26"/>
+      <c r="R36" s="26"/>
+      <c r="S36" s="26"/>
+      <c r="T36" s="26"/>
+      <c r="U36" s="2"/>
+    </row>
+    <row r="37" spans="1:21" ht="126" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1982</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="M37" s="19"/>
+      <c r="N37" s="19"/>
+      <c r="O37" s="19"/>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="19"/>
+      <c r="T37" s="19"/>
+      <c r="U37" s="2" t="str">
+        <f>IF(F37="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F37,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1981-le-secret-de-veronika-voss; film-1982-querelle</v>
       </c>
     </row>
@@ -4303,70 +4493,70 @@
   <sheetData>
     <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" s="16" t="s">
         <v>164</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.15">
       <c r="A16" s="17" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.15">
       <c r="A17" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>171</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" x14ac:dyDescent="0.15">
       <c r="A18" s="17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" x14ac:dyDescent="0.15">
       <c r="A19" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>178</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -4385,330 +4575,330 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -4731,40 +4921,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="399" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E33EDFAB-1071-244C-9F12-C4B23E71E635}"/>
+  <xr:revisionPtr revIDLastSave="490" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFA6C2F2-D5FA-7545-ABDC-1616DF9C9343}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8660" yWindow="3140" windowWidth="29400" windowHeight="18480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="322">
   <si>
     <t>ID période</t>
   </si>
@@ -126,9 +126,6 @@
     <t>Naissance de Rainer Werner Fassbinder le 31 mai à Bad Wörishofen, Bavière.</t>
   </si>
   <si>
-    <t>L'œuvre de Fassbinder proposera plus tard une radiographie critique de ce "point zéro" de la nouvelle Allemagne.</t>
-  </si>
-  <si>
     <t>Les génériques de Fassbinder</t>
   </si>
   <si>
@@ -147,16 +144,9 @@
     <t>Le miracle économique</t>
   </si>
   <si>
-    <t>Création de la RFA (1949). Ère Adenauer. Miracle économique ( Wirtschaftswunder )  entre 1950 et 1965 l'économie ouest-allemande croît de 8,2% en moyenne (contre 5% en France pendant les 30 glorieuses). La coccinelle de Wolkswagen devient l'emblème du "miracle économique". 
-Parallèmement, l'état  développe une politique sociale conservatrice. Réarmement de la RFA (1955).</t>
-  </si>
-  <si>
     <t>Enfance marquée par le divorce de ses parents (1951) et l'absence du père. Passion précoce pour le cinéma (refuge). Première lecture de Berlin Alexanderplatz vers 14 ans.</t>
   </si>
   <si>
-    <t>L'œuvre de Fassbinder analyse rétrospectivement cette période en mettant à distance le consensus social de la prospérité des années 50 et 60 et en révélant les mensonges du miracle économique.</t>
-  </si>
-  <si>
     <t>l-industrie-de-l-industrie-automobile-l-usine-volkswagen-vue-de-l-interieur-usine-wolfsburg-vers-1950.jpg</t>
   </si>
   <si>
@@ -169,9 +159,6 @@
     <t>Construction du Mur de Berlin (1961). Procès d'Auschwitz à Francfort (1963-1965). Démission d'Adenauer. Grande Coalition (1966).</t>
   </si>
   <si>
-    <t>Manifeste d'Oberhausen (1962) : naissance du Nouveau Cinéma Allemand. Une nouvelle génération de cinéastes s'affirme et conquiert son indépendance notamment par la création de structures de production indépendantes. Fondation de l'école de cinéma DFFB à Berlin (1966).</t>
-  </si>
-  <si>
     <t>Échec au concours d'entrée de la DFFB. Rencontre Hanna Schygulla et Irm Hermann dans un cours d'art dramatique. Rejoint l'Action-Theater (1967).</t>
   </si>
   <si>
@@ -181,9 +168,6 @@
     <t>Documentaire sur le nouveau cinéma allemand</t>
   </si>
   <si>
-    <t>"Le cinéma de Papa est mort. Nous croyons au nouveau cinéma " Manifeste d'Oberhausen (1962)</t>
-  </si>
-  <si>
     <t>1967-1970</t>
   </si>
   <si>
@@ -230,12 +214,6 @@
   </si>
   <si>
     <t>1977-1979</t>
-  </si>
-  <si>
-    <t>Automne Allemand (1977) : enlèvement de Schleyer, détournement du Landshut, morts à Stammheim. Diffusion de la série Holocaust (1979).</t>
-  </si>
-  <si>
-    <t>Film collectif L'Allemagne en automne (1978). Le mouvement atteint son apogée thématique et politique.</t>
   </si>
   <si>
     <t>Suicide d'Armin Meier (31 mai 1978). Début de la collaboration avec Juliane Lorenz. Fassbinder se filme en crise, exposant son angoisse face à l'État.</t>
@@ -495,31 +473,6 @@
   <si>
     <t xml:space="preserve">Adenauer fête ses 80 ans. 
 Le KDP, parti communiste ouest-allemand, est interdit. </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Décès de Bertold Brecht
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Nuit et brouillard </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>d'Alain Resnais</t>
-    </r>
   </si>
   <si>
     <t>découvrir Brecht avec l'INA</t>
@@ -676,6 +629,1420 @@
 Démission d'Adenauer à 87 ans. Ludwijg Ehrard, père du "miracle économique", devient Chancelier de la RFA.</t>
   </si>
   <si>
+    <t>RWF retourne à Munich et contitnue d'écire, pièces, romans, scénarios. Il travaille quelques temps au département documentation au journal Südedeutsche Zeitung . 
+RWF prend des cours privés de théâtre.</t>
+  </si>
+  <si>
+    <t>Portrait de Straub et carrière</t>
+  </si>
+  <si>
+    <t>Machorka Muff de Jean-Marie Straub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Court-métrage de Jean-Marie Straub. Straub exercera une influence certaine sur le début de carrière de RWF. Le court-métrage s'inscrit dans une réflexion sur le passé nazi de l'Allemagne et dénonce la remilitarisation de l'Allemagne. </t>
+  </si>
+  <si>
+    <t>Jean-Marie Straub.jpg</t>
+  </si>
+  <si>
+    <t>Jean-Marie Straub</t>
+  </si>
+  <si>
+    <t>RWF s'inscrit à l'école d'art dramatique Fridl Loeonhard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une grande coaltion chrétienne-démocrate voit le jour sous l'autorité du nouveau chancelier Kurt Georg Kiesinger. Willy Brandt est ministre des affaires étrangères et vice-chancelier. </t>
+  </si>
+  <si>
+    <t>Rejoint l'Action-Theater (1967).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une majorité sociale-libérale place Willy Brandt au pouvoir. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Whity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Prenez garde à la sainte putain</t>
+    </r>
+  </si>
+  <si>
+    <t>Terrorisme de la RAF (arrestations en 1972). Attentat des JO de Munich (1972). Démission de Willy Brandt (1974) suite à l'affaire Guillaume. Un virage conservateur s'opère.</t>
+  </si>
+  <si>
+    <t>Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international.</t>
+  </si>
+  <si>
+    <t>Maria_braun.jpeg</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Affiche du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mariage de Maria Braun</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Le monde sur un fil (1973)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, adaption libre d'un récit de science-fiction interroge la notion même de réalité. </t>
+    </r>
+  </si>
+  <si>
+    <t>Les années 55-75, celles pendant lesquelles RWF est sorti de l'enfance et s'est développé comme adolescent puis adulte, seront celles qui nourriront son inspiration cinémétographique et sa réflexion politique. Même les films dont l'action se situent avant 1945 sont à envisager comme "une archéologie de la société allemande d'après-guerre" (Elsaesser, p. 34)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"je trouve que l'Allemagne en particulier est dans une situation où beaucoup de choses régressent. Je dirais qu'en 1945, lorsque la guerre a pris fin, lorsque le troisième Reich a pris fin, on n'a pas perçu quelles chances s'offraient à l'Allemagne, mais je pense qu'au contraire, comme je l'ai écrit dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Die Zeit, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">les valeurs et les structures sur lesquelles repose cet Etat, aujourd'hui devenu démocratique, sont restées, fondamentalement les mêmes qu'autrefois. Cet état de fait, si on ajoute cette tendance régressive, va conduire à quelque chose, une forme d'Etat dans lequel je n'aimerais pas tellement vivre". Entreitne donné à Peter W. Jansen en 1978 et repris dans l'ouvra ge </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fassbinder par lui-même</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, p.342-343, G3J éditeur, 2010</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La première génération était celle de 1968. Des idéalistes qui voulaient changer le monde et qui s'imginaient pouvoir le faire avec des mots et des manifestes. La deuxième, celle du groupe Gaader-Meinhof, passa de la légalité à la lutte armée et à l'illégalité totale. la troisième génération est celle d'aujourd'hui, qui se contente d'agir sans réfélchir, qui n'a ni idéologie ni politique, et qui se fait manipuler à son insu comme une troupe de marionnettes" </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fassbinder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Jansen/Schütte, Collection Rivages-cinéma, 1986, p.106</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">La troisième génération, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">film inspiré par les actions de la RAF et la violence d'Etat, est compliqué à produire. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le Mariage de Maria Braun </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">allégorie de la reconstruction allemande, connaît un triomphe international.  </t>
+    </r>
+  </si>
+  <si>
+    <t>La première diffusion de Berlin Alexander Platz à la télévision déclenche une violente campagne de haine contre le réalisateur. Le journaliste Klaus Eder qualifie l'oeuvre de "mastubations malpropres" 
+Adaptant librement, près d'un siècle après sa parution - et quarante ans après la série culte de Fassbinder - le chef-d'oeuvre polyphonique d'Alfred Döblin, le réalisateur germano-afghan Burhan Qurbani en modernise le propos de manière radicale, en imaginant un réfugié sans papiers dans la peau de Franz Biberkopf, antihéros en quête de rédemption. Il transpose également à l'image l'audace formelle du roman, saturant les sens dans un tourbillon de musique, de mouvements et de couleurs. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"je ferai des films jusqu'à ce que j'ai conduit mon histoire de la RFA jusqu'à ici et aujourd'hui. Les histoires de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Lola </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">et </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Maria Braun</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ne sont possibles que dans l'époque où elles se déroulent. Et elles s'intègrent, je l'espère, dans un portrait d'ensemble de la République fédérale, elles aident à comprendre cette étrange entité, avec ses dangers et ses menaces. En ce sens, ce sont des films très politiques". in </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Rainer Werner Fassbinder, Dichter, Schapuspieler, Filmemacher, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Argon, 1992, p.77</t>
+    </r>
+  </si>
+  <si>
+    <t>Victoire de la CDU en octobre : Helmut Kohl devient chancelier. Fin d'une époque artistique et politique radicale.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Je ne pense pas qu'il fait fait un seul que l'on pourrait qualifier de chef-d'œuvre. Le chef-d'œuvre, c'est les 41 films et la vie et tout le reste. Les films ne sont que le résidu de cette vie."Peter Chatel </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">in  Die Sehnsucht des Rainer Werner Fassbinder » (La Nostalgie de Rainer Werner Fassbinder), De Kurt Raab et Karsten Peters, 1982, éditions Bertelsmann </t>
+    </r>
+  </si>
+  <si>
+    <t>Catégorie</t>
+  </si>
+  <si>
+    <t>Référence bibliographique</t>
+  </si>
+  <si>
+    <t>Usage dans la frise</t>
+  </si>
+  <si>
+    <t>Lien</t>
+  </si>
+  <si>
+    <t>Histoire allemande</t>
+  </si>
+  <si>
+    <r>
+      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>, de Thomas Elsaesser, Centre Pompidou, 2005</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>, pp. 490-507</t>
+    </r>
+  </si>
+  <si>
+    <t>Repères historiques, chronologie politique</t>
+  </si>
+  <si>
+    <t>Fassbinder</t>
+  </si>
+  <si>
+    <r>
+      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>, de Thomas Elsaesser, Centre Pompidou, 2005</t>
+    </r>
+  </si>
+  <si>
+    <t>Biographie et filmographie</t>
+  </si>
+  <si>
+    <t>URL éventuelle</t>
+  </si>
+  <si>
+    <t>Cinéma allemand</t>
+  </si>
+  <si>
+    <t>Référence complète</t>
+  </si>
+  <si>
+    <t>Contexte culturel et esthétique</t>
+  </si>
+  <si>
+    <t>Archives et sites</t>
+  </si>
+  <si>
+    <t>Nom du site ou de l’institution</t>
+  </si>
+  <si>
+    <t>Documents et vérifications</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Titre canonique</t>
+  </si>
+  <si>
+    <t>ID canonique</t>
+  </si>
+  <si>
+    <t>L’Amour est plus froid que la mort</t>
+  </si>
+  <si>
+    <t>film-1969-l-amour-est-plus-froid-que-la-mort</t>
+  </si>
+  <si>
+    <t>Le Bouc</t>
+  </si>
+  <si>
+    <t>film-1969-le-bouc</t>
+  </si>
+  <si>
+    <t>Les Dieux de la peste</t>
+  </si>
+  <si>
+    <t>film-1970-les-dieux-de-la-peste</t>
+  </si>
+  <si>
+    <t>Pourquoi M. R. est-il atteint de folie meurtrière ?</t>
+  </si>
+  <si>
+    <t>film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere</t>
+  </si>
+  <si>
+    <t>Le Soldat américain</t>
+  </si>
+  <si>
+    <t>film-1970-le-soldat-americain</t>
+  </si>
+  <si>
+    <t>Le Voyage à Niklashausen</t>
+  </si>
+  <si>
+    <t>film-1970-le-voyage-a-niklashausen</t>
+  </si>
+  <si>
+    <t>Whity</t>
+  </si>
+  <si>
+    <t>film-1971-whity</t>
+  </si>
+  <si>
+    <t>Prenez garde à la sainte putain</t>
+  </si>
+  <si>
+    <t>film-1971-prenez-garde-a-la-sainte-putain</t>
+  </si>
+  <si>
+    <t>Pionniers à Ingolstadt</t>
+  </si>
+  <si>
+    <t>film-1971-pionniers-a-ingolstadt</t>
+  </si>
+  <si>
+    <t>Le Marchand des quatre saisons</t>
+  </si>
+  <si>
+    <t>film-1972-le-marchand-des-quatre-saisons</t>
+  </si>
+  <si>
+    <t>Les Larmes amères de Petra von Kant</t>
+  </si>
+  <si>
+    <t>film-1972-les-larmes-ameres-de-petra-von-kant</t>
+  </si>
+  <si>
+    <t>Liberté à Brême</t>
+  </si>
+  <si>
+    <t>film-1972-liberte-a-breme</t>
+  </si>
+  <si>
+    <t>Huit heures ne font pas un jour</t>
+  </si>
+  <si>
+    <t>film-1972-huit-heures-ne-font-pas-un-jour</t>
+  </si>
+  <si>
+    <t>Gibier de passage</t>
+  </si>
+  <si>
+    <t>film-1973-gibier-de-passage</t>
+  </si>
+  <si>
+    <t>Le Monde sur un fil</t>
+  </si>
+  <si>
+    <t>film-1973-le-monde-sur-un-fil</t>
+  </si>
+  <si>
+    <t>Tous les autres s’appellent Ali</t>
+  </si>
+  <si>
+    <t>film-1974-tous-les-autres-s-appellent-ali</t>
+  </si>
+  <si>
+    <t>Effi Briest</t>
+  </si>
+  <si>
+    <t>film-1974-effi-briest</t>
+  </si>
+  <si>
+    <t>Nora Helmer</t>
+  </si>
+  <si>
+    <t>film-1974-nora-helmer</t>
+  </si>
+  <si>
+    <t>Martha</t>
+  </si>
+  <si>
+    <t>film-1974-martha</t>
+  </si>
+  <si>
+    <t>Le Droit du plus fort</t>
+  </si>
+  <si>
+    <t>film-1975-le-droit-du-plus-fort</t>
+  </si>
+  <si>
+    <t>Maman Küsters s’en va au ciel</t>
+  </si>
+  <si>
+    <t>film-1975-maman-kusters-s-en-va-au-ciel</t>
+  </si>
+  <si>
+    <t>Comme un oiseau sur le fil</t>
+  </si>
+  <si>
+    <t>film-1975-comme-un-oiseau-sur-le-fil</t>
+  </si>
+  <si>
+    <t>Peur de la peur</t>
+  </si>
+  <si>
+    <t>film-1975-peur-de-la-peur</t>
+  </si>
+  <si>
+    <t>L’Ombre des anges</t>
+  </si>
+  <si>
+    <t>film-1976-l-ombre-des-anges</t>
+  </si>
+  <si>
+    <t>Le Rôti de Satan</t>
+  </si>
+  <si>
+    <t>film-1976-le-roti-de-satan</t>
+  </si>
+  <si>
+    <t>Roulette chinoise</t>
+  </si>
+  <si>
+    <t>film-1976-roulette-chinoise</t>
+  </si>
+  <si>
+    <t>Je veux seulement que vous m’aimiez</t>
+  </si>
+  <si>
+    <t>film-1976-je-veux-seulement-que-vous-m-aimiez</t>
+  </si>
+  <si>
+    <t>Femmes à New York</t>
+  </si>
+  <si>
+    <t>film-1977-femmes-a-new-york</t>
+  </si>
+  <si>
+    <t>La Femme du chef de gare</t>
+  </si>
+  <si>
+    <t>film-1977-la-femme-du-chef-de-gare</t>
+  </si>
+  <si>
+    <t>L’Allemagne en automne</t>
+  </si>
+  <si>
+    <t>film-1978-l-allemagne-en-automne</t>
+  </si>
+  <si>
+    <t>Despair</t>
+  </si>
+  <si>
+    <t>film-1978-despair</t>
+  </si>
+  <si>
+    <t>L’Année des treize lunes</t>
+  </si>
+  <si>
+    <t>film-1978-l-annee-des-treize-lunes</t>
+  </si>
+  <si>
+    <t>Le Mariage de Maria Braun</t>
+  </si>
+  <si>
+    <t>film-1979-le-mariage-de-maria-braun</t>
+  </si>
+  <si>
+    <t>La Troisième génération</t>
+  </si>
+  <si>
+    <t>film-1979-la-troisieme-generation</t>
+  </si>
+  <si>
+    <t>Berlin Alexanderplatz</t>
+  </si>
+  <si>
+    <t>film-1980-berlin-alexanderplatz</t>
+  </si>
+  <si>
+    <t>Lili Marleen</t>
+  </si>
+  <si>
+    <t>film-1981-lili-marleen</t>
+  </si>
+  <si>
+    <t>Théâtre en transe</t>
+  </si>
+  <si>
+    <t>film-1981-theatre-en-transe</t>
+  </si>
+  <si>
+    <t>Lola, une femme allemande</t>
+  </si>
+  <si>
+    <t>film-1981-lola-une-femme-allemande</t>
+  </si>
+  <si>
+    <t>Le Secret de Veronika Voss</t>
+  </si>
+  <si>
+    <t>film-1981-le-secret-de-veronika-voss</t>
+  </si>
+  <si>
+    <t>Querelle</t>
+  </si>
+  <si>
+    <t>film-1982-querelle</t>
+  </si>
+  <si>
+    <t>RWF_Frise — IDs automatiques</t>
+  </si>
+  <si>
+    <t>Principe</t>
+  </si>
+  <si>
+    <t>Les colonnes IDs films — Œuvres sont calculées à partir des titres canoniques présents dans Œuvres.</t>
+  </si>
+  <si>
+    <t>Saisie</t>
+  </si>
+  <si>
+    <t>Employer les titres français canoniques du référentiel. Plusieurs titres peuvent figurer dans la même cellule.</t>
+  </si>
+  <si>
+    <t>Absence d’ID</t>
+  </si>
+  <si>
+    <t>Une œuvre absente du référentiel Films reste sans ID : aucun identifiant n’est inventé.</t>
+  </si>
+  <si>
+    <t>Mise à jour</t>
+  </si>
+  <si>
+    <t>Lorsqu’une nouvelle fiche Film est créée, ajouter son titre et son ID dans Référentiel films.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk . Période Sirkienne : Le Marchand des quatre saisons (1971). </t>
+  </si>
+  <si>
+    <t>Effi Briest, Martha</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">L'amour est plus froid que la mort (1969),  </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le Bouc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(1969, succès à Mannheim) : critique de la xénophobie et de l'apathie bourgeoise.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Premier film accueili froidement à Berlin. Le second,une critique de la xénophobie et de l'apathie bourgeoise,  remporte 5 distinctions cinématographiques en Allemagne. Le coût de production de 80000 marks est largement couvert : avec 650000 malrs de prix et 200000 marks de subventions a posteri, le film assure à RWF de quoi poursuivre son travail pour quelques années. </t>
+  </si>
+  <si>
+    <t>L'amour est plus froid que la mort (1969),  Le Bouc (1969)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>Le bouc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve"> est un tournant  tant en termes de reconnaissance que du point de vue économique. Le film aborde des problématiques contemporaines (sort des travailleurs immigrés) et des thématiques chères à RWF (l'univers étriqué de la bourgeoisie, en particulière bavaroise). </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La pièce </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">outrage au public </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">du dramaturge allemand Peter Handke témoigne du goût de l'avant-garde  artistique subentionnée pour une forme de provocation à l'égard du public, manière paradoxale de s'affranchir de la tutelle culturelle dont ils bénéficient. </t>
+    </r>
+  </si>
+  <si>
+    <t>"Il m'est impossible de comprende qu'on puisse travailler avec un outil comme la caméra en ne se souciant pas du spectateur", interview avec Norbert Sparrow, in Cinéste, WIII/2 automne 1977</t>
+  </si>
+  <si>
+    <t>Remariage de Lilo avec un journaliste, Wolff Eder. Relations difficiles entre RWF et son beau-père. 
+RWF revient à Munich mais vit dans un pensionnat.
+RWF commence à assumer ouvertement son homosexualité, fait rare pour l'époque.</t>
+  </si>
+  <si>
+    <t>RWF est pensionnaire à Augsbourg, sa mère étant hospitalisée pendant près de deux ans à la suite d'une opération. Il continue à fréquenter les salles obscures. Il voit toutes sortes de film sans distinction, des films noirs américains doublés en allemand, des films pornos sans budget qui se développent à partir de 1960. Le cinéma hollywoodien est alors plutôt dénigré par la bourgeoisie.</t>
+  </si>
+  <si>
+    <t>Si RWF ne renonce pas à l'expérimentation l'attention qu'il porte à la réception de ses films et donc au public est de plus en plus grande. L'intérêt pour le mélodrame, genre populaire américain, son travail pour la télévision et notamment la création de séries, plus tard le développement de productions internationales, traduisent sa volonté de toucher un public large et populaire. RWF intègre dans oeuvre sentiment et distanciation réflexive, échappant à la seule création de cas sociaux.</t>
+  </si>
+  <si>
+    <t>Effi Briest permet à RWF d'obtenir une reconnaissance plus large en Allemagne, qui tempère sa réputation d'enfant terrible du cinéma</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le militantisme et l'action politique violente, marquée à l'extrême gauche après 1968 en Allemagne, sont le terreau de plusieurs films de Fassbinder : Voyage à Niklashausen, , Maman Kusters s'en va au ciel, ou encore La troisième génération. Il est remarquable qu'un comique outrancier associe l'action violente à une forme de bêtise radicale.
+Fassbinder joue le rôle principal du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Droit du plus fort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, assumant une visibilité politique de son homosexualité.
+Une rétrospective de l'œuvre de RWF à New York suscite l'enthousiasme de la presse américaine. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Automne Allemand (1977) : enlèvement de Schleyer, détournement du Landshut, morts à Stammheim. </t>
+  </si>
+  <si>
+    <t>Dans les mélodrames de RWF , les personnages tentent en vain de s'affranchir des positions aliénantes produites par la famille, le couple, au sein du système capitaliste et de la classe bourgeoise. Une analogie s'établit alors entre famille et Allemagne. Le mélodrame fassbindérien met en scène des crises identitaires du sujet, comme crises de la perception (du regard), qui se traduit par une mise en crise de l'image (image de soi et image du film). Les films font dialogue subjectivité et affects avec mécanismes sociaux, évitant ainsi toute lecture simplisite etfigées de type psychologisque ou idéologique. Le mélidrame en interpénétrant le privé et le public, l'individuel et le collectif, joue d'un trouble qui participe à son caractère critique et prgoressiste : il est potentiellement facteur de changement pour un spectateur constamment soumis à la réflexion.</t>
+  </si>
+  <si>
+    <t>De l'année zéro au miracle économique; Jalousie de Catharina Valente</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Despair, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">deuxième coproduction internationale de RWF avec Dirk Bogarde et Andra Ferreol, deux acteurs importants du cinéma moderne européen, en compétition à Cannes en 1978
+Le mariage de Maria Braun, en compétition officielle à Berlin en 1979
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Année des treize lune</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">s poursuit la réflexion entamée   sur le désespoir. 
+L'épisode réalisé par RWF dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Allemagne en automne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> offre une relecture des actions commises par la RAF sur le mode de l'autofiction.</t>
+    </r>
+  </si>
+  <si>
+    <t>De l’année zéro au miracle économique|https://youtu.be/BC4BffkWyY8?si=e80MWCLF0K9Fgiub; Jalousie de Catharina Valente|https://youtu.be/-ugDTj7UFtU?si=vzGNySrsaYGKZW0k</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Despair est le film le plus rempli d'espoirt que j'ai jamais fait " RWF, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'anarchie de l'imaginaire</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>p.80-81</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Le film constitue un nouveau tournant dans la carrière de RWF en l'intégrant au club fermé des auteurs importants du cinéma européen même si son écho critique reste mitigé. Mais RWF présente aussi à Cannes, en projection non officielle </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le mariage de Maria Braun. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ce film exclipse </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Despair</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Fondation du Filmverlag der Autoren (1971), une société indépendante, par quelques cinéastes dont RWF. La société est d'abord autogérée.
+Accords Film-Télévision (1974) favorisant les coproductions (WDR).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFW devient actionnaire du Filmverlag der Autoren. </t>
+  </si>
+  <si>
+    <t>RWF projette d'adapter le roman de Freytag Soll und Haben (1855), œuvre notaoirement antismétique en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. 
+RWF quitte le Filmverlag der Autoren</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Suicide d'Armin Meier (31 mai 1978). Début de la collaboration avec Juliane Lorenz. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'année des treize lunes devient un film </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>expiatoire. Le tournage de</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Maria Braun </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">est compliqué : dépassement de budget, consommation explosive de cocaïne. Ceci explique peut être la fin de la collaboration entre Ballhaus et RWF.
+RWF travaille active à l'écriture de Berlin Alexander Platz, dont il dicte des passages dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'année des treize lunes. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le succès de Maria Braun amène RWF à espérer pour voir réaslier </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cocaïne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, l'adaptation d'un roman de Pitigrilli. Il lui permet aussi de renégocier à la hausse le budget de production de Berlin Alexander Platz : le projet devient le le plus couteux de l'histoire de la télévision allemande. </t>
+    </r>
+  </si>
+  <si>
+    <t>RWF parvient à évincer Werner Schroeter qui souhaitait réaliser une adaptation de Querelle de Jean Genet.  Mort de Fassbinder marquant symboliquement la fin du Nouveau Cinéma Allemand.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le mariage de Maria Braun </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">remporte un succès majeur en Allemagne et dans le monde, ouvrant les portes des studios américains à RWF. Aux Etats-Unis le film est distribué par United Artists. Le film fait de RWF et de son actrice Hanna Schygulla des stars et Fassbinder, l'enfant terrible du cinéma allemand, le metteur en scène des marges, devient paradoxalement l'incarnation même de la RFA. Le rêve de RWF de réaliser un "film hollywoodien allemand" semble accompli. Le film ouvre aussi la trilogie RFA. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Jusqu'à quel point les femmes de la trlogie RFA sont elles une allégorie de la nation allemande ? Quelle distance RWF prend-il avec la critique historique de son pays ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk grâce à Peer Raben .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international. Les films de RWF deviennent incontournables dans les grands festivals internationaux (Cannes, Venise, Berlin). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La RFA devient un état souverain, doté de sa propre armée. Elle est admise au sein de l'OTAN.
+La RFA remporte la coupe du monde de football, confirmation de son retour dans le concert des nations. 
+Les premiers travailleurs immigrés commencent à arriver de Grèce et d'Italie pour soutenir le "miracle économique". </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monumental Berlin Alexanderplatz (1980, 15h). </t>
+  </si>
+  <si>
+    <t>Suite de la Trilogie de la RFA : Lola, une femme allemande (1981) et Lili Marleen (1981).</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lola, une femme allemande</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> est d'abord conçu comme un remake de L</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">'ange bleu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>de Josphe von Sternberg (1930).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment l'Allemagne de l'ouest a-t-elle pu devenir une des premières nations industrielles capitalistes et une démocratie alors même qu'elle était marquée par le provincialisme, l'absence de morale et l'hypocrisie ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Que serait un cinéma nouveau prenant à bras le corps l'histoire de l'Allemagne et du cinéma, tout en s'en détachant ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qu'-est-ce qu'un cinéaste engagé ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment faire du cinéma allemand hollywoodien, qui attire et séduise le public le plus large tout en l'amenant à l'analyse et à la réflexion, sans didactisme ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment le rapport dominant/dominé structure-t-il toute relation, affective ou sociale ? </t>
+  </si>
+  <si>
+    <t>Quelles ambitions pour la série télévisuelle ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RWF, figure du collectif  politique des années 60 et 70 ou dhéritier de la figure du génie romantique et du poète maudit ? Auteur ou cinéaste populaire ? </t>
+  </si>
+  <si>
+    <t>Création de la RFA (1949). Ère Adenauer. Miracle économique ( Wirtschaftswunder )  entre 1950 et 1965 l'économie ouest-allemande croît de 8,2% en moyenne (contre 5% en France pendant les 30 glorieuses). La coccinelle de Wolkswagen devient l'emblème du "miracle économique". Les entreprise de taille moyenne constituent la colonne vertébrale de la puissance économique allemande en fournissant les outils spécialisés nécessaires à l'industrie. 
+Parallèmement, l'état  développe une politique sociale conservatrice. Réarmement de la RFA (1955).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">L'œuvre de Fassbinder proposera plus tard une radiographie critique de ce "point zéro" de la nouvelle Allemagne, notamment dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Le mariage de Maria Braun</t>
+    </r>
+  </si>
+  <si>
+    <t>"Le cinéma de Papa est mort. Nous croyons au nouveau cinéma " Manifeste d'Oberhausen (1962)
+« Toute une génération exorcisa son enfance déjà presque oubliée en soulignant sans répit combien étaient encombrantes et dévastatrices les ombres que le passé des parents avaient jetées sur le présent de leurs enfants ».Thomas Elsaesser, RWF un cinéaste d'Allemagne (2005) p.201</t>
+  </si>
+  <si>
+    <t>Manifeste d'Oberhausen (1962) : naissance du Nouveau Cinéma Allemand. Une nouvelle génération de cinéastes s'affirme et conquiert son indépendance notamment par la création de structures de production indépendantes. Fondation de l'école de cinéma DFFB à Berlin (1966).
+Cette génération incarne le phénomène de la "société sans père" et "la crise du patriarcat". L'absence ou la défaillance des pères devient un thème récurrent du Nouveau Cinéma allemand.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jochen et ses collègues, dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Huit heures ne font pas un jour, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">incarnent les ouvriers hautement qualifiés qui font la réussite économique de la RFA.
+L'œuvre de Fassbinder analyse rétrospectivement cette période en mettant à distance le consensus social de la prospérité des années 50 et 60 et en révélant les mensonges du miracle économique. Mais il met aussi en exergue l'optimisme et la vitalité anarchique de cette période où tout est possible (la garderie dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Huit heures ne font pas un jour</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, l'ascension de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Maria Braun)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Le chancelier Willy Brandt se rend en Pologne et s'agenouille devant le mémorial du ghetto de Varsovie. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Décès de Bertold Brecht
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Nuit et brouillard </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">d'Alain Resnais. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lola</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> est "un des films les plus intelligents, les plus pénétrants, mais aussi les plus grinçants sur la période d'après-guerre", Thomas Elsaesser, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>RWF un cinéaste d'Allemagne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, p. 1965
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lili Marleen (…) est ma première tentative de faire un film sur le IIIe Reich. Et je fera certainement encore plusieurs films sur le IIIe Reich. (...) Il en résultera peut-être pour finir un tableau d'ensemble de la bourgeoisie depuis 1848" Rainer Werner Fassbinder. Dichter, Schauspieler, Filmemacher</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 1992, p.178</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Domination du "cinéma de papa" ( Papas Kino ) : films de terroir ( Heimatfilm ), comédies légères dépolitisées, films en costumes , comédies musicales obitennent toujours les faveurs du public. Ces genres nés dans les années 10 et 20 ont été très exploités par les nazis.
+Freddy Quinn, Rocco Granata ou Catharina Valente sont les stars de la culture populaire allemande. 
+Il n'existe presque aucun film allemand des années 50 et 60 qui traite des camps de concentration nazis. Le cinéma allemand de la période s'intéresse peu à l'histoire. </t>
+  </si>
+  <si>
+    <t>Le tambour de Volker Schlondorff obtient la palme d'or à Cannes. 
+Diffusion de la série Holocaust (1979).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Le mouvement atteint son apogée thématique et politique.
+Hitler, un film d'Allemagne de Syberberg
+</t>
+  </si>
+  <si>
+    <t>Allemagne mère blafarde de Helma Sanders-Brahms.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Fondation du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Filmverlag der Autoren</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).
+Plusieurs cinéastes allemands ( Schlöndorff, Herzog notamment) réalisent des charges politiques violentes contre la politique et la société allemande. Pour l'amnénsie historique se poursuit dans le cinéma allemand. 
+A parti de 1968 l'industrie du cinéma commercial allemand agonise</t>
+    </r>
+  </si>
+  <si>
+    <t>Le cinéma allemand s'empare de son histoire passée et récente et réfléchit aux problèmes de représentation qu'elle pose. Film collectif L'Allemagne en automne (1978). La diffusion de la série Holocaust (1979) à la télévision allemande suscite des débats importants, auxquels participent des cinéastes comme Syberberg ou Edgard Reitz. Le mouvement du Nouveau Cinéma allemand atteint son apogée thématique et politique.</t>
+  </si>
+  <si>
+    <t>le cinéaste Edgar Reitz affirme la nécessité " de films, de livres, d'images qui nous fassent reprendre connaissance et rétablissent nos réflexes", Medium, 5/1979, p.21</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Les damnés</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, mélodrame de Visconti, travaille à interroger le régime nazi et sla manière dont l'imagerie nazie, qui érotise de manière spectaculaire le pouvoir, contamine moralment les esprits. L'éloignement du néoréalisme est maximal.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Mein Herr", numéro de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cabaret |</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://www.youtube.com/watch?v=qBjiQ5oDHBc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Aguirre, la colère de Dieu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>de Werner Herzog (1972)
+Cabaret de Bob Fosse met en scène la période de Weimar et l'ascension d'Htiler sous forme de comédie musicale. Sa mise en scène de l'homosexualité comme espace de réistance à l'oppression nazi fait advenir une représentation des persécutions dont la communauté LGBT a fait l'objet sous le nazisme, elle déconstruit aussi le cliché homophobe de l'officier nazi associé à une forme de perversion sexuelle souvent assimilée à une homosexualité refoulée. La mise en scène de la culture populaire (la chanson) et l'inscription dans un genre hollywoodien majeur constituent elles aussi des transfressions culturelles qui bouleversent l'histoire des représentations.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Portier de nuit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de Liliana Cavani</t>
+    </r>
+  </si>
+  <si>
+    <t>M. Klein de Joseph Losey</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La parution du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Deuil impossible</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de Alexander et Margarete Mitscherlich fait scandale. A travers l'exposé des troubles psychosomatiques de certains patients, les psychanalystes Alexander et Margarete Mitscherlich y analysent  le refoulement collectif des souvenirs du IIIe Reich en Allemagne. Il doit exister, selon les auteurs, un lien de cause à effet entre une forme de conservatisme teinté et de provincialisme, qui règneen RFA, le refoulement dedu passé. L'ouvrage exercce une influence sur les artistes allemands de l'époque. 
+Une réflexion sur la mémoire et l'oubli qui n'a rien perdu de son actualité</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Jean-Marie Straub sort son premier court-métrage, </t>
     </r>
@@ -729,1126 +2096,42 @@
       </rPr>
       <t>Eichmann à Jérusalem : Rapport sur la banalité du mal</t>
     </r>
-  </si>
-  <si>
-    <t>RWF retourne à Munich et contitnue d'écire, pièces, romans, scénarios. Il travaille quelques temps au département documentation au journal Südedeutsche Zeitung . 
-RWF prend des cours privés de théâtre.</t>
-  </si>
-  <si>
-    <t>Portrait de Straub et carrière</t>
-  </si>
-  <si>
-    <t>Machorka Muff de Jean-Marie Straub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Court-métrage de Jean-Marie Straub. Straub exercera une influence certaine sur le début de carrière de RWF. Le court-métrage s'inscrit dans une réflexion sur le passé nazi de l'Allemagne et dénonce la remilitarisation de l'Allemagne. </t>
-  </si>
-  <si>
-    <t>Jean-Marie Straub.jpg</t>
-  </si>
-  <si>
-    <t>Jean-Marie Straub</t>
-  </si>
-  <si>
-    <t>RWF s'inscrit à l'école d'art dramatique Fridl Loeonhard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Une grande coaltion chrétienne-démocrate voit le jour sous l'autorité du nouveau chancelier Kurt Georg Kiesinger. Willy Brandt est ministre des affaires étrangères et vice-chancelier. </t>
-  </si>
-  <si>
-    <t>Rejoint l'Action-Theater (1967).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Une majorité sociale-libérale place Willy Brandt au pouvoir. </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Whity</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Prenez garde à la sainte putain</t>
-    </r>
-  </si>
-  <si>
-    <t>Terrorisme de la RAF (arrestations en 1972). Attentat des JO de Munich (1972). Démission de Willy Brandt (1974) suite à l'affaire Guillaume. Un virage conservateur s'opère.</t>
-  </si>
-  <si>
-    <t>Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international.</t>
-  </si>
-  <si>
-    <t>Maria_braun.jpeg</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Affiche du </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mariage de Maria Braun</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Le monde sur un fil (1973)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, adaption libre d'un récit de science-fiction interroge la notion même de réalité. </t>
-    </r>
-  </si>
-  <si>
-    <t>Les années 55-75, celles pendant lesquelles RWF est sorti de l'enfance et s'est développé comme adolescent puis adulte, seront celles qui nourriront son inspiration cinémétographique et sa réflexion politique. Même les films dont l'action se situent avant 1945 sont à envisager comme "une archéologie de la société allemande d'après-guerre" (Elsaesser, p. 34)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"je trouve que l'Allemagne en particulier est dans une situation où beaucoup de choses régressent. Je dirais qu'en 1945, lorsque la guerre a pris fin, lorsque le troisième Reich a pris fin, on n'a pas perçu quelles chances s'offraient à l'Allemagne, mais je pense qu'au contraire, comme je l'ai écrit dans </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Die Zeit, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">les valeurs et les structures sur lesquelles repose cet Etat, aujourd'hui devenu démocratique, sont restées, fondamentalement les mêmes qu'autrefois. Cet état de fait, si on ajoute cette tendance régressive, va conduire à quelque chose, une forme d'Etat dans lequel je n'aimerais pas tellement vivre". Entreitne donné à Peter W. Jansen en 1978 et repris dans l'ouvra ge </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fassbinder par lui-même</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, p.342-343, G3J éditeur, 2010</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">La première génération était celle de 1968. Des idéalistes qui voulaient changer le monde et qui s'imginaient pouvoir le faire avec des mots et des manifestes. La deuxième, celle du groupe Gaader-Meinhof, passa de la légalité à la lutte armée et à l'illégalité totale. la troisième génération est celle d'aujourd'hui, qui se contente d'agir sans réfélchir, qui n'a ni idéologie ni politique, et qui se fait manipuler à son insu comme une troupe de marionnettes" </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fassbinder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, Jansen/Schütte, Collection Rivages-cinéma, 1986, p.106</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">La troisième génération, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">film inspiré par les actions de la RAF et la violence d'Etat, est compliqué à produire. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le Mariage de Maria Braun </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">allégorie de la reconstruction allemande, connaît un triomphe international.  </t>
-    </r>
-  </si>
-  <si>
-    <t>La première diffusion de Berlin Alexander Platz à la télévision déclenche une violente campagne de haine contre le réalisateur. Le journaliste Klaus Eder qualifie l'oeuvre de "mastubations malpropres" 
-Adaptant librement, près d'un siècle après sa parution - et quarante ans après la série culte de Fassbinder - le chef-d'oeuvre polyphonique d'Alfred Döblin, le réalisateur germano-afghan Burhan Qurbani en modernise le propos de manière radicale, en imaginant un réfugié sans papiers dans la peau de Franz Biberkopf, antihéros en quête de rédemption. Il transpose également à l'image l'audace formelle du roman, saturant les sens dans un tourbillon de musique, de mouvements et de couleurs. </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"je ferai des films jusqu'à ce que j'ai conduit mon histoire de la RFA jusqu'à ici et aujourd'hui. Les histoires de </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Lola </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">et </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Maria Braun</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ne sont possibles que dans l'époque où elles se déroulent. Et elles s'intègrent, je l'espère, dans un portrait d'ensemble de la République fédérale, elles aident à comprendre cette étrange entité, avec ses dangers et ses menaces. En ce sens, ce sont des films très politiques". in </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Rainer Werner Fassbinder, Dichter, Schapuspieler, Filmemacher, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Argon, 1992, p.77</t>
-    </r>
-  </si>
-  <si>
-    <t>Victoire de la CDU en octobre : Helmut Kohl devient chancelier. Fin d'une époque artistique et politique radicale.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"Je ne pense pas qu'il fait fait un seul que l'on pourrait qualifier de chef-d'œuvre. Le chef-d'œuvre, c'est les 41 films et la vie et tout le reste. Les films ne sont que le résidu de cette vie."Peter Chatel </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">in  Die Sehnsucht des Rainer Werner Fassbinder » (La Nostalgie de Rainer Werner Fassbinder), De Kurt Raab et Karsten Peters, 1982, éditions Bertelsmann </t>
-    </r>
-  </si>
-  <si>
-    <t>Catégorie</t>
-  </si>
-  <si>
-    <t>Référence bibliographique</t>
-  </si>
-  <si>
-    <t>Usage dans la frise</t>
-  </si>
-  <si>
-    <t>Lien</t>
-  </si>
-  <si>
-    <t>Histoire allemande</t>
-  </si>
-  <si>
-    <r>
-      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t>, de Thomas Elsaesser, Centre Pompidou, 2005</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t>, pp. 490-507</t>
-    </r>
-  </si>
-  <si>
-    <t>Repères historiques, chronologie politique</t>
-  </si>
-  <si>
-    <t>Fassbinder</t>
-  </si>
-  <si>
-    <r>
-      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t>, de Thomas Elsaesser, Centre Pompidou, 2005</t>
-    </r>
-  </si>
-  <si>
-    <t>Biographie et filmographie</t>
-  </si>
-  <si>
-    <t>URL éventuelle</t>
-  </si>
-  <si>
-    <t>Cinéma allemand</t>
-  </si>
-  <si>
-    <t>Référence complète</t>
-  </si>
-  <si>
-    <t>Contexte culturel et esthétique</t>
-  </si>
-  <si>
-    <t>Archives et sites</t>
-  </si>
-  <si>
-    <t>Nom du site ou de l’institution</t>
-  </si>
-  <si>
-    <t>Documents et vérifications</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>Titre canonique</t>
-  </si>
-  <si>
-    <t>ID canonique</t>
-  </si>
-  <si>
-    <t>L’Amour est plus froid que la mort</t>
-  </si>
-  <si>
-    <t>film-1969-l-amour-est-plus-froid-que-la-mort</t>
-  </si>
-  <si>
-    <t>Le Bouc</t>
-  </si>
-  <si>
-    <t>film-1969-le-bouc</t>
-  </si>
-  <si>
-    <t>Les Dieux de la peste</t>
-  </si>
-  <si>
-    <t>film-1970-les-dieux-de-la-peste</t>
-  </si>
-  <si>
-    <t>Pourquoi M. R. est-il atteint de folie meurtrière ?</t>
-  </si>
-  <si>
-    <t>film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere</t>
-  </si>
-  <si>
-    <t>Le Soldat américain</t>
-  </si>
-  <si>
-    <t>film-1970-le-soldat-americain</t>
-  </si>
-  <si>
-    <t>Le Voyage à Niklashausen</t>
-  </si>
-  <si>
-    <t>film-1970-le-voyage-a-niklashausen</t>
-  </si>
-  <si>
-    <t>Whity</t>
-  </si>
-  <si>
-    <t>film-1971-whity</t>
-  </si>
-  <si>
-    <t>Prenez garde à la sainte putain</t>
-  </si>
-  <si>
-    <t>film-1971-prenez-garde-a-la-sainte-putain</t>
-  </si>
-  <si>
-    <t>Pionniers à Ingolstadt</t>
-  </si>
-  <si>
-    <t>film-1971-pionniers-a-ingolstadt</t>
-  </si>
-  <si>
-    <t>Le Marchand des quatre saisons</t>
-  </si>
-  <si>
-    <t>film-1972-le-marchand-des-quatre-saisons</t>
-  </si>
-  <si>
-    <t>Les Larmes amères de Petra von Kant</t>
-  </si>
-  <si>
-    <t>film-1972-les-larmes-ameres-de-petra-von-kant</t>
-  </si>
-  <si>
-    <t>Liberté à Brême</t>
-  </si>
-  <si>
-    <t>film-1972-liberte-a-breme</t>
-  </si>
-  <si>
-    <t>Huit heures ne font pas un jour</t>
-  </si>
-  <si>
-    <t>film-1972-huit-heures-ne-font-pas-un-jour</t>
-  </si>
-  <si>
-    <t>Gibier de passage</t>
-  </si>
-  <si>
-    <t>film-1973-gibier-de-passage</t>
-  </si>
-  <si>
-    <t>Le Monde sur un fil</t>
-  </si>
-  <si>
-    <t>film-1973-le-monde-sur-un-fil</t>
-  </si>
-  <si>
-    <t>Tous les autres s’appellent Ali</t>
-  </si>
-  <si>
-    <t>film-1974-tous-les-autres-s-appellent-ali</t>
-  </si>
-  <si>
-    <t>Effi Briest</t>
-  </si>
-  <si>
-    <t>film-1974-effi-briest</t>
-  </si>
-  <si>
-    <t>Nora Helmer</t>
-  </si>
-  <si>
-    <t>film-1974-nora-helmer</t>
-  </si>
-  <si>
-    <t>Martha</t>
-  </si>
-  <si>
-    <t>film-1974-martha</t>
-  </si>
-  <si>
-    <t>Le Droit du plus fort</t>
-  </si>
-  <si>
-    <t>film-1975-le-droit-du-plus-fort</t>
-  </si>
-  <si>
-    <t>Maman Küsters s’en va au ciel</t>
-  </si>
-  <si>
-    <t>film-1975-maman-kusters-s-en-va-au-ciel</t>
-  </si>
-  <si>
-    <t>Comme un oiseau sur le fil</t>
-  </si>
-  <si>
-    <t>film-1975-comme-un-oiseau-sur-le-fil</t>
-  </si>
-  <si>
-    <t>Peur de la peur</t>
-  </si>
-  <si>
-    <t>film-1975-peur-de-la-peur</t>
-  </si>
-  <si>
-    <t>L’Ombre des anges</t>
-  </si>
-  <si>
-    <t>film-1976-l-ombre-des-anges</t>
-  </si>
-  <si>
-    <t>Le Rôti de Satan</t>
-  </si>
-  <si>
-    <t>film-1976-le-roti-de-satan</t>
-  </si>
-  <si>
-    <t>Roulette chinoise</t>
-  </si>
-  <si>
-    <t>film-1976-roulette-chinoise</t>
-  </si>
-  <si>
-    <t>Je veux seulement que vous m’aimiez</t>
-  </si>
-  <si>
-    <t>film-1976-je-veux-seulement-que-vous-m-aimiez</t>
-  </si>
-  <si>
-    <t>Femmes à New York</t>
-  </si>
-  <si>
-    <t>film-1977-femmes-a-new-york</t>
-  </si>
-  <si>
-    <t>La Femme du chef de gare</t>
-  </si>
-  <si>
-    <t>film-1977-la-femme-du-chef-de-gare</t>
-  </si>
-  <si>
-    <t>L’Allemagne en automne</t>
-  </si>
-  <si>
-    <t>film-1978-l-allemagne-en-automne</t>
-  </si>
-  <si>
-    <t>Despair</t>
-  </si>
-  <si>
-    <t>film-1978-despair</t>
-  </si>
-  <si>
-    <t>L’Année des treize lunes</t>
-  </si>
-  <si>
-    <t>film-1978-l-annee-des-treize-lunes</t>
-  </si>
-  <si>
-    <t>Le Mariage de Maria Braun</t>
-  </si>
-  <si>
-    <t>film-1979-le-mariage-de-maria-braun</t>
-  </si>
-  <si>
-    <t>La Troisième génération</t>
-  </si>
-  <si>
-    <t>film-1979-la-troisieme-generation</t>
-  </si>
-  <si>
-    <t>Berlin Alexanderplatz</t>
-  </si>
-  <si>
-    <t>film-1980-berlin-alexanderplatz</t>
-  </si>
-  <si>
-    <t>Lili Marleen</t>
-  </si>
-  <si>
-    <t>film-1981-lili-marleen</t>
-  </si>
-  <si>
-    <t>Théâtre en transe</t>
-  </si>
-  <si>
-    <t>film-1981-theatre-en-transe</t>
-  </si>
-  <si>
-    <t>Lola, une femme allemande</t>
-  </si>
-  <si>
-    <t>film-1981-lola-une-femme-allemande</t>
-  </si>
-  <si>
-    <t>Le Secret de Veronika Voss</t>
-  </si>
-  <si>
-    <t>film-1981-le-secret-de-veronika-voss</t>
-  </si>
-  <si>
-    <t>Querelle</t>
-  </si>
-  <si>
-    <t>film-1982-querelle</t>
-  </si>
-  <si>
-    <t>RWF_Frise — IDs automatiques</t>
-  </si>
-  <si>
-    <t>Principe</t>
-  </si>
-  <si>
-    <t>Les colonnes IDs films — Œuvres sont calculées à partir des titres canoniques présents dans Œuvres.</t>
-  </si>
-  <si>
-    <t>Saisie</t>
-  </si>
-  <si>
-    <t>Employer les titres français canoniques du référentiel. Plusieurs titres peuvent figurer dans la même cellule.</t>
-  </si>
-  <si>
-    <t>Absence d’ID</t>
-  </si>
-  <si>
-    <t>Une œuvre absente du référentiel Films reste sans ID : aucun identifiant n’est inventé.</t>
-  </si>
-  <si>
-    <t>Mise à jour</t>
-  </si>
-  <si>
-    <t>Lorsqu’une nouvelle fiche Film est créée, ajouter son titre et son ID dans Référentiel films.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> Fondation du </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Filmverlag der Autoren</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).
-Plusieurs cinéastes allemands ( Schlöndorff, Herzog notamment) réalisent des charges politiques violentes contre la politique et la société allemande.
-A parti de 1968 l'industrie du cinéma commercial allemand agonise</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk . Période Sirkienne : Le Marchand des quatre saisons (1971). </t>
-  </si>
-  <si>
-    <t>Effi Briest, Martha</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">L'amour est plus froid que la mort (1969),  </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le Bouc </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(1969, succès à Mannheim) : critique de la xénophobie et de l'apathie bourgeoise.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Premier film accueili froidement à Berlin. Le second,une critique de la xénophobie et de l'apathie bourgeoise,  remporte 5 distinctions cinématographiques en Allemagne. Le coût de production de 80000 marks est largement couvert : avec 650000 malrs de prix et 200000 marks de subventions a posteri, le film assure à RWF de quoi poursuivre son travail pour quelques années. </t>
-  </si>
-  <si>
-    <t>L'amour est plus froid que la mort (1969),  Le Bouc (1969)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>Le bouc</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t xml:space="preserve"> est un tournant  tant en termes de reconnaissance que du point de vue économique. Le film aborde des problématiques contemporaines (sort des travailleurs immigrés) et des thématiques chères à RWF (l'univers étriqué de la bourgeoisie, en particulière bavaroise). </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">La pièce </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">outrage au public </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">du dramaturge allemand Peter Handke témoigne du goût de l'avant-garde  artistique subentionnée pour une forme de provocation à l'égard du public, manière paradoxale de s'affranchir de la tutelle culturelle dont ils bénéficient. </t>
-    </r>
-  </si>
-  <si>
-    <t>"Il m'est impossible de comprende qu'on puisse travailler avec un outil comme la caméra en ne se souciant pas du spectateur", interview avec Norbert Sparrow, in Cinéste, WIII/2 automne 1977</t>
-  </si>
-  <si>
-    <t>Remariage de Lilo avec un journaliste, Wolff Eder. Relations difficiles entre RWF et son beau-père. 
-RWF revient à Munich mais vit dans un pensionnat.
-RWF commence à assumer ouvertement son homosexualité, fait rare pour l'époque.</t>
-  </si>
-  <si>
-    <t>RWF est pensionnaire à Augsbourg, sa mère étant hospitalisée pendant près de deux ans à la suite d'une opération. Il continue à fréquenter les salles obscures. Il voit toutes sortes de film sans distinction, des films noirs américains doublés en allemand, des films pornos sans budget qui se développent à partir de 1960. Le cinéma hollywoodien est alors plutôt dénigré par la bourgeoisie.</t>
-  </si>
-  <si>
-    <t>Si RWF ne renonce pas à l'expérimentation l'attention qu'il porte à la réception de ses films et donc au public est de plus en plus grande. L'intérêt pour le mélodrame, genre populaire américain, son travail pour la télévision et notamment la création de séries, plus tard le développement de productions internationales, traduisent sa volonté de toucher un public large et populaire. RWF intègre dans oeuvre sentiment et distanciation réflexive, échappant à la seule création de cas sociaux.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domination du "cinéma de papa" ( Papas Kino ) : films de terroir ( Heimatfilm ), comédies légères dépolitisées, films en costumes , comédies musicales obitennent toujours les faveurs du public. Ces genres nés dans les années 10 et 20 ont été très exploités par les nazis.
-Freddy Quinn, Rocco Granata ou Catharina Valente sont les stars de la culture populaire allemande. </t>
-  </si>
-  <si>
-    <t>Effi Briest permet à RWF d'obtenir une reconnaissance plus large en Allemagne, qui tempère sa réputation d'enfant terrible du cinéma</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Le militantisme et l'action politique violente, marquée à l'extrême gauche après 1968 en Allemagne, sont le terreau de plusieurs films de Fassbinder : Voyage à Niklashausen, , Maman Kusters s'en va au ciel, ou encore La troisième génération. Il est remarquable qu'un comique outrancier associe l'action violente à une forme de bêtise radicale.
-Fassbinder joue le rôle principal du </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Droit du plus fort</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, assumant une visibilité politique de son homosexualité.
-Une rétrospective de l'œuvre de RWF à New York suscite l'enthousiasme de la presse américaine. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Film collectif </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">L'Allemagne en automne </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(1978) initié par Alexander Kluge.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Automne Allemand (1977) : enlèvement de Schleyer, détournement du Landshut, morts à Stammheim. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Le mouvement atteint son apogée thématique et politique.
-Diffusion de la série Holocaust (1979).</t>
-  </si>
-  <si>
-    <t>Dans les mélodrames de RWF , les personnages tentent en vain de s'affranchir des positions aliénantes produites par la famille, le couple, au sein du système capitaliste et de la classe bourgeoise. Une analogie s'établit alors entre famille et Allemagne. Le mélodrame fassbindérien met en scène des crises identitaires du sujet, comme crises de la perception (du regard), qui se traduit par une mise en crise de l'image (image de soi et image du film). Les films font dialogue subjectivité et affects avec mécanismes sociaux, évitant ainsi toute lecture simplisite etfigées de type psychologisque ou idéologique. Le mélidrame en interpénétrant le privé et le public, l'individuel et le collectif, joue d'un trouble qui participe à son caractère critique et prgoressiste : il est potentiellement facteur de changement pour un spectateur constamment soumis à la réflexion.</t>
-  </si>
-  <si>
-    <t>De l'année zéro au miracle économique; Jalousie de Catharina Valente</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Despair, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">deuxième coproduction internationale de RWF avec Dirk Bogarde et Andra Ferreol, deux acteurs importants du cinéma moderne européen, en compétition à Cannes en 1978
-Le mariage de Maria Braun, en compétition officielle à Berlin en 1979
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'Année des treize lune</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">s poursuit la réflexion entamée   sur le désespoir. 
-L'épisode réalisé par RWF dans </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'Allemagne en automne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> offre une relecture des actions commises par la RAF sur le mode de l'autofiction.</t>
-    </r>
-  </si>
-  <si>
-    <t>De l’année zéro au miracle économique|https://youtu.be/BC4BffkWyY8?si=e80MWCLF0K9Fgiub; Jalousie de Catharina Valente|https://youtu.be/-ugDTj7UFtU?si=vzGNySrsaYGKZW0k</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Production de séries monumentales pour la télévision. Le Nouveau Cinéma Allemand atteint une maturité formelle extrême.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le tambour </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>de Volker Schlondorff obtient l'oscar du meilleur film étranger</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Le tambour de Volker Schlondorff obtient la palme d'or à Cannes. </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"Despair est le film le plus rempli d'espoirt que j'ai jamais fait " RWF, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'anarchie de l'imaginaire</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>p.80-81</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Le film constitue un nouveau tournant dans la carrière de RWF en l'intégrant au club fermé des auteurs importants du cinéma européen même si son écho critique reste mitigé. Mais RWF présente aussi à Cannes, en projection non officielle </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le mariage de Maria Braun. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ce film exclipse </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Despair</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>Fondation du Filmverlag der Autoren (1971), une société indépendante, par quelques cinéastes dont RWF. La société est d'abord autogérée.
-Accords Film-Télévision (1974) favorisant les coproductions (WDR).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFW devient actionnaire du Filmverlag der Autoren. </t>
-  </si>
-  <si>
-    <t>RWF projette d'adapter le roman de Freytag Soll und Haben (1855), œuvre notaoirement antismétique en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. 
-RWF quitte le Filmverlag der Autoren</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Suicide d'Armin Meier (31 mai 1978). Début de la collaboration avec Juliane Lorenz. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">L'année des treize lunes devient un film </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>expiatoire. Le tournage de</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Maria Braun </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">est compliqué : dépassement de budget, consommation explosive de cocaïne. Ceci explique peut être la fin de la collaboration entre Ballhaus et RWF.
-RWF travaille active à l'écriture de Berlin Alexander Platz, dont il dicte des passages dans </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">L'année des treize lunes. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Le succès de Maria Braun amène RWF à espérer pour voir réaslier </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cocaïne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, l'adaptation d'un roman de Pitigrilli. Il lui permet aussi de renégocier à la hausse le budget de production de Berlin Alexander Platz : le projet devient le le plus couteux de l'histoire de la télévision allemande. </t>
-    </r>
-  </si>
-  <si>
-    <t>RWF parvient à évincer Werner Schroeter qui souhaitait réaliser une adaptation de Querelle de Jean Genet.  Mort de Fassbinder marquant symboliquement la fin du Nouveau Cinéma Allemand.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le mariage de Maria Braun </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">remporte un succès majeur en Allemagne et dans le monde, ouvrant les portes des studios américains à RWF. Aux Etats-Unis le film est distribué par United Artists. Le film fait de RWF et de son actrice Hanna Schygulla des stars et Fassbinder, l'enfant terrible du cinéma allemand, le metteur en scène des marges, devient paradoxalement l'incarnation même de la RFA. Le rêve de RWF de réaliser un "film hollywoodien allemand" semble accompli. Le film ouvre aussi la trilogie RFA. </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Jusqu'à quel point les femmes de la trlogie RFA sont elles une allégorie de la nation allemande ? Quelle distance RWF prend-il avec la critique historique de son pays ? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk grâce à Peer Raben .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international. Les films de RWF deviennent incontournables dans les grands festivals internationaux (Cannes, Venise, Berlin). </t>
-  </si>
-  <si>
-    <t xml:space="preserve">La RFA devient un état souverain, doté de sa propre armée. Elle est admise au sein de l'OTAN.
-La RFA remporte la coupe du monde de football, confirmation de son retour dans le concert des nations. 
-Les premiers travailleurs immigrés commencent à arriver de Grèce et d'Italie pour soutenir le "miracle économique". </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monumental Berlin Alexanderplatz (1980, 15h). </t>
-  </si>
-  <si>
-    <t>Suite de la Trilogie de la RFA : Lola, une femme allemande (1981) et Lili Marleen (1981).</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Alexander Mitscherlich publie</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> La société sans père </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">qui décrit l'affaiblissement et la crise du système patriarcal dans les sociétés modernes d'après-guerre. La figure du père n'est plus un modèle absolu et le vide de son absence (d'abord concrète puisqu'il travaille mais aussi symbolique du fait du manque de figures crédibles ) entraine l'expression, plus ou moins anarchique et violente, des forces pulsionnelles négatives. celles-ci sont le fait d'une autorité sociale dont les contraintes paraissent de plus en plus absurdes et répressives puisqu'elles ne sont plus intégrées par l'identificaion à une figure individuelle affective. </t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1964,8 +2247,13 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="-webkit-standard"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1996,13 +2284,30 @@
         <bgColor rgb="FFEEF5FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -2011,7 +2316,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2084,9 +2389,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -2737,7 +3043,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="3" width="31.83203125" customWidth="1"/>
     <col min="4" max="4" width="35.5" customWidth="1"/>
@@ -2749,7 +3055,7 @@
     <col min="12" max="14" width="27.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="12" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" s="12" customFormat="1" ht="28" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2793,7 +3099,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="84" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -2817,37 +3123,39 @@
         <v/>
       </c>
       <c r="I2" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>23</v>
       </c>
-      <c r="M2" t="s">
+    </row>
+    <row r="3" spans="1:14" s="14" customFormat="1" ht="211" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" s="14" customFormat="1" ht="98" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="4" t="str">
@@ -2855,199 +3163,212 @@
         <v/>
       </c>
       <c r="I3" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="196" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="L3" s="15" t="s">
+      <c r="C4" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="E4" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="H4" s="4" t="str">
         <f>IF(G4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>37</v>
+      <c r="J4" s="13" t="s">
+        <v>33</v>
       </c>
       <c r="K4" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="85" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="85" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>IF(G5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
       <c r="I5" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="K5" t="s">
         <v>276</v>
       </c>
-      <c r="K5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="303" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:14" ht="303" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H6" s="4" t="str">
         <f>IF(G6="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="70" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>297</v>
+      </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H7" s="4" t="str">
         <f>IF(G7="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="129" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>274</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>56</v>
+        <v>313</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H8" s="4" t="str">
         <f>IF(G8="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1978-l-annee-des-treize-lunes; film-1979-le-mariage-de-maria-braun</v>
       </c>
+      <c r="K8" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="N8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.15">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="89" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="C9" s="15" t="s">
+        <v>298</v>
+      </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H9" s="4" t="str">
         <f>IF(G9="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1980-berlin-alexanderplatz; film-1981-lili-marleen; film-1981-lola-une-femme-allemande</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:14" ht="70" customHeight="1">
       <c r="A10" s="1">
         <v>1982</v>
       </c>
       <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>299</v>
+      </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H10" s="4" t="str">
         <f>IF(G10="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -3070,7 +3391,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="31.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.6640625" customWidth="1"/>
@@ -3084,9 +3405,9 @@
     <col min="21" max="21" width="56.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="12" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="12" customFormat="1" ht="28" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -3104,52 +3425,52 @@
         <v>6</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>10</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="S1" s="8" t="s">
         <v>13</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="U1" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="98" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="98">
       <c r="A2" s="1">
         <v>1945</v>
       </c>
@@ -3157,18 +3478,18 @@
         <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I2" s="20"/>
       <c r="J2" s="20"/>
@@ -3187,7 +3508,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="224" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="224">
       <c r="A3" s="1">
         <v>1946</v>
       </c>
@@ -3195,18 +3516,18 @@
         <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F3" s="19"/>
       <c r="G3" s="1"/>
       <c r="H3" s="20" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I3" s="20"/>
       <c r="J3" s="20"/>
@@ -3225,18 +3546,18 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="182" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="182">
       <c r="A4" s="1">
         <v>1947</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="19"/>
@@ -3254,40 +3575,40 @@
       <c r="R4" s="19"/>
       <c r="S4" s="19"/>
       <c r="T4" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="U4" s="2" t="str">
         <f>IF(F4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="182" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="182">
       <c r="A5" s="1">
         <v>1948</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="19"/>
       <c r="G5" s="1"/>
       <c r="H5" s="20" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="19"/>
@@ -3303,34 +3624,34 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="112" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" ht="112">
       <c r="A6" s="1">
         <v>1949</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="19"/>
       <c r="G6" s="1"/>
       <c r="H6" s="20" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I6" s="20"/>
       <c r="J6" s="20"/>
       <c r="K6" s="20"/>
       <c r="L6" s="1"/>
       <c r="M6" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O6" s="19"/>
       <c r="P6" s="19"/>
@@ -3343,17 +3664,17 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="70" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" ht="70">
       <c r="A7" s="1">
         <v>1950</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F7" s="19"/>
       <c r="G7" s="1"/>
@@ -3363,16 +3684,16 @@
       <c r="K7" s="20"/>
       <c r="L7" s="1"/>
       <c r="M7" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N7" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O7" s="19"/>
       <c r="P7" s="19"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="S7" s="19"/>
       <c r="T7" s="19"/>
@@ -3381,19 +3702,19 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="56" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" ht="56">
       <c r="A8" s="1">
         <v>1951</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="19"/>
@@ -3403,10 +3724,10 @@
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
       <c r="M8" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N8" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O8" s="19"/>
       <c r="P8" s="19"/>
@@ -3419,21 +3740,21 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="84" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" ht="84">
       <c r="A9" s="1">
         <v>1952</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="19"/>
@@ -3443,16 +3764,16 @@
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="O9" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
@@ -3463,34 +3784,34 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="70" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" ht="70">
       <c r="A10" s="1">
         <v>1953</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="19"/>
       <c r="H10" s="20" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
       <c r="M10" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N10" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O10" s="19"/>
       <c r="P10" s="19"/>
@@ -3503,40 +3824,40 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="140" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" ht="140">
       <c r="A11" s="1">
         <v>1954</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="19"/>
       <c r="H11" s="20" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="N11" s="19" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="O11" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P11" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
@@ -3547,17 +3868,17 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" ht="17">
       <c r="A12" s="1">
         <v>1955</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="19"/>
@@ -3579,36 +3900,36 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="154" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="154">
       <c r="A13" s="1">
         <v>1956</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>120</v>
+        <v>306</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="19"/>
       <c r="H13" s="23" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="I13" s="19"/>
       <c r="J13" s="19"/>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
       <c r="M13" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N13" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O13" s="19"/>
       <c r="P13" s="19"/>
@@ -3621,18 +3942,18 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="168" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="168">
       <c r="A14" s="1">
         <v>1957</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -3643,10 +3964,10 @@
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
       <c r="M14" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N14" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O14" s="19"/>
       <c r="P14" s="19"/>
@@ -3656,25 +3977,25 @@
       <c r="T14" s="19"/>
       <c r="U14" s="2"/>
     </row>
-    <row r="15" spans="1:21" ht="126" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" ht="126">
       <c r="A15" s="1">
         <v>1959</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="19" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
@@ -3682,10 +4003,10 @@
       <c r="K15" s="19"/>
       <c r="L15" s="19"/>
       <c r="M15" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N15" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O15" s="19"/>
       <c r="P15" s="19"/>
@@ -3698,21 +4019,21 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="126" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" ht="126">
       <c r="A16" s="1">
         <v>1960</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="19"/>
@@ -3722,10 +4043,10 @@
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
       <c r="M16" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N16" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O16" s="19"/>
       <c r="P16" s="19"/>
@@ -3738,19 +4059,19 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="126" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" ht="126">
       <c r="A17" s="1">
         <v>1961</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
@@ -3760,10 +4081,10 @@
       <c r="K17" s="19"/>
       <c r="L17" s="19"/>
       <c r="M17" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N17" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O17" s="19"/>
       <c r="P17" s="19"/>
@@ -3776,18 +4097,18 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="112" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" ht="112">
       <c r="A18" s="1">
         <v>1962</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -3797,13 +4118,13 @@
       <c r="J18" s="19"/>
       <c r="K18" s="19"/>
       <c r="L18" s="19" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M18" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N18" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O18" s="19"/>
       <c r="P18" s="19"/>
@@ -3816,38 +4137,38 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="126" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" ht="371">
       <c r="A19" s="1">
         <v>1963</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>136</v>
+        <v>321</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="19"/>
       <c r="H19" s="23" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="J19" s="19" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K19" s="19"/>
       <c r="L19" s="19"/>
       <c r="M19" s="19" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="N19" s="19" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="O19" s="19"/>
       <c r="P19" s="19"/>
@@ -3857,7 +4178,7 @@
       <c r="T19" s="19"/>
       <c r="U19" s="2"/>
     </row>
-    <row r="20" spans="1:21" ht="28" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="28">
       <c r="A20" s="1">
         <v>1964</v>
       </c>
@@ -3865,7 +4186,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="19"/>
@@ -3884,22 +4205,22 @@
       <c r="T20" s="19"/>
       <c r="U20" s="2"/>
     </row>
-    <row r="21" spans="1:21" ht="112" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" ht="112">
       <c r="A21" s="1">
         <v>1966</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
@@ -3920,17 +4241,19 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" ht="238">
       <c r="A22" s="1">
         <v>1967</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>320</v>
+      </c>
       <c r="E22" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="19"/>
@@ -3952,27 +4275,27 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="154" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" ht="154">
       <c r="A23" s="1">
         <v>1968</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
@@ -3992,17 +4315,19 @@
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="28" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21" ht="98">
       <c r="A24" s="1">
         <v>1969</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D24" s="1"/>
+        <v>137</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="24"/>
@@ -4021,16 +4346,18 @@
       <c r="T24" s="19"/>
       <c r="U24" s="2"/>
     </row>
-    <row r="25" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" ht="42">
       <c r="A25" s="1">
         <v>1970</v>
       </c>
       <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="C25" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D25" s="27"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G25" s="24"/>
       <c r="H25" s="19"/>
@@ -4048,47 +4375,47 @@
       <c r="T25" s="19"/>
       <c r="U25" s="2"/>
     </row>
-    <row r="26" spans="1:21" ht="196" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" ht="196">
       <c r="A26" s="1">
         <v>1971</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G26" s="19" t="s">
         <v>271</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>281</v>
       </c>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="15"/>
       <c r="K26" s="19"/>
       <c r="L26" s="19" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="N26" s="21" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="T26" s="19"/>
       <c r="U26" s="2" t="str">
@@ -4096,13 +4423,15 @@
         <v>film-1972-le-marchand-des-quatre-saisons</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:21" ht="306">
       <c r="A27" s="1">
         <v>1972</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
+      <c r="D27" s="1" t="s">
+        <v>317</v>
+      </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="15"/>
@@ -4121,19 +4450,23 @@
       <c r="T27" s="15"/>
       <c r="U27" s="2"/>
     </row>
-    <row r="28" spans="1:21" ht="42" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21" ht="84">
       <c r="A28" s="1">
         <v>1973</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
+      <c r="D28" s="26" t="s">
+        <v>318</v>
+      </c>
       <c r="E28" s="1"/>
       <c r="F28" s="25" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G28" s="1"/>
-      <c r="H28" s="15"/>
+      <c r="H28" s="15" t="s">
+        <v>316</v>
+      </c>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
@@ -4148,7 +4481,7 @@
       <c r="T28" s="15"/>
       <c r="U28" s="2"/>
     </row>
-    <row r="29" spans="1:21" ht="56" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21" ht="56">
       <c r="A29" s="1">
         <v>1974</v>
       </c>
@@ -4157,10 +4490,10 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
@@ -4177,27 +4510,27 @@
       <c r="T29" s="15"/>
       <c r="U29" s="2"/>
     </row>
-    <row r="30" spans="1:21" ht="238" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21" ht="238">
       <c r="A30" s="1">
         <v>1975</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
@@ -4217,17 +4550,19 @@
         <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="28" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" ht="28">
       <c r="A31" s="1">
         <v>1976</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="D31" s="25" t="s">
+        <v>319</v>
+      </c>
       <c r="E31" s="1" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -4246,21 +4581,21 @@
       <c r="T31" s="15"/>
       <c r="U31" s="2"/>
     </row>
-    <row r="32" spans="1:21" ht="252" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" ht="252">
       <c r="A32" s="1">
         <v>1977</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="19"/>
@@ -4268,10 +4603,10 @@
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
       <c r="K32" s="19" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="L32" s="19" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="M32" s="19"/>
       <c r="N32" s="19"/>
@@ -4286,30 +4621,28 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="196" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:21" ht="196">
       <c r="A33" s="1">
         <v>1978</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
-      <c r="D33" s="1" t="s">
-        <v>285</v>
-      </c>
+      <c r="D33" s="25"/>
       <c r="E33" s="1" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
       <c r="L33" s="15" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="M33" s="19"/>
       <c r="N33" s="19"/>
@@ -4321,23 +4654,23 @@
       <c r="T33" s="19"/>
       <c r="U33" s="2"/>
     </row>
-    <row r="34" spans="1:21" ht="210" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:21" ht="210">
       <c r="A34" s="1">
         <v>1979</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
@@ -4354,34 +4687,34 @@
       <c r="T34" s="19"/>
       <c r="U34" s="2"/>
     </row>
-    <row r="35" spans="1:21" ht="293" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:21" ht="293">
       <c r="A35" s="1">
         <v>1980</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>292</v>
+        <v>54</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>311</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
       <c r="L35" s="19" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="M35" s="19"/>
       <c r="N35" s="19"/>
@@ -4396,32 +4729,36 @@
         <v>film-1980-berlin-alexanderplatz</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="42" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:21" ht="182">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-      <c r="P36" s="26"/>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="26"/>
+        <v>291</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="15"/>
       <c r="U36" s="2"/>
     </row>
-    <row r="37" spans="1:21" ht="126" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:21" ht="126">
       <c r="A37" s="1">
         <v>1982</v>
       </c>
@@ -4429,16 +4766,16 @@
         <v>1982</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
@@ -4446,7 +4783,7 @@
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
       <c r="L37" s="19" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="M37" s="19"/>
       <c r="N37" s="19"/>
@@ -4484,79 +4821,79 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C07A15F-9849-0547-90EB-0E0C6153DA22}">
   <dimension ref="A15:D19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="37.5" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4">
       <c r="A15" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="51">
+      <c r="A16" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" s="17"/>
+    </row>
+    <row r="17" spans="1:4" ht="51">
+      <c r="A17" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="D17" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="C15" s="16" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="28">
+      <c r="A18" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="B18" s="17" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.15">
-      <c r="A16" s="17" t="s">
+      <c r="C18" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="D18" s="17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28">
+      <c r="A19" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="B19" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="D16" s="17"/>
-    </row>
-    <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.15">
-      <c r="A17" s="17" t="s">
+      <c r="C19" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="D19" s="17" t="s">
         <v>169</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="28" x14ac:dyDescent="0.15">
-      <c r="A18" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="28" x14ac:dyDescent="0.15">
-      <c r="A19" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -4567,338 +4904,338 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="46.83203125" customWidth="1"/>
     <col min="2" max="2" width="59.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="17">
       <c r="A1" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="17">
+      <c r="A2" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17">
+      <c r="A3" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17">
+      <c r="A4" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="17">
+      <c r="A5" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="7" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="17">
+      <c r="A6" s="9" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="B6" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="9" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="17">
+      <c r="A7" s="9" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+      <c r="B7" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B3" s="9" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="17">
+      <c r="A8" s="9" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="B8" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B4" s="9" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="17">
+      <c r="A9" s="9" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
+      <c r="B9" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="B5" s="9" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="17">
+      <c r="A10" s="9" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
+      <c r="B10" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="B6" s="9" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="17">
+      <c r="A11" s="9" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
+      <c r="B11" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="B7" s="9" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="17">
+      <c r="A12" s="9" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
+      <c r="B12" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="B8" s="9" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="17">
+      <c r="A13" s="9" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
+      <c r="B13" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="B9" s="9" t="s">
+    </row>
+    <row r="14" spans="1:2" ht="17">
+      <c r="A14" s="9" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
+      <c r="B14" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B10" s="9" t="s">
+    </row>
+    <row r="15" spans="1:2" ht="17">
+      <c r="A15" s="9" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
+      <c r="B15" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="B11" s="9" t="s">
+    </row>
+    <row r="16" spans="1:2" ht="17">
+      <c r="A16" s="9" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
+      <c r="B16" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B12" s="9" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="17">
+      <c r="A17" s="9" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
+      <c r="B17" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="B13" s="9" t="s">
+    </row>
+    <row r="18" spans="1:2" ht="17">
+      <c r="A18" s="9" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
+      <c r="B18" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="B14" s="9" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="17">
+      <c r="A19" s="9" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="9" t="s">
+      <c r="B19" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="B15" s="9" t="s">
+    </row>
+    <row r="20" spans="1:2" ht="17">
+      <c r="A20" s="9" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
+      <c r="B20" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="B16" s="9" t="s">
+    </row>
+    <row r="21" spans="1:2" ht="17">
+      <c r="A21" s="9" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
+      <c r="B21" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="B17" s="9" t="s">
+    </row>
+    <row r="22" spans="1:2" ht="17">
+      <c r="A22" s="9" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
+      <c r="B22" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="B18" s="9" t="s">
+    </row>
+    <row r="23" spans="1:2" ht="17">
+      <c r="A23" s="9" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
+      <c r="B23" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B19" s="9" t="s">
+    </row>
+    <row r="24" spans="1:2" ht="17">
+      <c r="A24" s="9" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
+      <c r="B24" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="B20" s="9" t="s">
+    </row>
+    <row r="25" spans="1:2" ht="17">
+      <c r="A25" s="9" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="9" t="s">
+      <c r="B25" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B21" s="9" t="s">
+    </row>
+    <row r="26" spans="1:2" ht="17">
+      <c r="A26" s="9" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
+      <c r="B26" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="B22" s="9" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="17">
+      <c r="A27" s="9" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
+      <c r="B27" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="B23" s="9" t="s">
+    </row>
+    <row r="28" spans="1:2" ht="17">
+      <c r="A28" s="9" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
+      <c r="B28" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="B24" s="9" t="s">
+    </row>
+    <row r="29" spans="1:2" ht="17">
+      <c r="A29" s="9" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="9" t="s">
+      <c r="B29" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="B25" s="9" t="s">
+    </row>
+    <row r="30" spans="1:2" ht="17">
+      <c r="A30" s="9" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="9" t="s">
+      <c r="B30" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B26" s="9" t="s">
+    </row>
+    <row r="31" spans="1:2" ht="17">
+      <c r="A31" s="9" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="9" t="s">
+      <c r="B31" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="B27" s="9" t="s">
+    </row>
+    <row r="32" spans="1:2" ht="17">
+      <c r="A32" s="9" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
+      <c r="B32" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="B28" s="9" t="s">
+    </row>
+    <row r="33" spans="1:2" ht="17">
+      <c r="A33" s="9" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="9" t="s">
+      <c r="B33" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="B29" s="9" t="s">
+    </row>
+    <row r="34" spans="1:2" ht="17">
+      <c r="A34" s="9" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
+      <c r="B34" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="B30" s="9" t="s">
+    </row>
+    <row r="35" spans="1:2" ht="17">
+      <c r="A35" s="9" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A31" s="9" t="s">
+      <c r="B35" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B31" s="9" t="s">
+    </row>
+    <row r="36" spans="1:2" ht="17">
+      <c r="A36" s="9" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" s="9" t="s">
+      <c r="B36" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="B32" s="9" t="s">
+    </row>
+    <row r="37" spans="1:2" ht="17">
+      <c r="A37" s="9" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="9" t="s">
+      <c r="B37" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="B33" s="9" t="s">
+    </row>
+    <row r="38" spans="1:2" ht="17">
+      <c r="A38" s="9" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A34" s="9" t="s">
+      <c r="B38" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="B34" s="9" t="s">
+    </row>
+    <row r="39" spans="1:2" ht="17">
+      <c r="A39" s="9" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A35" s="9" t="s">
+      <c r="B39" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="B35" s="9" t="s">
+    </row>
+    <row r="40" spans="1:2" ht="17">
+      <c r="A40" s="9" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="9" t="s">
+      <c r="B40" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="B36" s="9" t="s">
+    </row>
+    <row r="41" spans="1:2" ht="17">
+      <c r="A41" s="9" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="9" t="s">
+      <c r="B41" s="9" t="s">
         <v>251</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A38" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A39" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A40" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A41" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -4913,48 +5250,48 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="29.6640625" customWidth="1"/>
     <col min="2" max="2" width="101.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B1" s="10"/>
     </row>
-    <row r="2" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="34" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="490" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFA6C2F2-D5FA-7545-ABDC-1616DF9C9343}"/>
+  <xr:revisionPtr revIDLastSave="491" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD9D9288-57A5-1A4B-8D83-EB3E56F01DC2}"/>
   <bookViews>
-    <workbookView xWindow="8660" yWindow="3140" windowWidth="29400" windowHeight="18480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8660" yWindow="3140" windowWidth="29400" windowHeight="18480" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -2316,7 +2316,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2393,6 +2393,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -2408,6 +2411,20 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -2693,20 +2710,6 @@
         <scheme val="none"/>
       </font>
       <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2808,7 +2811,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:N10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID période"/>
@@ -2831,29 +2834,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A1:T37" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="3"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3232,7 +3235,7 @@
       <c r="I5" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="28" t="s">
         <v>276</v>
       </c>
     </row>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="491" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD9D9288-57A5-1A4B-8D83-EB3E56F01DC2}"/>
+  <xr:revisionPtr revIDLastSave="501" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FC69069-5F36-5246-971E-6AB17094E0DE}"/>
   <bookViews>
-    <workbookView xWindow="8660" yWindow="3140" windowWidth="29400" windowHeight="18480" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14420" yWindow="4920" windowWidth="29400" windowHeight="18480" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="322">
   <si>
     <t>ID période</t>
   </si>
@@ -1384,74 +1384,6 @@
     <t xml:space="preserve">Automne Allemand (1977) : enlèvement de Schleyer, détournement du Landshut, morts à Stammheim. </t>
   </si>
   <si>
-    <t>Dans les mélodrames de RWF , les personnages tentent en vain de s'affranchir des positions aliénantes produites par la famille, le couple, au sein du système capitaliste et de la classe bourgeoise. Une analogie s'établit alors entre famille et Allemagne. Le mélodrame fassbindérien met en scène des crises identitaires du sujet, comme crises de la perception (du regard), qui se traduit par une mise en crise de l'image (image de soi et image du film). Les films font dialogue subjectivité et affects avec mécanismes sociaux, évitant ainsi toute lecture simplisite etfigées de type psychologisque ou idéologique. Le mélidrame en interpénétrant le privé et le public, l'individuel et le collectif, joue d'un trouble qui participe à son caractère critique et prgoressiste : il est potentiellement facteur de changement pour un spectateur constamment soumis à la réflexion.</t>
-  </si>
-  <si>
-    <t>De l'année zéro au miracle économique; Jalousie de Catharina Valente</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Despair, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">deuxième coproduction internationale de RWF avec Dirk Bogarde et Andra Ferreol, deux acteurs importants du cinéma moderne européen, en compétition à Cannes en 1978
-Le mariage de Maria Braun, en compétition officielle à Berlin en 1979
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'Année des treize lune</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">s poursuit la réflexion entamée   sur le désespoir. 
-L'épisode réalisé par RWF dans </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'Allemagne en automne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> offre une relecture des actions commises par la RAF sur le mode de l'autofiction.</t>
-    </r>
-  </si>
-  <si>
     <t>De l’année zéro au miracle économique|https://youtu.be/BC4BffkWyY8?si=e80MWCLF0K9Fgiub; Jalousie de Catharina Valente|https://youtu.be/-ugDTj7UFtU?si=vzGNySrsaYGKZW0k</t>
   </si>
   <si>
@@ -1637,9 +1569,6 @@
       </rPr>
       <t xml:space="preserve">remporte un succès majeur en Allemagne et dans le monde, ouvrant les portes des studios américains à RWF. Aux Etats-Unis le film est distribué par United Artists. Le film fait de RWF et de son actrice Hanna Schygulla des stars et Fassbinder, l'enfant terrible du cinéma allemand, le metteur en scène des marges, devient paradoxalement l'incarnation même de la RFA. Le rêve de RWF de réaliser un "film hollywoodien allemand" semble accompli. Le film ouvre aussi la trilogie RFA. </t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Jusqu'à quel point les femmes de la trlogie RFA sont elles une allégorie de la nation allemande ? Quelle distance RWF prend-il avec la critique historique de son pays ? </t>
   </si>
   <si>
     <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk grâce à Peer Raben .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international. Les films de RWF deviennent incontournables dans les grands festivals internationaux (Cannes, Venise, Berlin). </t>
@@ -1897,35 +1826,6 @@
     <t>Allemagne mère blafarde de Helma Sanders-Brahms.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"> Fondation du </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Filmverlag der Autoren</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).
-Plusieurs cinéastes allemands ( Schlöndorff, Herzog notamment) réalisent des charges politiques violentes contre la politique et la société allemande. Pour l'amnénsie historique se poursuit dans le cinéma allemand. 
-A parti de 1968 l'industrie du cinéma commercial allemand agonise</t>
-    </r>
-  </si>
-  <si>
-    <t>Le cinéma allemand s'empare de son histoire passée et récente et réfléchit aux problèmes de représentation qu'elle pose. Film collectif L'Allemagne en automne (1978). La diffusion de la série Holocaust (1979) à la télévision allemande suscite des débats importants, auxquels participent des cinéastes comme Syberberg ou Edgard Reitz. Le mouvement du Nouveau Cinéma allemand atteint son apogée thématique et politique.</t>
-  </si>
-  <si>
     <t>le cinéaste Edgar Reitz affirme la nécessité " de films, de livres, d'images qui nous fassent reprendre connaissance et rétablissent nos réflexes", Medium, 5/1979, p.21</t>
   </si>
   <si>
@@ -2016,31 +1916,6 @@
   </si>
   <si>
     <t>M. Klein de Joseph Losey</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">La parution du </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Deuil impossible</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> de Alexander et Margarete Mitscherlich fait scandale. A travers l'exposé des troubles psychosomatiques de certains patients, les psychanalystes Alexander et Margarete Mitscherlich y analysent  le refoulement collectif des souvenirs du IIIe Reich en Allemagne. Il doit exister, selon les auteurs, un lien de cause à effet entre une forme de conservatisme teinté et de provincialisme, qui règneen RFA, le refoulement dedu passé. L'ouvrage exercce une influence sur les artistes allemands de l'époque. 
-Une réflexion sur la mémoire et l'oubli qui n'a rien perdu de son actualité</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2124,6 +1999,208 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">qui décrit l'affaiblissement et la crise du système patriarcal dans les sociétés modernes d'après-guerre. La figure du père n'est plus un modèle absolu et le vide de son absence (d'abord concrète puisqu'il travaille mais aussi symbolique du fait du manque de figures crédibles ) entraine l'expression, plus ou moins anarchique et violente, des forces pulsionnelles négatives. celles-ci sont le fait d'une autorité sociale dont les contraintes paraissent de plus en plus absurdes et répressives puisqu'elles ne sont plus intégrées par l'identificaion à une figure individuelle affective. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La parution du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Deuil impossible</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de Alexander et Margarete Mitscherlich fait scandale. A travers l'exposé des troubles psychosomatiques de certains patients, les psychanalystes Alexander et Margarete Mitscherlich y analysent  le refoulement collectif des souvenirs du IIIe Reich en Allemagne. Il doit exister, selon les auteurs, un lien de cause à effet entre une forme de conservatisme teinté et de provincialisme, qui règnent RFA, le refoulement dedu passé. L'ouvrage exercce une influence sur les artistes allemands de l'époque. 
+Une réflexion sur la mémoire et l'oubli qui n'a rien perdu de son actualité</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Fondation du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Filmverlag der Autoren</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).
+Plusieurs cinéastes allemands ( Schlöndorff, Herzog notamment) réalisent des charges politiques violentes contre la politique et la société allemande. Pourtant l'amnnésie historique se poursuit dans le cinéma allemand. 
+A parti de 1968 l'industrie du cinéma commercial allemand agonise</t>
+    </r>
+  </si>
+  <si>
+    <t>Dans les mélodrames de RWF , les personnages tentent en vain de s'affranchir des positions aliénantes produites par la famille, le couple, au sein du système capitaliste et de la classe bourgeoise. Une analogie s'établit alors entre famille et Allemagne. Le mélodrame fassbindérien met en scène des crises identitaires du sujet, comme crises de la perception (du regard), qui se traduisent par une mise en crise de l'image (image de soi et image du film). Les films font dialoguer subjectivité et affects avec mécanismes sociaux, évitant ainsi toute lecture simpliste et figées de type psychologique ou idéologique. Le mélodrame, en interpénétrant le privé et le public, l'individuel et le collectif, joue d'un trouble qui participe à son caractère critique et progressiste : il est potentiellement facteur de changement pour un spectateur constamment soumis à la réflexion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jusqu'à quel point les femmes de la trilogie RFA sont-elles une allégorie de la nation allemande ? Quelle distance RWF prend-il avec la critique historique de son pays ? </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Automne Allemand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1977) : enlèvement de Schleyer, détournement du Landshut, morts à Stammheim. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le cinéma allemand s'empare de son histoire passée et récente et réfléchit aux problèmes de représentation qu'elle pose. Film collectif </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Allemagne en automne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1978). La diffusion de la série</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Holocaust</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1979) à la télévision allemande suscite des débats importants, auxquels participent des cinéastes comme Syberberg ou Edgard Reitz. Le mouvement du Nouveau Cinéma allemand atteint son apogée thématique et politique.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Despair, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">deuxième coproduction internationale de RWF avec Dirk Bogarde et Andra Ferreol, deux acteurs importants du cinéma moderne européen, en compétition à Cannes en 1978
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Le mariage de Maria Braun</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, en compétition officielle à Berlin en 1979
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Année des treize lune</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">s poursuit la réflexion entamée   sur le désespoir. 
+L'épisode réalisé par RWF dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Allemagne en automne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> offre une relecture des actions commises par la RAF sur le mode de l'autofiction.</t>
     </r>
   </si>
 </sst>
@@ -2411,20 +2488,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -2710,6 +2773,20 @@
         <scheme val="none"/>
       </font>
       <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2811,7 +2888,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="22">
   <autoFilter ref="A1:N10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID période"/>
@@ -2834,29 +2911,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:T37" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3126,7 +3203,7 @@
         <v/>
       </c>
       <c r="I2" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>20</v>
@@ -3149,13 +3226,13 @@
         <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>26</v>
@@ -3166,10 +3243,10 @@
         <v/>
       </c>
       <c r="I3" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>27</v>
@@ -3183,13 +3260,13 @@
         <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>31</v>
@@ -3205,7 +3282,7 @@
         <v>33</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="85" customHeight="1">
@@ -3216,7 +3293,7 @@
         <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>36</v>
@@ -3235,9 +3312,7 @@
       <c r="I5" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="K5" s="28" t="s">
-        <v>276</v>
-      </c>
+      <c r="K5" s="28"/>
     </row>
     <row r="6" spans="1:14" ht="303" customHeight="1">
       <c r="A6" s="1" t="s">
@@ -3247,16 +3322,16 @@
         <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>42</v>
@@ -3266,7 +3341,7 @@
         <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>275</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="70" customHeight="1">
@@ -3275,7 +3350,7 @@
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>44</v>
@@ -3293,7 +3368,7 @@
         <f>IF(G7="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="5" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3303,13 +3378,13 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>50</v>
@@ -3322,9 +3397,9 @@
         <v>film-1978-l-annee-des-treize-lunes; film-1979-le-mariage-de-maria-braun</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="N8" t="s">
+        <v>308</v>
+      </c>
+      <c r="N8" s="14" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3334,7 +3409,7 @@
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="15" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>54</v>
@@ -3359,7 +3434,7 @@
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>58</v>
@@ -3835,7 +3910,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D11" s="22" t="s">
         <v>107</v>
@@ -3914,7 +3989,7 @@
         <v>112</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>270</v>
@@ -4149,7 +4224,7 @@
         <v>127</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>128</v>
@@ -4253,7 +4328,7 @@
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>136</v>
@@ -4329,7 +4404,7 @@
         <v>137</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -4355,7 +4430,7 @@
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="1"/>
@@ -4389,7 +4464,7 @@
         <v>139</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>140</v>
@@ -4433,7 +4508,7 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -4460,7 +4535,7 @@
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="26" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="25" t="s">
@@ -4468,7 +4543,7 @@
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="15" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
@@ -4562,10 +4637,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="25" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -4595,10 +4670,10 @@
         <v>274</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="19"/>
@@ -4632,13 +4707,13 @@
       <c r="C33" s="1"/>
       <c r="D33" s="25"/>
       <c r="E33" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>277</v>
+        <v>321</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
@@ -4664,16 +4739,16 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>147</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
@@ -4701,13 +4776,13 @@
         <v>54</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>56</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>148</v>
@@ -4739,17 +4814,17 @@
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H36" s="15"/>
       <c r="I36" s="15"/>
       <c r="J36" s="15"/>
       <c r="K36" s="15"/>
       <c r="L36" s="15" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
@@ -4772,7 +4847,7 @@
         <v>150</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>60</v>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="501" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FC69069-5F36-5246-971E-6AB17094E0DE}"/>
+  <xr:revisionPtr revIDLastSave="523" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C86F494E-31FA-0D4E-B239-90CFD7BB3603}"/>
   <bookViews>
-    <workbookView xWindow="14420" yWindow="4920" windowWidth="29400" windowHeight="18480" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="322">
   <si>
     <t>ID période</t>
   </si>
@@ -1187,9 +1187,6 @@
     <t>Le Mariage de Maria Braun</t>
   </si>
   <si>
-    <t>film-1979-le-mariage-de-maria-braun</t>
-  </si>
-  <si>
     <t>La Troisième génération</t>
   </si>
   <si>
@@ -2202,6 +2199,9 @@
       </rPr>
       <t xml:space="preserve"> offre une relecture des actions commises par la RAF sur le mode de l'autofiction.</t>
     </r>
+  </si>
+  <si>
+    <t>film-1978-le-mariage-de-maria-braun</t>
   </si>
 </sst>
 </file>
@@ -2330,7 +2330,7 @@
       <name val="-webkit-standard"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2367,6 +2367,12 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2393,7 +2399,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2473,6 +2479,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -2488,6 +2497,20 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -2773,20 +2796,6 @@
         <scheme val="none"/>
       </font>
       <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2888,7 +2897,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:N10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID période"/>
@@ -2911,29 +2920,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A1:T37" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="3"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3203,7 +3212,7 @@
         <v/>
       </c>
       <c r="I2" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>20</v>
@@ -3226,13 +3235,13 @@
         <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>26</v>
@@ -3243,10 +3252,10 @@
         <v/>
       </c>
       <c r="I3" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>27</v>
@@ -3260,13 +3269,13 @@
         <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>31</v>
@@ -3282,7 +3291,7 @@
         <v>33</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="85" customHeight="1">
@@ -3293,7 +3302,7 @@
         <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>36</v>
@@ -3303,14 +3312,14 @@
         <v>38</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>IF(G5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3322,16 +3331,16 @@
         <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>42</v>
@@ -3341,7 +3350,7 @@
         <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="70" customHeight="1">
@@ -3350,7 +3359,7 @@
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>44</v>
@@ -3378,13 +3387,13 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>50</v>
@@ -3394,10 +3403,10 @@
       </c>
       <c r="H8" s="4" t="str">
         <f>IF(G8="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1978-l-annee-des-treize-lunes; film-1979-le-mariage-de-maria-braun</v>
+        <v>film-1978-l-annee-des-treize-lunes; film-1978-le-mariage-de-maria-braun</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N8" s="14" t="s">
         <v>52</v>
@@ -3409,7 +3418,7 @@
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>54</v>
@@ -3434,7 +3443,7 @@
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>58</v>
@@ -3544,7 +3553,7 @@
       <c r="T1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="29" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3910,7 +3919,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D11" s="22" t="s">
         <v>107</v>
@@ -3989,10 +3998,10 @@
         <v>112</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="19"/>
@@ -4053,7 +4062,10 @@
       <c r="R14" s="19"/>
       <c r="S14" s="19"/>
       <c r="T14" s="19"/>
-      <c r="U14" s="2"/>
+      <c r="U14" s="2" t="str">
+        <f>IF(F14="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" spans="1:21" ht="126">
       <c r="A15" s="1">
@@ -4069,7 +4081,7 @@
         <v>117</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="19" t="s">
@@ -4224,7 +4236,7 @@
         <v>127</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>128</v>
@@ -4254,7 +4266,10 @@
       <c r="R19" s="19"/>
       <c r="S19" s="19"/>
       <c r="T19" s="19"/>
-      <c r="U19" s="2"/>
+      <c r="U19" s="2" t="str">
+        <f>IF(F19="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" spans="1:21" ht="28">
       <c r="A20" s="1">
@@ -4281,7 +4296,10 @@
       <c r="R20" s="19"/>
       <c r="S20" s="19"/>
       <c r="T20" s="19"/>
-      <c r="U20" s="2"/>
+      <c r="U20" s="2" t="str">
+        <f>IF(F20="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" spans="1:21" ht="112">
       <c r="A21" s="1">
@@ -4294,7 +4312,7 @@
         <v>135</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
@@ -4328,7 +4346,7 @@
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>136</v>
@@ -4370,10 +4388,10 @@
         <v>38</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G23" s="24" t="s">
         <v>263</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>264</v>
       </c>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
@@ -4404,7 +4422,7 @@
         <v>137</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -4422,7 +4440,10 @@
       <c r="R24" s="19"/>
       <c r="S24" s="19"/>
       <c r="T24" s="19"/>
-      <c r="U24" s="2"/>
+      <c r="U24" s="2" t="str">
+        <f>IF(F24="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" spans="1:21" ht="42">
       <c r="A25" s="1">
@@ -4430,7 +4451,7 @@
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="1"/>
@@ -4451,7 +4472,10 @@
       <c r="R25" s="19"/>
       <c r="S25" s="19"/>
       <c r="T25" s="19"/>
-      <c r="U25" s="2"/>
+      <c r="U25" s="2" t="str">
+        <f>IF(F25="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1971-whity; film-1971-prenez-garde-a-la-sainte-putain</v>
+      </c>
     </row>
     <row r="26" spans="1:21" ht="196">
       <c r="A26" s="1">
@@ -4464,23 +4488,23 @@
         <v>139</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>140</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="15"/>
       <c r="K26" s="19"/>
       <c r="L26" s="19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>141</v>
@@ -4508,7 +4532,7 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -4526,7 +4550,10 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="15"/>
-      <c r="U27" s="2"/>
+      <c r="U27" s="2" t="str">
+        <f>IF(F27="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" spans="1:21" ht="84">
       <c r="A28" s="1">
@@ -4535,7 +4562,7 @@
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="26" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="25" t="s">
@@ -4543,7 +4570,7 @@
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
@@ -4557,7 +4584,10 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="15"/>
-      <c r="U28" s="2"/>
+      <c r="U28" s="2" t="str">
+        <f>IF(F28="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1973-le-monde-sur-un-fil</v>
+      </c>
     </row>
     <row r="29" spans="1:21" ht="56">
       <c r="A29" s="1">
@@ -4568,10 +4598,10 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="25" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
@@ -4586,7 +4616,10 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="15"/>
-      <c r="U29" s="2"/>
+      <c r="U29" s="2" t="str">
+        <f>IF(F29="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1974-effi-briest; film-1974-martha</v>
+      </c>
     </row>
     <row r="30" spans="1:21" ht="238">
       <c r="A30" s="1">
@@ -4608,7 +4641,7 @@
         <v>47</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
@@ -4637,10 +4670,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="25" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -4657,7 +4690,10 @@
       <c r="R31" s="15"/>
       <c r="S31" s="15"/>
       <c r="T31" s="15"/>
-      <c r="U31" s="2"/>
+      <c r="U31" s="2" t="str">
+        <f>IF(F31="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" spans="1:21" ht="252">
       <c r="A32" s="1">
@@ -4667,13 +4703,13 @@
         <v>49</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="19"/>
@@ -4695,7 +4731,7 @@
       <c r="S32" s="19"/>
       <c r="T32" s="19"/>
       <c r="U32" s="2" t="str">
-        <f>IF(E32="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(E32,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <f>IF(F32="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
     </row>
@@ -4703,17 +4739,19 @@
       <c r="A33" s="1">
         <v>1978</v>
       </c>
-      <c r="B33" s="1"/>
+      <c r="B33" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="C33" s="1"/>
       <c r="D33" s="25"/>
       <c r="E33" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
@@ -4730,25 +4768,30 @@
       <c r="R33" s="19"/>
       <c r="S33" s="19"/>
       <c r="T33" s="19"/>
-      <c r="U33" s="2"/>
+      <c r="U33" s="2" t="str">
+        <f>IF(F33="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F33,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1978-l-allemagne-en-automne; film-1978-despair; film-1978-l-annee-des-treize-lunes; film-1978-le-mariage-de-maria-braun</v>
+      </c>
     </row>
     <row r="34" spans="1:21" ht="210">
       <c r="A34" s="1">
         <v>1979</v>
       </c>
-      <c r="B34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>147</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
@@ -4763,7 +4806,10 @@
       <c r="R34" s="19"/>
       <c r="S34" s="19"/>
       <c r="T34" s="19"/>
-      <c r="U34" s="2"/>
+      <c r="U34" s="2" t="str">
+        <f>IF(F34="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F34,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1978-le-mariage-de-maria-braun; film-1979-la-troisieme-generation</v>
+      </c>
     </row>
     <row r="35" spans="1:21" ht="293">
       <c r="A35" s="1">
@@ -4776,13 +4822,13 @@
         <v>54</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>56</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>148</v>
@@ -4808,23 +4854,27 @@
       </c>
     </row>
     <row r="36" spans="1:21" ht="182">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
+      <c r="A36" s="1">
+        <v>1981</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="H36" s="15"/>
       <c r="I36" s="15"/>
       <c r="J36" s="15"/>
       <c r="K36" s="15"/>
       <c r="L36" s="15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
@@ -4834,7 +4884,10 @@
       <c r="R36" s="15"/>
       <c r="S36" s="15"/>
       <c r="T36" s="15"/>
-      <c r="U36" s="2"/>
+      <c r="U36" s="2" t="str">
+        <f>IF(F36="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1981-lili-marleen; film-1981-lola-une-femme-allemande</v>
+      </c>
     </row>
     <row r="37" spans="1:21" ht="126">
       <c r="A37" s="1">
@@ -4847,7 +4900,7 @@
         <v>150</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>60</v>
@@ -5257,63 +5310,63 @@
         <v>236</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>237</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17">
       <c r="A35" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17">
       <c r="A36" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17">
       <c r="A37" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17">
       <c r="A38" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>244</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17">
       <c r="A39" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17">
       <c r="A40" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B40" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17">
       <c r="A41" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>250</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -5336,40 +5389,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:2" ht="34" customHeight="1">
       <c r="A2" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>253</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>257</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>259</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="523" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C86F494E-31FA-0D4E-B239-90CFD7BB3603}"/>
+  <xr:revisionPtr revIDLastSave="557" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82C6A24F-50B3-FE44-8D2C-A07A2E9F1D20}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="326">
   <si>
     <t>ID période</t>
   </si>
@@ -229,9 +229,6 @@
   </si>
   <si>
     <t>Fondation des Verts (1980). Manifestations écologistes. Fin de l'ère sociale-libérale.</t>
-  </si>
-  <si>
-    <t>Production de séries monumentales pour la télévision. Le Nouveau Cinéma Allemand atteint une maturité formelle extrême.</t>
   </si>
   <si>
     <t>Travaille frénétiquement. Réalise son projet de vie : l'adaptation de Döblin. Épuisement physique dû aux excès.</t>
@@ -1384,79 +1381,6 @@
     <t>De l’année zéro au miracle économique|https://youtu.be/BC4BffkWyY8?si=e80MWCLF0K9Fgiub; Jalousie de Catharina Valente|https://youtu.be/-ugDTj7UFtU?si=vzGNySrsaYGKZW0k</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">"Despair est le film le plus rempli d'espoirt que j'ai jamais fait " RWF, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'anarchie de l'imaginaire</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>p.80-81</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Le film constitue un nouveau tournant dans la carrière de RWF en l'intégrant au club fermé des auteurs importants du cinéma européen même si son écho critique reste mitigé. Mais RWF présente aussi à Cannes, en projection non officielle </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le mariage de Maria Braun. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ce film exclipse </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Despair</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Fondation du Filmverlag der Autoren (1971), une société indépendante, par quelques cinéastes dont RWF. La société est d'abord autogérée.
 Accords Film-Télévision (1974) favorisant les coproductions (WDR).</t>
   </si>
@@ -1464,10 +1388,6 @@
     <t xml:space="preserve">RFW devient actionnaire du Filmverlag der Autoren. </t>
   </si>
   <si>
-    <t>RWF projette d'adapter le roman de Freytag Soll und Haben (1855), œuvre notaoirement antismétique en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. 
-RWF quitte le Filmverlag der Autoren</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Suicide d'Armin Meier (31 mai 1978). Début de la collaboration avec Juliane Lorenz. </t>
     </r>
@@ -1522,50 +1442,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Le succès de Maria Braun amène RWF à espérer pour voir réaslier </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cocaïne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, l'adaptation d'un roman de Pitigrilli. Il lui permet aussi de renégocier à la hausse le budget de production de Berlin Alexander Platz : le projet devient le le plus couteux de l'histoire de la télévision allemande. </t>
-    </r>
-  </si>
-  <si>
     <t>RWF parvient à évincer Werner Schroeter qui souhaitait réaliser une adaptation de Querelle de Jean Genet.  Mort de Fassbinder marquant symboliquement la fin du Nouveau Cinéma Allemand.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le mariage de Maria Braun </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">remporte un succès majeur en Allemagne et dans le monde, ouvrant les portes des studios américains à RWF. Aux Etats-Unis le film est distribué par United Artists. Le film fait de RWF et de son actrice Hanna Schygulla des stars et Fassbinder, l'enfant terrible du cinéma allemand, le metteur en scène des marges, devient paradoxalement l'incarnation même de la RFA. Le rêve de RWF de réaliser un "film hollywoodien allemand" semble accompli. Le film ouvre aussi la trilogie RFA. </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk grâce à Peer Raben .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international. Les films de RWF deviennent incontournables dans les grands festivals internationaux (Cannes, Venise, Berlin). </t>
@@ -1579,9 +1456,6 @@
     <t xml:space="preserve">Monumental Berlin Alexanderplatz (1980, 15h). </t>
   </si>
   <si>
-    <t>Suite de la Trilogie de la RFA : Lola, une femme allemande (1981) et Lili Marleen (1981).</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <i/>
@@ -1638,9 +1512,6 @@
   </si>
   <si>
     <t>Quelles ambitions pour la série télévisuelle ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RWF, figure du collectif  politique des années 60 et 70 ou dhéritier de la figure du génie romantique et du poète maudit ? Auteur ou cinéaste populaire ? </t>
   </si>
   <si>
     <t>Création de la RFA (1949). Ère Adenauer. Miracle économique ( Wirtschaftswunder )  entre 1950 et 1965 l'économie ouest-allemande croît de 8,2% en moyenne (contre 5% en France pendant les 30 glorieuses). La coccinelle de Wolkswagen devient l'emblème du "miracle économique". Les entreprise de taille moyenne constituent la colonne vertébrale de la puissance économique allemande en fournissant les outils spécialisés nécessaires à l'industrie. 
@@ -1811,40 +1682,7 @@
 Il n'existe presque aucun film allemand des années 50 et 60 qui traite des camps de concentration nazis. Le cinéma allemand de la période s'intéresse peu à l'histoire. </t>
   </si>
   <si>
-    <t>Le tambour de Volker Schlondorff obtient la palme d'or à Cannes. 
-Diffusion de la série Holocaust (1979).</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Le mouvement atteint son apogée thématique et politique.
-Hitler, un film d'Allemagne de Syberberg
-</t>
-  </si>
-  <si>
-    <t>Allemagne mère blafarde de Helma Sanders-Brahms.</t>
-  </si>
-  <si>
     <t>le cinéaste Edgar Reitz affirme la nécessité " de films, de livres, d'images qui nous fassent reprendre connaissance et rétablissent nos réflexes", Medium, 5/1979, p.21</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Les damnés</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, mélodrame de Visconti, travaille à interroger le régime nazi et sla manière dont l'imagerie nazie, qui érotise de manière spectaculaire le pouvoir, contamine moralment les esprits. L'éloignement du néoréalisme est maximal.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2024,32 +1862,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"> Fondation du </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Filmverlag der Autoren</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).
-Plusieurs cinéastes allemands ( Schlöndorff, Herzog notamment) réalisent des charges politiques violentes contre la politique et la société allemande. Pourtant l'amnnésie historique se poursuit dans le cinéma allemand. 
-A parti de 1968 l'industrie du cinéma commercial allemand agonise</t>
-    </r>
-  </si>
-  <si>
     <t>Dans les mélodrames de RWF , les personnages tentent en vain de s'affranchir des positions aliénantes produites par la famille, le couple, au sein du système capitaliste et de la classe bourgeoise. Une analogie s'établit alors entre famille et Allemagne. Le mélodrame fassbindérien met en scène des crises identitaires du sujet, comme crises de la perception (du regard), qui se traduisent par une mise en crise de l'image (image de soi et image du film). Les films font dialoguer subjectivité et affects avec mécanismes sociaux, évitant ainsi toute lecture simpliste et figées de type psychologique ou idéologique. Le mélodrame, en interpénétrant le privé et le public, l'individuel et le collectif, joue d'un trouble qui participe à son caractère critique et progressiste : il est potentiellement facteur de changement pour un spectateur constamment soumis à la réflexion.</t>
   </si>
   <si>
@@ -2074,49 +1886,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> (1977) : enlèvement de Schleyer, détournement du Landshut, morts à Stammheim. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Le cinéma allemand s'empare de son histoire passée et récente et réfléchit aux problèmes de représentation qu'elle pose. Film collectif </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'Allemagne en automne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (1978). La diffusion de la série</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Holocaust</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (1979) à la télévision allemande suscite des débats importants, auxquels participent des cinéastes comme Syberberg ou Edgard Reitz. Le mouvement du Nouveau Cinéma allemand atteint son apogée thématique et politique.</t>
     </r>
   </si>
   <si>
@@ -2202,6 +1971,453 @@
   </si>
   <si>
     <t>film-1978-le-mariage-de-maria-braun</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le succès de Maria Braun amène RWF à espérer pour voir réaliser </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cocaïne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, l'adaptation d'un roman de Pitigrilli. Il lui permet aussi de renégocier à la hausse le budget de production de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Berlin Alexanderplatz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> : le projet devient le le plus coûteux de l'histoire de la télévision allemande. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Les damnés</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, mélodrame de Visconti, travaille à interroger le régime nazi et sla manière dont l'imagerie nazie, qui érotise de manière spectaculaire le pouvoir, contamine moralement les esprits. L'éloignement du néoréalisme est maximal.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Fondation du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Filmverlag der Autoren</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).
+Plusieurs cinéastes allemands ( Schlöndorff, Herzog notamment) réalisent des charges politiques violentes contre la politique et la société allemande. Pourtant l'amnnésie historique se poursuit dans le cinéma allemand de fiction. Seuls des documentaires s'emparent de l'histoire du nazisme.
+A parti de 1968 l'industrie du cinéma commercial allemand agonise</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RWF, figure du collectif  politique des années 60 et 70 ou d'héritier de la figure du génie romantique et du poète maudit ? Auteur ou cinéaste populaire ? </t>
+  </si>
+  <si>
+    <t>Le retour de l'histoire</t>
+  </si>
+  <si>
+    <t>La fin d'un ère</t>
+  </si>
+  <si>
+    <t>La mort du Maître</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">RWF projette d'adapter le roman de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Freytag Soll und Haben</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1855), œuvre notaoirement antismétique en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. 
+RWF quitte le Filmverlag der Autoren</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le mariage de Maria Braun </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">remporte un succès majeur en Allemagne et dans le monde, ouvrant les portes des studios américains à RWF. Aux Etats-Unis le film est distribué par United Artists. Le film fait de RWF et de son actrice Hanna Schygulla des stars et Fassbinder, l'enfant terrible du cinéma allemand, le metteur en scène des marges, devient paradoxalement l'incarnation même de la RFA. Le rêve de RWF de réaliser un "film hollywoodien allemand" semble accompli. Le film ouvre aussi la trilogie RFA. 
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Despair est le film le plus rempli d'espoir que j'ai jamais fait " RWF, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'anarchie de l'imaginaire</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>p.80-81</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Le film constitue un nouveau tournant dans la carrière de RWF en l'intégrant au club fermé des auteurs importants du cinéma européen même si son écho critique reste mitigé. Mais RWF présente aussi à Cannes, en projection non officielle </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le mariage de Maria Braun. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ce film exclipse </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Despair.
+L'allemagne en automne n'est vu que par un public limité. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Allemagne mère blafarde </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>de Helma Sanders-Brahms. 
+Début du tournage d'</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Heima</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de Karl Reitz qui sera diffusé en 1984</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Le mouvement atteint son apogée thématique et politique.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hitler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, un film d'Allemagne de Syberberg interroge le nazisme à travers son usage des médias (radio et cinéma) et sa mise en spectacle du politique. Le show business moderne en dévoile sa dimension fasciste. 
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Maman Küsters s'en va au ciel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1975). </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Le Droit du plus fort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1975) : </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le tambour de Volker Schlondorff obtient la palme d'or à Cannes. 
+La diffusion de la série américaine  </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Holocaust</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de Marvin J. Chomsky (1976) touche le grand public qui découvre l'ampleur des crimes commis et déclenche de vifs débatà travers le parcours de deux familles : comment l'histoire du pays peut-elle toucher le grand public à travers une production américaine et non allemande ? Si la série ouvre les vannes de la mémoire, Certains lui reprochent son sentimentalisme de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>soap opera.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le cinéma allemand s'empare de son histoire passée et récente et réfléchit aux problèmes de représentation qu'elle pose. Film collectif </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Allemagne en automne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1978). La diffusion de la série</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Holocaust</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de Marvin J. Chomsky (1979) à la télévision allemande suscite des débats importants, auxquels participent des cinéastes comme Syberberg ou Edgard Reitz. Le mouvement du Nouveau Cinéma allemand atteint son apogée thématique et politique.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hanna Schygulla doit interpréter </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lola une femme allemande</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, mais Fassbinder lui retire le rôle furieux que l'actrice ait déclaré qu'elle s'était elle-même distribuée dans le film.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Suite de la Trilogie de la RFA :  </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lili Marleen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1981) et Lola, une femme allemande (1981)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3212,7 +3428,7 @@
         <v/>
       </c>
       <c r="I2" s="1" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>20</v>
@@ -3235,13 +3451,13 @@
         <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>26</v>
@@ -3252,10 +3468,10 @@
         <v/>
       </c>
       <c r="I3" s="1" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>27</v>
@@ -3269,13 +3485,13 @@
         <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>31</v>
@@ -3291,7 +3507,7 @@
         <v>33</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="85" customHeight="1">
@@ -3302,7 +3518,7 @@
         <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>36</v>
@@ -3312,14 +3528,14 @@
         <v>38</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>IF(G5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3331,16 +3547,16 @@
         <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>42</v>
@@ -3350,7 +3566,7 @@
         <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="70" customHeight="1">
@@ -3359,7 +3575,7 @@
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>44</v>
@@ -3385,15 +3601,17 @@
       <c r="A8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="C8" s="1" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>50</v>
@@ -3405,8 +3623,9 @@
         <f>IF(G8="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1978-l-annee-des-treize-lunes; film-1978-le-mariage-de-maria-braun</v>
       </c>
+      <c r="I8" s="15"/>
       <c r="K8" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="N8" s="14" t="s">
         <v>52</v>
@@ -3416,21 +3635,20 @@
       <c r="A9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="C9" s="15" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="H9" s="4" t="str">
         <f>IF(G9="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -3438,24 +3656,26 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="70" customHeight="1">
-      <c r="A10" s="1">
+      <c r="A10" s="24">
         <v>1982</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="C10" s="1" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="H10" s="4" t="str">
         <f>IF(G10="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -3494,7 +3714,7 @@
   <sheetData>
     <row r="1" spans="1:21" s="12" customFormat="1" ht="28" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -3512,49 +3732,49 @@
         <v>6</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="I1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>10</v>
       </c>
       <c r="M1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="S1" s="8" t="s">
         <v>13</v>
       </c>
       <c r="T1" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="U1" s="29" t="s">
         <v>73</v>
-      </c>
-      <c r="U1" s="29" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="98">
@@ -3565,13 +3785,13 @@
         <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -3603,18 +3823,18 @@
         <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="F3" s="19"/>
       <c r="G3" s="1"/>
       <c r="H3" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I3" s="20"/>
       <c r="J3" s="20"/>
@@ -3641,10 +3861,10 @@
         <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="19"/>
@@ -3662,7 +3882,7 @@
       <c r="R4" s="19"/>
       <c r="S4" s="19"/>
       <c r="T4" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U4" s="2" t="str">
         <f>IF(F4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -3677,25 +3897,25 @@
         <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>86</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="19"/>
       <c r="G5" s="1"/>
       <c r="H5" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="K5" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="19"/>
@@ -3719,16 +3939,16 @@
         <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>91</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>92</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="19"/>
       <c r="G6" s="1"/>
       <c r="H6" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I6" s="20"/>
       <c r="J6" s="20"/>
@@ -3738,7 +3958,7 @@
         <v>22</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O6" s="19"/>
       <c r="P6" s="19"/>
@@ -3761,7 +3981,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F7" s="19"/>
       <c r="G7" s="1"/>
@@ -3774,13 +3994,13 @@
         <v>22</v>
       </c>
       <c r="N7" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O7" s="19"/>
       <c r="P7" s="19"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S7" s="19"/>
       <c r="T7" s="19"/>
@@ -3797,11 +4017,11 @@
         <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="19"/>
@@ -3814,7 +4034,7 @@
         <v>22</v>
       </c>
       <c r="N8" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O8" s="19"/>
       <c r="P8" s="19"/>
@@ -3835,13 +4055,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="19"/>
@@ -3851,16 +4071,16 @@
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="O9" s="19" t="s">
         <v>22</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
@@ -3879,16 +4099,16 @@
         <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="19"/>
       <c r="H10" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
@@ -3898,7 +4118,7 @@
         <v>22</v>
       </c>
       <c r="N10" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O10" s="19"/>
       <c r="P10" s="19"/>
@@ -3919,32 +4139,32 @@
         <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="19"/>
       <c r="H11" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="N11" s="19" t="s">
         <v>109</v>
-      </c>
-      <c r="N11" s="19" t="s">
-        <v>110</v>
       </c>
       <c r="O11" s="19" t="s">
         <v>22</v>
       </c>
       <c r="P11" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
@@ -3965,7 +4185,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="19"/>
@@ -3995,18 +4215,18 @@
         <v>24</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="19"/>
       <c r="H13" s="23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I13" s="19"/>
       <c r="J13" s="19"/>
@@ -4016,7 +4236,7 @@
         <v>22</v>
       </c>
       <c r="N13" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O13" s="19"/>
       <c r="P13" s="19"/>
@@ -4037,10 +4257,10 @@
         <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -4054,7 +4274,7 @@
         <v>22</v>
       </c>
       <c r="N14" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O14" s="19"/>
       <c r="P14" s="19"/>
@@ -4075,17 +4295,17 @@
         <v>24</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="E15" s="21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
@@ -4096,7 +4316,7 @@
         <v>22</v>
       </c>
       <c r="N15" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O15" s="19"/>
       <c r="P15" s="19"/>
@@ -4117,13 +4337,13 @@
         <v>24</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="19"/>
@@ -4136,7 +4356,7 @@
         <v>22</v>
       </c>
       <c r="N16" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O16" s="19"/>
       <c r="P16" s="19"/>
@@ -4157,11 +4377,11 @@
         <v>28</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
@@ -4174,7 +4394,7 @@
         <v>22</v>
       </c>
       <c r="N17" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O17" s="19"/>
       <c r="P17" s="19"/>
@@ -4195,10 +4415,10 @@
         <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -4208,13 +4428,13 @@
       <c r="J18" s="19"/>
       <c r="K18" s="19"/>
       <c r="L18" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M18" s="19" t="s">
         <v>22</v>
       </c>
       <c r="N18" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O18" s="19"/>
       <c r="P18" s="19"/>
@@ -4233,32 +4453,32 @@
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="19"/>
       <c r="H19" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="I19" s="23" t="s">
+      <c r="J19" s="19" t="s">
         <v>130</v>
-      </c>
-      <c r="J19" s="19" t="s">
-        <v>131</v>
       </c>
       <c r="K19" s="19"/>
       <c r="L19" s="19"/>
       <c r="M19" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="N19" s="19" t="s">
         <v>132</v>
-      </c>
-      <c r="N19" s="19" t="s">
-        <v>133</v>
       </c>
       <c r="O19" s="19"/>
       <c r="P19" s="19"/>
@@ -4279,7 +4499,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="19"/>
@@ -4309,10 +4529,10 @@
         <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
@@ -4346,10 +4566,10 @@
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="19"/>
@@ -4388,10 +4608,10 @@
         <v>38</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G23" s="24" t="s">
         <v>262</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>263</v>
       </c>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
@@ -4419,10 +4639,10 @@
         <v>34</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -4451,12 +4671,12 @@
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G25" s="24"/>
       <c r="H25" s="19"/>
@@ -4485,32 +4705,32 @@
         <v>39</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="15"/>
       <c r="K26" s="19"/>
       <c r="L26" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N26" s="21" t="s">
         <v>141</v>
-      </c>
-      <c r="N26" s="21" t="s">
-        <v>142</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -4532,7 +4752,7 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -4562,15 +4782,15 @@
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="26" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="15" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
@@ -4598,10 +4818,10 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="25" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
@@ -4638,10 +4858,10 @@
         <v>46</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>47</v>
+        <v>321</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
@@ -4670,10 +4890,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="25" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -4703,13 +4923,13 @@
         <v>49</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>278</v>
+        <v>316</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="19"/>
@@ -4717,10 +4937,10 @@
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
       <c r="K32" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="L32" s="19" t="s">
         <v>144</v>
-      </c>
-      <c r="L32" s="19" t="s">
-        <v>145</v>
       </c>
       <c r="M32" s="19"/>
       <c r="N32" s="19"/>
@@ -4745,20 +4965,20 @@
       <c r="C33" s="1"/>
       <c r="D33" s="25"/>
       <c r="E33" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
       <c r="L33" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M33" s="19"/>
       <c r="N33" s="19"/>
@@ -4773,7 +4993,7 @@
         <v>film-1978-l-allemagne-en-automne; film-1978-despair; film-1978-l-annee-des-treize-lunes; film-1978-le-mariage-de-maria-braun</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="210">
+    <row r="34" spans="1:21" ht="224">
       <c r="A34" s="1">
         <v>1979</v>
       </c>
@@ -4782,16 +5002,16 @@
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
@@ -4822,23 +5042,23 @@
         <v>54</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
       <c r="L35" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M35" s="19"/>
       <c r="N35" s="19"/>
@@ -4861,20 +5081,22 @@
         <v>53</v>
       </c>
       <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
+      <c r="D36" s="15" t="s">
+        <v>324</v>
+      </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>286</v>
+        <v>325</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="H36" s="15"/>
       <c r="I36" s="15"/>
       <c r="J36" s="15"/>
       <c r="K36" s="15"/>
       <c r="L36" s="15" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
@@ -4897,16 +5119,16 @@
         <v>1982</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
@@ -4914,7 +5136,7 @@
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
       <c r="L37" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M37" s="19"/>
       <c r="N37" s="19"/>
@@ -4961,70 +5183,70 @@
   <sheetData>
     <row r="15" spans="1:4">
       <c r="A15" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="C15" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="D15" s="16" t="s">
         <v>154</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="51">
       <c r="A16" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="C16" s="17" t="s">
         <v>157</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>158</v>
       </c>
       <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:4" ht="51">
       <c r="A17" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="C17" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="D17" s="17" t="s">
         <v>161</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28">
       <c r="A18" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C18" s="17" t="s">
-        <v>165</v>
-      </c>
       <c r="D18" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28">
       <c r="A19" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="D19" s="17" t="s">
         <v>168</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -5043,330 +5265,330 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17">
       <c r="A1" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>170</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17">
       <c r="A2" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17">
       <c r="A3" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17">
       <c r="A4" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>176</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17">
       <c r="A5" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>178</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17">
       <c r="A6" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17">
       <c r="A7" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17">
       <c r="A8" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17">
       <c r="A9" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>186</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17">
       <c r="A10" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17">
       <c r="A11" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17">
       <c r="A12" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>192</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17">
       <c r="A13" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>194</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17">
       <c r="A14" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17">
       <c r="A15" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17">
       <c r="A16" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17">
       <c r="A17" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17">
       <c r="A18" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17">
       <c r="A19" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17">
       <c r="A20" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17">
       <c r="A21" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17">
       <c r="A22" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17">
       <c r="A23" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17">
       <c r="A24" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>216</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17">
       <c r="A25" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>218</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17">
       <c r="A26" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>220</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17">
       <c r="A27" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17">
       <c r="A28" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>224</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17">
       <c r="A29" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17">
       <c r="A30" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>228</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17">
       <c r="A31" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17">
       <c r="A32" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17">
       <c r="A33" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17">
       <c r="A34" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17">
       <c r="A35" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17">
       <c r="A36" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17">
       <c r="A37" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17">
       <c r="A38" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>243</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17">
       <c r="A39" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17">
       <c r="A40" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B40" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17">
       <c r="A41" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>249</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -5389,40 +5611,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:2" ht="34" customHeight="1">
       <c r="A2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>252</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>256</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>258</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="557" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82C6A24F-50B3-FE44-8D2C-A07A2E9F1D20}"/>
+  <xr:revisionPtr revIDLastSave="629" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9D4352E-5F5D-F34B-8A2F-EC6695115120}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14680" yWindow="600" windowWidth="22800" windowHeight="24600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="332">
   <si>
     <t>ID période</t>
   </si>
@@ -657,37 +657,6 @@
     <t xml:space="preserve">Une majorité sociale-libérale place Willy Brandt au pouvoir. </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Whity</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Prenez garde à la sainte putain</t>
-    </r>
-  </si>
-  <si>
     <t>Terrorisme de la RAF (arrestations en 1972). Attentat des JO de Munich (1972). Démission de Willy Brandt (1974) suite à l'affaire Guillaume. Un virage conservateur s'opère.</t>
   </si>
   <si>
@@ -709,20 +678,6 @@
         <family val="2"/>
       </rPr>
       <t>Mariage de Maria Braun</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Le monde sur un fil (1973)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, adaption libre d'un récit de science-fiction interroge la notion même de réalité. </t>
     </r>
   </si>
   <si>
@@ -1251,36 +1206,6 @@
   </si>
   <si>
     <t>Lorsqu’une nouvelle fiche Film est créée, ajouter son titre et son ID dans Référentiel films.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk . Période Sirkienne : Le Marchand des quatre saisons (1971). </t>
-  </si>
-  <si>
-    <t>Effi Briest, Martha</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">L'amour est plus froid que la mort (1969),  </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le Bouc </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(1969, succès à Mannheim) : critique de la xénophobie et de l'apathie bourgeoise.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Premier film accueili froidement à Berlin. Le second,une critique de la xénophobie et de l'apathie bourgeoise,  remporte 5 distinctions cinématographiques en Allemagne. Le coût de production de 80000 marks est largement couvert : avec 650000 malrs de prix et 200000 marks de subventions a posteri, le film assure à RWF de quoi poursuivre son travail pour quelques années. </t>
@@ -1375,9 +1300,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Automne Allemand (1977) : enlèvement de Schleyer, détournement du Landshut, morts à Stammheim. </t>
-  </si>
-  <si>
     <t>De l’année zéro au miracle économique|https://youtu.be/BC4BffkWyY8?si=e80MWCLF0K9Fgiub; Jalousie de Catharina Valente|https://youtu.be/-ugDTj7UFtU?si=vzGNySrsaYGKZW0k</t>
   </si>
   <si>
@@ -1453,9 +1375,6 @@
 Les premiers travailleurs immigrés commencent à arriver de Grèce et d'Italie pour soutenir le "miracle économique". </t>
   </si>
   <si>
-    <t xml:space="preserve">Monumental Berlin Alexanderplatz (1980, 15h). </t>
-  </si>
-  <si>
     <r>
       <rPr>
         <i/>
@@ -1974,49 +1893,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Le succès de Maria Braun amène RWF à espérer pour voir réaliser </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cocaïne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, l'adaptation d'un roman de Pitigrilli. Il lui permet aussi de renégocier à la hausse le budget de production de </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Berlin Alexanderplatz</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> : le projet devient le le plus coûteux de l'histoire de la télévision allemande. </t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <i/>
         <sz val="10"/>
@@ -2076,31 +1952,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">RWF projette d'adapter le roman de </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Freytag Soll und Haben</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (1855), œuvre notaoirement antismétique en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. 
-RWF quitte le Filmverlag der Autoren</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <i/>
         <sz val="10"/>
@@ -2231,6 +2082,184 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Le cinéma allemand s'empare de son histoire passée et récente et réfléchit aux problèmes de représentation qu'elle pose. Film collectif </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Allemagne en automne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1978). La diffusion de la série</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Holocaust</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de Marvin J. Chomsky (1979) à la télévision allemande suscite des débats importants, auxquels participent des cinéastes comme Syberberg ou Edgard Reitz. Le mouvement du Nouveau Cinéma allemand atteint son apogée thématique et politique.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hanna Schygulla doit interpréter </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lola une femme allemande</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, mais Fassbinder lui retire le rôle furieux que l'actrice ait déclaré qu'elle s'était elle-même distribuée dans le film.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Le tambour</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de V. Schlondorff obtient la palme d'or à Cannes. 
+La diffusion de la série américaine  </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Holocaust</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de Marvin J. Chomsky (1976) touche le grand public qui découvre l'ampleur des crimes commis et déclenche de vifs débatà travers le parcours de deux familles : comment l'histoire du pays peut-elle toucher le grand public à travers une production américaine et non allemande ? Si la série ouvre les vannes de la mémoire, Certains lui reprochent son sentimentalisme de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>soap opera.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le succès du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mariage de Maria Braun</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> amène RWF à espérer pour voir réaliser </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cocaïne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, l'adaptation d'un roman de Pitigrilli. Il lui permet aussi de renégocier à la hausse le budget de production de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Berlin Alexanderplatz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> : le projet devient le le plus coûteux de l'histoire de la télévision allemande. </t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve"> Le mouvement atteint son apogée thématique et politique.
 </t>
     </r>
@@ -2251,12 +2280,285 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">, un film d'Allemagne de Syberberg interroge le nazisme à travers son usage des médias (radio et cinéma) et sa mise en spectacle du politique. Le show business moderne en dévoile sa dimension fasciste. 
+      <t xml:space="preserve">, un film d'Allemagne de Syberberg interroge le nazisme à travers son usage des médias (radio et cinéma) et sa mise en spectacle du politique.  Le film révèle commentl Le show business moderne présente une dimension fasciste. 
 </t>
     </r>
   </si>
   <si>
     <r>
+      <t xml:space="preserve">RWF projette d'adapter le roman de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Freytag Soll und Haben</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1855), œuvre notaoirement antisémite en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. 
+RWF quitte le Filmverlag der Autoren</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Automne Allemand </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(1977) : enlèvement de Schleyer, détournement du Landshut, morts à Stammheim. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Réalise ses premiers courts métrages : </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>This Night</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1966) et </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le Clochard </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(1966). Confrontation de la mémoire de la Shoah.</t>
+    </r>
+  </si>
+  <si>
+    <t>Petit chaos, court-métrage</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'amour est plus froid que la mort </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(1969),  </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le Bouc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(1969, succès à Mannheim) : critique de la xénophobie et de l'apathie bourgeoise.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Les dieux de la peste
+Pourquoi M. R. est-il atteint de folie meurtrière ?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le soldat américain
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le Voyage à Niklashausen - Téléfilm
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Rio das mortes
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Whity
+Prenez garde à la sainte putain
+Pionniers à Ingolstadt - Téléfilm</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le Marchand des quatre saisons
+Les larmes amères de Petra von Kant
+Liberté à Brême </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>- Téléfilm</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Huit heures ne font pas un jour </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - série</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gibier de passage </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-Téléfilm</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Le monde sur un fil</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - Téléfilm en parties</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Effi Briest
+Martha - Téléfilm
+Tous les autres s'appellent Ali
+Noral Helmer - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Téléfilm</t>
+    </r>
+  </si>
+  <si>
+    <t>Femmes à New York  -Téléfilm
+La femme du chef de gare  - Téléfilm</t>
+  </si>
+  <si>
+    <r>
       <rPr>
         <i/>
         <sz val="10"/>
@@ -2273,7 +2575,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (1975). </t>
+      <t xml:space="preserve"> 
+</t>
     </r>
     <r>
       <rPr>
@@ -2292,113 +2595,81 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (1975) : </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Le tambour de Volker Schlondorff obtient la palme d'or à Cannes. 
-La diffusion de la série américaine  </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Holocaust</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> de Marvin J. Chomsky (1976) touche le grand public qui découvre l'ampleur des crimes commis et déclenche de vifs débatà travers le parcours de deux familles : comment l'histoire du pays peut-elle toucher le grand public à travers une production américaine et non allemande ? Si la série ouvre les vannes de la mémoire, Certains lui reprochent son sentimentalisme de </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>soap opera.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Le cinéma allemand s'empare de son histoire passée et récente et réfléchit aux problèmes de représentation qu'elle pose. Film collectif </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'Allemagne en automne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (1978). La diffusion de la série</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Holocaust</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> de Marvin J. Chomsky (1979) à la télévision allemande suscite des débats importants, auxquels participent des cinéastes comme Syberberg ou Edgard Reitz. Le mouvement du Nouveau Cinéma allemand atteint son apogée thématique et politique.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Hanna Schygulla doit interpréter </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Lola une femme allemande</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, mais Fassbinder lui retire le rôle furieux que l'actrice ait déclaré qu'elle s'était elle-même distribuée dans le film.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Suite de la Trilogie de la RFA :  </t>
-    </r>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Comme un oiseau sur le film</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - Téléfilm
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Peur de la peur</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> -Téléfilm
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ombre des anges
+Le rôti de satan 
+Je veux seulement que vous m'aimiez - Téléfilm
+Roulette chinoise </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Monumental </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Berlin Alexanderplatz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  - série en 14 épisodes et un épiloque </t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <i/>
@@ -2416,7 +2687,73 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (1981) et Lola, une femme allemande (1981)</t>
+      <t xml:space="preserve">
+Suite de la Trilogie de la RFA :   </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lola, une femme allemande</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Théâtre en transe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, documentaire</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le secret de Veronika Voss, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ours d'or à Berlin</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Querelle
+RWF laisse un héritage de plus de 40 films.</t>
     </r>
   </si>
 </sst>
@@ -3428,7 +3765,7 @@
         <v/>
       </c>
       <c r="I2" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>20</v>
@@ -3451,13 +3788,13 @@
         <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>26</v>
@@ -3468,10 +3805,10 @@
         <v/>
       </c>
       <c r="I3" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>27</v>
@@ -3485,13 +3822,13 @@
         <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>31</v>
@@ -3507,7 +3844,7 @@
         <v>33</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="85" customHeight="1">
@@ -3518,7 +3855,7 @@
         <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>36</v>
@@ -3528,14 +3865,14 @@
         <v>38</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>IF(G5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="K5" s="28"/>
     </row>
@@ -3547,16 +3884,16 @@
         <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>42</v>
@@ -3566,7 +3903,7 @@
         <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="70" customHeight="1">
@@ -3575,7 +3912,7 @@
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>44</v>
@@ -3602,16 +3939,16 @@
         <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>50</v>
@@ -3625,7 +3962,7 @@
       </c>
       <c r="I8" s="15"/>
       <c r="K8" s="15" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="N8" s="14" t="s">
         <v>52</v>
@@ -3636,10 +3973,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>54</v>
@@ -3660,10 +3997,10 @@
         <v>1982</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>57</v>
@@ -4139,7 +4476,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D11" s="22" t="s">
         <v>106</v>
@@ -4218,10 +4555,10 @@
         <v>111</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="19"/>
@@ -4301,7 +4638,7 @@
         <v>116</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="19" t="s">
@@ -4456,7 +4793,7 @@
         <v>126</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>127</v>
@@ -4532,11 +4869,11 @@
         <v>134</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>32</v>
+        <v>318</v>
       </c>
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
@@ -4566,12 +4903,14 @@
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F22" s="1"/>
+      <c r="F22" s="25" t="s">
+        <v>319</v>
+      </c>
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
@@ -4607,11 +4946,9 @@
       <c r="E23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>261</v>
-      </c>
+      <c r="F23" s="15"/>
       <c r="G23" s="24" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
@@ -4627,7 +4964,7 @@
       <c r="S23" s="19"/>
       <c r="T23" s="19"/>
       <c r="U23" s="2" t="str">
-        <f>IF(F23="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F23,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <f>IF(F24="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
     </row>
@@ -4642,10 +4979,12 @@
         <v>136</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="F24" s="1" t="s">
+        <v>320</v>
+      </c>
       <c r="G24" s="24"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
@@ -4660,23 +4999,23 @@
       <c r="R24" s="19"/>
       <c r="S24" s="19"/>
       <c r="T24" s="19"/>
-      <c r="U24" s="2" t="str">
-        <f>IF(F24="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F24,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:21" ht="42">
+      <c r="U24" s="2" t="e">
+        <f>IF(#REF!="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(#REF!,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="98">
       <c r="A25" s="1">
         <v>1970</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>137</v>
+        <v>321</v>
       </c>
       <c r="G25" s="24"/>
       <c r="H25" s="19"/>
@@ -4694,7 +5033,7 @@
       <c r="T25" s="19"/>
       <c r="U25" s="2" t="str">
         <f>IF(F25="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F25,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1971-whity; film-1971-prenez-garde-a-la-sainte-putain</v>
+        <v>film-1970-les-dieux-de-la-peste; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1970-le-soldat-americain; film-1970-le-voyage-a-niklashausen</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="196">
@@ -4705,32 +5044,32 @@
         <v>39</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>259</v>
+      <c r="F26" s="25" t="s">
+        <v>322</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="15"/>
       <c r="K26" s="19"/>
       <c r="L26" s="19" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="M26" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="N26" s="21" t="s">
         <v>140</v>
-      </c>
-      <c r="N26" s="21" t="s">
-        <v>141</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -4742,7 +5081,7 @@
       <c r="T26" s="19"/>
       <c r="U26" s="2" t="str">
         <f>IF(F26="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F26,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1972-le-marchand-des-quatre-saisons</v>
+        <v>film-1971-whity; film-1971-prenez-garde-a-la-sainte-putain; film-1971-pionniers-a-ingolstadt</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="306">
@@ -4752,10 +5091,12 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
+      <c r="F27" s="25" t="s">
+        <v>323</v>
+      </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
@@ -4772,7 +5113,7 @@
       <c r="T27" s="15"/>
       <c r="U27" s="2" t="str">
         <f>IF(F27="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F27,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v/>
+        <v>film-1972-le-marchand-des-quatre-saisons; film-1972-les-larmes-ameres-de-petra-von-kant; film-1972-liberte-a-breme; film-1972-huit-heures-ne-font-pas-un-jour</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="84">
@@ -4782,15 +5123,15 @@
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="26" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="25" t="s">
-        <v>142</v>
+        <v>324</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="15" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
@@ -4806,7 +5147,7 @@
       <c r="T28" s="15"/>
       <c r="U28" s="2" t="str">
         <f>IF(F28="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F28,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1973-le-monde-sur-un-fil</v>
+        <v>film-1973-gibier-de-passage; film-1973-le-monde-sur-un-fil</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="56">
@@ -4818,10 +5159,10 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="25" t="s">
-        <v>260</v>
+        <v>325</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
@@ -4838,7 +5179,7 @@
       <c r="T29" s="15"/>
       <c r="U29" s="2" t="str">
         <f>IF(F29="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F29,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1974-effi-briest; film-1974-martha</v>
+        <v>film-1974-tous-les-autres-s-appellent-ali; film-1974-effi-briest; film-1974-martha</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="238">
@@ -4858,10 +5199,10 @@
         <v>46</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
@@ -4878,10 +5219,10 @@
       <c r="T30" s="19"/>
       <c r="U30" s="2" t="str">
         <f>IF(F30="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F30,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" ht="28">
+        <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel; film-1975-comme-un-oiseau-sur-le-fil; film-1975-peur-de-la-peur</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="70">
       <c r="A31" s="1">
         <v>1976</v>
       </c>
@@ -4890,12 +5231,14 @@
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="25" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="F31" s="1"/>
+        <v>269</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>328</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
@@ -4912,7 +5255,7 @@
       <c r="T31" s="15"/>
       <c r="U31" s="2" t="str">
         <f>IF(F31="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F31,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v/>
+        <v>film-1976-l-ombre-des-anges; film-1976-le-roti-de-satan; film-1976-roulette-chinoise; film-1976-je-veux-seulement-que-vous-m-aimiez</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="252">
@@ -4923,24 +5266,26 @@
         <v>49</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F32" s="15"/>
+      <c r="F32" s="15" t="s">
+        <v>326</v>
+      </c>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
       <c r="K32" s="19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L32" s="19" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M32" s="19"/>
       <c r="N32" s="19"/>
@@ -4952,7 +5297,7 @@
       <c r="T32" s="19"/>
       <c r="U32" s="2" t="str">
         <f>IF(F32="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F32,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v/>
+        <v>film-1977-femmes-a-new-york; film-1977-la-femme-du-chef-de-gare</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="196">
@@ -4965,20 +5310,20 @@
       <c r="C33" s="1"/>
       <c r="D33" s="25"/>
       <c r="E33" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
       <c r="L33" s="15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M33" s="19"/>
       <c r="N33" s="19"/>
@@ -5002,16 +5347,16 @@
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
@@ -5042,23 +5387,23 @@
         <v>54</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>280</v>
+        <v>329</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
       <c r="L35" s="19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M35" s="19"/>
       <c r="N35" s="19"/>
@@ -5082,21 +5427,21 @@
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="15" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="H36" s="15"/>
       <c r="I36" s="15"/>
       <c r="J36" s="15"/>
       <c r="K36" s="15"/>
       <c r="L36" s="15" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
@@ -5108,10 +5453,10 @@
       <c r="T36" s="15"/>
       <c r="U36" s="2" t="str">
         <f>IF(F36="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F36,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1981-lili-marleen; film-1981-lola-une-femme-allemande</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" ht="126">
+        <v>film-1981-lili-marleen; film-1981-theatre-en-transe; film-1981-lola-une-femme-allemande</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="112">
       <c r="A37" s="1">
         <v>1982</v>
       </c>
@@ -5119,16 +5464,16 @@
         <v>1982</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>60</v>
+      <c r="F37" s="25" t="s">
+        <v>331</v>
       </c>
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
@@ -5136,7 +5481,7 @@
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
       <c r="L37" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M37" s="19"/>
       <c r="N37" s="19"/>
@@ -5183,70 +5528,70 @@
   <sheetData>
     <row r="15" spans="1:4">
       <c r="A15" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="D15" s="16" t="s">
         <v>152</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="51">
       <c r="A16" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>155</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>157</v>
       </c>
       <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:4" ht="51">
       <c r="A17" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="D17" s="17" t="s">
         <v>159</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28">
       <c r="A18" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>164</v>
-      </c>
       <c r="D18" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28">
       <c r="A19" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="D19" s="17" t="s">
         <v>166</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -5265,330 +5610,330 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17">
       <c r="A1" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17">
       <c r="A2" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17">
       <c r="A3" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17">
       <c r="A4" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17">
       <c r="A5" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17">
       <c r="A6" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17">
       <c r="A7" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17">
       <c r="A8" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17">
       <c r="A9" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17">
       <c r="A10" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17">
       <c r="A11" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17">
       <c r="A12" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17">
       <c r="A13" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17">
       <c r="A14" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17">
       <c r="A15" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17">
       <c r="A16" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17">
       <c r="A17" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17">
       <c r="A18" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17">
       <c r="A19" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17">
       <c r="A20" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17">
       <c r="A21" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17">
       <c r="A22" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17">
       <c r="A23" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17">
       <c r="A24" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17">
       <c r="A25" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17">
       <c r="A26" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17">
       <c r="A27" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17">
       <c r="A28" s="9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17">
       <c r="A29" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17">
       <c r="A30" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17">
       <c r="A31" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17">
       <c r="A32" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17">
       <c r="A33" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17">
       <c r="A34" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17">
       <c r="A35" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17">
       <c r="A36" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17">
       <c r="A37" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17">
       <c r="A38" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17">
       <c r="A39" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17">
       <c r="A40" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17">
       <c r="A41" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -5611,40 +5956,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:2" ht="34" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="629" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9D4352E-5F5D-F34B-8A2F-EC6695115120}"/>
+  <xr:revisionPtr revIDLastSave="702" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A139AEF-2092-EB45-9C09-9E8DB9663B2E}"/>
   <bookViews>
-    <workbookView xWindow="14680" yWindow="600" windowWidth="22800" windowHeight="24600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9560" yWindow="2960" windowWidth="39280" windowHeight="24500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="340">
   <si>
     <t>ID période</t>
   </si>
@@ -135,9 +135,6 @@
     <t>Adenauer.jpeg</t>
   </si>
   <si>
-    <t>Adénauer</t>
-  </si>
-  <si>
     <t>1947-1960</t>
   </si>
   <si>
@@ -235,9 +232,6 @@
   </si>
   <si>
     <t>Monumental Berlin Alexanderplatz (1980, 15h). Suite de la Trilogie de la RFA : Lola, une femme allemande (1981) et Lili Marleen (1981).</t>
-  </si>
-  <si>
-    <t>Victoire d'Helmut Kohl (CDU) en octobre. Fin d'une époque artistique et politique radicale.</t>
   </si>
   <si>
     <t>Mort de Fassbinder marquant symboliquement la fin du Nouveau Cinéma Allemand.</t>
@@ -592,9 +586,6 @@
     <t xml:space="preserve">RWF interrompt ses études avant le baccalauréat. Il rejoint son père à Cologne. Il collecte pour lui des loyers dans des immeubles principalement occupés par des Gastarbeiters (travaillers "invités" c'est-à-dire immigrés). RWF prend des cours du soir, écrit, f'équente les bars homosexuels. </t>
   </si>
   <si>
-    <t>Exécution d'Eichmann après sa condamnation à la peine de mort</t>
-  </si>
-  <si>
     <t>A l'occasion du festival du film documentaire d'Oberhausen, publication du Manifeste d'Oberhausen : naissance du Nouveau Cinéma Allemand ("Le vieux cinéma est mort").
 Les Beatles entament eur carrière par un concert à Hambourg</t>
   </si>
@@ -648,9 +639,6 @@
     <t>RWF s'inscrit à l'école d'art dramatique Fridl Loeonhard</t>
   </si>
   <si>
-    <t xml:space="preserve">Une grande coaltion chrétienne-démocrate voit le jour sous l'autorité du nouveau chancelier Kurt Georg Kiesinger. Willy Brandt est ministre des affaires étrangères et vice-chancelier. </t>
-  </si>
-  <si>
     <t>Rejoint l'Action-Theater (1967).</t>
   </si>
   <si>
@@ -682,45 +670,6 @@
   </si>
   <si>
     <t>Les années 55-75, celles pendant lesquelles RWF est sorti de l'enfance et s'est développé comme adolescent puis adulte, seront celles qui nourriront son inspiration cinémétographique et sa réflexion politique. Même les films dont l'action se situent avant 1945 sont à envisager comme "une archéologie de la société allemande d'après-guerre" (Elsaesser, p. 34)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"je trouve que l'Allemagne en particulier est dans une situation où beaucoup de choses régressent. Je dirais qu'en 1945, lorsque la guerre a pris fin, lorsque le troisième Reich a pris fin, on n'a pas perçu quelles chances s'offraient à l'Allemagne, mais je pense qu'au contraire, comme je l'ai écrit dans </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Die Zeit, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">les valeurs et les structures sur lesquelles repose cet Etat, aujourd'hui devenu démocratique, sont restées, fondamentalement les mêmes qu'autrefois. Cet état de fait, si on ajoute cette tendance régressive, va conduire à quelque chose, une forme d'Etat dans lequel je n'aimerais pas tellement vivre". Entreitne donné à Peter W. Jansen en 1978 et repris dans l'ouvra ge </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fassbinder par lui-même</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, p.342-343, G3J éditeur, 2010</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1274,94 +1223,11 @@
     <t>Effi Briest permet à RWF d'obtenir une reconnaissance plus large en Allemagne, qui tempère sa réputation d'enfant terrible du cinéma</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Le militantisme et l'action politique violente, marquée à l'extrême gauche après 1968 en Allemagne, sont le terreau de plusieurs films de Fassbinder : Voyage à Niklashausen, , Maman Kusters s'en va au ciel, ou encore La troisième génération. Il est remarquable qu'un comique outrancier associe l'action violente à une forme de bêtise radicale.
-Fassbinder joue le rôle principal du </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Droit du plus fort</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, assumant une visibilité politique de son homosexualité.
-Une rétrospective de l'œuvre de RWF à New York suscite l'enthousiasme de la presse américaine. </t>
-    </r>
-  </si>
-  <si>
     <t>De l’année zéro au miracle économique|https://youtu.be/BC4BffkWyY8?si=e80MWCLF0K9Fgiub; Jalousie de Catharina Valente|https://youtu.be/-ugDTj7UFtU?si=vzGNySrsaYGKZW0k</t>
   </si>
   <si>
     <t>Fondation du Filmverlag der Autoren (1971), une société indépendante, par quelques cinéastes dont RWF. La société est d'abord autogérée.
 Accords Film-Télévision (1974) favorisant les coproductions (WDR).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFW devient actionnaire du Filmverlag der Autoren. </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Suicide d'Armin Meier (31 mai 1978). Début de la collaboration avec Juliane Lorenz. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">L'année des treize lunes devient un film </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>expiatoire. Le tournage de</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Maria Braun </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">est compliqué : dépassement de budget, consommation explosive de cocaïne. Ceci explique peut être la fin de la collaboration entre Ballhaus et RWF.
-RWF travaille active à l'écriture de Berlin Alexander Platz, dont il dicte des passages dans </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">L'année des treize lunes. </t>
-    </r>
   </si>
   <si>
     <t>RWF parvient à évincer Werner Schroeter qui souhaitait réaliser une adaptation de Querelle de Jean Genet.  Mort de Fassbinder marquant symboliquement la fin du Nouveau Cinéma Allemand.</t>
@@ -1972,72 +1838,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">"Despair est le film le plus rempli d'espoir que j'ai jamais fait " RWF, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'anarchie de l'imaginaire</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>p.80-81</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Le film constitue un nouveau tournant dans la carrière de RWF en l'intégrant au club fermé des auteurs importants du cinéma européen même si son écho critique reste mitigé. Mais RWF présente aussi à Cannes, en projection non officielle </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le mariage de Maria Braun. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ce film exclipse </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Despair.
-L'allemagne en automne n'est vu que par un public limité. </t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Allemagne mère blafarde </t>
     </r>
     <r>
@@ -2147,57 +1947,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Le tambour</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> de V. Schlondorff obtient la palme d'or à Cannes. 
-La diffusion de la série américaine  </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Holocaust</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> de Marvin J. Chomsky (1976) touche le grand public qui découvre l'ampleur des crimes commis et déclenche de vifs débatà travers le parcours de deux familles : comment l'histoire du pays peut-elle toucher le grand public à travers une production américaine et non allemande ? Si la série ouvre les vannes de la mémoire, Certains lui reprochent son sentimentalisme de </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>soap opera.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Le succès du </t>
     </r>
     <r>
@@ -2286,31 +2035,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">RWF projette d'adapter le roman de </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Freytag Soll und Haben</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (1855), œuvre notaoirement antisémite en série télévisée. Il s'agit pour RWF d'interroger les origines de la bourgeoisie allemande. Face aux articles polémiques, le directeur de la WDR annule le projet. 
-RWF quitte le Filmverlag der Autoren</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <i/>
         <sz val="10"/>
@@ -2375,91 +2099,6 @@
   </si>
   <si>
     <t>Petit chaos, court-métrage</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">L'amour est plus froid que la mort </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(1969),  </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le Bouc </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(1969, succès à Mannheim) : critique de la xénophobie et de l'apathie bourgeoise.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Les dieux de la peste
-Pourquoi M. R. est-il atteint de folie meurtrière ?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le soldat américain
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Le Voyage à Niklashausen - Téléfilm
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Rio das mortes
-</t>
-    </r>
   </si>
   <si>
     <t>Whity
@@ -2640,120 +2279,684 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">L'ombre des anges
+    <r>
+      <t xml:space="preserve">Monumental </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Berlin Alexanderplatz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  - série en 14 épisodes et un épiloque </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lili Marleen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Suite de la Trilogie de la RFA :   </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lola, une femme allemande</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Théâtre en transe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, documentaire</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le secret de Veronika Voss, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ours d'or à Berlin</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Querelle
+RWF laisse un héritage de plus de 40 films.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Les dieux de la peste
+Pourquoi M. R. est-il atteint de folie meurtrière ?
+Le soldat américain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Le Voyage à Niklashausen - Téléfilm
+Rio das mortes
+Le café -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Téléfilm tiré d'une création théâtrale de Peer Raben et RWF
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'amour est plus froid que la mort
+Le Bouc (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>succès à Mannheim) : critique de la xénophobie et de l'apathie bourgeoise.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Une grande coalition chrétienne-démocrate voit le jour sous l'autorité du nouveau chancelier Kurt Georg Kiesinger. Willy Brandt est ministre des affaires étrangères et vice-chancelier. </t>
+  </si>
+  <si>
+    <t>Procès d'Eichmann à Jerusalem</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Le tambour</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de V. Schlondorff obtient la palme d'or à Cannes. 
+La diffusion de la série américaine  </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Holocaust</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de Marvin J. Chomsky (1976) touche le grand public qui découvre l'ampleur des crimes commis pendant la seconde guerre mondiale à l'égard de la population juive.  La série suit le parcours de deux familles , l'une  "aryenne", l'autre juive. La série déclenche de vifs débats en RFA : comment l'histoire du pays peut-elle toucher le grand public à travers une production américaine et non allemande ? Si la série ouvre les vannes de la mémoire, Certains lui reprochent son sentimentalisme de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>soap opera.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Procès Maïdanek à Hambourg
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holocaust, une serie eveille les consciences|https://www.ina.fr/ina-eclaire-actu/video/s1313279_001/1979-une-serie-eveille-les-consciences-sur-la-shoah; </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"je trouve que l'Allemagne en particulier est dans une situation où beaucoup de choses régressent. Je dirais qu'en 1945, lorsque la guerre a pris fin, lorsque le troisième Reich a pris fin, on n'a pas perçu quelles chances s'offraient à l'Allemagne, mais je pense qu'au contraire, comme je l'ai écrit dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Die Zeit, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">les valeurs et les structures sur lesquelles repose cet Etat, aujourd'hui devenu démocratique, sont restées, fondamentalement les mêmes qu'autrefois. Cet état de fait, si on ajoute cette tendance régressive, va conduire à quelque chose, une forme d'Etat dans lequel je n'aimerais pas tellement vivre". Entretien donné à Peter W. Jansen en 1978 et repris dans l'ouvra ge </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fassbinder par lui-même</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, p.342-343, G3J éditeur, 2010</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans "devoir de l'avoir - avoir du devoir" un article repris dans Les films libèrent la tête, RWF revient sur le roman de Freytag  et son projet empêché .  Son propos marque la conscience précoce du cinéaste de l'antisémitisme  cosncient ou inconscient qui règne encore et du positionnement ambigu de la population allemande à l'égard de sa responsabilité historique dans le génocide juif, de son absence de regard critique sur l'histoire du pays. Il revient sur le "péché originel" qu'a été la constitution dune identité de la bourgeoisie allemande fondamentalement antisémite et défend le choix d'une oeuvre antisémite selon deux arguments : 1. le roman est bien construit et narrativement divertissant, ce qui en fait un bon support pour une adaptation cinématographique. 2. L'oeuvre permettrait de mettre à jour avec justesse, c'est-à-dire historiquement, le point de vue "faux" de la bourgeoisie allemande du XIXè, ce que justement cette classe sociale considérait comme "juste". C'est donc, comme toujours chez RWF, un travail des points de vue et de leur agencement qui intéresse le cinéaste en ce qu'il permettrait de déconstruire le point de vue du spectateur contemporain, de l'amener à interroger son propre regard. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFW devient actionnaire du Filmverlag der Autoren. 
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">RWF écrit la pièce </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Les ordures, la ville et la mort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, qu'il doit mettre en scène au Theater und Sturm de Francfort. La pièce, qui traite de corruption et de spéculation immobilière, a pour protagoniste un homme juif, désigné comme "le juif riche". Son ton satirique vise surtout l'administration municipale de la ville. Avant même sa plublication et l'ouverture du spectacle, la pièce fait scandale. Suite à la circulation de quelques copies du texte et de la publication d'un communiqué de presse,</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">RWF est accusé d'antisémtisme, notammant par Joachim C. Fest dont le livre </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hitler une carrière </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">avait contribué à mettre à jour l'existence d'une "vague Hitler" nostalgique au sein de la population, qu'il associait notamment à une gauche "rouge" affilée au fascisme de Moscou. La pièce est abandonnée et RWF interdit qu'on la représente de son vivant en Allemagne. Le projet de téléfilm </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">La terre est inhabitable comme la lune, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>qui s'inspirait en partie des personnages de la pièce, perd ses financements. 
+Liaison avec Armin Meier.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Il faut bien qu'on ait la possibilité d'aborder un thème d'une manière dangereuse, peut-être contestable, et pas seulement en avançant à couvert; sinon ce qu'on fait est encore une fois aussi mort que tout le reste dans le paysage théâtral allemand. Plus rien de vivant de s'y produit ; rien que des gens gentils, sympas et rien que des gens qui veulent plaire. A long terme ce n'est pas possible". RWF, "les philosémites sont des antisémites", avril 1976, repris dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'anarchie de l'imagination P; 76</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoire d'Helmut Kohl (CDU) en octobre. Fin d'une époque artistique et politique radicale.Kohk se donne comme mission de réconcilier le peuple ouest-allemand avec son passé </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le militantisme et l'action politique violente, marquée à l'extrême gauche après 1968 en Allemagne, sont le terreau de plusieurs films de Fassbinder : Voyage à Niklashausen, , Maman Kusters s'en va au ciel, ou encore La troisième génération. Il est remarquable qu'un comique outrancier associe l'action violente à une forme de bêtise radicale.
+Fassbinder joue le rôle principal du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Droit du plus fort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, assumant une visibilité politique de son homosexualité.
+Une rétrospective de l'œuvre de RWF à New York suscite l'enthousiasme de la presse américaine. 
+Suite au scandale déclenché par Les ordures, la ville et la mort</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">RWF subira le soupçon d'antisémtisme dans tous ses autres projets associés à cette question. Pour apprécier la position de RWF, lire "les philosémites sont des antisémites" dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'anarchie de l'imagination, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">et "prise de postion à propos de L'ordure, la ville et la mort dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Les films libèrent la tête. La pièce Les ordures, la ville et la mort est toujours un texte polémique, rarement monté. En 1985, le projet de le mettre sur scène à Francfort déclencha de vifs débats, le projet, d'abord retiré, fut monté à huis-clos devant un public restreint de journalistes dans unautre théâtre de Francfort dans un contexte politique d'affirmation de l'unité refondée du peuple allemand mais de sensibilités mémorielles toujours vives. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">L'ombre des anges de Daniel Schmid,  d'après la pièce </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Les ordures, la ville et la mort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 Le rôti de satan 
 Je veux seulement que vous m'aimiez - Téléfilm
 Roulette chinoise </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Monumental </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Berlin Alexanderplatz</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  - série en 14 épisodes et un épiloque </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Lili Marleen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Suite de la Trilogie de la RFA :   </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Lola, une femme allemande</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Théâtre en transe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, documentaire</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Le secret de Veronika Voss, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ours d'or à Berlin</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Querelle
-RWF laisse un héritage de plus de 40 films.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Il joue dans  </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'ombre des anges</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, l'adaptation de sa propre pièce, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Les ordures la ville et la mort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, mise en scène au cinéma par D. Schmid, et en partie financée par Fassbinder et produit par la société Albatros films de Fengler. C'est tout l'entourage de Fassbinder qui se joint au film, notamment Ingrid Caven. </t>
+    </r>
+  </si>
+  <si>
+    <t>Fassbinder_fox.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Allemagne_zones.jpeg</t>
+  </si>
+  <si>
+    <t>Le découpage de l'Allemagne et de Berlin en 4 zones d'occupation alliée</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mai 1978 : RWF quitte Armin Meier pendant un voyage à New York.Meier rentre seul à Munich tandis que RWF se rend à Cannes. Le 31 mai 1978, jour d'anniversaire de RWF, Armin Meier se suicide dans leur appartement. Le corps n'est découvert qu'une seumaine plus tard. Scandale. RWF se jette dans le travail. L'année des treize lunes, qui sort trois mois plus tard est dédié à Armin (et à tous les autres). 
+Début de la collaboration avec Juliane Lorenz. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'année des treize lunes devient un film </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>expiatoire. Le tournage de</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Maria Braun </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">est compliqué : dépassement de budget, consommation explosive de cocaïne. Ceci explique peut être la fin de la collaboration entre Ballhaus et RWF.
+RWF travaille active à l'écriture de Berlin Alexander Platz, dont il dicte des passages dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'année des treize lunes. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'année des treize lunes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> est un projet très personnel pour RWF. Outre son sujet, qui se nourrit du deuil et de la culpabilité liés à la mort d'Armin Meier, RWF y participe à toutes les étapes, y compris le cadrage et le montage. La critique est divisée, entre enthouasisme et rejet, entre lecture sentimentale et lecture politique. 
+"Despair est le film le plus rempli d'espoir que j'ai jamais fait " RWF, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'anarchie de l'imaginaire</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>p.80-81</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Le film constitue un nouveau tournant dans la carrière de RWF en l'intégrant au club fermé des auteurs importants du cinéma européen même si son écho critique reste mitigé. Mais RWF présente aussi à Cannes, en projection non officielle </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le mariage de Maria Braun. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ce film exclipse </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Despair.
+L'allemagne en automne n'est vu que par un public limité. </t>
     </r>
   </si>
 </sst>
@@ -3050,20 +3253,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -3349,6 +3538,20 @@
         <scheme val="none"/>
       </font>
       <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3450,7 +3653,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="22">
   <autoFilter ref="A1:N10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID période"/>
@@ -3473,29 +3676,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:T37" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3741,7 +3944,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="84" customHeight="1">
+    <row r="2" spans="1:14" ht="84">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -3765,7 +3968,7 @@
         <v/>
       </c>
       <c r="I2" s="1" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>20</v>
@@ -3773,31 +3976,31 @@
       <c r="K2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="L2" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="14" customFormat="1" ht="210">
+      <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" s="14" customFormat="1" ht="211" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="4" t="str">
@@ -3805,156 +4008,156 @@
         <v/>
       </c>
       <c r="I3" s="1" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="L3" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="170">
+      <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="196" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="H4" s="4" t="str">
         <f>IF(G4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
       <c r="J4" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="136">
+      <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="85" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>IF(G5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="K5" s="28"/>
     </row>
-    <row r="6" spans="1:14" ht="303" customHeight="1">
+    <row r="6" spans="1:14" ht="319">
       <c r="A6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="H6" s="4" t="str">
         <f>IF(G6="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="70" customHeight="1">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="56">
       <c r="A7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="H7" s="4" t="str">
         <f>IF(G7="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
       </c>
       <c r="I7" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="140">
+      <c r="A8" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="129" customHeight="1">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="H8" s="4" t="str">
         <f>IF(G8="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -3962,57 +4165,57 @@
       </c>
       <c r="I8" s="15"/>
       <c r="K8" s="15" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="N8" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="56">
+      <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="89" customHeight="1">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="H9" s="4" t="str">
         <f>IF(G9="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v>film-1980-berlin-alexanderplatz; film-1981-lili-marleen; film-1981-lola-une-femme-allemande</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="70" customHeight="1">
+    <row r="10" spans="1:14" ht="70">
       <c r="A10" s="24">
         <v>1982</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="H10" s="4" t="str">
         <f>IF(G10="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -4051,7 +4254,7 @@
   <sheetData>
     <row r="1" spans="1:21" s="12" customFormat="1" ht="28" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -4069,49 +4272,49 @@
         <v>6</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="I1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>65</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>10</v>
       </c>
       <c r="M1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="O1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="S1" s="8" t="s">
         <v>13</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="U1" s="29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="98">
@@ -4122,13 +4325,13 @@
         <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -4160,18 +4363,18 @@
         <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="F3" s="19"/>
       <c r="G3" s="1"/>
       <c r="H3" s="20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I3" s="20"/>
       <c r="J3" s="20"/>
@@ -4195,13 +4398,13 @@
         <v>1947</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="19"/>
@@ -4219,7 +4422,7 @@
       <c r="R4" s="19"/>
       <c r="S4" s="19"/>
       <c r="T4" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="U4" s="2" t="str">
         <f>IF(F4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -4231,28 +4434,28 @@
         <v>1948</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="19"/>
       <c r="G5" s="1"/>
       <c r="H5" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="19"/>
@@ -4273,19 +4476,19 @@
         <v>1949</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="19"/>
       <c r="G6" s="1"/>
       <c r="H6" s="20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I6" s="20"/>
       <c r="J6" s="20"/>
@@ -4295,7 +4498,7 @@
         <v>22</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O6" s="19"/>
       <c r="P6" s="19"/>
@@ -4313,12 +4516,12 @@
         <v>1950</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F7" s="19"/>
       <c r="G7" s="1"/>
@@ -4331,13 +4534,13 @@
         <v>22</v>
       </c>
       <c r="N7" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O7" s="19"/>
       <c r="P7" s="19"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S7" s="19"/>
       <c r="T7" s="19"/>
@@ -4351,14 +4554,14 @@
         <v>1951</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="19"/>
@@ -4371,7 +4574,7 @@
         <v>22</v>
       </c>
       <c r="N8" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O8" s="19"/>
       <c r="P8" s="19"/>
@@ -4389,16 +4592,16 @@
         <v>1952</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="19"/>
@@ -4408,16 +4611,16 @@
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="O9" s="19" t="s">
         <v>22</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
@@ -4433,19 +4636,19 @@
         <v>1953</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="19"/>
       <c r="H10" s="20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
@@ -4455,7 +4658,7 @@
         <v>22</v>
       </c>
       <c r="N10" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O10" s="19"/>
       <c r="P10" s="19"/>
@@ -4473,35 +4676,35 @@
         <v>1954</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="19"/>
       <c r="H11" s="20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N11" s="19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O11" s="19" t="s">
         <v>22</v>
       </c>
       <c r="P11" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
@@ -4517,12 +4720,12 @@
         <v>1955</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="19"/>
@@ -4549,21 +4752,21 @@
         <v>1956</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="19"/>
       <c r="H13" s="23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I13" s="19"/>
       <c r="J13" s="19"/>
@@ -4573,7 +4776,7 @@
         <v>22</v>
       </c>
       <c r="N13" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O13" s="19"/>
       <c r="P13" s="19"/>
@@ -4591,13 +4794,13 @@
         <v>1957</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -4611,7 +4814,7 @@
         <v>22</v>
       </c>
       <c r="N14" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O14" s="19"/>
       <c r="P14" s="19"/>
@@ -4629,20 +4832,20 @@
         <v>1959</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
@@ -4653,7 +4856,7 @@
         <v>22</v>
       </c>
       <c r="N15" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O15" s="19"/>
       <c r="P15" s="19"/>
@@ -4671,16 +4874,16 @@
         <v>1960</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="19"/>
@@ -4693,7 +4896,7 @@
         <v>22</v>
       </c>
       <c r="N16" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O16" s="19"/>
       <c r="P16" s="19"/>
@@ -4711,14 +4914,14 @@
         <v>1961</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
@@ -4731,7 +4934,7 @@
         <v>22</v>
       </c>
       <c r="N17" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O17" s="19"/>
       <c r="P17" s="19"/>
@@ -4749,13 +4952,11 @@
         <v>1962</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>123</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -4765,13 +4966,13 @@
       <c r="J18" s="19"/>
       <c r="K18" s="19"/>
       <c r="L18" s="19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="M18" s="19" t="s">
         <v>22</v>
       </c>
       <c r="N18" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O18" s="19"/>
       <c r="P18" s="19"/>
@@ -4790,32 +4991,32 @@
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="19"/>
       <c r="H19" s="23" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J19" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K19" s="19"/>
       <c r="L19" s="19"/>
       <c r="M19" s="19" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="N19" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="O19" s="19"/>
       <c r="P19" s="19"/>
@@ -4833,10 +5034,12 @@
         <v>1964</v>
       </c>
       <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
+      <c r="C20" s="1" t="s">
+        <v>321</v>
+      </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="19"/>
@@ -4863,17 +5066,17 @@
         <v>1966</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>134</v>
+        <v>320</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
@@ -4899,17 +5102,19 @@
         <v>1967</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>323</v>
+      </c>
       <c r="D22" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
@@ -4935,20 +5140,20 @@
         <v>1968</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="24" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
@@ -4973,17 +5178,17 @@
         <v>1969</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G24" s="24"/>
       <c r="H24" s="19"/>
@@ -5004,18 +5209,18 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="98">
+    <row r="25" spans="1:21" ht="126">
       <c r="A25" s="1">
         <v>1970</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G25" s="24"/>
       <c r="H25" s="19"/>
@@ -5041,42 +5246,42 @@
         <v>1971</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="15"/>
       <c r="K26" s="19"/>
       <c r="L26" s="19" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N26" s="21" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T26" s="19"/>
       <c r="U26" s="2" t="str">
@@ -5091,11 +5296,11 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="25" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
@@ -5123,15 +5328,15 @@
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="26" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="25" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="15" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
@@ -5159,10 +5364,10 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="25" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
@@ -5182,35 +5387,41 @@
         <v>film-1974-tous-les-autres-s-appellent-ali; film-1974-effi-briest; film-1974-martha</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="238">
+    <row r="30" spans="1:21" ht="409.6">
       <c r="A30" s="1">
         <v>1975</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="E30" s="1" t="s">
-        <v>46</v>
+        <v>328</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>266</v>
+        <v>331</v>
       </c>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
       <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
+      <c r="L30" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="N30" s="19" t="s">
+        <v>335</v>
+      </c>
       <c r="O30" s="19"/>
       <c r="P30" s="19"/>
       <c r="Q30" s="19"/>
@@ -5222,22 +5433,22 @@
         <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel; film-1975-comme-un-oiseau-sur-le-fil; film-1975-peur-de-la-peur</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="70">
+    <row r="31" spans="1:21" ht="98">
       <c r="A31" s="1">
         <v>1976</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="25" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>269</v>
+        <v>327</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="15"/>
@@ -5258,34 +5469,36 @@
         <v>film-1976-l-ombre-des-anges; film-1976-le-roti-de-satan; film-1976-roulette-chinoise; film-1976-je-veux-seulement-que-vous-m-aimiez</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="252">
+    <row r="32" spans="1:21" ht="409.6">
       <c r="A32" s="1">
         <v>1977</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="F32" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="G32" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="G32" s="19"/>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
       <c r="K32" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="L32" s="19" t="s">
-        <v>142</v>
+        <v>137</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>325</v>
       </c>
       <c r="M32" s="19"/>
       <c r="N32" s="19"/>
@@ -5300,30 +5513,30 @@
         <v>film-1977-femmes-a-new-york; film-1977-la-femme-du-chef-de-gare</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="196">
+    <row r="33" spans="1:21" ht="332">
       <c r="A33" s="1">
         <v>1978</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="25"/>
       <c r="E33" s="1" t="s">
-        <v>270</v>
+        <v>338</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
       <c r="L33" s="15" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M33" s="19"/>
       <c r="N33" s="19"/>
@@ -5338,27 +5551,29 @@
         <v>film-1978-l-allemagne-en-automne; film-1978-despair; film-1978-l-annee-des-treize-lunes; film-1978-le-mariage-de-maria-braun</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="224">
+    <row r="34" spans="1:21" ht="252">
       <c r="A34" s="1">
         <v>1979</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="H34" s="19"/>
+        <v>300</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>324</v>
+      </c>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
@@ -5381,29 +5596,29 @@
         <v>1980</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="25" t="s">
-        <v>310</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F35" s="1" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
       <c r="L35" s="19" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="M35" s="19"/>
       <c r="N35" s="19"/>
@@ -5423,25 +5638,25 @@
         <v>1981</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="15" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="H36" s="15"/>
       <c r="I36" s="15"/>
       <c r="J36" s="15"/>
       <c r="K36" s="15"/>
       <c r="L36" s="15" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
@@ -5456,7 +5671,7 @@
         <v>film-1981-lili-marleen; film-1981-theatre-en-transe; film-1981-lola-une-femme-allemande</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="112">
+    <row r="37" spans="1:21" ht="126">
       <c r="A37" s="1">
         <v>1982</v>
       </c>
@@ -5464,16 +5679,16 @@
         <v>1982</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
@@ -5481,7 +5696,7 @@
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
       <c r="L37" s="19" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="M37" s="19"/>
       <c r="N37" s="19"/>
@@ -5528,70 +5743,70 @@
   <sheetData>
     <row r="15" spans="1:4">
       <c r="A15" s="16" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="51">
       <c r="A16" s="17" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:4" ht="51">
       <c r="A17" s="17" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28">
       <c r="A18" s="17" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28">
       <c r="A19" s="17" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -5610,330 +5825,330 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17">
       <c r="A1" s="7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17">
       <c r="A2" s="9" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17">
       <c r="A3" s="9" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17">
       <c r="A4" s="9" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17">
       <c r="A5" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17">
       <c r="A6" s="9" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17">
       <c r="A7" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17">
       <c r="A8" s="9" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17">
       <c r="A9" s="9" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17">
       <c r="A10" s="9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17">
       <c r="A11" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17">
       <c r="A12" s="9" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17">
       <c r="A13" s="9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17">
       <c r="A14" s="9" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17">
       <c r="A15" s="9" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17">
       <c r="A16" s="9" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17">
       <c r="A17" s="9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17">
       <c r="A18" s="9" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17">
       <c r="A19" s="9" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17">
       <c r="A20" s="9" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17">
       <c r="A21" s="9" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17">
       <c r="A22" s="9" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17">
       <c r="A23" s="9" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17">
       <c r="A24" s="9" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17">
       <c r="A25" s="9" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17">
       <c r="A26" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17">
       <c r="A27" s="9" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17">
       <c r="A28" s="9" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17">
       <c r="A29" s="9" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17">
       <c r="A30" s="9" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17">
       <c r="A31" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17">
       <c r="A32" s="9" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17">
       <c r="A33" s="9" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17">
       <c r="A34" s="9" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17">
       <c r="A35" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17">
       <c r="A36" s="9" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17">
       <c r="A37" s="9" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17">
       <c r="A38" s="9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17">
       <c r="A39" s="9" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17">
       <c r="A40" s="9" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17">
       <c r="A41" s="9" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -5956,40 +6171,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:2" ht="34" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="702" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A139AEF-2092-EB45-9C09-9E8DB9663B2E}"/>
+  <xr:revisionPtr revIDLastSave="709" documentId="11_6BE08DF89F0657832A60AF55EF513509DE63B29B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41D7067C-F90E-6A44-9976-AA5C86264089}"/>
   <bookViews>
-    <workbookView xWindow="9560" yWindow="2960" windowWidth="39280" windowHeight="24500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5520" yWindow="700" windowWidth="39280" windowHeight="24500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -1674,87 +1674,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Despair, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">deuxième coproduction internationale de RWF avec Dirk Bogarde et Andra Ferreol, deux acteurs importants du cinéma moderne européen, en compétition à Cannes en 1978
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Le mariage de Maria Braun</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, en compétition officielle à Berlin en 1979
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'Année des treize lune</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">s poursuit la réflexion entamée   sur le désespoir. 
-L'épisode réalisé par RWF dans </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'Allemagne en automne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> offre une relecture des actions commises par la RAF sur le mode de l'autofiction.</t>
-    </r>
-  </si>
-  <si>
     <t>film-1978-le-mariage-de-maria-braun</t>
   </si>
   <si>
@@ -2883,6 +2802,47 @@
       <rPr>
         <i/>
         <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Despair, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">deuxième coproduction internationale de RWF avec Dirk Bogarde et Andra Ferreol, deux acteurs importants du cinéma moderne européen, en compétition à Cannes en 1978
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Le mariage de Maria Braun</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, en compétition officielle à Berlin en 1979
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -2891,11 +2851,68 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> poursuit la réflexion entamée sur le désespoir. 
+L'épisode réalisé par RWF dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Allemagne en automne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> offre une relecture des actions commises par la RAF sur le mode de l'autofiction.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'année des treize lunes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> est un projet très personnel pour RWF. Outre son sujet, qui se nourrit du deuil et de la culpabilité liés à la mort d'Armin Meier, RWF y participe à toutes les étapes, y compris le cadrage et le montage. La critique est divisée, entre enthouasisme et rejet, entre lecture sentimentale et lecture politique. 
-"Despair est le film le plus rempli d'espoir que j'ai jamais fait " RWF, </t>
+"</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Despair </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">est le film le plus rempli d'espoir que j'ai jamais fait " RWF, </t>
     </r>
     <r>
       <rPr>
@@ -3253,6 +3270,20 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -3538,20 +3569,6 @@
         <scheme val="none"/>
       </font>
       <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3648,12 +3665,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:N10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID période"/>
@@ -3676,29 +3689,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A1:T37" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="3"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3977,10 +3990,10 @@
         <v>21</v>
       </c>
       <c r="L2" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="M2" s="15" t="s">
         <v>336</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="14" customFormat="1" ht="210">
@@ -4079,7 +4092,7 @@
       </c>
       <c r="K5" s="28"/>
     </row>
-    <row r="6" spans="1:14" ht="319">
+    <row r="6" spans="1:14" ht="332">
       <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
@@ -4093,7 +4106,7 @@
         <v>40</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>264</v>
@@ -4142,7 +4155,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>290</v>
@@ -4151,7 +4164,7 @@
         <v>291</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>49</v>
@@ -4176,7 +4189,7 @@
         <v>52</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>272</v>
@@ -4200,13 +4213,13 @@
         <v>1982</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>56</v>
@@ -5035,7 +5048,7 @@
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
@@ -5069,14 +5082,14 @@
         <v>27</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>255</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
@@ -5105,7 +5118,7 @@
         <v>33</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>288</v>
@@ -5114,7 +5127,7 @@
         <v>131</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
@@ -5184,11 +5197,11 @@
         <v>132</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G24" s="24"/>
       <c r="H24" s="19"/>
@@ -5220,7 +5233,7 @@
       <c r="D25" s="27"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G25" s="24"/>
       <c r="H25" s="19"/>
@@ -5258,7 +5271,7 @@
         <v>134</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G26" s="19" t="s">
         <v>259</v>
@@ -5300,7 +5313,7 @@
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="25" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
@@ -5332,7 +5345,7 @@
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="25" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="15" t="s">
@@ -5364,7 +5377,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="25" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>260</v>
@@ -5401,26 +5414,26 @@
         <v>44</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
       <c r="K30" s="19"/>
       <c r="L30" s="15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M30" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="N30" s="19" t="s">
         <v>334</v>
-      </c>
-      <c r="N30" s="19" t="s">
-        <v>335</v>
       </c>
       <c r="O30" s="19"/>
       <c r="P30" s="19"/>
@@ -5445,10 +5458,10 @@
         <v>286</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="15"/>
@@ -5477,19 +5490,19 @@
         <v>48</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
@@ -5498,7 +5511,7 @@
         <v>137</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M32" s="19"/>
       <c r="N32" s="19"/>
@@ -5523,10 +5536,10 @@
       <c r="C33" s="1"/>
       <c r="D33" s="25"/>
       <c r="E33" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="G33" s="15" t="s">
         <v>339</v>
@@ -5560,19 +5573,19 @@
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>139</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
@@ -5602,13 +5615,13 @@
         <v>53</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>140</v>
@@ -5642,11 +5655,11 @@
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>266</v>
@@ -5688,7 +5701,7 @@
         <v>57</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
@@ -6092,7 +6105,7 @@
         <v>228</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17">

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frederiquehammerli/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FDAE5B-7F65-8C43-B511-7F09BBCED8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{87FDAE5B-7F65-8C43-B511-7F09BBCED8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A5380B5-DA5F-E047-88BF-C7408B5A262F}"/>
   <bookViews>
-    <workbookView xWindow="13800" yWindow="1120" windowWidth="26580" windowHeight="24080" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7620" yWindow="1120" windowWidth="26580" windowHeight="24080" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="368">
   <si>
     <t>ID période</t>
   </si>
@@ -420,9 +420,6 @@
   </si>
   <si>
     <t>Fassbinder_fox.jpeg</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>M. Klein de Joseph Losey</t>
@@ -971,10 +968,6 @@
 L’arrivée du millionième travailleur immigré en RFA donne lieu à une célébration médiatique : les Gastarbeiter sont publiquement présentés comme les acteurs du miracle économique, alors même que leur installation reste pensée comme provisoire.</t>
   </si>
   <si>
-    <t>Une grande coalition chrétienne-démocrate voit le jour sous l'autorité du nouveau chancelier Kurt Georg Kiesinger. Willy Brandt est ministre des affaires étrangères et vice-chancelier.
-La Grande Coalition CDU-SPD réduit l’opposition parlementaire et favorise l’essor d’une opposition extraparlementaire, particulièrement active dans les milieux étudiants. Les 15-29 ans représentent près de 22 % de la population.</t>
-  </si>
-  <si>
     <t>La pièce outrage au public du dramaturge allemand Peter Handke témoigne du goût de l'avant-garde  artistique subentionnée pour une forme de provocation à l'égard du public, manière paradoxale de s'affranchir de la tutelle culturelle dont ils bénéficient.
 La publication du Journal de Spandau d’Albert Speer participe à la mise en récit du passé nazi.
 Le rock et les cultures venues des États-Unis, de Grande-Bretagne et de France gagnent en légitimité. Chansons et culture populaire diffusent des idées critiques envers l’État, la famille, la religion, les rapports de genre et les formes traditionnelles d’autorité.</t>
@@ -982,11 +975,6 @@
   <si>
     <t>Émergence de l'Anti-teater à Munich. Influence de la Nouvelle Vague française. Le cinéma devient politique et théorique.
 La redécouverte de l’École de Francfort nourrit la critique du capitalisme, de la consommation et des structures d’autorité. La revue Konkret, dont Ulrike Meinhof est rédactrice en chef, devient l’un des relais intellectuels de la gauche radicale.</t>
-  </si>
-  <si>
-    <t>Une majorité sociale-libérale place Willy Brandt au pouvoir.
-Willy Brandt engage une politique de rapprochement avec la RDA et le bloc de l’Est. Environ deux millions d’étrangers vivent en RFA ; les Gastarbeiter occupent souvent les emplois les plus pénibles et les moins bien payés et subissent des discriminations.
-La réforme du paragraphe 175 accompagne l’assouplissement de la répression de l’homosexualité. Après leur condamnation en appel, Baader, Ensslin et leurs camarades passent dans la clandestinité.</t>
   </si>
   <si>
     <t>Le premier choc pétrolier met fin à la haute croissance et entraîne l’arrêt du recrutement de Gastarbeiter. Cette décision favorise ensuite l’installation durable des travailleurs déjà présents et le regroupement familial.</t>
@@ -1676,15 +1664,6 @@
 La RFA atteint le plein emploi et signe de nouveaux accords de recrutement avec la Grèce et l’Espagne. La croissance et l’immigration de travail deviennent deux dimensions indissociables du modèle ouest-allemand.</t>
   </si>
   <si>
-    <t>Construction du Mur de Berlin (1961). Procès d'Auschwitz à Francfort (1963-1965). Démission d'Adenauer. Grande Coalition (1966).
-Le Mur matérialise la division allemande, tandis que les procès Eichmann et d’Auschwitz replacent les crimes nazis au centre du débat public. La fin de l’ère Adenauer et la Grande Coalition accompagnent l’émergence d’une nouvelle génération nombreuse, plus critique envers les institutions et l’autorité.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mouvements étudiants de 1968. Tentative d'assassinat contre Rudi Dutschke, marxiste et  figure de l’opposition étudiante. Victoire de Willy Brandt (SPD, 1969). Abrogation partielle de l'article 175 (homosexualité).
-La contestation étudiante dénonce à la fois la guerre du Vietnam, les continuités autoritaires de la RFA et l’aliénation produite par la société de consommation. La tentative d’assassinat de Rudi Dutschke, les incendies de grands magasins et l’adoption des lois d’exception installent un climat de violence.  Beate Klarsfeld, une militante de la mémoire qui vient d’être licenciée en France de l’office Franco-allemand de la jeunesse pour son activisme, gifle le chancelier Kiesinger
-À l’Est, l’écrasement du Printemps de Prague dissipe les espoirs d’un « socialisme à visage humain ». </t>
-  </si>
-  <si>
     <t>Le chancelier Willy Brandt se rend en Pologne et s'agenouille devant le mémorial du ghetto de Varsovie.Le geste de Willy Brandt s'acccompagne de la reconnaissance de la frontière Oder-Neisse avec la Pologne.
 L’abaissement de la majorité électorale à 18 ans reconnaît  et intègre la politisation de la jeunesse. 
 La libération armée d’Andreas Baader, à laquelle participe Ulrike Meinhof, puis le manifeste « Bâtir l’Armée rouge » marquent la naissance de la RAF. Le groupe se finance par des braquages.
@@ -3032,11 +3011,6 @@
     </r>
   </si>
   <si>
-    <t>Willy Brandt démissionne : aGuillaume, un de ses conseillers est démasqué comme espion de la RDA. cependant l'Ostpolitik qu'il a initiée se poursuit.
-Environ quatre millions d’étrangers vivent désormais en RFA.
-Ulrike Meinhof est condamnée à huit ans de prison pour son implication dans l'évasion de Baader. Les détenus de la RAF dénoncent l’isolement carcéral et multiplient les grèves de la faim ; Holger Meins en meurt. Jean-Paul Sartre rencontre Andreas Baader à la prison de Stuttgart-Stammheim et critique publiquement ses conditions de détention.</t>
-  </si>
-  <si>
     <t>Tensions sociales et crises du logement (Westend). Débats sur la visibilité des minorités. Lois limitant les libertés civiles.
 Confronté à l’enlèvement du candidat CDU Peter Lorenz par le Mouvement du 2-Juin ; le gouvernement ouest-allemand autorise  la libération de cinq militants de la RAD. La prise d’otages de l’ambassade de RFA à Stockholm par un commando de la RAF s’achève dans le sang.
 Le procès des principaux dirigeants de la RAF s’ouvre à Stuttgart-Stammheim, tandis que se structurent en Allemagne et à l’étranger des comités de soutien.</t>
@@ -3342,13 +3316,87 @@
     <t xml:space="preserve">Automne Allemand (1977) : enlèvement de Schleyer, détournement du Landshut, morts à Stammheim.
 La réforme du droit de la famille supprime l’obligation faite à l’épouse de se consacrer prioritairement au foyer et lui permet de travailler sans l’autorisation de son mari.
 Avril : Le procureur fédéral Sigfried Bubak est assassiné avec son chauffeur et son garde du corps. L’offensive 77, qui se développe dans le contexte du procès des leaders de la RAF, est lancée. Après 192 jours de procès à Stammheim, les accusés du groupe Baader sont condamnés pour assassinat à une peine d'emprisonnement à perpétuité. Juillet 1977 :  Jürgen Ponto, président de la Dresdner Bank est assassiné par un commando dont fait partie sa filleule. L’automne allemand de 1977 désigne un climat de terreur et d’oppression qui règne en RAD, apogée de qui est nommé « les années de plomb ». Septembre 1977 : pour obtenir la libération de ses membres détenus à la prison de Stuttgart-Stammheim, la RAF enlève le président du patronat allemand Hanns Martin Schleyer. Il est dénoncé comme ancien membre du parti nazi et des SS. Onze prisonniers sont réclamés en échange de sa vie. La famille Schleyer n'a pas le droit de payer la rançon. Octobre 1977 : un avion de la Lufthansa est détourné sur Mogadiscio en Somalie par le commando palestinien « Martyr Halimeh », prenant en otages 86 passagers et cinq membres d'équipage. Le commando assassine le commandant de bord. La prise d'otages prend fin avec l'intervention des forces spéciales allemandes durant laquelle trois des quatre membres du commando palestinien sont tués. Le même jour, les autorités allemandes annoncent la mort d'Andreas Baader, Gudrun Ensslin, la compagne de Baader, et Jan-Carl Raspe, par suicide lors de ce qu'il est convenu d'appeler « la nuit de la mort de Stammheim ». En représailles, la RAF annonce la mort de Hanns Martin Schleyer. Son corps est retrouvé dans le coffre d'une automobile à Mulhouse, en France. Brigitte Mohnhaupt, leader de la seconde génération, impliquée dans ce meurtre, est alors considérée comme la femme la plus dangereuse d'Allemagne. Novembre 1977 : Ingrid Shubert est retrouvée pendue dans sa cellule de la prison de Munich. </t>
+  </si>
+  <si>
+    <t>Construction du Mur de Berlin (1961). Procès d'Auschwitz à Francfort (1963-1965). Démission d'Adenauer. Le chancelier Erhard (CDU) est chancelier jusqu'en 1966. Grande Coalition CDU-SPD en 1966.
+Le Mur matérialise la division allemande, tandis que les procès Eichmann et d’Auschwitz replacent les crimes nazis au centre du débat public. La fin de l’ère Adenauer et la Grande Coalition accompagnent l’émergence d’une nouvelle génération nombreuse, plus critique envers les institutions et l’autorité.</t>
+  </si>
+  <si>
+    <t>Erhard.jpg</t>
+  </si>
+  <si>
+    <t>Le chancelier Ehrard (CDU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une grande coalition chrétienne-démocrate voit le jour sous l'autorité du nouveau chancelier Kurt Georg Kiesinger. Willy Brandt est ministre des affaires étrangères et vice-chancelier.
+La Grande Coalition CDU-SPD réduit l’opposition parlementaire et favorise l’essor d’une opposition extraparlementaire, particulièrement active dans les milieux étudiants. Les 15-29 ans représentent près de 22 % de la population.
+</t>
+  </si>
+  <si>
+    <t>2 Juin : l’étudiant Bennon Ohnesorg est tué par un policier lors d’une manifestation contre le Shah d’Iran. Les mouvements protestataires font le parallèle avec le IIIème Reich : se développe alors un discours critique à l’égard de la génération précédente et de son rôle, favorable ou passif, face que nazisme. La radicalisation des mouvements d'extrême-gauche est en cours.</t>
+  </si>
+  <si>
+    <t>Rudi DUTSCHKE, figure de proue de la contestation estudiantine en RFA|https://www.ina.fr/ina-eclaire-actu/video/caf86014980/l-allemagne-de-rudi-le-rouge</t>
+  </si>
+  <si>
+    <t>Une majorité sociale-libérale place Willy Brandt (SPD) au pouvoir.
+Willy Brandt engage une politique de rapprochement avec la RDA et le bloc de l’Est. Environ deux millions d’étrangers vivent en RFA ; les Gastarbeiter occupent souvent les emplois les plus pénibles et les moins bien payés et subissent des discriminations.
+La réforme du paragraphe 175 accompagne l’assouplissement de la répression de l’homosexualité. Après leur condamnation en appel, Baader, Ensslin et leurs camarades passent dans la clandestinité.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouvements étudiants de 1968. Tentative d'assassinat contre Rudi Dutschke, marxiste et  figure de l’opposition étudiante. 
+La contestation étudiante dénonce à la fois la guerre du Vietnam, les continuités autoritaires de la RFA et l’aliénation produite par la société de consommation. La tentative d’assassinat de Rudi Dutschke, les incendies de grands magasins et l’adoption des lois d’exception installent un climat de violence.  Beate Klarsfeld, une militante de la mémoire qui vient d’être licenciée en France de l’office Franco-allemand de la jeunesse pour son activisme, gifle le chancelier Kiesinger
+À l’Est, l’écrasement du Printemps de Prague dissipe les espoirs d’un « socialisme à visage humain ». </t>
+  </si>
+  <si>
+    <t>Brandt.jpg</t>
+  </si>
+  <si>
+    <t>Le chancelier Willy Brandt (SPD)</t>
+  </si>
+  <si>
+    <t>Kiesinger.jpg</t>
+  </si>
+  <si>
+    <t>Le chancelier Kiesinger (Grande Coalition CDU-SPD)</t>
+  </si>
+  <si>
+    <t>Schmidt.jpg</t>
+  </si>
+  <si>
+    <t>Le chancelier Helmut Schmidt (SPD)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">RWF interprète Fox dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Le droit du plus fort</t>
+    </r>
+  </si>
+  <si>
+    <t>Willy Brandt démissionne : aGuillaume, un de ses conseillers est démasqué comme espion de la RDA. cependant l'Ostpolitik qu'il a initiée se poursuit. Helmut Schmidt (SPD) lui succède.
+Environ quatre millions d’étrangers vivent désormais en RFA.
+Ulrike Meinhof est condamnée à huit ans de prison pour son implication dans l'évasion de Baader. Les détenus de la RAF dénoncent l’isolement carcéral et multiplient les grèves de la faim ; Holger Meins en meurt. Jean-Paul Sartre rencontre Andreas Baader à la prison de Stuttgart-Stammheim et critique publiquement ses conditions de détention.</t>
+  </si>
+  <si>
+    <t>Kohl.jpg</t>
+  </si>
+  <si>
+    <t>Le Chancelier Hemult Kohl (CDU)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -3497,8 +3545,14 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3535,6 +3589,12 @@
         <fgColor theme="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -3561,7 +3621,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3661,6 +3721,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3676,6 +3739,166 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
@@ -3918,166 +4141,6 @@
         <sz val="10"/>
         <name val="Arial"/>
         <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
       </font>
     </dxf>
   </dxfs>
@@ -4162,52 +4225,52 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:N10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID période" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre période" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="question directrice" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Événement histoire et politique" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Contexte culturel" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Biographie de Fassbinder" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Œuvres" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="ID films - Œuvres" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Analyse et réception critique" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Liens" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Citation" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Image" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Legende" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Notion" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID période" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre période" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="question directrice" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Événement histoire et politique" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Contexte culturel" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Biographie de Fassbinder" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Œuvres" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="ID films - Œuvres" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Analyse et réception critique" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Liens" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Citation" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Image" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Legende" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Notion" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tableau1" displayName="Tableau1" ref="A1:T37" totalsRowShown="0" dataDxfId="36">
   <autoFilter ref="A1:T37" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Année" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ID période" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Événement histoire et politique" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Contexte culturel" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biographie de Fassbinder" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Œuvres" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Analyse et Réception critique" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Liens" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Extraits" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Description de l'extrait" dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Consigne d'analyse" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Citation" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Image 1" dataDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Légende 1" dataDxfId="22"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Image 2" dataDxfId="21"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Légende 2" dataDxfId="20"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Image 3" dataDxfId="19"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Légende 3" dataDxfId="18"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Notion" dataDxfId="17"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Source" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4464,10 +4527,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="E2" s="22" t="s">
         <v>243</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>244</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>17</v>
@@ -4478,7 +4541,7 @@
         <v/>
       </c>
       <c r="I2" s="22" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>18</v>
@@ -4505,10 +4568,10 @@
         <v>24</v>
       </c>
       <c r="D3" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="E3" s="22" t="s">
         <v>245</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>246</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>25</v>
@@ -4519,7 +4582,7 @@
         <v/>
       </c>
       <c r="I3" s="22" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="J3" s="29" t="s">
         <v>26</v>
@@ -4542,10 +4605,10 @@
         <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>31</v>
@@ -4579,10 +4642,10 @@
         <v>37</v>
       </c>
       <c r="D5" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="E5" s="22" t="s">
         <v>248</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>249</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>38</v>
@@ -4595,7 +4658,7 @@
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="J5" s="23"/>
       <c r="K5" s="32"/>
@@ -4614,10 +4677,10 @@
         <v>42</v>
       </c>
       <c r="D6" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>250</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>251</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>43</v>
@@ -4647,10 +4710,10 @@
         <v>47</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>48</v>
@@ -4682,10 +4745,10 @@
         <v>53</v>
       </c>
       <c r="D8" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>253</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>254</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>54</v>
@@ -4719,10 +4782,10 @@
         <v>60</v>
       </c>
       <c r="D9" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="E9" s="23" t="s">
         <v>255</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>256</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>61</v>
@@ -4752,10 +4815,10 @@
         <v>64</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>65</v>
@@ -4876,10 +4939,10 @@
         <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>80</v>
@@ -4914,10 +4977,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>260</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>81</v>
@@ -4952,10 +5015,10 @@
         <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="13"/>
@@ -4988,10 +5051,10 @@
         <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="13"/>
@@ -5003,7 +5066,7 @@
         <v>85</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>86</v>
@@ -5030,10 +5093,10 @@
         <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="13"/>
@@ -5070,10 +5133,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>90</v>
@@ -5112,10 +5175,10 @@
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>92</v>
@@ -5152,10 +5215,10 @@
         <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>93</v>
@@ -5196,10 +5259,10 @@
         <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -5236,10 +5299,10 @@
         <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -5280,10 +5343,10 @@
         <v>22</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>100</v>
@@ -5316,10 +5379,10 @@
         <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>101</v>
@@ -5358,10 +5421,10 @@
         <v>22</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -5396,17 +5459,17 @@
         <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>103</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="13" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
@@ -5438,10 +5501,10 @@
         <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>104</v>
@@ -5478,7 +5541,7 @@
         <v>28</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="1" t="s">
@@ -5527,7 +5590,7 @@
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
       <c r="L18" s="13" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>88</v>
@@ -5552,10 +5615,10 @@
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>107</v>
@@ -5579,8 +5642,12 @@
       <c r="N19" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
+      <c r="O19" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>352</v>
+      </c>
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
       <c r="S19" s="13"/>
@@ -5596,7 +5663,7 @@
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
@@ -5611,8 +5678,12 @@
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
+      <c r="O20" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="P20" s="13" t="s">
+        <v>352</v>
+      </c>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
       <c r="S20" s="13"/>
@@ -5630,14 +5701,14 @@
         <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>276</v>
+        <v>353</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
@@ -5645,12 +5716,20 @@
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
+      <c r="M21" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
       <c r="S21" s="13"/>
       <c r="T21" s="13"/>
       <c r="U21" s="2" t="str">
@@ -5666,10 +5745,10 @@
         <v>35</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>114</v>
@@ -5683,9 +5762,13 @@
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
+      <c r="M22" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="O22" s="36"/>
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
@@ -5704,10 +5787,10 @@
         <v>35</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>310</v>
+        <v>357</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>38</v>
@@ -5716,13 +5799,19 @@
       <c r="G23" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="H23" s="13"/>
+      <c r="H23" s="13" t="s">
+        <v>355</v>
+      </c>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
+      <c r="M23" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="N23" s="37" t="s">
+        <v>361</v>
+      </c>
       <c r="O23" s="13"/>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
@@ -5742,14 +5831,14 @@
         <v>35</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>279</v>
+        <v>356</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G24" s="17"/>
       <c r="H24" s="13"/>
@@ -5757,8 +5846,12 @@
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
+      <c r="M24" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>359</v>
+      </c>
       <c r="O24" s="13"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
@@ -5776,12 +5869,12 @@
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D25" s="34"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G25" s="17"/>
       <c r="H25" s="13"/>
@@ -5789,8 +5882,12 @@
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
+      <c r="M25" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="N25" s="13" t="s">
+        <v>359</v>
+      </c>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
@@ -5810,7 +5907,7 @@
         <v>40</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>117</v>
@@ -5835,10 +5932,14 @@
         <v>122</v>
       </c>
       <c r="N26" s="15" t="s">
-        <v>333</v>
-      </c>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
+        <v>328</v>
+      </c>
+      <c r="O26" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="P26" s="13" t="s">
+        <v>359</v>
+      </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1" t="s">
@@ -5856,25 +5957,29 @@
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="18" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="35" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="15"/>
+      <c r="M27" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>359</v>
+      </c>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -5892,14 +5997,14 @@
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="18" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="36"/>
@@ -5907,8 +6012,12 @@
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="15"/>
+      <c r="M28" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="N28" s="13" t="s">
+        <v>359</v>
+      </c>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
@@ -5926,12 +6035,12 @@
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="18" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>123</v>
@@ -5941,10 +6050,18 @@
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
+      <c r="M29" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="N29" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>363</v>
+      </c>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
@@ -5962,35 +6079,39 @@
         <v>46</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
       <c r="L30" s="13" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>124</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="O30" s="13"/>
-      <c r="P30" s="13"/>
+        <v>364</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>363</v>
+      </c>
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
       <c r="S30" s="13"/>
@@ -6008,16 +6129,16 @@
         <v>46</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="F31" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="13"/>
@@ -6025,8 +6146,12 @@
       <c r="J31" s="13"/>
       <c r="K31" s="13"/>
       <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
+      <c r="M31" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>363</v>
+      </c>
       <c r="O31" s="13"/>
       <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
@@ -6046,31 +6171,35 @@
         <v>51</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="F32" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="G32" s="13" t="s">
         <v>128</v>
-      </c>
-      <c r="G32" s="13" t="s">
-        <v>129</v>
       </c>
       <c r="H32" s="13"/>
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
       <c r="K32" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
+        <v>336</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>363</v>
+      </c>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
@@ -6092,23 +6221,27 @@
       <c r="C33" s="1"/>
       <c r="D33" s="18"/>
       <c r="E33" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="H33" s="13"/>
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
       <c r="K33" s="13"/>
       <c r="L33" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
+        <v>337</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>363</v>
+      </c>
       <c r="O33" s="13"/>
       <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
@@ -6128,29 +6261,33 @@
         <v>51</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
+      <c r="M34" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>363</v>
+      </c>
       <c r="O34" s="13"/>
       <c r="P34" s="13"/>
       <c r="Q34" s="13"/>
@@ -6170,29 +6307,33 @@
         <v>58</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>61</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H35" s="13"/>
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
       <c r="L35" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
+        <v>338</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>363</v>
+      </c>
       <c r="O35" s="13"/>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
@@ -6212,27 +6353,31 @@
         <v>58</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
       <c r="L36" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
+        <v>339</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>363</v>
+      </c>
       <c r="O36" s="13"/>
       <c r="P36" s="13"/>
       <c r="Q36" s="13"/>
@@ -6252,16 +6397,16 @@
         <v>1982</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
@@ -6269,10 +6414,14 @@
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
       <c r="L37" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
+        <v>340</v>
+      </c>
+      <c r="M37" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="N37" s="13" t="s">
+        <v>367</v>
+      </c>
       <c r="O37" s="13"/>
       <c r="P37" s="13"/>
       <c r="Q37" s="13"/>
@@ -6315,70 +6464,70 @@
   <sheetData>
     <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="C15" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="D15" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A16" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>139</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>140</v>
       </c>
       <c r="D16" s="11"/>
     </row>
     <row r="17" spans="1:4" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A17" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="D17" s="11" t="s">
         <v>143</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" x14ac:dyDescent="0.15">
       <c r="A18" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="D18" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" x14ac:dyDescent="0.15">
       <c r="A19" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="C19" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="D19" s="11" t="s">
         <v>150</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -6397,330 +6546,330 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>154</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>166</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>174</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>230</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>232</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -6742,40 +6891,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:2" ht="45.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{87FDAE5B-7F65-8C43-B511-7F09BBCED8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A5380B5-DA5F-E047-88BF-C7408B5A262F}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{87FDAE5B-7F65-8C43-B511-7F09BBCED8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75E1538E-30D9-C949-8C87-8AD658F42C5E}"/>
   <bookViews>
-    <workbookView xWindow="7620" yWindow="1120" windowWidth="26580" windowHeight="24080" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11100" yWindow="1620" windowWidth="26580" windowHeight="18620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="370">
   <si>
     <t>ID période</t>
   </si>
@@ -966,11 +966,6 @@
   <si>
     <t>Procès d'Eichmann à Jerusalem
 L’arrivée du millionième travailleur immigré en RFA donne lieu à une célébration médiatique : les Gastarbeiter sont publiquement présentés comme les acteurs du miracle économique, alors même que leur installation reste pensée comme provisoire.</t>
-  </si>
-  <si>
-    <t>La pièce outrage au public du dramaturge allemand Peter Handke témoigne du goût de l'avant-garde  artistique subentionnée pour une forme de provocation à l'égard du public, manière paradoxale de s'affranchir de la tutelle culturelle dont ils bénéficient.
-La publication du Journal de Spandau d’Albert Speer participe à la mise en récit du passé nazi.
-Le rock et les cultures venues des États-Unis, de Grande-Bretagne et de France gagnent en légitimité. Chansons et culture populaire diffusent des idées critiques envers l’État, la famille, la religion, les rapports de genre et les formes traditionnelles d’autorité.</t>
   </si>
   <si>
     <t>Émergence de l'Anti-teater à Munich. Influence de la Nouvelle Vague française. Le cinéma devient politique et théorique.
@@ -3390,6 +3385,57 @@
   </si>
   <si>
     <t>Le Chancelier Hemult Kohl (CDU)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La pièce </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>outrage au public</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> du dramaturge allemand Peter Handke témoigne du goût de l'avant-garde  artistique subentionnée pour une forme de provocation à l'égard du public, manière paradoxale de s'affranchir de la tutelle culturelle dont ils bénéficient.
+La publication du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Journal de Spandau</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> d’Albert Speer participe à la mise en récit du passé nazi.
+Le rock et les cultures venues des États-Unis, de Grande-Bretagne et de France gagnent en légitimité. Chansons et culture populaire diffusent des idées critiques envers l’État, la famille, la religion, les rapports de genre et les formes traditionnelles d’autorité.</t>
+    </r>
+  </si>
+  <si>
+    <t>Fassbinder_jeunesse.jpeg</t>
+  </si>
+  <si>
+    <t>RWF jeune</t>
   </si>
 </sst>
 </file>
@@ -4222,6 +4268,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4541,7 +4591,7 @@
         <v/>
       </c>
       <c r="I2" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>18</v>
@@ -4582,7 +4632,7 @@
         <v/>
       </c>
       <c r="I3" s="22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J3" s="29" t="s">
         <v>26</v>
@@ -4605,7 +4655,7 @@
         <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>246</v>
@@ -4658,7 +4708,7 @@
         <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J5" s="23"/>
       <c r="K5" s="32"/>
@@ -4713,7 +4763,7 @@
         <v>251</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>48</v>
@@ -4815,7 +4865,7 @@
         <v>64</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>256</v>
@@ -4942,7 +4992,7 @@
         <v>257</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>80</v>
@@ -5051,10 +5101,10 @@
         <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>286</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>287</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="13"/>
@@ -5066,7 +5116,7 @@
         <v>85</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>86</v>
@@ -5096,7 +5146,7 @@
         <v>262</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="13"/>
@@ -5178,7 +5228,7 @@
         <v>265</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>92</v>
@@ -5218,7 +5268,7 @@
         <v>266</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>93</v>
@@ -5302,7 +5352,7 @@
         <v>269</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -5346,7 +5396,7 @@
         <v>270</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>100</v>
@@ -5379,10 +5429,10 @@
         <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>101</v>
@@ -5421,10 +5471,10 @@
         <v>22</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -5462,14 +5512,14 @@
         <v>271</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>103</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
@@ -5501,10 +5551,10 @@
         <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>104</v>
@@ -5590,7 +5640,7 @@
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
       <c r="L18" s="13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>88</v>
@@ -5618,7 +5668,7 @@
         <v>273</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>107</v>
@@ -5643,10 +5693,10 @@
         <v>112</v>
       </c>
       <c r="O19" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="P19" s="13" t="s">
         <v>351</v>
-      </c>
-      <c r="P19" s="13" t="s">
-        <v>352</v>
       </c>
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
@@ -5676,13 +5726,17 @@
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
+      <c r="M20" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>369</v>
+      </c>
       <c r="O20" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="P20" s="13" t="s">
         <v>351</v>
-      </c>
-      <c r="P20" s="13" t="s">
-        <v>352</v>
       </c>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
@@ -5701,14 +5755,14 @@
         <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>275</v>
+        <v>367</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
@@ -5717,16 +5771,16 @@
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
       <c r="M21" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="N21" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="N21" s="13" t="s">
-        <v>352</v>
-      </c>
       <c r="O21" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="P21" s="13" t="s">
         <v>360</v>
-      </c>
-      <c r="P21" s="13" t="s">
-        <v>361</v>
       </c>
       <c r="Q21" s="36"/>
       <c r="R21" s="36"/>
@@ -5745,10 +5799,10 @@
         <v>35</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>114</v>
@@ -5763,10 +5817,10 @@
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
       <c r="M22" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>360</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>361</v>
       </c>
       <c r="O22" s="36"/>
       <c r="P22" s="13"/>
@@ -5787,10 +5841,10 @@
         <v>35</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>38</v>
@@ -5800,17 +5854,17 @@
         <v>116</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
       <c r="M23" s="37" t="s">
+        <v>359</v>
+      </c>
+      <c r="N23" s="37" t="s">
         <v>360</v>
-      </c>
-      <c r="N23" s="37" t="s">
-        <v>361</v>
       </c>
       <c r="O23" s="13"/>
       <c r="P23" s="13"/>
@@ -5831,14 +5885,14 @@
         <v>35</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G24" s="17"/>
       <c r="H24" s="13"/>
@@ -5847,10 +5901,10 @@
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
       <c r="M24" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="N24" s="13" t="s">
         <v>358</v>
-      </c>
-      <c r="N24" s="13" t="s">
-        <v>359</v>
       </c>
       <c r="O24" s="13"/>
       <c r="P24" s="13"/>
@@ -5869,12 +5923,12 @@
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D25" s="34"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G25" s="17"/>
       <c r="H25" s="13"/>
@@ -5883,10 +5937,10 @@
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
       <c r="M25" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="N25" s="13" t="s">
         <v>358</v>
-      </c>
-      <c r="N25" s="13" t="s">
-        <v>359</v>
       </c>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
@@ -5907,7 +5961,7 @@
         <v>40</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>117</v>
@@ -5932,13 +5986,13 @@
         <v>122</v>
       </c>
       <c r="N26" s="15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O26" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="P26" s="13" t="s">
         <v>358</v>
-      </c>
-      <c r="P26" s="13" t="s">
-        <v>359</v>
       </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
@@ -5957,28 +6011,28 @@
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="18" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="35" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
       <c r="M27" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="N27" s="13" t="s">
         <v>358</v>
-      </c>
-      <c r="N27" s="13" t="s">
-        <v>359</v>
       </c>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -5997,14 +6051,14 @@
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="36"/>
@@ -6013,10 +6067,10 @@
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
       <c r="M28" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="N28" s="13" t="s">
         <v>358</v>
-      </c>
-      <c r="N28" s="13" t="s">
-        <v>359</v>
       </c>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
@@ -6035,12 +6089,12 @@
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>123</v>
@@ -6051,16 +6105,16 @@
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
       <c r="M29" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="N29" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="N29" s="13" t="s">
-        <v>359</v>
-      </c>
       <c r="O29" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="P29" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
@@ -6079,38 +6133,38 @@
         <v>46</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E30" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="F30" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="G30" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>346</v>
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
       <c r="L30" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>124</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O30" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="P30" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
@@ -6129,7 +6183,7 @@
         <v>46</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>125</v>
@@ -6138,7 +6192,7 @@
         <v>126</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="13"/>
@@ -6147,10 +6201,10 @@
       <c r="K31" s="13"/>
       <c r="L31" s="13"/>
       <c r="M31" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="N31" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="O31" s="13"/>
       <c r="P31" s="13"/>
@@ -6171,13 +6225,13 @@
         <v>51</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>127</v>
@@ -6192,13 +6246,13 @@
         <v>129</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M32" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="N32" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
@@ -6221,26 +6275,26 @@
       <c r="C33" s="1"/>
       <c r="D33" s="18"/>
       <c r="E33" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="13" t="s">
         <v>316</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>317</v>
       </c>
       <c r="H33" s="13"/>
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
       <c r="K33" s="13"/>
       <c r="L33" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M33" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="N33" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="O33" s="13"/>
       <c r="P33" s="13"/>
@@ -6261,19 +6315,19 @@
         <v>51</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="G34" s="13" t="s">
         <v>320</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>321</v>
       </c>
       <c r="H34" s="13" t="s">
         <v>130</v>
@@ -6283,10 +6337,10 @@
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
       <c r="M34" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="N34" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="O34" s="13"/>
       <c r="P34" s="13"/>
@@ -6307,16 +6361,16 @@
         <v>58</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>61</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>131</v>
@@ -6326,13 +6380,13 @@
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
       <c r="L35" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M35" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="O35" s="13"/>
       <c r="P35" s="13"/>
@@ -6353,30 +6407,30 @@
         <v>58</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
       <c r="L36" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M36" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="N36" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="O36" s="13"/>
       <c r="P36" s="13"/>
@@ -6397,7 +6451,7 @@
         <v>1982</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>132</v>
@@ -6406,7 +6460,7 @@
         <v>65</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
@@ -6414,13 +6468,13 @@
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
       <c r="L37" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M37" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="N37" s="13" t="s">
         <v>366</v>
-      </c>
-      <c r="N37" s="13" t="s">
-        <v>367</v>
       </c>
       <c r="O37" s="13"/>
       <c r="P37" s="13"/>

--- a/RWF_Frise.xlsx
+++ b/RWF_Frise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{87FDAE5B-7F65-8C43-B511-7F09BBCED8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75E1538E-30D9-C949-8C87-8AD658F42C5E}"/>
+  <xr:revisionPtr revIDLastSave="356" documentId="13_ncr:1_{87FDAE5B-7F65-8C43-B511-7F09BBCED8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0674B42B-78C0-FA47-8247-15583F0EBD86}"/>
   <bookViews>
-    <workbookView xWindow="11100" yWindow="1620" windowWidth="26580" windowHeight="18620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="980" windowWidth="44800" windowHeight="23260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Périodes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="354">
   <si>
     <t>ID période</t>
   </si>
@@ -81,12 +81,6 @@
     <t>Notion</t>
   </si>
   <si>
-    <t>1945-1946</t>
-  </si>
-  <si>
-    <t>Les ruines l'Heure zéro</t>
-  </si>
-  <si>
     <t>Le "point zéro" de l'histoire de l'Allemagne d'après-guerre est-il un point zéro pour la vie et l'œuvre de RWF ?</t>
   </si>
   <si>
@@ -108,12 +102,6 @@
     <t>1947-1960</t>
   </si>
   <si>
-    <t>Le miracle économique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comment l'Allemagne de l'ouest a-t-elle pu devenir une des premières nations industrielles capitalistes et une démocratie alors même qu'elle était marquée par le provincialisme, l'absence de morale et l'hypocrisie ? </t>
-  </si>
-  <si>
     <t>Enfance marquée par le divorce de ses parents (1951) et l'absence du père. Passion précoce pour le cinéma (refuge). Première lecture de Berlin Alexanderplatz vers 14 ans.</t>
   </si>
   <si>
@@ -123,12 +111,6 @@
     <t>l-industrie-de-l-industrie-automobile-l-usine-volkswagen-vue-de-l-interieur-usine-wolfsburg-vers-1950.jpg</t>
   </si>
   <si>
-    <t>1961-1966</t>
-  </si>
-  <si>
-    <t>naissance du Nouveau cinéma allemand</t>
-  </si>
-  <si>
     <t xml:space="preserve">Que serait un cinéma nouveau prenant à bras le corps l'histoire de l'Allemagne et du cinéma, tout en s'en détachant ? </t>
   </si>
   <si>
@@ -141,106 +123,33 @@
     <t>Documentaire sur le nouveau cinéma allemand</t>
   </si>
   <si>
-    <t>"Le cinéma de Papa est mort. Nous croyons au nouveau cinéma " Manifeste d'Oberhausen (1962)
-« Toute une génération exorcisa son enfance déjà presque oubliée en soulignant sans répit combien étaient encombrantes et dévastatrices les ombres que le passé des parents avaient jetées sur le présent de leurs enfants ».Thomas Elsaesser, RWF un cinéaste d'Allemagne (2005) p.201</t>
-  </si>
-  <si>
-    <t>1967-1970</t>
-  </si>
-  <si>
-    <t>Antitheater et politisation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Qu'-est-ce qu'un cinéaste engagé ? </t>
   </si>
   <si>
     <t>Fonde l' antiteater (1968). Collaboration intense avec sa "troupe" (Schygulla, Hermann, Raab, Baer, Lommel). Mariage avec Ingrid Caven (1970).</t>
   </si>
   <si>
-    <t>L'amour est plus froid que la mort (1969),  Le Bouc (1969)</t>
-  </si>
-  <si>
-    <t>1971-1974</t>
-  </si>
-  <si>
-    <t>Terrorisme et mélodrame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comment faire du cinéma allemand hollywoodien, qui attire et séduise le public le plus large tout en l'amenant à l'analyse et à la réflexion, sans didactisme ? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Découverte des mélodrames de Douglas Sirk grâce à Peer Raben .Liaison avec El Hedi ben Salem. Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. Succès international. Les films de RWF deviennent incontournables dans les grands festivals internationaux (Cannes, Venise, Berlin). </t>
-  </si>
-  <si>
-    <t>Période Sirkienne : Le Marchand des quatre saisons (1971). Tous les autres s'appellent Ali (1974, succès mondial à Cannes) : critique du racisme ordinaire. Martha (1974).</t>
-  </si>
-  <si>
     <t>Dans les mélodrames de RWF , les personnages tentent en vain de s'affranchir des positions aliénantes produites par la famille, le couple, au sein du système capitaliste et de la classe bourgeoise. Une analogie s'établit alors entre famille et Allemagne. Le mélodrame fassbindérien met en scène des crises identitaires du sujet, comme crises de la perception (du regard), qui se traduisent par une mise en crise de l'image (image de soi et image du film). Les films font dialoguer subjectivité et affects avec mécanismes sociaux, évitant ainsi toute lecture simpliste et figées de type psychologique ou idéologique. Le mélodrame, en interpénétrant le privé et le public, l'individuel et le collectif, joue d'un trouble qui participe à son caractère critique et progressiste : il est potentiellement facteur de changement pour un spectateur constamment soumis à la réflexion.</t>
   </si>
   <si>
-    <t>1975-1976</t>
-  </si>
-  <si>
     <t xml:space="preserve">Comment le rapport dominant/dominé structure-t-il toute relation, affective ou sociale ? </t>
   </si>
   <si>
-    <t>Scandale théâtral autour de la pièce L'Ordure, la ville et la mort (accusations d'antisémitisme). Liaison avec Armin Meier.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maman Küsters s'en va au ciel (1975). Le Droit du plus fort (1975) : </t>
-  </si>
-  <si>
-    <t>Fassbinder y joue un rôle principal, assumant une visibilité politique de son homosexualité.</t>
-  </si>
-  <si>
-    <t>1977-1979</t>
-  </si>
-  <si>
-    <t>Le retour de l'histoire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jusqu'à quel point les femmes de la trilogie RFA sont-elles une allégorie de la nation allemande ? Quelle distance RWF prend-il avec la critique historique de son pays ? </t>
-  </si>
-  <si>
-    <t>Suicide d'Armin Meier (31 mai 1978). Début de la collaboration avec Juliane Lorenz. Fassbinder se filme en crise, exposant son angoisse face à l'État.</t>
-  </si>
-  <si>
-    <t>L'Année des treize lunes (1978) : œuvre radicale sur le désespoir. Le Mariage de Maria Braun (1979) : triomphe international, allégorie de la reconstruction.</t>
-  </si>
-  <si>
     <t>le cinéaste Edgar Reitz affirme la nécessité " de films, de livres, d'images qui nous fassent reprendre connaissance et rétablissent nos réflexes", Medium, 5/1979, p.21</t>
   </si>
   <si>
     <t>mélodrame</t>
   </si>
   <si>
-    <t>1980-1981</t>
-  </si>
-  <si>
     <t>La fin d'un ère</t>
   </si>
   <si>
-    <t>Quelles ambitions pour la série télévisuelle ?</t>
-  </si>
-  <si>
     <t>Travaille frénétiquement. Réalise son projet de vie : l'adaptation de Döblin. Épuisement physique dû aux excès.</t>
   </si>
   <si>
-    <t>Monumental Berlin Alexanderplatz (1980, 15h). Suite de la Trilogie de la RFA : Lola, une femme allemande (1981) et Lili Marleen (1981).</t>
-  </si>
-  <si>
-    <t>La mort du Maître</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RWF, figure du collectif  politique des années 60 et 70 ou d'héritier de la figure du génie romantique et du poète maudit ? Auteur ou cinéaste populaire ? </t>
-  </si>
-  <si>
     <t>Décès de Fassbinder le 10 juin à Munich, à l'âge de 37 ans (épuisement et overdose).</t>
   </si>
   <si>
-    <t>Le Secret de Veronika Voss (Ours d'Or à Berlin). Querelle (œuvre posthume). Fassbinder laisse un héritage de plus de 40 films.</t>
-  </si>
-  <si>
     <t>Année</t>
   </si>
   <si>
@@ -305,9 +214,6 @@
   </si>
   <si>
     <t>Adenauer.jpeg</t>
-  </si>
-  <si>
-    <t>Portrait d'Adenauer</t>
   </si>
   <si>
     <t xml:space="preserve">La mère de Fassbinder Lisolette Eder, née Pempeit, dite aussi Lilo Pempeit, est hospitalisée pour cause de tuberculose. </t>
@@ -464,61 +370,12 @@
     <t>Histoire allemande</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="409.55"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="409.55"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t>, de Thomas Elsaesser, Centre Pompidou, 2005</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="409.55"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t>, pp. 490-507</t>
-    </r>
-  </si>
-  <si>
     <t>Repères historiques, chronologie politique</t>
   </si>
   <si>
     <t>Fassbinder</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="409.55"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="409.55"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t>, de Thomas Elsaesser, Centre Pompidou, 2005</t>
-    </r>
-  </si>
-  <si>
     <t>Biographie et filmographie</t>
   </si>
   <si>
@@ -817,70 +674,6 @@
   </si>
   <si>
     <t>Lorsqu’une nouvelle fiche Film est créée, ajouter son titre et son ID dans Référentiel films.</t>
-  </si>
-  <si>
-    <t>Capitulation du Troisième Reich (mai). L'Allemagne est en ruines (Année Zéro). Début de l'occupation alliée et de l'amnésie collective sur le passé nazi. Le pays et berlin sont partagés en zone sous contrôle des différentes forces alliées.
-L’« heure zéro » désigne moins une rupture absolue qu’une société de l’effondrement : destructions, déplacements, pertes humaines et continuités avec le personnel du régime précédent. L’occupation alliée engage simultanément division territoriale, dénazification, démilitarisation et apprentissage démocratique, tandis que Nuremberg fonde de nouvelles catégories de justice internationale.</t>
-  </si>
-  <si>
-    <t>Le cinéma est en ruines. Période des films de décombres ( Trümmerfilme ) comme Les assassins sont parmi nous (Staudte, 1946).
-La reconstruction culturelle est pensée comme une rééducation. Presse, édition, radio et cinéma renaissent sous le contrôle des puissances occupantes ; œuvres interdites et artistes exilés retrouvent une place publique. L’esthétique des ruines met en scène la catastrophe matérielle et morale.</t>
-  </si>
-  <si>
-    <t>Création de la RFA (1949). Ère Adenauer. Miracle économique ( Wirtschaftswunder )  entre 1950 et 1965 l'économie ouest-allemande croît de 8,2% en moyenne (contre 5% en France pendant les 30 glorieuses). La coccinelle de Wolkswagen devient l'emblème du "miracle économique". Les entreprise de taille moyenne constituent la colonne vertébrale de la puissance économique allemande en fournissant les outils spécialisés nécessaires à l'industrie. 
-Parallèmement, l'état  développe une politique sociale conservatrice. Réarmement de la RFA (1955).
-La stabilisation de la RFA repose sur la Loi fondamentale, l’ancrage occidental, l’économie sociale de marché et une croissance rapide, soutenue par l’immigration de travail. Ce succès coexiste avec la division durable du pays, la répression du soulèvement est-allemand de 1953, un anticommunisme puissant et d’importantes continuités administratives avec le nazisme.</t>
-  </si>
-  <si>
-    <t>Domination du "cinéma de papa" ( Papas Kino ) : films de terroir ( Heimatfilm ), comédies légères dépolitisées, films en costumes , comédies musicales obitennent toujours les faveurs du public. Ces genres nés dans les années 10 et 20 ont été très exploités par les nazis.
-Freddy Quinn, Rocco Granata ou Catharina Valente sont les stars de la culture populaire allemande. 
-Il n'existe presque aucun film allemand des années 50 et 60 qui traite des camps de concentration nazis. Le cinéma allemand de la période s'intéresse peu à l'histoire.
-Sous l’apparente dépolitisation du Schlager, du Heimatfilm et de la télévision familiale, les écrivains du Groupe 47, la littérature des ruines, Brecht, Andersch, Böll, Adorno et Horkheimer interrogent la guerre, l’exil et les responsabilités collectives. Les modèles culturels américains et le rock transforment progressivement les pratiques de la jeunesse.</t>
-  </si>
-  <si>
-    <t>Manifeste d'Oberhausen (1962) : naissance du Nouveau Cinéma Allemand. Une nouvelle génération de cinéastes s'affirme et conquiert son indépendance notamment par la création de structures de production indépendantes. Fondation de l'école de cinéma DFFB à Berlin (1966).
-Cette génération incarne le phénomène de la "société sans père" et "la crise du patriarcat". L'absence ou la défaillance des pères devient un thème récurrent du Nouveau Cinéma allemand.
-Le Manifeste d’Oberhausen, l’essor de nouvelles structures de production et l’influence du rock, des cultures étrangères et des sciences sociales rompent avec les modèles des années 1950. La crise du père et la confrontation au passé deviennent des motifs structurants du Nouveau Cinéma allemand.</t>
-  </si>
-  <si>
-    <t>Mouvements étudiants de 1968. Tentative d'assassinat contre Rudi Dutschke. Victoire de Willy Brandt (SPD, 1969). Abrogation partielle de l'article 175 (homosexualité).
-De la mort de Benno Ohnesorg à l’adoption des lois d’exception, la contestation étudiante dénonce la guerre du Vietnam, les continuités autoritaires et le refoulement du nazisme. L’arrivée de Willy Brandt, l’Ostpolitik et la réforme du paragraphe 175 ouvrent une phase de réformes, tandis qu’une minorité choisit la clandestinité armée et fonde la RAF.</t>
-  </si>
-  <si>
-    <t>La redécouverte de l’École de Francfort, Le Deuil impossible et la circulation de modèles venus de la Nouvelle Vague, du théâtre d’avant-garde et de la culture rock font de la critique des institutions, de la famille et des représentations un enjeu esthétique autant que politique.</t>
-  </si>
-  <si>
-    <t>Terrorisme de la RAF (arrestations en 1972). Attentat des JO de Munich (1972). Démission de Willy Brandt (1974) suite à l'affaire Guillaume.
-L’Ostpolitik aboutit à la reconnaissance mutuelle des deux Allemagne, mais la période est aussi marquée par les attentats et l’arrestation de la première génération de la RAF, le choc pétrolier, la fin du recrutement des Gastarbeiter et la démission de Willy Brandt. La crise économique et le terrorisme infléchissent le climat réformateur.</t>
-  </si>
-  <si>
-    <t>Fondation du Filmverlag der Autoren (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR).
-Plusieurs cinéastes allemands ( Schlöndorff, Herzog notamment) réalisent des charges politiques violentes contre la politique et la société allemande. Pourtant l'amnnésie historique se poursuit dans le cinéma allemand de fiction. Seuls des documentaires s'emparent de l'histoire du nazisme.
-A parti de 1968 l'industrie du cinéma commercial allemand agonise
-Le cinéma s’appuie sur de nouvelles structures indépendantes et sur la télévision, alors que les cinéastes interrogent plus frontalement l’histoire, la violence et les contradictions de la société ouest-allemande. Les genres populaires deviennent des instruments de distanciation critique.</t>
-  </si>
-  <si>
-    <t>Tensions sociales et crises du logement (Westend). Débats sur la visibilité des minorités. Lois limitant les libertés civiles.
-Procès, enlèvements, prises d’otages et morts en détention installent la RAF au centre du débat public. Les réponses judiciaires et sécuritaires renforcent les tensions autour des libertés civiles, tandis que les réformes de société, notamment sur l’avortement, demeurent limitées et conflictuelles.</t>
-  </si>
-  <si>
-    <t>Automne Allemand (1977) : enlèvement de Schleyer, détournement du Landshut, morts à Stammheim.
-L’Automne allemand concentre l’affrontement entre la RAF et l’État : assassinats, enlèvement de Schleyer, détournement du Landshut et morts de Stammheim. À la fin de la décennie, le retour des tensions Est-Ouest relance les mobilisations pacifistes.</t>
-  </si>
-  <si>
-    <t>Le cinéma allemand s'empare de son histoire passée et récente et réfléchit aux problèmes de représentation qu'elle pose. Film collectif L'Allemagne en automne (1978). La diffusion de la série Holocaust de Marvin J. Chomsky (1979) à la télévision allemande suscite des débats importants, auxquels participent des cinéastes comme Syberberg ou Edgard Reitz. Le mouvement du Nouveau Cinéma allemand atteint son apogée thématique et politique.
-La représentation de l’histoire récente et du nazisme devient un enjeu central. L’Allemagne en automne, Hitler, un film d’Allemagne puis la diffusion de Holocaust confrontent cinéma et télévision aux limites du témoignage, au sentimentalisme, à la mémoire collective et à la capacité des images populaires à rouvrir le passé.</t>
-  </si>
-  <si>
-    <t>Fondation des Verts (1980). Manifestations écologistes. Fin de l'ère sociale-libérale.
-Les mouvements écologistes, féministes et pacifistes se structurent avec la fondation des Verts et les grandes mobilisations contre la course aux armements. Ils reconfigurent un système politique jusque-là dominé par trois partis.</t>
-  </si>
-  <si>
-    <t>Le cinéma allemand poursuit son travail sur la mémoire familiale et nationale, notamment avec Allemagne mère blafarde et le projet Heimat. La télévision devient un lieu majeur pour les récits historiques de longue durée.</t>
-  </si>
-  <si>
-    <t>Mort de Fassbinder marquant symboliquement la fin du Nouveau Cinéma Allemand.
-La mort de Fassbinder symbolise l’épuisement du Nouveau Cinéma allemand comme mouvement collectif, au moment où ses principaux enjeux — histoire nationale, mémoire, culture populaire et télévision — se déplacent vers de nouvelles formes.</t>
   </si>
   <si>
     <t>Les alliés aident à la relance de médias d'information et promeuvent une nouvelle politique éducative. 
@@ -970,9 +763,6 @@
   <si>
     <t>Émergence de l'Anti-teater à Munich. Influence de la Nouvelle Vague française. Le cinéma devient politique et théorique.
 La redécouverte de l’École de Francfort nourrit la critique du capitalisme, de la consommation et des structures d’autorité. La revue Konkret, dont Ulrike Meinhof est rédactrice en chef, devient l’un des relais intellectuels de la gauche radicale.</t>
-  </si>
-  <si>
-    <t>Le premier choc pétrolier met fin à la haute croissance et entraîne l’arrêt du recrutement de Gastarbeiter. Cette décision favorise ensuite l’installation durable des travailleurs déjà présents et le regroupement familial.</t>
   </si>
   <si>
     <t>Après quatre années de débats, l’IVG est autorisée sur indication médico-sociale, tout en demeurant pénalisée hors de ce cadre.
@@ -3011,10 +2801,6 @@
 Le procès des principaux dirigeants de la RAF s’ouvre à Stuttgart-Stammheim, tandis que se structurent en Allemagne et à l’étranger des comités de soutien.</t>
   </si>
   <si>
-    <t xml:space="preserve">Développement du "film amphibie" (cinéma/TV). Le cinéma devient un outil de critique sociale directe.
-</t>
-  </si>
-  <si>
     <t>Le cinéma et la télévision s’emparent des violences politiques, des minorités et des rapports de domination. Le « film amphibie », conçu pour circuler entre petit et grand écran, élargit le public de cette critique sociale.</t>
   </si>
   <si>
@@ -3304,19 +3090,11 @@
     </r>
   </si>
   <si>
-    <t>Victoire d'Helmut Kohl (CDU) en octobre. Fin d'une époque artistique et politique radicale.Kohl se donne comme mission de réconcilier le peuple ouest-allemand avec son passé
-L’accession d’Helmut Kohl à la chancellerie clôt la période sociale-libérale sans rompre avec l’Ostpolitik. Le nouveau gouvernement réaffirme la réunification comme horizon et fait de la coopération franco-allemande un axe majeur.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automne Allemand (1977) : enlèvement de Schleyer, détournement du Landshut, morts à Stammheim.
 La réforme du droit de la famille supprime l’obligation faite à l’épouse de se consacrer prioritairement au foyer et lui permet de travailler sans l’autorisation de son mari.
 Avril : Le procureur fédéral Sigfried Bubak est assassiné avec son chauffeur et son garde du corps. L’offensive 77, qui se développe dans le contexte du procès des leaders de la RAF, est lancée. Après 192 jours de procès à Stammheim, les accusés du groupe Baader sont condamnés pour assassinat à une peine d'emprisonnement à perpétuité. Juillet 1977 :  Jürgen Ponto, président de la Dresdner Bank est assassiné par un commando dont fait partie sa filleule. L’automne allemand de 1977 désigne un climat de terreur et d’oppression qui règne en RAD, apogée de qui est nommé « les années de plomb ». Septembre 1977 : pour obtenir la libération de ses membres détenus à la prison de Stuttgart-Stammheim, la RAF enlève le président du patronat allemand Hanns Martin Schleyer. Il est dénoncé comme ancien membre du parti nazi et des SS. Onze prisonniers sont réclamés en échange de sa vie. La famille Schleyer n'a pas le droit de payer la rançon. Octobre 1977 : un avion de la Lufthansa est détourné sur Mogadiscio en Somalie par le commando palestinien « Martyr Halimeh », prenant en otages 86 passagers et cinq membres d'équipage. Le commando assassine le commandant de bord. La prise d'otages prend fin avec l'intervention des forces spéciales allemandes durant laquelle trois des quatre membres du commando palestinien sont tués. Le même jour, les autorités allemandes annoncent la mort d'Andreas Baader, Gudrun Ensslin, la compagne de Baader, et Jan-Carl Raspe, par suicide lors de ce qu'il est convenu d'appeler « la nuit de la mort de Stammheim ». En représailles, la RAF annonce la mort de Hanns Martin Schleyer. Son corps est retrouvé dans le coffre d'une automobile à Mulhouse, en France. Brigitte Mohnhaupt, leader de la seconde génération, impliquée dans ce meurtre, est alors considérée comme la femme la plus dangereuse d'Allemagne. Novembre 1977 : Ingrid Shubert est retrouvée pendue dans sa cellule de la prison de Munich. </t>
   </si>
   <si>
-    <t>Construction du Mur de Berlin (1961). Procès d'Auschwitz à Francfort (1963-1965). Démission d'Adenauer. Le chancelier Erhard (CDU) est chancelier jusqu'en 1966. Grande Coalition CDU-SPD en 1966.
-Le Mur matérialise la division allemande, tandis que les procès Eichmann et d’Auschwitz replacent les crimes nazis au centre du débat public. La fin de l’ère Adenauer et la Grande Coalition accompagnent l’émergence d’une nouvelle génération nombreuse, plus critique envers les institutions et l’autorité.</t>
-  </si>
-  <si>
     <t>Erhard.jpg</t>
   </si>
   <si>
@@ -3376,73 +3154,811 @@
     </r>
   </si>
   <si>
-    <t>Willy Brandt démissionne : aGuillaume, un de ses conseillers est démasqué comme espion de la RDA. cependant l'Ostpolitik qu'il a initiée se poursuit. Helmut Schmidt (SPD) lui succède.
+    <t>Kohl.jpg</t>
+  </si>
+  <si>
+    <t>Le Chancelier Hemult Kohl (CDU)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La pièce </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>outrage au public</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> du dramaturge allemand Peter Handke témoigne du goût de l'avant-garde  artistique subentionnée pour une forme de provocation à l'égard du public, manière paradoxale de s'affranchir de la tutelle culturelle dont ils bénéficient.
+La publication du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Journal de Spandau</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> d’Albert Speer participe à la mise en récit du passé nazi.
+Le rock et les cultures venues des États-Unis, de Grande-Bretagne et de France gagnent en légitimité. Chansons et culture populaire diffusent des idées critiques envers l’État, la famille, la religion, les rapports de genre et les formes traditionnelles d’autorité.</t>
+    </r>
+  </si>
+  <si>
+    <t>Fassbinder_jeunesse.jpeg</t>
+  </si>
+  <si>
+    <t>RWF jeune</t>
+  </si>
+  <si>
+    <t>Le chancelier Adenauer (CDU)</t>
+  </si>
+  <si>
+    <t>Des ruines de l'Heure zéro à la division</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Retour des intellectuels exilés : Adorno, Horkheimer (École de Francfort), Brecht. 
+Le cinéma est en ruines. Création de la DEFA (Deutsche Film-Aktiengesellschaft) le 17 mai 1946, entreprise d'État monopolistique en zone soviétique, qui produira 740 longs-métrages en RDA jusqu'à sa dissolution en 1992 
+Naissance du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trümmerfilm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (film des ruines) : premier genre cinématographique de l'après-guerre, tourné dans les villes détruites. L</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>es Meurtriers sont parmi nous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Wolfgang Staudte, 1946) — premier film allemand d'après-guerre, produit par la DEFA naissante, avec Hildegard Knef dans son premier rôle. La censure soviétique impose une fin modifiée : que des Allemands se vengent eux-mêmes de criminels nazis est jugé inacceptable . 
+Les Alliés occidentaux pratiquent également le cinéma comme outil de rééducation. La reconstruction culturelle est pensée comme une rééducation. Presse, édition, radio et cinéma renaissent sous le contrôle des puissances occupantes ; œuvres interdites et artistes exilés retrouvent une place publique. 
+des cinéastes étrangers s'intérressent aussi à l'Allemagne et posent un regard sur les ruines : </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">A foreign affair </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(Billy Wilder, 1946) offre un regard satirique sir le Berlin occupé, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Allemagne année zéro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de Rossellini (1948) rend compte, dans la mouvance néoréaliste, de la ruinemorale et matérielle que traverse la population allemande. 
+ </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Deux États allemands : miracle occidental et socialisme d'État </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrée dans l'ère Adenauer (DU), chancelier. La stabilisation de la RFA repose sur la Loi fondamentale, l’ancrage occidental, l’économie sociale de marché et une croissance rapide, soutenue par l’immigration de travail. Ce succès coexiste avec la division durable du pays, la répression du soulèvement est-allemand de 1953, un anticommunisme puissant et d’importantes continuités administratives avec le nazisme.
+La RFA réintègre progressivement les nations occidentales. Accords de Paris (1954) qui mettent fin à l'occupation de l'Allemagne et confèrent à la RFA et la RDA leur  pleine souveraineté. Entrée de la RFA dans l'OTAN (1955) et début du réarmement de la RFA. Traité de Rome (1957) : la RFA est membre fondatrice de la CEE.
+La RDA intégre le pacte de Varsovie. Insurrection ouvrière du 17 juin 1953 à Berlin-Est, réprimée par les chars soviétiques. La RDA soutient politiquement la répression soviétique de l'insurrection hongroise (1956).
+La Guerre Froide devient structurelle : le KPD est interdit en RFA (1956). Ultimatum de Khrouchtchev sur Berlin (1958) en raison de la fuite massive des citoyens est-allemands vers l'Ouest , principalement par Berlin. 2,7 millions de personnes  passeront à l'OUest jusqu'en 1961.
+Miracle économique ( Wirtschaftswunder ) :  Ludwig Erhard, ministre de l'Économie théorise l'« économie sociale de marché » d'essence néo-libérale. Entre 1950 et 1965 l'économie ouest-allemande croît de 8,2% en moyenne (contre 5% en France pendant les 30 glorieuses).Le plein emploi est atteint en 1960). Le système des Gastarbeiter (travailleurs invités) est lancé par traité avec l'Italie (1955), puis Grèce et Espagne (1960).L'absence d'industrie d'armement profite aux secteurs de consommation. La coccinelle de Wolkswagen devient l'emblème du "miracle économique". Le taux d'équipement des ménages (télévision) est en avance de 10 ans sur la France. Les entreprises de taille moyenne constituent la colonne vertébrale de la puissance économique allemande en fournissant les outils spécialisés nécessaires à l'industrie. Parallèmement, l'Etat  développe une politique sociale conservatrice. L'Anticommunisme domine. La société  subit un mouvement de « remasculinisation » : l'égalité des sexes inscrite dans la Loi fondamentale ne s'applique réellement qu'à partir de 1953 (droit de la famille) et le maintien de la femme au foyer est encouragé.RDA : économie planifiée et collectivisée sur le modèle soviétique ; fuite des cerveaux et de la main-d'œuvre vers l'Ouest.
+RFA et Israël : entrée en pourparlers pour les réparations (1951), livraisons d'armes à partir de 1952. en RFA, Création de la Centrale judiciaire de Ludwigsburg (1958) pour poursuivre les criminels nazis.Cependant,  la continuité avec le nazisme est réelle : on retrouve  jusqu'à 40 % d'anciens membres du NSDAP dans les institutions à la fin des années 1950. Création de la Centrale judiciaire de Ludwigsburg (1958) pour poursuivre les criminels nazis.
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sous l’apparente dépolitisation du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Schlager </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(chanson de variété), du</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Heimatfilm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>et de la télévision familiale, les écrivains du Groupe 47, la littérature des ruines, Brecht, Andersch, Böll, Adorno et Horkheimer interrogent la guerre, l’exil et les responsabilités collectives. Les modèles culturels américains et le rock transforment progressivement les pratiques de la jeunesse.
+Freddy Quinn, Rocco Granata ou Catharina Valente sont les stars de la culture populaire allemande (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Schlager)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Le rock est encore associé à une forme de  délinquance de la jeunesse. 
+Le cinéma ouest-allemand se conforme au modèle conservateur et conformiste de la société de consommation : domination du "cinéma de papa" ( Papas Kino ) : films de terroir ( Heimatfilm ), comédies légères dépolitisées, films en costumes , comédies musicales obitennent toujours les faveurs du public. Ces genres nés dans les années 10 et 20 ont été très exploités par les nazis. C'est l'âge d'or du Heimatfilm : la RFA devient la cinquième productrice mondiale de films, mais la majorité de la production est constituée de ces « films de la patrie » de qualité médiocre, tournés dans des paysages alpins idéalisés. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Grün ist die Heide</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Hans Deppe, 1951) exemplifie la fonction de ce genre : traiter indirectement la question des expulsés des territoires orientaux en projetant leurs pertes dans un paysage fantasmé et harmonieux. Le </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Heimatfilm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">est un cinéma  sentimental de fuite de la réalité.
+Il n'existe presque aucun film allemand des années 50 et 60 qui traite des camps de concentration nazis. Le cinéma allemand de la période s'intéresse peu à l'histoire.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Capitulation du Troisième Reich (mai). Bilan humain de la guerre : 4,2 millions de soldats tués, 500 000 morts civils dans les bombardements, 300 000 victimes des persécutions nazies, 11 millions de prisonniers de guerre (dont 3,3 millions en URSS, le dernier rentrant en 1956). L'Allemagne est en ruines (Heure Zéro). L’« heure zéro » désigne moins une rupture absolue qu’une société de l’effondrement : ruines matérielles : 25 % des logements détruits, 20 millions de sans-abri, 90 % du réseau ferroviaire inutilisable, production industrielle de la Ruhr paralysée, pénuries alimentaires. L'inflation est persistante et le chômage élevé (jusqu'en 1951).
+Conférences de Yalta (février 1945) et de Potsdam (juillet 1945) : division de l'Allemagne en quatre zones d'occupation (États-Unis, URSS, Grande-Bretagne, France) et amputation territoriale de 25 % à l'Est (ligne Oder-Neisse).Un gouvernement militaire est placé à la tête de chaque zone.  L’occupation alliée engage simultanément division territoriale, dénazification, démilitarisation et apprentissage démocratique. 
+Procès de Nuremberg (novembre 1945) : création des catégories pénales « crime contre la paix », « crime contre l'humanité ». Cependant face aux divergences croissantes entre Alliés occidentaux et URSS, la dénazification cède le pas à la confrontation des deux blocs. L'article 131 de la Loi fondamentale (1949) permet aux anciens adhérents du NSDAP de réintégrer la fonction publique.
+Fusion des zones américaine et britannique (bizone, décembre 1946), puis française (trizone ,mars 1948). En réaction, blocus de Berlin (juin 1948 et pont aérien allié). Réforme monétaire de juin 1948 : le Deutsche Mark remplace le Reichsmark dans la trizone — acte fondateur de la séparation économique.Création de la RFA (Loi fondamentale du 23 mai 1949) et, par réaction, de la RDA (7 octobre 1949).
+À l'Est, fusion forcée KPD-SPD dans le SED (1946) ; pluralisme encadré.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Mur, stabilisation froide et modernités cinématographiques contrariées </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> De la Grande Coalition à l'Ostpolitik : contestation, réforme et détente (1966-1974)</t>
+  </si>
+  <si>
+    <t>Willy Brandt démissionne : Guillaume, un de ses conseillers est démasqué comme espion de la RDA. cependant l'Ostpolitik qu'il a initiée se poursuit. Helmut Schmidt (SPD) lui succède.
 Environ quatre millions d’étrangers vivent désormais en RFA.
 Ulrike Meinhof est condamnée à huit ans de prison pour son implication dans l'évasion de Baader. Les détenus de la RAF dénoncent l’isolement carcéral et multiplient les grèves de la faim ; Holger Meins en meurt. Jean-Paul Sartre rencontre Andreas Baader à la prison de Stuttgart-Stammheim et critique publiquement ses conditions de détention.</t>
   </si>
   <si>
-    <t>Kohl.jpg</t>
-  </si>
-  <si>
-    <t>Le Chancelier Hemult Kohl (CDU)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">La pièce </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>outrage au public</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> du dramaturge allemand Peter Handke témoigne du goût de l'avant-garde  artistique subentionnée pour une forme de provocation à l'égard du public, manière paradoxale de s'affranchir de la tutelle culturelle dont ils bénéficient.
-La publication du </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Journal de Spandau</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> d’Albert Speer participe à la mise en récit du passé nazi.
-Le rock et les cultures venues des États-Unis, de Grande-Bretagne et de France gagnent en légitimité. Chansons et culture populaire diffusent des idées critiques envers l’État, la famille, la religion, les rapports de genre et les formes traditionnelles d’autorité.</t>
-    </r>
-  </si>
-  <si>
-    <t>Fassbinder_jeunesse.jpeg</t>
-  </si>
-  <si>
-    <t>RWF jeune</t>
+    <t>Entrée des deux états allemands à l'ONU
+Le premier choc pétrolier met fin à la haute croissance et entraîne l’arrêt du recrutement de Gastarbeiter. Cette décision favorise ensuite l’installation durable des travailleurs déjà présents et le regroupement familial.</t>
+  </si>
+  <si>
+    <t>De la mort de Benno Ohnesorg à l’adoption des lois d’exception, la contestation étudiante dénonce la guerre du Vietnam, les continuités autoritaires et le refoulement du nazisme. En 1969, l’arrivée de Willy Brandt (SPD), l’Ostpolitik et la réforme du paragraphe 175 ouvrent une phase de réformes, tandis qu’une minorité choisit la clandestinité armée (émergence de la bande à Baader)
+La Grande coalition (1966-1969) CDU/SPD sous Kurt Georg Kiesinger : pour la première fois, le SPD entre au gouvernement fédéral en coalition avec la CDU. Le FDP devient la seule force d'opposition parlementaire. Ce vide d'opposition engendre l'APO (Außerparlamentarische Opposition, opposition extra-parlementaire) porté par la jeunesse. Mort de Benno Ohnesorg (2 juin 1967) : étudiant tué par la police lors d'une manifestation contre le Shah d'Iran . Loi sur l'État d'urgence (mai 1968) limitant les droits fondamentaux : manifestations massives à Bonn. Le mouvement contestataire d'ampleur, se singularise des autres mouvements européeens par sa dénonciation du fascisme « de l'intérieur ». Les étudiants dénoncent les dérives autoritaires de la RFA et la société de consommation aliénante. Tentative d'assassinat contre Rudi Dutschke, leader de la contestation. Des mouvements de contestation émergent des groupes féministes et écologistes. Un frange d'extrrême gauche choisit la radicalité : Baader et Ensslin sont arrêtés après des attentats à Francfort (1968). 
+Beate Klarsfeld gifle le chancelier Kiesinger (novembre 1968).
+Première récession de la RFA (1966-1967) : fin de l'évidence du Miracle économique. Loi de stabilité de 1967, gestion keynésienne sous Karl Schiller. Serpent monétaire européen (1972) qui stabilise les taux de change entre les monnaies européennes.
+Charnière de 1969 : élection de Willy Brandt (SPD) au poste de chancelier. Il incarne l'« autre Allemagne » (il a été opposant à Hitler et s'est 'exilé en Norvègeen 1933). Brandt initie l'Ostpolirtik,  politique de rapprochement entre les deux États allemands, dans un contexte de détente internationale. Il rompt un tabou en parlant de « deux États en Allemagne ». Cela aboutit à la reconnaissance mutuelle des deux Allemagne. 
+Genoux de Varsovie (décembre 1970) : Brandt s'agenouille devant le monument du ghetto de Varsovie, acte de reconnaissance de la culpabilité de l'Etat allemand à l'égard de la population juive sous le régime nazi. Traité de reconnaissance de la ligne Oder-Neisse avec la Pologne.  
+Willy Brandt est prix Nobel de la paix  (1971).
+Entrée des deux états allemands à l'ONU (1973)
+Les Gastarbeiter subissent discriminations systématiques : salaires inférieurs, emplois plus pénibles et dangereux, logement en foyers aux règles strictes. 2 millions d'étrangers en RFA (1969).</t>
+  </si>
+  <si>
+    <t>L'amour est plus froid que la mort (1969)
+Le Bouc (1969) met en scène un Gastarbeiter grec, victime du racisme. 
+Amorce de la période sirkienne :Le Marchand des quatre saisons (1971)</t>
+  </si>
+  <si>
+    <t>1974-1979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Après le miracle : crise, années de plomb et désenchantement 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonde l' antiteater (1968). Collaboration intense avec sa "troupe" (Schygulla, Hermann, Raab, Baer, Lommel). 
+Mariage avec Ingrid Caven (1970).
+Découverte des mélodrames de Douglas Sirk grâce à Peer Raben .Liaison avec El Hedi ben Salem. 
+Direction du TAT à Francfort. Collaboration avec le caméraman Michael Ballhaus. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La période est marquée par les attentats et l’arrestation de la première génération de la RAF, le choc pétrolier, la fin du recrutement des Gastarbeiter et la démission de Willy Brandt. La crise économique et le terrorisme infléchissent le climat réformateur.
+Démission de Willy Brandt (1974) suite à l'affaire Guillaume, un collaborateur accusé d'espionnage pour le compte de la RDA. L'Ostpolitik se poursuit sous Helmut Schmidt (SPD). Conférence d'Helsinki (1975) : la RFA reconnaît le statu quo territorial européen.
+Premier choc pétrolier (1973) et crise économique qui en découle mettent fin au système des Gastarbeiter. 4 millions d'étrangers en RFA (1974) : la politique de regroupement familial a accru les arrivées. Fin du plein emploi : montée structurelle du chômage. Tensions sociales et crises du logement (Westend). Débats sur la visibilité des minorités. 
+Terrorisme de la RAF (arrestations en 1972). Attentat des JO de Munich (1972).
+Procès, enlèvements, prises d’otages et morts en détention installent la RAF au centre du débat public. L'« Automne allemand » (1977) : apogée du terrorisme en RFA. Assassinat du procureur fédéral Buback (avril 1977), de Jürgen Ponto, président de la Dresdner Bank (juillet 1977). Enlèvement et assassinat de Hanns Martin Schleyer, président du patronat allemand (septembre-octobre 1977). Détournement du vol Lufthansa à Mogadiscio ; intervention des forces spéciales allemandes. Nuit de la mort de Stammheim : Baader, Ensslin et Raspe se suicident en prison (octobre 1977) 
+Les réformes sociétales se poursuivent : Loi sur l'avortement (1976) et réforme du droit de la famille (1977) qui confère plus d'autonomie aux femmes.
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La jeunesse affirme sa présence. Le Manifeste d’Oberhausen, l’essor de nouvelles structures de production et l’influence du rock, des cultures étrangères et des sciences sociales rompent avec les modèles des années 1950. La crise du père et la confrontation au passé deviennent des motifs structurants du Nouveau Cinéma allemand.
+La génération des 15-29 ans (22 % de la population) développe un regard critique sur les structures d'autorité (État, famille, religion, rapports de genre). La culture rock gagne en légitimité. Redécouverte des intellectuels de l'École de Francfort
+Manifeste d'Oberhausen (1962), acte de naissance du Nouveau Cinéma Allemand. Un groupe de jeunes réalisateurs (Alexander Kluge, Edgar Reitz, — mais ni Fassbinder, ni Wenders, ni Herzog) déclare « Le vieux cinéma est mort. Nous croyons au nouveau » (« Der alte Film ist tot. Wir glauben an den neuen»). ). La presse popularise le slogan « Papas Kino ist tot ! » (« Le cinéma de papa est mort »). Le mouvement revendique un nouveau cinéma allemand, rompant avec l'héritage du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Heimatfilm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">et du cinéma de divertissement. Une nouvelle génération de cinéastes s'affirme et conquiert son indépendance notamment par la création de structures de production indépendantes. Alexander Kluge : </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Abschied von gestern </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(1966) — Lion d'argent à Venise. Considéré comme le penseur du cinéma d'auteur allemand, il fonde l'Institut de formation cinématographique à l'École d'Ulm.Volker Schlöndorff : </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Der junge Törless </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(1966) — adaptation de Robert Musil, exploration des structures autoritaires et de la « préhistoire du fascisme » dans une académie militaire prussienne. Werner Herzog : Signs of Life (1967), son premier long-métrage, introduit le thème de la descente dans la folie qui traversera toute son œuvre 
+Fondation de l'école de cinéma DFFB à Berlin (1966).
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La représentation de l’histoire récente et du nazisme devient un enjeu central. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L’Allemagne en automne,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hitler, un film d’Allemagne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> puis la diffusion de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Holocaust</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> confrontent cinéma et télévision aux limites du témoignage, au sentimentalisme, à la mémoire collective et à la capacité des images populaires à rouvrir le passé. Le cinéma allemand s'empare de son histoire passée et récente et réfléchit aux problèmes de représentation qu'elle pose. 
+Développement du "film amphibie" (cinéma/TV). Le cinéma devient un outil de critique sociale directe.
+Film collectif </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Allemagne en automne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1978). 
+La diffusion de la série </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Holocaust</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de Marvin J. Chomsky (1979) à la télévision allemande suscite des débats importants, auxquels participent des cinéastes comme Syberberg ou Edgard Reitz. 
+La mémoire du nazisme est désormais un enjeu cinématographique : les films de la RFA explorent les continuités entre le Troisième Reich et l'Allemagne contemporaine
+Le mouvement du Nouveau Cinéma allemand atteint son apogée thématique et politique.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La période Sirkienne se poursuit  : Tous les autres s'appellent Ali (1974), </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le droit du plus fort </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(1975)  
+Le segement de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'atuomne Allemand et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Maman Küsters s'en va au ciel (1975) résonnent avec l'actualité politique brulante qui secoue la RFA et confronte aussi l'Allemagne à son passé et ses crimes.
+L'Année des treize lunes (1978) : œuvre radicale sur le désespoir, résonne avec l'histoire intime de RWF et les questionnements politiques du cinéaste
+Le Mariage de Maria Braun (1979) intie la trilogie de la RFA. Le mélodrame devient réflexion sur  l'état allemand d'après-guerre.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Redécouverte de l’École de Francfort. La circulation de modèles venus de la Nouvelle Vague, du théâtre d’avant-garde et de la culture rock font de la critique des institutions, de la famille et des représentations un enjeu esthétique autant que politique.
+Maturation du Nouveau cinéma allemand : le manifeste d'Oberhausen (1962) porte ses premiers fruits institutionnels. Le Kuratorium junger deutscher Film (1965) et la Filmförderungsgesetz (FFG, 1967) structurent un cinéma d'auteur subventionné, rompant avec la logique commerciale des années 1950. Fondation du Filmverlag der Autoren (1971). Accords Film-Télévision (1974) favorisant les coproductions (WDR). A parti de 1968 l'industrie du cinéma commercial allemand agonise.
+Plusieurs cinéastes allemands ( Schlöndorff, Herzog notamment) réalisent des charges politiques violentes contre la politique et la société allemande. Pourtant, dans un premier temps, l'amnésie historique se poursuit dans le cinéma allemand de fiction. Seuls des documentaires s'emparent de l'histoire du nazisme
+Alexander Kluge : Artisten in der Zirkuskuppel: ratlos (1968) — Lion d'or à Venise. Considéré comme l'un des chef-d'œuvre du cinéma moderne
+Werner Herzog : Aguirre, la colère de Dieu (1972) — descente vers la folie de conquistadors en Amazonie, métaphore du délire totalitaire
+Wim Wenders : Alice dans les villes (1974) — road movie mélancolique, réflexion sur l'aliénation et la perte de repères dans l'Allemagne des années 1970
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Succès international. Les films de RWF deviennent incontournables dans les grands festivals internationaux (Cannes, Venise, Berlin). 
+Fassbinder joue  Fox le rôle principal, du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Droit du plus fort(1975), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">assumant une visibilité politique de son homosexualité. Il maigrit et se muscle pour le rôle, renonçant aux excès.
+Suicide d'Armin Meier (31 mai 1978). Début de la collaboration avec Juliane Lorenz. 
+Dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">L'automne allemand (1978), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fassbinder se filme en crise, exposant son angoisse face à l'État.</t>
+    </r>
+  </si>
+  <si>
+    <t>« Toute une génération exorcisa son enfance déjà presque oubliée en soulignant sans répit combien étaient encombrantes et dévastatrices les ombres que le passé des parents avaient jetées sur le présent de leurs enfants ».Thomas Elsaesser, RWF un cinéaste d'Allemagne (2005) p.201</t>
+  </si>
+  <si>
+    <r>
+      <t>Le cinéma allemand poursuit son travail sur la mémoire familiale et nationale, notamment avec Allemagne mère blafarde et le projet Heimat. La télévision devient un lieu majeur pour les récits historiques de longue durée.
+Herzog —</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Fitzcarraldo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(1982) : tournage légendaire en Amazonie, métaphore de la folie des grandeurs. La documentation du tournage par Les Blank (Burden of Dreams, 1982) devient elle-même un mythe du cinéma.
+Fin d'une époque artistique et politique radicale</t>
+    </r>
+  </si>
+  <si>
+    <t>La fin de la détente amorcée en 1979 relance la course à l'armement. 
+Les mouvements écologistes, féministes et pacifistes se structurent avec la fondation des Verts (1980) et les grandes mobilisations contre la course aux armements. Ils reconfigurent un système politique jusque-là dominé par trois partis.
+Fin de l'ère sociale-libérale : arrivée au pouvoir du chancelier Helmut Kohl (CDU) en 1982 :  Kohl se donne comme mission de réconcilier le peuple ouest-allemand avec son passé. Il ne remet pas en cause l'Ostpolitik mais soutient un projet de réunification. Il cultive l'entente avec la France de François Mitterrand
+La crise structurelle s'installe. Le chômage s'élève à 8 % en 1983 :  le modèle de l'économie sociale de marché est contesté de l'intérieur par les écologistes et les pacifistes.
+Rapport d'une commission d'enquête (« Femme et société », 1980) qui défend encore le modèle de la femme au foyer. La part des femmes élues n'atteint pas 10 %.
+La mémoire du nazisme reste un enjeu vif : la figure de Schleyer, ancien SS, a révélé les continuités entre élites économiques et régime nazi.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Monumental Berlin Alexanderplatz (1980, 15h). 
+Suite de la Trilogie de la RFA : </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lola, une femme allemande</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1981) et </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lili Marleen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1981).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Le Secret de Veronika Voss </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(Ours d'Or à Berlin). </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Querell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">e (œuvre posthume). </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RWF Travaille frénétiquement. Réalise son projet de vie : l'adaptation de Döblin. Épuisement physique dû aux excès.
+Décès de Fassbinder le 10 juin 1982 à Munich, à l'âge de 37 ans (épuisement et overdose).Fassbinder laisse un héritage de plus de 40 films. Sa disparition marque la fin d'une époque du Nouveau cinéma allemand </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jusqu'à quel point les femmes de la trilogie RFA sont-elles une allégorie de la nation allemande ? </t>
+  </si>
+  <si>
+    <t>L'Allemagne des années 50, la période de référence pour l'œuvre de RWF ?</t>
+  </si>
+  <si>
+    <t>1949-1960</t>
+  </si>
+  <si>
+    <t>1961-1965</t>
+  </si>
+  <si>
+    <t>Construction du Mur de Berlin (1961) :  traumatisme national, division consommée. Willy Brandt, alors maire de Berlin-Ouest, réunit 300 000 personnes pour en appeler à la solidarité internationale. Visite de Kennedy à Berlin-Ouest (1963) : « Ich bin ein Berliner ». Le Mur matérialise la division allemande qui sefige institutionnellement.Le rapprochement franco-allemand (de Gaulle/Adenauer)  est initié par le Traité de l'Élysée (1963)  ; création de l'Office franco-allemand de la jeunesse.
+Fin de l'ère Adenauer. 1963.  : Ludwijg Ehrard, père du "miracle économique", devient Chancelier (CDU) de la RFA  
+La croissance économique est toujours forte mais commence à montrer des signes d'essoufflement. Traité de recrutement de "travailleurs invités" avec la Turquie (1961), le Maroc (1963), le Portugal et la Tunisie (1965). Le millionième Gastarbeiter est célébré à son arrivée en 1964.
+Procès d'Auschwitz à Francfort (1963-1965). 
+Les procès Eichmann et d’Auschwitz replacent les crimes nazis au centre du débat public. La fin de l’ère Adenauer et la Grande Coalition accompagnent l’émergence d’une nouvelle génération nombreuse, plus critique envers les institutions et l’autorité.</t>
+  </si>
+  <si>
+    <t>1966-1973</t>
+  </si>
+  <si>
+    <t>1945-1948</t>
+  </si>
+  <si>
+    <t>1980-1982</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, de Thomas Elsaesser, Centre Pompidou, 2005</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, pp. 490-507</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>R. W. Fassbinder, cinéaste d’Allemagne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, de Thomas Elsaesser, Centre Pompidou, 2005</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -3512,11 +4028,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="12"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
@@ -3530,30 +4041,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="409.55"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="409.55"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="409.55"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
@@ -3562,11 +4049,6 @@
     <font>
       <sz val="10"/>
       <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -3667,7 +4149,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3698,19 +4180,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -3725,39 +4204,23 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3770,6 +4233,18 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3779,6 +4254,7 @@
   <dxfs count="37">
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3789,6 +4265,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3799,6 +4276,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3809,6 +4287,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3819,6 +4298,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3829,6 +4309,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3839,6 +4320,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3849,6 +4331,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3859,6 +4342,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3869,6 +4353,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3879,6 +4364,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3889,6 +4375,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3899,6 +4386,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3909,6 +4397,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3919,6 +4408,7 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -4275,8 +4765,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N10" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:N10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau2" displayName="Tableau2" ref="A1:N7" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N7" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID période" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre période" dataDxfId="12"/>
@@ -4509,7 +4999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="31.83203125" customWidth="1"/>
@@ -4523,369 +5013,268 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="8" customFormat="1" ht="37.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="N1" s="20" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="D2" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="23"/>
-      <c r="H2" s="24" t="str">
+      <c r="G2" s="29"/>
+      <c r="H2" s="21" t="str">
         <f>IF(G2="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G2,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
-      <c r="I2" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="J2" s="25" t="s">
+      <c r="I2" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="M2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="26" t="s">
+      <c r="N2" s="29"/>
+    </row>
+    <row r="3" spans="1:14" s="9" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="23"/>
-    </row>
-    <row r="3" spans="1:14" s="9" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="28" t="str">
+      <c r="G3" s="1"/>
+      <c r="H3" s="23" t="str">
         <f>IF(G3="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G3,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
-      <c r="I3" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="J3" s="29" t="s">
+      <c r="I3" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="31"/>
+      <c r="L3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+    </row>
+    <row r="4" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="27"/>
-      <c r="L3" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-    </row>
-    <row r="4" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>246</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="28" t="str">
+      <c r="H4" s="23" t="str">
         <f>IF(G4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
       </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="30" t="s">
+      <c r="I4" s="29"/>
+      <c r="J4" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+    </row>
+    <row r="5" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="H5" s="23" t="str">
+        <f>IF(G5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc; film-1972-le-marchand-des-quatre-saisons</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="J5" s="29"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+    </row>
+    <row r="6" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="H6" s="23" t="str">
+        <f>IF(G6="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$41,"")))</f>
+        <v>film-1974-tous-les-autres-s-appellent-ali; film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel; film-1978-l-annee-des-treize-lunes; film-1978-le-mariage-de-maria-braun</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="29"/>
+      <c r="K6" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+    </row>
+    <row r="7" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-    </row>
-    <row r="5" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="28" t="str">
-        <f>IF(G5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc</v>
-      </c>
-      <c r="I5" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-    </row>
-    <row r="6" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="28" t="str">
-        <f>IF(G6="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G6,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1972-le-marchand-des-quatre-saisons; film-1974-tous-les-autres-s-appellent-ali; film-1974-martha</v>
-      </c>
-      <c r="I6" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-    </row>
-    <row r="7" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="C7" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F7" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="28" t="str">
+      <c r="E7" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="H7" s="23" t="str">
         <f>IF(G7="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G7,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-    </row>
-    <row r="8" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="28" t="str">
-        <f>IF(G8="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G8,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1978-l-annee-des-treize-lunes; film-1978-le-mariage-de-maria-braun</v>
-      </c>
-      <c r="I8" s="26"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="28" t="str">
-        <f>IF(G9="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G9,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1980-berlin-alexanderplatz; film-1981-lili-marleen; film-1981-lola-une-femme-allemande</v>
-      </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-    </row>
-    <row r="10" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="33">
-        <v>1982</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="28" t="str">
-        <f>IF(G10="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(G10,"’","'"))),'Référentiel films'!$B$41,"")))</f>
-        <v>film-1981-le-secret-de-veronika-voss; film-1982-querelle</v>
-      </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
+        <v>film-1980-berlin-alexanderplatz; film-1981-lili-marleen; film-1981-lola-une-femme-allemande; film-1981-le-secret-de-veronika-voss; film-1982-querelle</v>
+      </c>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4918,7 +5307,7 @@
   <sheetData>
     <row r="1" spans="1:21" s="8" customFormat="1" ht="37.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -4936,49 +5325,49 @@
         <v>6</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>13</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="U1" s="20" t="s">
-        <v>79</v>
+        <v>48</v>
+      </c>
+      <c r="U1" s="19" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="368" customHeight="1" x14ac:dyDescent="0.2">
@@ -4986,34 +5375,34 @@
         <v>1945</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>350</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>257</v>
+        <v>209</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>287</v>
+        <v>238</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
+      <c r="H2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
       <c r="U2" s="2" t="str">
         <f>IF(F2="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F2,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5024,34 +5413,34 @@
         <v>1946</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>350</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>259</v>
+        <v>211</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F3" s="13"/>
+        <v>51</v>
+      </c>
+      <c r="F3" s="12"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
+      <c r="H3" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
       <c r="U3" s="2" t="str">
         <f>IF(F3="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F3,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5062,31 +5451,31 @@
         <v>1947</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>350</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>260</v>
+        <v>212</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>261</v>
+        <v>213</v>
       </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="13"/>
+      <c r="F4" s="12"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
       <c r="T4" s="1" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="U4" s="2" t="str">
         <f>IF(F4="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F4,"’","'"))),'Référentiel films'!$B$41,"")))</f>
@@ -5098,38 +5487,38 @@
         <v>1948</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>286</v>
+        <v>236</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>237</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="13"/>
+      <c r="F5" s="12"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="14" t="s">
-        <v>84</v>
+      <c r="H5" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>329</v>
+        <v>55</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>280</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="L5" s="1"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
       <c r="U5" s="2" t="str">
         <f>IF(F5="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F5,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5140,36 +5529,36 @@
         <v>1949</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>346</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>288</v>
+        <v>214</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>239</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="13"/>
+      <c r="F6" s="12"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
+      <c r="H6" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
+      <c r="M6" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
       <c r="U6" s="2" t="str">
         <f>IF(F6="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F6,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5180,38 +5569,38 @@
         <v>1950</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>346</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>263</v>
+        <v>215</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F7" s="13"/>
+        <v>59</v>
+      </c>
+      <c r="F7" s="12"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
+      <c r="M7" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
       <c r="U7" s="2" t="str">
         <f>IF(F7="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F7,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5222,36 +5611,36 @@
         <v>1951</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>346</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
       <c r="U8" s="2" t="str">
         <f>IF(F8="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F8,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5262,40 +5651,40 @@
         <v>1952</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>346</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
       <c r="M9" s="1" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>89</v>
+        <v>64</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>317</v>
       </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="13"/>
+      <c r="T9" s="12"/>
       <c r="U9" s="2" t="str">
         <f>IF(F9="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F9,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5306,36 +5695,36 @@
         <v>1953</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>346</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="N10" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
       <c r="U10" s="2" t="str">
         <f>IF(F10="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F10,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5346,40 +5735,40 @@
         <v>1954</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>346</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>291</v>
+        <v>221</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>242</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
       <c r="U11" s="2" t="str">
         <f>IF(F11="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F11,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5390,32 +5779,32 @@
         <v>1955</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>346</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
       <c r="U12" s="2" t="str">
         <f>IF(F12="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F12,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5426,38 +5815,38 @@
         <v>1956</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>346</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>330</v>
+        <v>253</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>281</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="N13" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
       <c r="U13" s="2" t="str">
         <f>IF(F13="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F13,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5468,34 +5857,34 @@
         <v>1957</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>22</v>
+        <v>346</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
       <c r="U14" s="2" t="str">
         <f>IF(F14="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F14,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5506,38 +5895,38 @@
         <v>1959</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>346</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>103</v>
+        <v>244</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>72</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
+      <c r="G15" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
       <c r="U15" s="2" t="str">
         <f>IF(F15="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F15,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5548,36 +5937,36 @@
         <v>1960</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>22</v>
+        <v>346</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>304</v>
+        <v>255</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>294</v>
+        <v>245</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="N16" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
       <c r="U16" s="2" t="str">
         <f>IF(F16="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F16,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5588,34 +5977,34 @@
         <v>1961</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>347</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="D17" s="13"/>
+        <v>224</v>
+      </c>
+      <c r="D17" s="12"/>
       <c r="E17" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="N17" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
+        <v>74</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
       <c r="U17" s="2" t="str">
         <f>IF(F17="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F17,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5626,34 +6015,30 @@
         <v>1962</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>347</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="M18" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="N18" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
       <c r="U18" s="2" t="str">
         <f>IF(F18="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F18,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5663,45 +6048,51 @@
       <c r="A19" s="1">
         <v>1963</v>
       </c>
-      <c r="B19" s="1"/>
+      <c r="B19" s="1" t="s">
+        <v>347</v>
+      </c>
       <c r="C19" s="1" t="s">
-        <v>273</v>
+        <v>225</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="F19" s="1"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="N19" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="O19" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="P19" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="P19" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q19" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="R19" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
       <c r="U19" s="2" t="str">
         <f>IF(F19="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$37,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$38,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$38,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$39,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$39,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$40,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$40,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$41,"’","'"),SUBSTITUTE(F19,"’","'"))),'Référentiel films'!$B$41,"")))</f>
         <v/>
@@ -5711,37 +6102,39 @@
       <c r="A20" s="1">
         <v>1964</v>
       </c>
-      <c r="B20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>347</v>
+      </c>
       <c r="C20" s="1" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="N20" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="O20" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="P20" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="13"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
       <c r="U20" s="2" t="str">
         <f>IF(F20="","",_xlfn.TEXTJOIN("; ",TRUE(),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$2,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$2,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$3,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$3,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$4,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$4,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$5,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$5,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$6,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$6,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$7,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$7,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$8,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$8,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$9,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$9,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$10,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$10,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$11,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$11,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$12,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$12,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$13,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$13,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$14,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$14,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$15,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$15,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$16,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$16,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$17,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$17,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$18,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$18,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$19,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$19,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$20,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$20,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$21,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$21,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$22,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$22,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$23,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$23,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$24,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$24,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$25,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$25,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$26,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$26,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$27,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$27,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$28,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$28,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$29,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$29,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$30,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$30,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$31,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$31,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$32,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$32,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$33,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$33,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$34,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$34,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$35,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$35,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$36,"’","'"),SUBSTITUTE(F20,"’","'"))),'Référentiel films'!$B$36,""),IF(ISNUMBER(SEARCH(SUBSTITUTE('Référentiel films'!$A$37,